--- a/docs/price-review.xlsx
+++ b/docs/price-review.xlsx
@@ -542,7 +542,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>Every researched price on the rate card - 28 approved, 19 revoked, 12 undecided - beside the rate it would replace, with its evidence and what its approval does to the sample baselines.</t>
+          <t>Every researched price on the rate card - 28 approved, 21 revoked, 10 undecided - beside the rate it would replace, with its evidence and what its approval does to the sample baselines.</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="G4" s="8" t="inlineStr">
         <is>
-          <t>Direct Telecom publishes a 100/100 Mbps guaranteed circuit at €159.99/month. Hold because it is a single reseller list price and has a large model effect.</t>
+          <t>Held: Direct Telecom's EUR 159.99 is a guaranteed rather than dedicated circuit, below Kompara's EUR 200-300 for 100 Mbps dedicated fibre. The card now prices Spain DIA 100 at that range's EUR 250 midpoint as a sourced rate; approving this row would displace it.</t>
         </is>
       </c>
       <c r="H4" s="9">
@@ -1063,14 +1063,16 @@
       <c r="L4" s="10" t="n">
         <v>183.66</v>
       </c>
-      <c r="M4" s="10" t="n"/>
+      <c r="M4" s="10" t="n">
+        <v>287</v>
+      </c>
       <c r="N4" s="11">
         <f>IF(OR(L4="",M4=""),"",L4/M4)</f>
         <v/>
       </c>
       <c r="O4" s="5" t="inlineStr">
         <is>
-          <t>none - new tier</t>
+          <t>SEED</t>
         </is>
       </c>
       <c r="P4" s="3" t="inlineStr">
@@ -1101,14 +1103,14 @@
         </is>
       </c>
       <c r="W4" s="12" t="n">
-        <v>-19536535.26</v>
+        <v>-2357511.18</v>
       </c>
       <c r="X4" s="5" t="n">
         <v>2072</v>
       </c>
       <c r="Y4" s="3" t="inlineStr">
         <is>
-          <t>santander -14,590,860; fresenius -4,811,403; carrefour -134,272</t>
+          <t>santander -1,760,707; fresenius -580,601; carrefour -16,203</t>
         </is>
       </c>
       <c r="Z4" s="3" t="inlineStr">
@@ -1121,12 +1123,12 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>ES-DIA-600-researched</t>
+          <t>GB-DIA-100-researched</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
@@ -1135,7 +1137,7 @@
         </is>
       </c>
       <c r="D5" s="5" t="n">
-        <v>600</v>
+        <v>100</v>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
@@ -1149,7 +1151,7 @@
       </c>
       <c r="G5" s="8" t="inlineStr">
         <is>
-          <t>Direct Telecom's published business-class page lists a 600/600 Mbps dedicated circuit at €1,100/month. Hold because it is a single reseller list price and the service variant should be confirmed before country-wide use.</t>
+          <t>Virgin's 'packages start at' floor. The seed it would replace is survey-sourced (grade C) and sits inside the GBP 175-320 range the same research quotes.</t>
         </is>
       </c>
       <c r="H5" s="9">
@@ -1161,39 +1163,53 @@
         <v/>
       </c>
       <c r="J5" s="10" t="n">
-        <v>1100</v>
+        <v>185</v>
       </c>
       <c r="K5" s="5" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>GBP</t>
         </is>
       </c>
       <c r="L5" s="10" t="n">
-        <v>1262.77</v>
-      </c>
-      <c r="M5" s="10" t="n"/>
+        <v>247.89</v>
+      </c>
+      <c r="M5" s="10" t="n">
+        <v>335</v>
+      </c>
       <c r="N5" s="11">
         <f>IF(OR(L5="",M5=""),"",L5/M5)</f>
         <v/>
       </c>
       <c r="O5" s="5" t="inlineStr">
         <is>
-          <t>none - new tier</t>
+          <t>SEED</t>
         </is>
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t>single source; untraceable</t>
-        </is>
-      </c>
-      <c r="Q5" s="3" t="inlineStr"/>
+          <t>floor; read from a snippet</t>
+        </is>
+      </c>
+      <c r="Q5" s="3" t="inlineStr">
+        <is>
+          <t>GB DIA 100 Mbps MRC – Virgin Media Business published tariff</t>
+        </is>
+      </c>
       <c r="R5" s="5" t="inlineStr">
         <is>
-          <t>run narrative (the disposition was replaced)</t>
-        </is>
-      </c>
-      <c r="S5" s="3" t="inlineStr"/>
-      <c r="T5" s="5" t="inlineStr"/>
+          <t>Virgin Media Business; COMPANY_PUBLISHED/SNIPPET_ONLY</t>
+        </is>
+      </c>
+      <c r="S5" s="3" t="inlineStr">
+        <is>
+          <t>Our packages start at £185 per month which provided 100Mbps upload and download speeds.</t>
+        </is>
+      </c>
+      <c r="T5" s="5" t="inlineStr">
+        <is>
+          <t>https://www.virginmediabusiness.co.uk/connectivity/internet-access/leased-lines-for-business/</t>
+        </is>
+      </c>
       <c r="U5" s="5" t="inlineStr">
         <is>
           <t>2025</t>
@@ -1201,32 +1217,40 @@
       </c>
       <c r="V5" s="5" t="inlineStr">
         <is>
-          <t>carrefour</t>
+          <t>unilever</t>
         </is>
       </c>
       <c r="W5" s="12" t="n">
-        <v>0</v>
+        <v>-2414090.918069141</v>
       </c>
       <c r="X5" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y5" s="3" t="inlineStr"/>
+        <v>2429</v>
+      </c>
+      <c r="Y5" s="3" t="inlineStr">
+        <is>
+          <t>nhs-england -1,121,155; saint-gobain -796,760; santander -280,459</t>
+        </is>
+      </c>
       <c r="Z5" s="3" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AA5" s="3" t="inlineStr"/>
+      <c r="AA5" s="3" t="inlineStr">
+        <is>
+          <t>deutsche-post-dhl 206 GBP; eon 139 GBP; iberdrola 130 GBP; nhs-england 222 GBP; unilever 185 GBP</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>ES-DIA-1000-researched</t>
+          <t>GB-DIA-500-researched</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
@@ -1235,7 +1259,7 @@
         </is>
       </c>
       <c r="D6" s="5" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
@@ -1249,7 +1273,7 @@
       </c>
       <c r="G6" s="8" t="inlineStr">
         <is>
-          <t>Direct Telecom publishes a 1,000/1,000 Mbps dedicated circuit at €449/month. Hold because it is a single reseller list price and reprices lower Spanish DIA tiers.</t>
+          <t>Vodafone 'from' GBP 257 on a 60-month term. The same research puts urban 500 Mbps at GBP 350-500 on 36 months.</t>
         </is>
       </c>
       <c r="H6" s="9">
@@ -1261,18 +1285,18 @@
         <v/>
       </c>
       <c r="J6" s="10" t="n">
-        <v>449</v>
+        <v>257</v>
       </c>
       <c r="K6" s="5" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>GBP</t>
         </is>
       </c>
       <c r="L6" s="10" t="n">
-        <v>515.4400000000001</v>
+        <v>344.37</v>
       </c>
       <c r="M6" s="10" t="n">
-        <v>1300</v>
+        <v>690</v>
       </c>
       <c r="N6" s="11">
         <f>IF(OR(L6="",M6=""),"",L6/M6)</f>
@@ -1285,21 +1309,29 @@
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t>single source; re-prices lower tiers</t>
-        </is>
-      </c>
-      <c r="Q6" s="3" t="inlineStr"/>
+          <t>floor; single source; re-prices lower tiers</t>
+        </is>
+      </c>
+      <c r="Q6" s="3" t="inlineStr">
+        <is>
+          <t>DIA 500Mbps MRC – Vodafone Business published retail tariff</t>
+        </is>
+      </c>
       <c r="R6" s="5" t="inlineStr">
         <is>
-          <t>run narrative (the disposition was replaced)</t>
+          <t>Vodafone Business; COMPANY_PUBLISHED/FULL_PAGE</t>
         </is>
       </c>
       <c r="S6" s="3" t="inlineStr">
         <is>
-          <t>ional players plus resellers. Telefónica Global Solutions offers DIA on its own Tier 1 global infrastructure. A domestic reseller (Direct Telecom) lists 100/100 Mbps DIA at €159.99/month and 1 Gbps dedicated circuit at €449/month (2025 prices). Telefónica and MasOrange are exploring acquisition of Vodafone España (as of mid-2025); if completed this would reduce the market to three</t>
-        </is>
-      </c>
-      <c r="T6" s="5" t="inlineStr"/>
+          <t>Vodafone Dedicated Internet Access (Managed) 500 Mbps Monthly price from £257 (ex. VAT) 60 months</t>
+        </is>
+      </c>
+      <c r="T6" s="5" t="inlineStr">
+        <is>
+          <t>https://www.vodafone.co.uk/business/connectivity/data-connectivity/dedicated-internet-access</t>
+        </is>
+      </c>
       <c r="U6" s="5" t="inlineStr">
         <is>
           <t>2025</t>
@@ -1307,31 +1339,35 @@
       </c>
       <c r="V6" s="5" t="inlineStr">
         <is>
-          <t>inditex</t>
+          <t>nhs-england</t>
         </is>
       </c>
       <c r="W6" s="12" t="n">
-        <v>-12196995.84</v>
+        <v>-2330376.070015842</v>
       </c>
       <c r="X6" s="5" t="n">
-        <v>2100</v>
+        <v>520</v>
       </c>
       <c r="Y6" s="3" t="inlineStr">
         <is>
-          <t>santander -8,937,825; fresenius -2,947,289; iberdrola -164,023</t>
+          <t>deutsche-post-dhl -1,892,302; royal-mail -272,780; ups -112,906</t>
         </is>
       </c>
       <c r="Z6" s="3" t="inlineStr">
         <is>
-          <t>500 Mbps at 1196 &gt; 1000 Mbps at 515 USD</t>
-        </is>
-      </c>
-      <c r="AA6" s="3" t="inlineStr"/>
+          <t>300 Mbps at 600 &gt; 500 Mbps at 344 USD</t>
+        </is>
+      </c>
+      <c r="AA6" s="3" t="inlineStr">
+        <is>
+          <t>deutsche-post-dhl 243 GBP; nhs-england 257 GBP</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>GB-DIA-100-researched</t>
+          <t>GB-DIA-1000-researched</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
@@ -1345,7 +1381,7 @@
         </is>
       </c>
       <c r="D7" s="5" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
@@ -1359,7 +1395,7 @@
       </c>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>Virgin's 'packages start at' floor. The seed it would replace is survey-sourced (grade C) and sits inside the GBP 175-320 range the same research quotes.</t>
+          <t>CompareNet publishes a 1 Gbps symmetric leased-line floor of £195/month. Hold—not reject—because it is an aggregator 'from' price below the broader market range and needs address/term validation.</t>
         </is>
       </c>
       <c r="H7" s="9">
@@ -1371,7 +1407,7 @@
         <v/>
       </c>
       <c r="J7" s="10" t="n">
-        <v>185</v>
+        <v>195</v>
       </c>
       <c r="K7" s="5" t="inlineStr">
         <is>
@@ -1379,10 +1415,10 @@
         </is>
       </c>
       <c r="L7" s="10" t="n">
-        <v>247.89</v>
+        <v>261.29</v>
       </c>
       <c r="M7" s="10" t="n">
-        <v>335</v>
+        <v>737</v>
       </c>
       <c r="N7" s="11">
         <f>IF(OR(L7="",M7=""),"",L7/M7)</f>
@@ -1395,65 +1431,65 @@
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t>floor; read from a snippet</t>
+          <t>floor; single source; read from a snippet; re-prices lower tiers</t>
         </is>
       </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t>GB DIA 100 Mbps MRC – Virgin Media Business published tariff</t>
+          <t>GB enterprise leased line (DIA) monthly cost — 1 Gbps enterprise</t>
         </is>
       </c>
       <c r="R7" s="5" t="inlineStr">
         <is>
-          <t>Virgin Media Business; COMPANY_PUBLISHED/SNIPPET_ONLY</t>
+          <t>ComparenetUK; AGGREGATOR/SNIPPET_ONLY</t>
         </is>
       </c>
       <c r="S7" s="3" t="inlineStr">
         <is>
-          <t>Our packages start at £185 per month which provided 100Mbps upload and download speeds.</t>
+          <t>1Gbps Symmetric — From £195/month, enterprise-grade with dedicated account manager</t>
         </is>
       </c>
       <c r="T7" s="5" t="inlineStr">
         <is>
-          <t>https://www.virginmediabusiness.co.uk/connectivity/internet-access/leased-lines-for-business/</t>
+          <t>https://comparenet.co.uk/dedicated-fibre-leased-lines</t>
         </is>
       </c>
       <c r="U7" s="5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="V7" s="5" t="inlineStr">
         <is>
-          <t>unilever</t>
+          <t>iberdrola</t>
         </is>
       </c>
       <c r="W7" s="12" t="n">
-        <v>-2414090.918069141</v>
+        <v>-659380.2940418924</v>
       </c>
       <c r="X7" s="5" t="n">
-        <v>2429</v>
+        <v>133</v>
       </c>
       <c r="Y7" s="3" t="inlineStr">
         <is>
-          <t>nhs-england -1,121,155; saint-gobain -796,760; santander -280,459</t>
+          <t>nhs-england -183,990; siemens -119,345; network-rail -119,345</t>
         </is>
       </c>
       <c r="Z7" s="3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>500 Mbps at 690 &gt; 1000 Mbps at 261 USD</t>
         </is>
       </c>
       <c r="AA7" s="3" t="inlineStr">
         <is>
-          <t>deutsche-post-dhl 206 GBP; eon 139 GBP; iberdrola 130 GBP; nhs-england 222 GBP; unilever 185 GBP</t>
+          <t>deutsche-post-dhl 267 GBP; iberdrola 195 GBP; nhs-england 300 GBP</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>GB-DIA-500-researched</t>
+          <t>GB-DIA-10000-researched</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
@@ -1467,7 +1503,7 @@
         </is>
       </c>
       <c r="D8" s="5" t="n">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
@@ -1481,7 +1517,7 @@
       </c>
       <c r="G8" s="8" t="inlineStr">
         <is>
-          <t>Vodafone 'from' GBP 257 on a 60-month term. The same research puts urban 500 Mbps at GBP 350-500 on 36 months.</t>
+          <t>Spitfire publishes 10 Gbps symmetric leased-line pricing from £450/month. Hold—not reject—because it is a single-carrier floor that needs location, term and installation-cost validation.</t>
         </is>
       </c>
       <c r="H8" s="9">
@@ -1493,7 +1529,7 @@
         <v/>
       </c>
       <c r="J8" s="10" t="n">
-        <v>257</v>
+        <v>450</v>
       </c>
       <c r="K8" s="5" t="inlineStr">
         <is>
@@ -1501,86 +1537,80 @@
         </is>
       </c>
       <c r="L8" s="10" t="n">
-        <v>344.37</v>
-      </c>
-      <c r="M8" s="10" t="n">
-        <v>690</v>
-      </c>
+        <v>602.97</v>
+      </c>
+      <c r="M8" s="10" t="n"/>
       <c r="N8" s="11">
         <f>IF(OR(L8="",M8=""),"",L8/M8)</f>
         <v/>
       </c>
       <c r="O8" s="5" t="inlineStr">
         <is>
-          <t>SEED</t>
+          <t>none - new tier</t>
         </is>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t>floor; single source; re-prices lower tiers</t>
+          <t>single source; read from a snippet; re-prices lower tiers</t>
         </is>
       </c>
       <c r="Q8" s="3" t="inlineStr">
         <is>
-          <t>DIA 500Mbps MRC – Vodafone Business published retail tariff</t>
+          <t>DIA 10000Mbps MRC (Spitfire, retail)</t>
         </is>
       </c>
       <c r="R8" s="5" t="inlineStr">
         <is>
-          <t>Vodafone Business; COMPANY_PUBLISHED/FULL_PAGE</t>
+          <t>Spitfire Networks — product page; COMPANY_PUBLISHED/SNIPPET_ONLY</t>
         </is>
       </c>
       <c r="S8" s="3" t="inlineStr">
         <is>
-          <t>Vodafone Dedicated Internet Access (Managed) 500 Mbps Monthly price from £257 (ex. VAT) 60 months</t>
+          <t>10 Gbps From: £450/month — 10Gbps Upload — 10Gbps Download</t>
         </is>
       </c>
       <c r="T8" s="5" t="inlineStr">
         <is>
-          <t>https://www.vodafone.co.uk/business/connectivity/data-connectivity/dedicated-internet-access</t>
+          <t>https://www.spitfire.co.uk/connectivity/fibre-ethernet-leased-line/</t>
         </is>
       </c>
       <c r="U8" s="5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="V8" s="5" t="inlineStr">
         <is>
-          <t>nhs-england</t>
+          <t>deutsche-post-dhl</t>
         </is>
       </c>
       <c r="W8" s="12" t="n">
-        <v>-2330376.070015842</v>
+        <v>0</v>
       </c>
       <c r="X8" s="5" t="n">
-        <v>520</v>
-      </c>
-      <c r="Y8" s="3" t="inlineStr">
-        <is>
-          <t>deutsche-post-dhl -1,892,302; royal-mail -272,780; ups -112,906</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Y8" s="3" t="inlineStr"/>
       <c r="Z8" s="3" t="inlineStr">
         <is>
-          <t>300 Mbps at 600 &gt; 500 Mbps at 344 USD</t>
+          <t>1000 Mbps at 737 &gt; 10000 Mbps at 603 USD</t>
         </is>
       </c>
       <c r="AA8" s="3" t="inlineStr">
         <is>
-          <t>deutsche-post-dhl 243 GBP; nhs-england 257 GBP</t>
+          <t>deutsche-post-dhl 450 GBP</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>GB-DIA-1000-researched</t>
+          <t>SG-DIA-100-researched</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -1589,7 +1619,7 @@
         </is>
       </c>
       <c r="D9" s="5" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
@@ -1603,7 +1633,7 @@
       </c>
       <c r="G9" s="8" t="inlineStr">
         <is>
-          <t>CompareNet publishes a 1 Gbps symmetric leased-line floor of £195/month. Hold—not reject—because it is an aggregator 'from' price below the broader market range and needs address/term validation.</t>
+          <t>Published on SPTel's promotion page (valid to 31 Dec 2026). No circuit in the set uses it.</t>
         </is>
       </c>
       <c r="H9" s="9">
@@ -1615,18 +1645,18 @@
         <v/>
       </c>
       <c r="J9" s="10" t="n">
-        <v>195</v>
+        <v>312</v>
       </c>
       <c r="K9" s="5" t="inlineStr">
         <is>
-          <t>GBP</t>
+          <t>SGD</t>
         </is>
       </c>
       <c r="L9" s="10" t="n">
-        <v>261.29</v>
+        <v>243.75</v>
       </c>
       <c r="M9" s="10" t="n">
-        <v>737</v>
+        <v>660</v>
       </c>
       <c r="N9" s="11">
         <f>IF(OR(L9="",M9=""),"",L9/M9)</f>
@@ -1639,27 +1669,27 @@
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t>floor; single source; read from a snippet; re-prices lower tiers</t>
+          <t>single source; read from a snippet</t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t>GB enterprise leased line (DIA) monthly cost — 1 Gbps enterprise</t>
+          <t>DIA 100 Mbps MRC — Singapore (SPTel enterprise tariff)</t>
         </is>
       </c>
       <c r="R9" s="5" t="inlineStr">
         <is>
-          <t>ComparenetUK; AGGREGATOR/SNIPPET_ONLY</t>
+          <t>SPTel; COMPANY_PUBLISHED/SNIPPET_ONLY</t>
         </is>
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t>1Gbps Symmetric — From £195/month, enterprise-grade with dedicated account manager</t>
+          <t>Enterprise Internet 100Mbps $312/mth (on 24-month contract)</t>
         </is>
       </c>
       <c r="T9" s="5" t="inlineStr">
         <is>
-          <t>https://comparenet.co.uk/dedicated-fibre-leased-lines</t>
+          <t>https://sptel.com/promotion/business-broadband-singapore/</t>
         </is>
       </c>
       <c r="U9" s="5" t="inlineStr">
@@ -1669,49 +1699,45 @@
       </c>
       <c r="V9" s="5" t="inlineStr">
         <is>
-          <t>iberdrola</t>
+          <t>dbs</t>
         </is>
       </c>
       <c r="W9" s="12" t="n">
-        <v>-659380.2940418924</v>
+        <v>0</v>
       </c>
       <c r="X9" s="5" t="n">
-        <v>133</v>
-      </c>
-      <c r="Y9" s="3" t="inlineStr">
-        <is>
-          <t>nhs-england -183,990; siemens -119,345; network-rail -119,345</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Y9" s="3" t="inlineStr"/>
       <c r="Z9" s="3" t="inlineStr">
         <is>
-          <t>500 Mbps at 690 &gt; 1000 Mbps at 261 USD</t>
+          <t>no</t>
         </is>
       </c>
       <c r="AA9" s="3" t="inlineStr">
         <is>
-          <t>deutsche-post-dhl 267 GBP; iberdrola 195 GBP; nhs-england 300 GBP</t>
+          <t>dbs 312 SGD; dbs 312 SGD</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>GB-DIA-10000-researched</t>
+          <t>US-BROADBAND_PON-300-researched</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>DIA</t>
+          <t>BROADBAND_PON</t>
         </is>
       </c>
       <c r="D10" s="5" t="n">
-        <v>10000</v>
+        <v>300</v>
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
@@ -1725,7 +1751,7 @@
       </c>
       <c r="G10" s="8" t="inlineStr">
         <is>
-          <t>Spitfire publishes 10 Gbps symmetric leased-line pricing from £450/month. Hold—not reject—because it is a single-carrier floor that needs location, term and installation-cost validation.</t>
+          <t>AT&amp;T Business Fiber 300, inside AT&amp;T's footprint only. At $70 it is below the national median for 100 Mbps, and would price every US PON circuit up to 300 Mbps at it.</t>
         </is>
       </c>
       <c r="H10" s="9">
@@ -1737,15 +1763,15 @@
         <v/>
       </c>
       <c r="J10" s="10" t="n">
-        <v>450</v>
+        <v>70</v>
       </c>
       <c r="K10" s="5" t="inlineStr">
         <is>
-          <t>GBP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="L10" s="10" t="n">
-        <v>602.97</v>
+        <v>70</v>
       </c>
       <c r="M10" s="10" t="n"/>
       <c r="N10" s="11">
@@ -1759,27 +1785,27 @@
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t>single source; read from a snippet; re-prices lower tiers</t>
+          <t>read from a snippet; re-prices lower tiers</t>
         </is>
       </c>
       <c r="Q10" s="3" t="inlineStr">
         <is>
-          <t>DIA 10000Mbps MRC (Spitfire, retail)</t>
+          <t>BROADBAND_PON 300 Mbps MRC – US (AT&amp;T Business Fiber published rate)</t>
         </is>
       </c>
       <c r="R10" s="5" t="inlineStr">
         <is>
-          <t>Spitfire Networks — product page; COMPANY_PUBLISHED/SNIPPET_ONLY</t>
+          <t>business.org (AT&amp;T Business Internet Review 2026); AGGREGATOR/SNIPPET_ONLY</t>
         </is>
       </c>
       <c r="S10" s="3" t="inlineStr">
         <is>
-          <t>10 Gbps From: £450/month — 10Gbps Upload — 10Gbps Download</t>
+          <t>Business Fiber 300: $70.00/mo</t>
         </is>
       </c>
       <c r="T10" s="5" t="inlineStr">
         <is>
-          <t>https://www.spitfire.co.uk/connectivity/fibre-ethernet-leased-line/</t>
+          <t>https://www.business.org/services/internet/att-business-internet-review/</t>
         </is>
       </c>
       <c r="U10" s="5" t="inlineStr">
@@ -1789,36 +1815,40 @@
       </c>
       <c r="V10" s="5" t="inlineStr">
         <is>
-          <t>deutsche-post-dhl</t>
+          <t>simmons-bank</t>
         </is>
       </c>
       <c r="W10" s="12" t="n">
-        <v>0</v>
+        <v>-75873.6111235</v>
       </c>
       <c r="X10" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y10" s="3" t="inlineStr"/>
+        <v>243</v>
+      </c>
+      <c r="Y10" s="3" t="inlineStr">
+        <is>
+          <t>simmons-bank -39,654; basf -8,430; siemens -7,181</t>
+        </is>
+      </c>
       <c r="Z10" s="3" t="inlineStr">
         <is>
-          <t>1000 Mbps at 737 &gt; 10000 Mbps at 603 USD</t>
+          <t>250 Mbps at 114 &gt; 300 Mbps at 70 USD</t>
         </is>
       </c>
       <c r="AA10" s="3" t="inlineStr">
         <is>
-          <t>deutsche-post-dhl 450 GBP</t>
+          <t>simmons-bank 70 USD</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>SG-DIA-100-researched</t>
+          <t>ZA-DIA-100-researched</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>ZA</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
@@ -1841,7 +1871,7 @@
       </c>
       <c r="G11" s="8" t="inlineStr">
         <is>
-          <t>Published on SPTel's promotion page (valid to 31 Dec 2026). No circuit in the set uses it.</t>
+          <t>MWCom 'from around R8,000'; the same research gives R8,000-25,000 depending on distance and capacity.</t>
         </is>
       </c>
       <c r="H11" s="9">
@@ -1853,51 +1883,49 @@
         <v/>
       </c>
       <c r="J11" s="10" t="n">
-        <v>312</v>
+        <v>8000</v>
       </c>
       <c r="K11" s="5" t="inlineStr">
         <is>
-          <t>SGD</t>
+          <t>ZAR</t>
         </is>
       </c>
       <c r="L11" s="10" t="n">
-        <v>243.75</v>
-      </c>
-      <c r="M11" s="10" t="n">
-        <v>660</v>
-      </c>
+        <v>444.44</v>
+      </c>
+      <c r="M11" s="10" t="n"/>
       <c r="N11" s="11">
         <f>IF(OR(L11="",M11=""),"",L11/M11)</f>
         <v/>
       </c>
       <c r="O11" s="5" t="inlineStr">
         <is>
-          <t>SEED</t>
+          <t>none - new tier</t>
         </is>
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t>single source; read from a snippet</t>
+          <t>floor; read from a snippet</t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
-          <t>DIA 100 Mbps MRC — Singapore (SPTel enterprise tariff)</t>
+          <t>DIA 100 Mbps MRC ZA (leased line / dedicated fibre)</t>
         </is>
       </c>
       <c r="R11" s="5" t="inlineStr">
         <is>
-          <t>SPTel; COMPANY_PUBLISHED/SNIPPET_ONLY</t>
+          <t>mwcom.co.za; COMPANY_PUBLISHED/SNIPPET_ONLY</t>
         </is>
       </c>
       <c r="S11" s="3" t="inlineStr">
         <is>
-          <t>Enterprise Internet 100Mbps $312/mth (on 24-month contract)</t>
+          <t>Leased lines start from around R8,000/mo for 100 Mbps symmetric.</t>
         </is>
       </c>
       <c r="T11" s="5" t="inlineStr">
         <is>
-          <t>https://sptel.com/promotion/business-broadband-singapore/</t>
+          <t>https://www.mwcom.co.za/business-internet-south-africa</t>
         </is>
       </c>
       <c r="U11" s="5" t="inlineStr">
@@ -1907,59 +1935,59 @@
       </c>
       <c r="V11" s="5" t="inlineStr">
         <is>
-          <t>dbs</t>
+          <t>not recorded</t>
         </is>
       </c>
       <c r="W11" s="12" t="n">
-        <v>0</v>
+        <v>-16474.2432</v>
       </c>
       <c r="X11" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y11" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="Y11" s="3" t="inlineStr">
+        <is>
+          <t>anglo-american -16,474</t>
+        </is>
+      </c>
       <c r="Z11" s="3" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AA11" s="3" t="inlineStr">
-        <is>
-          <t>dbs 312 SGD; dbs 312 SGD</t>
-        </is>
-      </c>
+      <c r="AA11" s="3" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>US-BROADBAND_PON-300-researched</t>
+          <t>AU-BROADBAND_HFC-250-researched</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>BROADBAND_PON</t>
+          <t>BROADBAND_HFC</t>
         </is>
       </c>
       <c r="D12" s="5" t="n">
-        <v>300</v>
-      </c>
-      <c r="E12" s="6" t="inlineStr">
-        <is>
-          <t>undecided</t>
+        <v>250</v>
+      </c>
+      <c r="E12" s="13" t="inlineStr">
+        <is>
+          <t>approved by Christian Bartosch</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Approve</t>
         </is>
       </c>
       <c r="G12" s="8" t="inlineStr">
         <is>
-          <t>AT&amp;T Business Fiber 300, inside AT&amp;T's footprint only. At $70 it is below the national median for 100 Mbps, and would price every US PON circuit up to 300 Mbps at it.</t>
+          <t>Swoop's published standard business nbn 250/100 price of A$104/month. The introductory discount is excluded.</t>
         </is>
       </c>
       <c r="H12" s="9">
@@ -1971,115 +1999,105 @@
         <v/>
       </c>
       <c r="J12" s="10" t="n">
-        <v>70</v>
+        <v>104</v>
       </c>
       <c r="K12" s="5" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>AUD</t>
         </is>
       </c>
       <c r="L12" s="10" t="n">
-        <v>70</v>
-      </c>
-      <c r="M12" s="10" t="n"/>
+        <v>70.27</v>
+      </c>
+      <c r="M12" s="10" t="n">
+        <v>155</v>
+      </c>
       <c r="N12" s="11">
         <f>IF(OR(L12="",M12=""),"",L12/M12)</f>
         <v/>
       </c>
       <c r="O12" s="5" t="inlineStr">
         <is>
-          <t>none - new tier</t>
+          <t>SEED</t>
         </is>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t>read from a snippet; re-prices lower tiers</t>
-        </is>
-      </c>
-      <c r="Q12" s="3" t="inlineStr">
-        <is>
-          <t>BROADBAND_PON 300 Mbps MRC – US (AT&amp;T Business Fiber published rate)</t>
-        </is>
-      </c>
+          <t>single source; re-prices lower tiers</t>
+        </is>
+      </c>
+      <c r="Q12" s="3" t="inlineStr"/>
       <c r="R12" s="5" t="inlineStr">
         <is>
-          <t>business.org (AT&amp;T Business Internet Review 2026); AGGREGATOR/SNIPPET_ONLY</t>
+          <t>run narrative (the disposition was replaced)</t>
         </is>
       </c>
       <c r="S12" s="3" t="inlineStr">
         <is>
-          <t>Business Fiber 300: $70.00/mo</t>
-        </is>
-      </c>
-      <c r="T12" s="5" t="inlineStr">
-        <is>
-          <t>https://www.business.org/services/internet/att-business-internet-review/</t>
-        </is>
-      </c>
+          <t>ise NBN (symmetric, SLA-backed) list prices in AUD excl. GST: 100/100 Mbps A$399/mo, 250/250 Mbps A$399/mo, 500/500 Mbps A$469/mo, 1000/1000 Mbps A$699/mo (36-month term). Swoop published business NBN prices: 250 Mbps A$104/mo (FTTP), 1000 Mbps A$129/mo (FTTP/HFC). Kookaburra Comms (trade press, 2026) cites typical published range A$400 for 100-250 Mbps to A$700-A$1,500 for 1 Gbps</t>
+        </is>
+      </c>
+      <c r="T12" s="5" t="inlineStr"/>
       <c r="U12" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="V12" s="5" t="inlineStr">
         <is>
-          <t>simmons-bank</t>
+          <t>woolworths</t>
         </is>
       </c>
       <c r="W12" s="12" t="n">
-        <v>-75873.6111235</v>
+        <v>-925814.4972972973</v>
       </c>
       <c r="X12" s="5" t="n">
-        <v>243</v>
+        <v>1130</v>
       </c>
       <c r="Y12" s="3" t="inlineStr">
         <is>
-          <t>simmons-bank -39,654; basf -8,430; siemens -7,181</t>
+          <t>woolworths -925,814</t>
         </is>
       </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
-          <t>250 Mbps at 114 &gt; 300 Mbps at 70 USD</t>
-        </is>
-      </c>
-      <c r="AA12" s="3" t="inlineStr">
-        <is>
-          <t>simmons-bank 70 USD</t>
-        </is>
-      </c>
+          <t>100 Mbps at 115 &gt; 250 Mbps at 70 USD; 1000 Mbps at 250 &gt; 2000 Mbps at 149 USD</t>
+        </is>
+      </c>
+      <c r="AA12" s="3" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>ZA-DIA-100-researched</t>
+          <t>AU-BROADBAND_HFC-2000-researched</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>ZA</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>DIA</t>
+          <t>BROADBAND_HFC</t>
         </is>
       </c>
       <c r="D13" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="E13" s="6" t="inlineStr">
-        <is>
-          <t>undecided</t>
+        <v>2000</v>
+      </c>
+      <c r="E13" s="13" t="inlineStr">
+        <is>
+          <t>approved by Christian Bartosch</t>
         </is>
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Approve</t>
         </is>
       </c>
       <c r="G13" s="8" t="inlineStr">
         <is>
-          <t>MWCom 'from around R8,000'; the same research gives R8,000-25,000 depending on distance and capacity.</t>
+          <t>Aussie Broadband business Hyperfast 2000, published; a trade guide puts business fibre plans at A$100-220.</t>
         </is>
       </c>
       <c r="H13" s="9">
@@ -2091,15 +2109,15 @@
         <v/>
       </c>
       <c r="J13" s="10" t="n">
-        <v>8000</v>
+        <v>220</v>
       </c>
       <c r="K13" s="5" t="inlineStr">
         <is>
-          <t>ZAR</t>
+          <t>AUD</t>
         </is>
       </c>
       <c r="L13" s="10" t="n">
-        <v>444.44</v>
+        <v>148.65</v>
       </c>
       <c r="M13" s="10" t="n"/>
       <c r="N13" s="11">
@@ -2113,27 +2131,27 @@
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t>floor; read from a snippet</t>
+          <t>read from a snippet; re-prices lower tiers</t>
         </is>
       </c>
       <c r="Q13" s="3" t="inlineStr">
         <is>
-          <t>DIA 100 Mbps MRC ZA (leased line / dedicated fibre)</t>
+          <t>BROADBAND_HFC AU 2000Mbps MRC (Aussie Broadband Business Hyperfast HFC)</t>
         </is>
       </c>
       <c r="R13" s="5" t="inlineStr">
         <is>
-          <t>mwcom.co.za; COMPANY_PUBLISHED/SNIPPET_ONLY</t>
+          <t>Aussie Broadband / WhistleOut; AGGREGATOR/SNIPPET_ONLY</t>
         </is>
       </c>
       <c r="S13" s="3" t="inlineStr">
         <is>
-          <t>Leased lines start from around R8,000/mo for 100 Mbps symmetric.</t>
+          <t>Aussie Broadband FTTP Business Hyperfast Plus 2000/500 Unlimited Data $220/mth</t>
         </is>
       </c>
       <c r="T13" s="5" t="inlineStr">
         <is>
-          <t>https://www.mwcom.co.za/business-internet-south-africa</t>
+          <t>https://www.whistleout.com.au/Broadband/Guides/NBN-business-plans-compared</t>
         </is>
       </c>
       <c r="U13" s="5" t="inlineStr">
@@ -2143,31 +2161,31 @@
       </c>
       <c r="V13" s="5" t="inlineStr">
         <is>
-          <t>not recorded</t>
+          <t>woolworths</t>
         </is>
       </c>
       <c r="W13" s="12" t="n">
-        <v>-16474.2432</v>
+        <v>0</v>
       </c>
       <c r="X13" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y13" s="3" t="inlineStr">
-        <is>
-          <t>anglo-american -16,474</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Y13" s="3" t="inlineStr"/>
       <c r="Z13" s="3" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="AA13" s="3" t="inlineStr"/>
+          <t>100 Mbps at 115 &gt; 250 Mbps at 70 USD; 1000 Mbps at 250 &gt; 2000 Mbps at 149 USD</t>
+        </is>
+      </c>
+      <c r="AA13" s="3" t="inlineStr">
+        <is>
+          <t>woolworths 220 AUD</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>AU-BROADBAND_HFC-250-researched</t>
+          <t>AU-BROADBAND_PON-250-researched</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
@@ -2177,7 +2195,7 @@
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>BROADBAND_HFC</t>
+          <t>BROADBAND_PON</t>
         </is>
       </c>
       <c r="D14" s="5" t="n">
@@ -2195,7 +2213,7 @@
       </c>
       <c r="G14" s="8" t="inlineStr">
         <is>
-          <t>Swoop's published standard business nbn 250/100 price of A$104/month. The introductory discount is excluded.</t>
+          <t>Aussie Broadband business FTTP 250/100, published by the provider and confirmed by an aggregator.</t>
         </is>
       </c>
       <c r="H14" s="9">
@@ -2207,7 +2225,7 @@
         <v/>
       </c>
       <c r="J14" s="10" t="n">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="K14" s="5" t="inlineStr">
         <is>
@@ -2215,10 +2233,10 @@
         </is>
       </c>
       <c r="L14" s="10" t="n">
-        <v>70.27</v>
+        <v>77.03</v>
       </c>
       <c r="M14" s="10" t="n">
-        <v>155</v>
+        <v>101</v>
       </c>
       <c r="N14" s="11">
         <f>IF(OR(L14="",M14=""),"",L14/M14)</f>
@@ -2231,24 +2249,32 @@
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t>single source; re-prices lower tiers</t>
-        </is>
-      </c>
-      <c r="Q14" s="3" t="inlineStr"/>
+          <t>read from a snippet</t>
+        </is>
+      </c>
+      <c r="Q14" s="3" t="inlineStr">
+        <is>
+          <t>BROADBAND_PON AU 250Mbps MRC (Aussie Broadband Business FTTP 250/100)</t>
+        </is>
+      </c>
       <c r="R14" s="5" t="inlineStr">
         <is>
-          <t>run narrative (the disposition was replaced)</t>
+          <t>Aussie Broadband Enterprise; COMPANY_PUBLISHED/SNIPPET_ONLY</t>
         </is>
       </c>
       <c r="S14" s="3" t="inlineStr">
         <is>
-          <t>ise NBN (symmetric, SLA-backed) list prices in AUD excl. GST: 100/100 Mbps A$399/mo, 250/250 Mbps A$399/mo, 500/500 Mbps A$469/mo, 1000/1000 Mbps A$699/mo (36-month term). Swoop published business NBN prices: 250 Mbps A$104/mo (FTTP), 1000 Mbps A$129/mo (FTTP/HFC). Kookaburra Comms (trade press, 2026) cites typical published range A$400 for 100-250 Mbps to A$700-A$1,500 for 1 Gbps</t>
-        </is>
-      </c>
-      <c r="T14" s="5" t="inlineStr"/>
+          <t>Superfast Plus 250/100 $114/month</t>
+        </is>
+      </c>
+      <c r="T14" s="5" t="inlineStr">
+        <is>
+          <t>https://www.aussiebroadband.com.au/enterprise/internet/nbn-plans/</t>
+        </is>
+      </c>
       <c r="U14" s="5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="V14" s="5" t="inlineStr">
@@ -2257,27 +2283,27 @@
         </is>
       </c>
       <c r="W14" s="12" t="n">
-        <v>-925814.4972972973</v>
+        <v>0</v>
       </c>
       <c r="X14" s="5" t="n">
-        <v>1130</v>
-      </c>
-      <c r="Y14" s="3" t="inlineStr">
-        <is>
-          <t>woolworths -925,814</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Y14" s="3" t="inlineStr"/>
       <c r="Z14" s="3" t="inlineStr">
         <is>
-          <t>100 Mbps at 115 &gt; 250 Mbps at 70 USD; 1000 Mbps at 250 &gt; 2000 Mbps at 149 USD</t>
-        </is>
-      </c>
-      <c r="AA14" s="3" t="inlineStr"/>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="AA14" s="3" t="inlineStr">
+        <is>
+          <t>woolworths 114 AUD</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>AU-BROADBAND_HFC-2000-researched</t>
+          <t>AU-ETHERNET-250-researched</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
@@ -2287,11 +2313,11 @@
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>BROADBAND_HFC</t>
+          <t>ETHERNET</t>
         </is>
       </c>
       <c r="D15" s="5" t="n">
-        <v>2000</v>
+        <v>250</v>
       </c>
       <c r="E15" s="13" t="inlineStr">
         <is>
@@ -2305,7 +2331,7 @@
       </c>
       <c r="G15" s="8" t="inlineStr">
         <is>
-          <t>Aussie Broadband business Hyperfast 2000, published; a trade guide puts business fibre plans at A$100-220.</t>
+          <t>NBN Enterprise Ethernet retail, ex GST, 36-month: Swoop and Vocus publish the same A$399.</t>
         </is>
       </c>
       <c r="H15" s="9">
@@ -2317,7 +2343,7 @@
         <v/>
       </c>
       <c r="J15" s="10" t="n">
-        <v>220</v>
+        <v>399</v>
       </c>
       <c r="K15" s="5" t="inlineStr">
         <is>
@@ -2325,7 +2351,7 @@
         </is>
       </c>
       <c r="L15" s="10" t="n">
-        <v>148.65</v>
+        <v>269.59</v>
       </c>
       <c r="M15" s="10" t="n"/>
       <c r="N15" s="11">
@@ -2339,27 +2365,27 @@
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t>read from a snippet; re-prices lower tiers</t>
+          <t>wholesale; floor; read from a snippet</t>
         </is>
       </c>
       <c r="Q15" s="3" t="inlineStr">
         <is>
-          <t>BROADBAND_HFC AU 2000Mbps MRC (Aussie Broadband Business Hyperfast HFC)</t>
+          <t>ETHERNET AU 250Mbps MRC (NBN Enterprise Ethernet retail, ex GST)</t>
         </is>
       </c>
       <c r="R15" s="5" t="inlineStr">
         <is>
-          <t>Aussie Broadband / WhistleOut; AGGREGATOR/SNIPPET_ONLY</t>
+          <t>Swoop; COMPANY_PUBLISHED/SNIPPET_ONLY</t>
         </is>
       </c>
       <c r="S15" s="3" t="inlineStr">
         <is>
-          <t>Aussie Broadband FTTP Business Hyperfast Plus 2000/500 Unlimited Data $220/mth</t>
+          <t>Business Fibre 250/250 Mbps $399 per month</t>
         </is>
       </c>
       <c r="T15" s="5" t="inlineStr">
         <is>
-          <t>https://www.whistleout.com.au/Broadband/Guides/NBN-business-plans-compared</t>
+          <t>https://www.swoop.com.au/business/enterprise-ethernet/</t>
         </is>
       </c>
       <c r="U15" s="5" t="inlineStr">
@@ -2373,27 +2399,31 @@
         </is>
       </c>
       <c r="W15" s="12" t="n">
-        <v>0</v>
+        <v>-2472.04054054054</v>
       </c>
       <c r="X15" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y15" s="3" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="Y15" s="3" t="inlineStr">
+        <is>
+          <t>woolworths -2,472</t>
+        </is>
+      </c>
       <c r="Z15" s="3" t="inlineStr">
         <is>
-          <t>100 Mbps at 115 &gt; 250 Mbps at 70 USD; 1000 Mbps at 250 &gt; 2000 Mbps at 149 USD</t>
+          <t>no</t>
         </is>
       </c>
       <c r="AA15" s="3" t="inlineStr">
         <is>
-          <t>woolworths 220 AUD</t>
+          <t>woolworths 399 AUD</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>AU-BROADBAND_PON-250-researched</t>
+          <t>AU-ETHERNET-500-researched</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
@@ -2403,11 +2433,11 @@
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>BROADBAND_PON</t>
+          <t>ETHERNET</t>
         </is>
       </c>
       <c r="D16" s="5" t="n">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="E16" s="13" t="inlineStr">
         <is>
@@ -2421,7 +2451,7 @@
       </c>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>Aussie Broadband business FTTP 250/100, published by the provider and confirmed by an aggregator.</t>
+          <t>NBN Enterprise Ethernet retail, ex GST, 36-month: Vocus A$469, Swoop A$499.</t>
         </is>
       </c>
       <c r="H16" s="9">
@@ -2433,7 +2463,7 @@
         <v/>
       </c>
       <c r="J16" s="10" t="n">
-        <v>114</v>
+        <v>469</v>
       </c>
       <c r="K16" s="5" t="inlineStr">
         <is>
@@ -2441,10 +2471,10 @@
         </is>
       </c>
       <c r="L16" s="10" t="n">
-        <v>77.03</v>
+        <v>316.89</v>
       </c>
       <c r="M16" s="10" t="n">
-        <v>101</v>
+        <v>1288</v>
       </c>
       <c r="N16" s="11">
         <f>IF(OR(L16="",M16=""),"",L16/M16)</f>
@@ -2457,27 +2487,27 @@
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t>read from a snippet</t>
+          <t>floor; read from a snippet</t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t>BROADBAND_PON AU 250Mbps MRC (Aussie Broadband Business FTTP 250/100)</t>
+          <t>ETHERNET AU 500Mbps MRC (NBN Enterprise Ethernet retail, ex GST)</t>
         </is>
       </c>
       <c r="R16" s="5" t="inlineStr">
         <is>
-          <t>Aussie Broadband Enterprise; COMPANY_PUBLISHED/SNIPPET_ONLY</t>
+          <t>Vocus; COMPANY_PUBLISHED/SNIPPET_ONLY</t>
         </is>
       </c>
       <c r="S16" s="3" t="inlineStr">
         <is>
-          <t>Superfast Plus 250/100 $114/month</t>
+          <t>500/500Mbps Starting at $469 / per month (ex. GST)</t>
         </is>
       </c>
       <c r="T16" s="5" t="inlineStr">
         <is>
-          <t>https://www.aussiebroadband.com.au/enterprise/internet/nbn-plans/</t>
+          <t>https://www.vocus.com.au/enterprise/internet-and-networks/nbn-enterprise-ethernet</t>
         </is>
       </c>
       <c r="U16" s="5" t="inlineStr">
@@ -2504,14 +2534,14 @@
       </c>
       <c r="AA16" s="3" t="inlineStr">
         <is>
-          <t>woolworths 114 AUD</t>
+          <t>woolworths 469 AUD</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>AU-ETHERNET-250-researched</t>
+          <t>AU-ETHERNET-1000-researched</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
@@ -2525,7 +2555,7 @@
         </is>
       </c>
       <c r="D17" s="5" t="n">
-        <v>250</v>
+        <v>1000</v>
       </c>
       <c r="E17" s="13" t="inlineStr">
         <is>
@@ -2539,7 +2569,7 @@
       </c>
       <c r="G17" s="8" t="inlineStr">
         <is>
-          <t>NBN Enterprise Ethernet retail, ex GST, 36-month: Swoop and Vocus publish the same A$399.</t>
+          <t>NBN Enterprise Ethernet retail, ex GST, 36-month: Swoop and Vocus A$699, Telstra via Telair A$659.</t>
         </is>
       </c>
       <c r="H17" s="9">
@@ -2551,7 +2581,7 @@
         <v/>
       </c>
       <c r="J17" s="10" t="n">
-        <v>399</v>
+        <v>699</v>
       </c>
       <c r="K17" s="5" t="inlineStr">
         <is>
@@ -2559,26 +2589,28 @@
         </is>
       </c>
       <c r="L17" s="10" t="n">
-        <v>269.59</v>
-      </c>
-      <c r="M17" s="10" t="n"/>
+        <v>472.3</v>
+      </c>
+      <c r="M17" s="10" t="n">
+        <v>1450</v>
+      </c>
       <c r="N17" s="11">
         <f>IF(OR(L17="",M17=""),"",L17/M17)</f>
         <v/>
       </c>
       <c r="O17" s="5" t="inlineStr">
         <is>
-          <t>none - new tier</t>
+          <t>SEED</t>
         </is>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t>wholesale; floor; read from a snippet</t>
+          <t>floor; read from a snippet</t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr">
         <is>
-          <t>ETHERNET AU 250Mbps MRC (NBN Enterprise Ethernet retail, ex GST)</t>
+          <t>ETHERNET AU 1000Mbps MRC (NBN Enterprise Ethernet retail, ex GST)</t>
         </is>
       </c>
       <c r="R17" s="5" t="inlineStr">
@@ -2588,7 +2620,7 @@
       </c>
       <c r="S17" s="3" t="inlineStr">
         <is>
-          <t>Business Fibre 250/250 Mbps $399 per month</t>
+          <t>Business Fibre 1000/1000 Mbps $699 per month</t>
         </is>
       </c>
       <c r="T17" s="5" t="inlineStr">
@@ -2607,14 +2639,14 @@
         </is>
       </c>
       <c r="W17" s="12" t="n">
-        <v>-2472.04054054054</v>
+        <v>-304559.635439</v>
       </c>
       <c r="X17" s="5" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
-          <t>woolworths -2,472</t>
+          <t>rio-tinto -304,560</t>
         </is>
       </c>
       <c r="Z17" s="3" t="inlineStr">
@@ -2624,28 +2656,28 @@
       </c>
       <c r="AA17" s="3" t="inlineStr">
         <is>
-          <t>woolworths 399 AUD</t>
+          <t>woolworths 699 AUD</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>AU-ETHERNET-500-researched</t>
+          <t>BE-BROADBAND_PON-150-researched</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>ETHERNET</t>
+          <t>BROADBAND_PON</t>
         </is>
       </c>
       <c r="D18" s="5" t="n">
-        <v>500</v>
+        <v>150</v>
       </c>
       <c r="E18" s="13" t="inlineStr">
         <is>
@@ -2659,7 +2691,7 @@
       </c>
       <c r="G18" s="8" t="inlineStr">
         <is>
-          <t>NBN Enterprise Ethernet retail, ex GST, 36-month: Vocus A$469, Swoop A$499.</t>
+          <t>Proximus Business Go Fiber 150, the standard price after the 12-month promotion, ex VAT, read from the full page.</t>
         </is>
       </c>
       <c r="H18" s="9">
@@ -2671,61 +2703,59 @@
         <v/>
       </c>
       <c r="J18" s="10" t="n">
-        <v>469</v>
+        <v>60</v>
       </c>
       <c r="K18" s="5" t="inlineStr">
         <is>
-          <t>AUD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="L18" s="10" t="n">
-        <v>316.89</v>
-      </c>
-      <c r="M18" s="10" t="n">
-        <v>1288</v>
-      </c>
+        <v>68.88</v>
+      </c>
+      <c r="M18" s="10" t="n"/>
       <c r="N18" s="11">
         <f>IF(OR(L18="",M18=""),"",L18/M18)</f>
         <v/>
       </c>
       <c r="O18" s="5" t="inlineStr">
         <is>
-          <t>SEED</t>
+          <t>none - new tier</t>
         </is>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t>floor; read from a snippet</t>
+          <t>promotional; single source</t>
         </is>
       </c>
       <c r="Q18" s="3" t="inlineStr">
         <is>
-          <t>ETHERNET AU 500Mbps MRC (NBN Enterprise Ethernet retail, ex GST)</t>
+          <t>BROADBAND_PON 150 Mbps MRC (business shared fibre, Proximus Go Fiber)</t>
         </is>
       </c>
       <c r="R18" s="5" t="inlineStr">
         <is>
-          <t>Vocus; COMPANY_PUBLISHED/SNIPPET_ONLY</t>
+          <t>Proximus (proximus.be); COMPANY_PUBLISHED/FULL_PAGE</t>
         </is>
       </c>
       <c r="S18" s="3" t="inlineStr">
         <is>
-          <t>500/500Mbps Starting at $469 / per month (ex. GST)</t>
+          <t>Business Internet Go Fiber 150 Mbps: €45/month during 12 months, then €60/month</t>
         </is>
       </c>
       <c r="T18" s="5" t="inlineStr">
         <is>
-          <t>https://www.vocus.com.au/enterprise/internet-and-networks/nbn-enterprise-ethernet</t>
+          <t>https://www.proximus.be/en/business/internet-subscription</t>
         </is>
       </c>
       <c r="U18" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="V18" s="5" t="inlineStr">
         <is>
-          <t>woolworths</t>
+          <t>bnp-paribas</t>
         </is>
       </c>
       <c r="W18" s="12" t="n">
@@ -2742,24 +2772,24 @@
       </c>
       <c r="AA18" s="3" t="inlineStr">
         <is>
-          <t>woolworths 469 AUD</t>
+          <t>bnp-paribas 60 EUR</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>AU-ETHERNET-1000-researched</t>
+          <t>FR-DIA-1000-researched</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>ETHERNET</t>
+          <t>DIA</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
@@ -2777,7 +2807,7 @@
       </c>
       <c r="G19" s="8" t="inlineStr">
         <is>
-          <t>NBN Enterprise Ethernet retail, ex GST, 36-month: Swoop and Vocus A$699, Telstra via Telair A$659.</t>
+          <t>Orange Business FTTO 1 Gbps, approximately EUR 1,200 per a trade-press snippet. It sits close to the seed (0.91x).</t>
         </is>
       </c>
       <c r="H19" s="9">
@@ -2789,18 +2819,18 @@
         <v/>
       </c>
       <c r="J19" s="10" t="n">
-        <v>699</v>
+        <v>1200</v>
       </c>
       <c r="K19" s="5" t="inlineStr">
         <is>
-          <t>AUD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="L19" s="10" t="n">
-        <v>472.3</v>
+        <v>1377.57</v>
       </c>
       <c r="M19" s="10" t="n">
-        <v>1450</v>
+        <v>1520</v>
       </c>
       <c r="N19" s="11">
         <f>IF(OR(L19="",M19=""),"",L19/M19)</f>
@@ -2813,79 +2843,79 @@
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t>floor; read from a snippet</t>
+          <t>single source; read from a snippet; re-prices lower tiers</t>
         </is>
       </c>
       <c r="Q19" s="3" t="inlineStr">
         <is>
-          <t>ETHERNET AU 1000Mbps MRC (NBN Enterprise Ethernet retail, ex GST)</t>
+          <t>DIA 1000 Mbps MRC France (Orange Business FTTO dedicated fibre)</t>
         </is>
       </c>
       <c r="R19" s="5" t="inlineStr">
         <is>
-          <t>Swoop; COMPANY_PUBLISHED/SNIPPET_ONLY</t>
+          <t>myadsl.fr; TRADE_PRESS/SNIPPET_ONLY</t>
         </is>
       </c>
       <c r="S19" s="3" t="inlineStr">
         <is>
-          <t>Business Fibre 1000/1000 Mbps $699 per month</t>
+          <t>Offre intermédiaire: 1 Gb/s, SLA amélioré, support 24/7 – tarif mensuel approximatif: 1 200 €</t>
         </is>
       </c>
       <c r="T19" s="5" t="inlineStr">
         <is>
-          <t>https://www.swoop.com.au/business/enterprise-ethernet/</t>
+          <t>https://www.myadsl.fr/cout-ftto-orange-2025/</t>
         </is>
       </c>
       <c r="U19" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="V19" s="5" t="inlineStr">
         <is>
-          <t>woolworths</t>
+          <t>bnp-paribas</t>
         </is>
       </c>
       <c r="W19" s="12" t="n">
-        <v>-304559.635439</v>
+        <v>-106959.98274275</v>
       </c>
       <c r="X19" s="5" t="n">
-        <v>20</v>
+        <v>72</v>
       </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
-          <t>rio-tinto -304,560</t>
+          <t>bnp-paribas -29,777; siemens -26,800; capgemini -14,889</t>
         </is>
       </c>
       <c r="Z19" s="3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>500 Mbps at 1398 &gt; 1000 Mbps at 1378 USD</t>
         </is>
       </c>
       <c r="AA19" s="3" t="inlineStr">
         <is>
-          <t>woolworths 699 AUD</t>
+          <t>bnp-paribas ~1200 EUR</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>BE-BROADBAND_PON-150-researched</t>
+          <t>GB-BROADBAND_HFC-200-researched</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>BE</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>BROADBAND_PON</t>
+          <t>BROADBAND_HFC</t>
         </is>
       </c>
       <c r="D20" s="5" t="n">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="E20" s="13" t="inlineStr">
         <is>
@@ -2899,7 +2929,7 @@
       </c>
       <c r="G20" s="8" t="inlineStr">
         <is>
-          <t>Proximus Business Go Fiber 150, the standard price after the 12-month promotion, ex VAT, read from the full page.</t>
+          <t>Virgin Media Business Voom 200, published, ex VAT, 24-month.</t>
         </is>
       </c>
       <c r="H20" s="9">
@@ -2911,15 +2941,15 @@
         <v/>
       </c>
       <c r="J20" s="10" t="n">
-        <v>60</v>
+        <v>29.95</v>
       </c>
       <c r="K20" s="5" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>GBP</t>
         </is>
       </c>
       <c r="L20" s="10" t="n">
-        <v>68.88</v>
+        <v>40.13</v>
       </c>
       <c r="M20" s="10" t="n"/>
       <c r="N20" s="11">
@@ -2933,75 +2963,79 @@
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t>promotional; single source</t>
+          <t>floor; read from a snippet; re-prices lower tiers</t>
         </is>
       </c>
       <c r="Q20" s="3" t="inlineStr">
         <is>
-          <t>BROADBAND_PON 150 Mbps MRC (business shared fibre, Proximus Go Fiber)</t>
+          <t>BROADBAND_HFC 200Mbps MRC (Virgin Media Business Voom 200)</t>
         </is>
       </c>
       <c r="R20" s="5" t="inlineStr">
         <is>
-          <t>Proximus (proximus.be); COMPANY_PUBLISHED/FULL_PAGE</t>
+          <t>virginmediabusiness.co.uk; COMPANY_PUBLISHED/SNIPPET_ONLY</t>
         </is>
       </c>
       <c r="S20" s="3" t="inlineStr">
         <is>
-          <t>Business Internet Go Fiber 150 Mbps: €45/month during 12 months, then €60/month</t>
+          <t>Prices start from just £29.95 per month</t>
         </is>
       </c>
       <c r="T20" s="5" t="inlineStr">
         <is>
-          <t>https://www.proximus.be/en/business/internet-subscription</t>
+          <t>https://www.virginmediabusiness.co.uk/connectivity/internet-access/business-broadband/</t>
         </is>
       </c>
       <c r="U20" s="5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="V20" s="5" t="inlineStr">
         <is>
-          <t>bnp-paribas</t>
+          <t>boots</t>
         </is>
       </c>
       <c r="W20" s="12" t="n">
-        <v>0</v>
+        <v>-421041.3935414713</v>
       </c>
       <c r="X20" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y20" s="3" t="inlineStr"/>
+        <v>5864</v>
+      </c>
+      <c r="Y20" s="3" t="inlineStr">
+        <is>
+          <t>tesco -269,489; boots -151,552</t>
+        </is>
+      </c>
       <c r="Z20" s="3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>100 Mbps at 80 &gt; 200 Mbps at 40 USD; 250 Mbps at 108 &gt; 400 Mbps at 47 USD; 500 Mbps at 140 &gt; 600 Mbps at 52 USD</t>
         </is>
       </c>
       <c r="AA20" s="3" t="inlineStr">
         <is>
-          <t>bnp-paribas 60 EUR</t>
+          <t>boots 29.95 GBP</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>FR-DIA-1000-researched</t>
+          <t>GB-BROADBAND_HFC-400-researched</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>DIA</t>
+          <t>BROADBAND_HFC</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
-        <v>1000</v>
+        <v>400</v>
       </c>
       <c r="E21" s="13" t="inlineStr">
         <is>
@@ -3015,7 +3049,7 @@
       </c>
       <c r="G21" s="8" t="inlineStr">
         <is>
-          <t>Orange Business FTTO 1 Gbps, approximately EUR 1,200 per a trade-press snippet. It sits close to the seed (0.91x).</t>
+          <t>Virgin Media Business Voom 400, published, ex VAT, 24-month.</t>
         </is>
       </c>
       <c r="H21" s="9">
@@ -3027,89 +3061,83 @@
         <v/>
       </c>
       <c r="J21" s="10" t="n">
-        <v>1200</v>
+        <v>34.95</v>
       </c>
       <c r="K21" s="5" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>GBP</t>
         </is>
       </c>
       <c r="L21" s="10" t="n">
-        <v>1377.57</v>
-      </c>
-      <c r="M21" s="10" t="n">
-        <v>1520</v>
-      </c>
+        <v>46.83</v>
+      </c>
+      <c r="M21" s="10" t="n"/>
       <c r="N21" s="11">
         <f>IF(OR(L21="",M21=""),"",L21/M21)</f>
         <v/>
       </c>
       <c r="O21" s="5" t="inlineStr">
         <is>
-          <t>SEED</t>
+          <t>none - new tier</t>
         </is>
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
-          <t>single source; read from a snippet; re-prices lower tiers</t>
+          <t>read from a snippet; re-prices lower tiers</t>
         </is>
       </c>
       <c r="Q21" s="3" t="inlineStr">
         <is>
-          <t>DIA 1000 Mbps MRC France (Orange Business FTTO dedicated fibre)</t>
+          <t>BROADBAND_HFC 400Mbps MRC — Virgin Media Business Voom 400</t>
         </is>
       </c>
       <c r="R21" s="5" t="inlineStr">
         <is>
-          <t>myadsl.fr; TRADE_PRESS/SNIPPET_ONLY</t>
+          <t>virginmediabusiness.co.uk; COMPANY_PUBLISHED/SNIPPET_ONLY</t>
         </is>
       </c>
       <c r="S21" s="3" t="inlineStr">
         <is>
-          <t>Offre intermédiaire: 1 Gb/s, SLA amélioré, support 24/7 – tarif mensuel approximatif: 1 200 €</t>
+          <t>Voom 400 | Download 400Mbps | £34.95 per month</t>
         </is>
       </c>
       <c r="T21" s="5" t="inlineStr">
         <is>
-          <t>https://www.myadsl.fr/cout-ftto-orange-2025/</t>
+          <t>https://www.virginmediabusiness.co.uk/connectivity/internet-access/business-broadband/</t>
         </is>
       </c>
       <c r="U21" s="5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="V21" s="5" t="inlineStr">
         <is>
-          <t>bnp-paribas</t>
+          <t>not recorded</t>
         </is>
       </c>
       <c r="W21" s="12" t="n">
-        <v>-106959.98274275</v>
+        <v>-111641.2488303241</v>
       </c>
       <c r="X21" s="5" t="n">
-        <v>72</v>
+        <v>1916</v>
       </c>
       <c r="Y21" s="3" t="inlineStr">
         <is>
-          <t>bnp-paribas -29,777; siemens -26,800; capgemini -14,889</t>
+          <t>mcdonalds -87,810; deutsche-post-dhl -20,102; royal-mail -2,622</t>
         </is>
       </c>
       <c r="Z21" s="3" t="inlineStr">
         <is>
-          <t>500 Mbps at 1398 &gt; 1000 Mbps at 1378 USD</t>
-        </is>
-      </c>
-      <c r="AA21" s="3" t="inlineStr">
-        <is>
-          <t>bnp-paribas ~1200 EUR</t>
-        </is>
-      </c>
+          <t>100 Mbps at 80 &gt; 200 Mbps at 40 USD; 250 Mbps at 108 &gt; 400 Mbps at 47 USD; 500 Mbps at 140 &gt; 600 Mbps at 52 USD</t>
+        </is>
+      </c>
+      <c r="AA21" s="3" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>GB-BROADBAND_HFC-200-researched</t>
+          <t>GB-BROADBAND_HFC-600-researched</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
@@ -3123,7 +3151,7 @@
         </is>
       </c>
       <c r="D22" s="5" t="n">
-        <v>200</v>
+        <v>600</v>
       </c>
       <c r="E22" s="13" t="inlineStr">
         <is>
@@ -3137,7 +3165,7 @@
       </c>
       <c r="G22" s="8" t="inlineStr">
         <is>
-          <t>Virgin Media Business Voom 200, published, ex VAT, 24-month.</t>
+          <t>Virgin Media Business Voom 600, published, ex VAT, 24-month.</t>
         </is>
       </c>
       <c r="H22" s="9">
@@ -3149,7 +3177,7 @@
         <v/>
       </c>
       <c r="J22" s="10" t="n">
-        <v>29.95</v>
+        <v>38.95</v>
       </c>
       <c r="K22" s="5" t="inlineStr">
         <is>
@@ -3157,7 +3185,7 @@
         </is>
       </c>
       <c r="L22" s="10" t="n">
-        <v>40.13</v>
+        <v>52.19</v>
       </c>
       <c r="M22" s="10" t="n"/>
       <c r="N22" s="11">
@@ -3171,12 +3199,12 @@
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
-          <t>floor; read from a snippet; re-prices lower tiers</t>
+          <t>read from a snippet; re-prices lower tiers</t>
         </is>
       </c>
       <c r="Q22" s="3" t="inlineStr">
         <is>
-          <t>BROADBAND_HFC 200Mbps MRC (Virgin Media Business Voom 200)</t>
+          <t>BROADBAND_HFC 600Mbps MRC — Virgin Media Business Voom 600</t>
         </is>
       </c>
       <c r="R22" s="5" t="inlineStr">
@@ -3186,7 +3214,7 @@
       </c>
       <c r="S22" s="3" t="inlineStr">
         <is>
-          <t>Prices start from just £29.95 per month</t>
+          <t>Voom 600 | Download 600Mbps | £38.95 per month</t>
         </is>
       </c>
       <c r="T22" s="5" t="inlineStr">
@@ -3201,35 +3229,27 @@
       </c>
       <c r="V22" s="5" t="inlineStr">
         <is>
-          <t>boots</t>
+          <t>not recorded</t>
         </is>
       </c>
       <c r="W22" s="12" t="n">
-        <v>-421041.3935414713</v>
+        <v>0</v>
       </c>
       <c r="X22" s="5" t="n">
-        <v>5864</v>
-      </c>
-      <c r="Y22" s="3" t="inlineStr">
-        <is>
-          <t>tesco -269,489; boots -151,552</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Y22" s="3" t="inlineStr"/>
       <c r="Z22" s="3" t="inlineStr">
         <is>
           <t>100 Mbps at 80 &gt; 200 Mbps at 40 USD; 250 Mbps at 108 &gt; 400 Mbps at 47 USD; 500 Mbps at 140 &gt; 600 Mbps at 52 USD</t>
         </is>
       </c>
-      <c r="AA22" s="3" t="inlineStr">
-        <is>
-          <t>boots 29.95 GBP</t>
-        </is>
-      </c>
+      <c r="AA22" s="3" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>GB-BROADBAND_HFC-400-researched</t>
+          <t>GB-BROADBAND_HFC-1000-researched</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
@@ -3243,7 +3263,7 @@
         </is>
       </c>
       <c r="D23" s="5" t="n">
-        <v>400</v>
+        <v>1000</v>
       </c>
       <c r="E23" s="13" t="inlineStr">
         <is>
@@ -3257,7 +3277,7 @@
       </c>
       <c r="G23" s="8" t="inlineStr">
         <is>
-          <t>Virgin Media Business Voom 400, published, ex VAT, 24-month.</t>
+          <t>Virgin Media Business Voom Gig1, published, ex VAT, 24-month.</t>
         </is>
       </c>
       <c r="H23" s="9">
@@ -3269,7 +3289,7 @@
         <v/>
       </c>
       <c r="J23" s="10" t="n">
-        <v>34.95</v>
+        <v>43.95</v>
       </c>
       <c r="K23" s="5" t="inlineStr">
         <is>
@@ -3277,16 +3297,18 @@
         </is>
       </c>
       <c r="L23" s="10" t="n">
-        <v>46.83</v>
-      </c>
-      <c r="M23" s="10" t="n"/>
+        <v>58.89</v>
+      </c>
+      <c r="M23" s="10" t="n">
+        <v>176</v>
+      </c>
       <c r="N23" s="11">
         <f>IF(OR(L23="",M23=""),"",L23/M23)</f>
         <v/>
       </c>
       <c r="O23" s="5" t="inlineStr">
         <is>
-          <t>none - new tier</t>
+          <t>SEED</t>
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr">
@@ -3296,7 +3318,7 @@
       </c>
       <c r="Q23" s="3" t="inlineStr">
         <is>
-          <t>BROADBAND_HFC 400Mbps MRC — Virgin Media Business Voom 400</t>
+          <t>BROADBAND_HFC 1000Mbps MRC — Virgin Media Business Voom Gig1</t>
         </is>
       </c>
       <c r="R23" s="5" t="inlineStr">
@@ -3306,7 +3328,7 @@
       </c>
       <c r="S23" s="3" t="inlineStr">
         <is>
-          <t>Voom 400 | Download 400Mbps | £34.95 per month</t>
+          <t>Voom Gig1 | Download 1000Mbps | £43.95 per month</t>
         </is>
       </c>
       <c r="T23" s="5" t="inlineStr">
@@ -3325,27 +3347,27 @@
         </is>
       </c>
       <c r="W23" s="12" t="n">
-        <v>-111641.2488303241</v>
+        <v>0</v>
       </c>
       <c r="X23" s="5" t="n">
-        <v>1916</v>
-      </c>
-      <c r="Y23" s="3" t="inlineStr">
-        <is>
-          <t>mcdonalds -87,810; deutsche-post-dhl -20,102; royal-mail -2,622</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Y23" s="3" t="inlineStr"/>
       <c r="Z23" s="3" t="inlineStr">
         <is>
           <t>100 Mbps at 80 &gt; 200 Mbps at 40 USD; 250 Mbps at 108 &gt; 400 Mbps at 47 USD; 500 Mbps at 140 &gt; 600 Mbps at 52 USD</t>
         </is>
       </c>
-      <c r="AA23" s="3" t="inlineStr"/>
+      <c r="AA23" s="3" t="inlineStr">
+        <is>
+          <t>boots 53.95 GBP</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>GB-BROADBAND_HFC-600-researched</t>
+          <t>GB-BROADBAND_HFC-2000-researched</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
@@ -3359,7 +3381,7 @@
         </is>
       </c>
       <c r="D24" s="5" t="n">
-        <v>600</v>
+        <v>2000</v>
       </c>
       <c r="E24" s="13" t="inlineStr">
         <is>
@@ -3373,7 +3395,7 @@
       </c>
       <c r="G24" s="8" t="inlineStr">
         <is>
-          <t>Virgin Media Business Voom 600, published, ex VAT, 24-month.</t>
+          <t>Virgin Media Business Voom Gig2, published, ex VAT, 24-month.</t>
         </is>
       </c>
       <c r="H24" s="9">
@@ -3385,7 +3407,7 @@
         <v/>
       </c>
       <c r="J24" s="10" t="n">
-        <v>38.95</v>
+        <v>83.95</v>
       </c>
       <c r="K24" s="5" t="inlineStr">
         <is>
@@ -3393,7 +3415,7 @@
         </is>
       </c>
       <c r="L24" s="10" t="n">
-        <v>52.19</v>
+        <v>112.49</v>
       </c>
       <c r="M24" s="10" t="n"/>
       <c r="N24" s="11">
@@ -3407,29 +3429,21 @@
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t>read from a snippet; re-prices lower tiers</t>
-        </is>
-      </c>
-      <c r="Q24" s="3" t="inlineStr">
-        <is>
-          <t>BROADBAND_HFC 600Mbps MRC — Virgin Media Business Voom 600</t>
-        </is>
-      </c>
+          <t>floor; single source; re-prices lower tiers</t>
+        </is>
+      </c>
+      <c r="Q24" s="3" t="inlineStr"/>
       <c r="R24" s="5" t="inlineStr">
         <is>
-          <t>virginmediabusiness.co.uk; COMPANY_PUBLISHED/SNIPPET_ONLY</t>
+          <t>run narrative (the disposition was replaced)</t>
         </is>
       </c>
       <c r="S24" s="3" t="inlineStr">
         <is>
-          <t>Voom 600 | Download 600Mbps | £38.95 per month</t>
-        </is>
-      </c>
-      <c r="T24" s="5" t="inlineStr">
-        <is>
-          <t>https://www.virginmediabusiness.co.uk/connectivity/internet-access/business-broadband/</t>
-        </is>
-      </c>
+          <t>e DIA. (2) BROADBAND_HFC: Virgin Media Business publishes HFC/cable broadband: Voom 200 (200 Mbps) from £29.95/month, Voom 400 (400 Mbps) from £34.95/month, Voom Gig1 (1 Gbps) from £43.95/month, Voom Gig2 (2 Gbps) from £83.95/month, all ex-VAT 24-month contract, October 2026. New symmetric XGS-PON (BROADBAND_PON) Full Fibre X plans: 200 Mbps from £39.95/month, 1 Gbps from £53.95/mon</t>
+        </is>
+      </c>
+      <c r="T24" s="5" t="inlineStr"/>
       <c r="U24" s="5" t="inlineStr">
         <is>
           <t>2026</t>
@@ -3437,7 +3451,7 @@
       </c>
       <c r="V24" s="5" t="inlineStr">
         <is>
-          <t>not recorded</t>
+          <t>royal-mail</t>
         </is>
       </c>
       <c r="W24" s="12" t="n">
@@ -3457,7 +3471,7 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>GB-BROADBAND_HFC-1000-researched</t>
+          <t>GB-BROADBAND_PON-100-researched</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
@@ -3467,11 +3481,11 @@
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>BROADBAND_HFC</t>
+          <t>BROADBAND_PON</t>
         </is>
       </c>
       <c r="D25" s="5" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="E25" s="13" t="inlineStr">
         <is>
@@ -3485,7 +3499,7 @@
       </c>
       <c r="G25" s="8" t="inlineStr">
         <is>
-          <t>Virgin Media Business Voom Gig1, published, ex VAT, 24-month.</t>
+          <t>BT Business Full Fibre 100 at GBP 35 a month ex VAT, published (verified May 2026).</t>
         </is>
       </c>
       <c r="H25" s="9">
@@ -3497,7 +3511,7 @@
         <v/>
       </c>
       <c r="J25" s="10" t="n">
-        <v>43.95</v>
+        <v>35</v>
       </c>
       <c r="K25" s="5" t="inlineStr">
         <is>
@@ -3505,10 +3519,10 @@
         </is>
       </c>
       <c r="L25" s="10" t="n">
-        <v>58.89</v>
+        <v>46.9</v>
       </c>
       <c r="M25" s="10" t="n">
-        <v>176</v>
+        <v>70</v>
       </c>
       <c r="N25" s="11">
         <f>IF(OR(L25="",M25=""),"",L25/M25)</f>
@@ -3521,75 +3535,73 @@
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t>read from a snippet; re-prices lower tiers</t>
-        </is>
-      </c>
-      <c r="Q25" s="3" t="inlineStr">
-        <is>
-          <t>BROADBAND_HFC 1000Mbps MRC — Virgin Media Business Voom Gig1</t>
-        </is>
-      </c>
+          <t>floor; single source; re-prices lower tiers</t>
+        </is>
+      </c>
+      <c r="Q25" s="3" t="inlineStr"/>
       <c r="R25" s="5" t="inlineStr">
         <is>
-          <t>virginmediabusiness.co.uk; COMPANY_PUBLISHED/SNIPPET_ONLY</t>
+          <t>run narrative (the disposition was replaced)</t>
         </is>
       </c>
       <c r="S25" s="3" t="inlineStr">
         <is>
-          <t>Voom Gig1 | Download 1000Mbps | £43.95 per month</t>
-        </is>
-      </c>
-      <c r="T25" s="5" t="inlineStr">
-        <is>
-          <t>https://www.virginmediabusiness.co.uk/connectivity/internet-access/business-broadband/</t>
-        </is>
-      </c>
+          <t xml:space="preserve"> €700–€1,300/month (≈USD 765–1,420). The model's assumed GB MPLS 100 Mbps of USD 750–1,250/month is within this band.
+**GB — BROADBAND_PON / HFC**
+BT Business published tariffs (verified May 2026): Full Fibre 100 Mbps £35/month ex-VAT; Full Fibre 500 Mbps £55/month; Full Fibre 900 Mbps £65/month. Virgin Media Business (cable/HFC): from £29.95/month. Vodafone Business entry-level</t>
+        </is>
+      </c>
+      <c r="T25" s="5" t="inlineStr"/>
       <c r="U25" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="V25" s="5" t="inlineStr">
         <is>
-          <t>not recorded</t>
+          <t>saint-gobain</t>
         </is>
       </c>
       <c r="W25" s="12" t="n">
-        <v>0</v>
+        <v>-742283.2166248914</v>
       </c>
       <c r="X25" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y25" s="3" t="inlineStr"/>
+        <v>2847</v>
+      </c>
+      <c r="Y25" s="3" t="inlineStr">
+        <is>
+          <t>iberdrola -243,421; network-rail -216,375; nhs-england -161,315</t>
+        </is>
+      </c>
       <c r="Z25" s="3" t="inlineStr">
         <is>
-          <t>100 Mbps at 80 &gt; 200 Mbps at 40 USD; 250 Mbps at 108 &gt; 400 Mbps at 47 USD; 500 Mbps at 140 &gt; 600 Mbps at 52 USD</t>
+          <t>50 Mbps at 58 &gt; 100 Mbps at 47 USD</t>
         </is>
       </c>
       <c r="AA25" s="3" t="inlineStr">
         <is>
-          <t>boots 53.95 GBP</t>
+          <t>deutsche-post-dhl 29 GBP</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>GB-BROADBAND_HFC-2000-researched</t>
+          <t>NL-DIA-200-researched</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>NL</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>BROADBAND_HFC</t>
+          <t>DIA</t>
         </is>
       </c>
       <c r="D26" s="5" t="n">
-        <v>2000</v>
+        <v>200</v>
       </c>
       <c r="E26" s="13" t="inlineStr">
         <is>
@@ -3603,7 +3615,7 @@
       </c>
       <c r="G26" s="8" t="inlineStr">
         <is>
-          <t>Virgin Media Business Voom Gig2, published, ex VAT, 24-month.</t>
+          <t>Eurofiber DIA 200 from about EUR 348, as quoted by a broker; a carrier's indicative business price. No circuit in the set uses it.</t>
         </is>
       </c>
       <c r="H26" s="9">
@@ -3615,15 +3627,15 @@
         <v/>
       </c>
       <c r="J26" s="10" t="n">
-        <v>83.95</v>
+        <v>348</v>
       </c>
       <c r="K26" s="5" t="inlineStr">
         <is>
-          <t>GBP</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="L26" s="10" t="n">
-        <v>112.49</v>
+        <v>399.49</v>
       </c>
       <c r="M26" s="10" t="n"/>
       <c r="N26" s="11">
@@ -3640,26 +3652,34 @@
           <t>floor; single source; re-prices lower tiers</t>
         </is>
       </c>
-      <c r="Q26" s="3" t="inlineStr"/>
+      <c r="Q26" s="3" t="inlineStr">
+        <is>
+          <t>DIA MRC 200 Mbps (NL, Eurofiber)</t>
+        </is>
+      </c>
       <c r="R26" s="5" t="inlineStr">
         <is>
-          <t>run narrative (the disposition was replaced)</t>
+          <t>Connected Networks; COMPANY_PUBLISHED/FULL_PAGE</t>
         </is>
       </c>
       <c r="S26" s="3" t="inlineStr">
         <is>
-          <t>e DIA. (2) BROADBAND_HFC: Virgin Media Business publishes HFC/cable broadband: Voom 200 (200 Mbps) from £29.95/month, Voom 400 (400 Mbps) from £34.95/month, Voom Gig1 (1 Gbps) from £43.95/month, Voom Gig2 (2 Gbps) from £83.95/month, all ex-VAT 24-month contract, October 2026. New symmetric XGS-PON (BROADBAND_PON) Full Fibre X plans: 200 Mbps from £39.95/month, 1 Gbps from £53.95/mon</t>
-        </is>
-      </c>
-      <c r="T26" s="5" t="inlineStr"/>
+          <t>DIA pricing via Eurofiber starts from approximately €348/month for 200Mbps.</t>
+        </is>
+      </c>
+      <c r="T26" s="5" t="inlineStr">
+        <is>
+          <t>https://www.connectednetworks.io/countries/holland-the-netherlands-business-internet-connectivity</t>
+        </is>
+      </c>
       <c r="U26" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="V26" s="5" t="inlineStr">
         <is>
-          <t>royal-mail</t>
+          <t>ahold-delhaize</t>
         </is>
       </c>
       <c r="W26" s="12" t="n">
@@ -3671,20 +3691,24 @@
       <c r="Y26" s="3" t="inlineStr"/>
       <c r="Z26" s="3" t="inlineStr">
         <is>
-          <t>100 Mbps at 80 &gt; 200 Mbps at 40 USD; 250 Mbps at 108 &gt; 400 Mbps at 47 USD; 500 Mbps at 140 &gt; 600 Mbps at 52 USD</t>
-        </is>
-      </c>
-      <c r="AA26" s="3" t="inlineStr"/>
+          <t>100 Mbps at 500 &gt; 200 Mbps at 399 USD</t>
+        </is>
+      </c>
+      <c r="AA26" s="3" t="inlineStr">
+        <is>
+          <t>ahold-delhaize 348 EUR; deutsche-post-dhl 348 EUR; douglas 348 EUR; maersk 348 EUR; shell ~€348 EUR; shell 348 EUR; unilever 348 EUR; unilever 348 EUR</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>GB-BROADBAND_PON-100-researched</t>
+          <t>SG-BROADBAND_PON-500-researched</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
@@ -3693,7 +3717,7 @@
         </is>
       </c>
       <c r="D27" s="5" t="n">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="E27" s="13" t="inlineStr">
         <is>
@@ -3707,7 +3731,7 @@
       </c>
       <c r="G27" s="8" t="inlineStr">
         <is>
-          <t>BT Business Full Fibre 100 at GBP 35 a month ex VAT, published (verified May 2026).</t>
+          <t>Business dynamic fibre on a 24-month contract: StarHub S$109, Singtel S$118.</t>
         </is>
       </c>
       <c r="H27" s="9">
@@ -3719,18 +3743,18 @@
         <v/>
       </c>
       <c r="J27" s="10" t="n">
-        <v>35</v>
+        <v>109</v>
       </c>
       <c r="K27" s="5" t="inlineStr">
         <is>
-          <t>GBP</t>
+          <t>SGD</t>
         </is>
       </c>
       <c r="L27" s="10" t="n">
-        <v>46.9</v>
+        <v>85.16</v>
       </c>
       <c r="M27" s="10" t="n">
-        <v>70</v>
+        <v>115</v>
       </c>
       <c r="N27" s="11">
         <f>IF(OR(L27="",M27=""),"",L27/M27)</f>
@@ -3743,73 +3767,79 @@
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
-          <t>floor; single source; re-prices lower tiers</t>
-        </is>
-      </c>
-      <c r="Q27" s="3" t="inlineStr"/>
+          <t>single source; read from a snippet; re-prices lower tiers</t>
+        </is>
+      </c>
+      <c r="Q27" s="3" t="inlineStr">
+        <is>
+          <t>BROADBAND_PON 500 Mbps MRC business dynamic — Singapore (Singtel)</t>
+        </is>
+      </c>
       <c r="R27" s="5" t="inlineStr">
         <is>
-          <t>run narrative (the disposition was replaced)</t>
+          <t>DollarsAndSense.sg; AGGREGATOR/SNIPPET_ONLY</t>
         </is>
       </c>
       <c r="S27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> €700–€1,300/month (≈USD 765–1,420). The model's assumed GB MPLS 100 Mbps of USD 750–1,250/month is within this band.
-**GB — BROADBAND_PON / HFC**
-BT Business published tariffs (verified May 2026): Full Fibre 100 Mbps £35/month ex-VAT; Full Fibre 500 Mbps £55/month; Full Fibre 900 Mbps £65/month. Virgin Media Business (cable/HFC): from £29.95/month. Vodafone Business entry-level</t>
-        </is>
-      </c>
-      <c r="T27" s="5" t="inlineStr"/>
+          <t>Singtel · $118 · $178 [for 500Mbps and 1Gbps dynamic broadband, 24-month contract]</t>
+        </is>
+      </c>
+      <c r="T27" s="5" t="inlineStr">
+        <is>
+          <t>https://dollarsandsense.sg/price-guide-to-business-broadband-plans-for-offices-in-singapore/</t>
+        </is>
+      </c>
       <c r="U27" s="5" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="V27" s="5" t="inlineStr">
         <is>
-          <t>saint-gobain</t>
+          <t>dbs</t>
         </is>
       </c>
       <c r="W27" s="12" t="n">
-        <v>-742283.2166248914</v>
+        <v>-2199.09195</v>
       </c>
       <c r="X27" s="5" t="n">
-        <v>2847</v>
+        <v>36</v>
       </c>
       <c r="Y27" s="3" t="inlineStr">
         <is>
-          <t>iberdrola -243,421; network-rail -216,375; nhs-england -161,315</t>
+          <t>dbs -2,199</t>
         </is>
       </c>
       <c r="Z27" s="3" t="inlineStr">
         <is>
-          <t>50 Mbps at 58 &gt; 100 Mbps at 47 USD</t>
+          <t>250 Mbps at 91 &gt; 500 Mbps at 85 USD</t>
         </is>
       </c>
       <c r="AA27" s="3" t="inlineStr">
         <is>
-          <t>deutsche-post-dhl 29 GBP</t>
+          <t>dbs 118 SGD; dbs 109 SGD</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>NL-DIA-200-researched</t>
+          <t>SG-BROADBAND_PON-1000-researched</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>NL</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>DIA</t>
+          <t>BROADBAND_PON</t>
         </is>
       </c>
       <c r="D28" s="5" t="n">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="E28" s="13" t="inlineStr">
         <is>
@@ -3823,7 +3853,7 @@
       </c>
       <c r="G28" s="8" t="inlineStr">
         <is>
-          <t>Eurofiber DIA 200 from about EUR 348, as quoted by a broker; a carrier's indicative business price. No circuit in the set uses it.</t>
+          <t>Business dynamic fibre on a 24-month contract: Singtel S$178, StarHub S$174.</t>
         </is>
       </c>
       <c r="H28" s="9">
@@ -3835,49 +3865,51 @@
         <v/>
       </c>
       <c r="J28" s="10" t="n">
-        <v>348</v>
+        <v>178</v>
       </c>
       <c r="K28" s="5" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>SGD</t>
         </is>
       </c>
       <c r="L28" s="10" t="n">
-        <v>399.49</v>
-      </c>
-      <c r="M28" s="10" t="n"/>
+        <v>139.06</v>
+      </c>
+      <c r="M28" s="10" t="n">
+        <v>149</v>
+      </c>
       <c r="N28" s="11">
         <f>IF(OR(L28="",M28=""),"",L28/M28)</f>
         <v/>
       </c>
       <c r="O28" s="5" t="inlineStr">
         <is>
-          <t>none - new tier</t>
+          <t>SEED</t>
         </is>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t>floor; single source; re-prices lower tiers</t>
+          <t>single source; read from a snippet; re-prices lower tiers</t>
         </is>
       </c>
       <c r="Q28" s="3" t="inlineStr">
         <is>
-          <t>DIA MRC 200 Mbps (NL, Eurofiber)</t>
+          <t>BROADBAND_PON 1000 Mbps MRC business dynamic — Singapore (Singtel)</t>
         </is>
       </c>
       <c r="R28" s="5" t="inlineStr">
         <is>
-          <t>Connected Networks; COMPANY_PUBLISHED/FULL_PAGE</t>
+          <t>DollarsAndSense.sg; AGGREGATOR/SNIPPET_ONLY</t>
         </is>
       </c>
       <c r="S28" s="3" t="inlineStr">
         <is>
-          <t>DIA pricing via Eurofiber starts from approximately €348/month for 200Mbps.</t>
+          <t>Singtel · $118 · $178 [for 500Mbps and 1Gbps dynamic broadband, 24-month contract]</t>
         </is>
       </c>
       <c r="T28" s="5" t="inlineStr">
         <is>
-          <t>https://www.connectednetworks.io/countries/holland-the-netherlands-business-internet-connectivity</t>
+          <t>https://dollarsandsense.sg/price-guide-to-business-broadband-plans-for-offices-in-singapore/</t>
         </is>
       </c>
       <c r="U28" s="5" t="inlineStr">
@@ -3887,31 +3919,35 @@
       </c>
       <c r="V28" s="5" t="inlineStr">
         <is>
-          <t>ahold-delhaize</t>
+          <t>dbs</t>
         </is>
       </c>
       <c r="W28" s="12" t="n">
-        <v>0</v>
+        <v>-320.98946125</v>
       </c>
       <c r="X28" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y28" s="3" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="Y28" s="3" t="inlineStr">
+        <is>
+          <t>novartis -321</t>
+        </is>
+      </c>
       <c r="Z28" s="3" t="inlineStr">
         <is>
-          <t>100 Mbps at 500 &gt; 200 Mbps at 399 USD</t>
+          <t>250 Mbps at 91 &gt; 500 Mbps at 85 USD</t>
         </is>
       </c>
       <c r="AA28" s="3" t="inlineStr">
         <is>
-          <t>ahold-delhaize 348 EUR; deutsche-post-dhl 348 EUR; douglas 348 EUR; maersk 348 EUR; shell ~€348 EUR; shell 348 EUR; unilever 348 EUR; unilever 348 EUR</t>
+          <t>dbs 178 SGD; dbs 53.89 SGD</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>SG-BROADBAND_PON-500-researched</t>
+          <t>SG-DIA-10000-researched</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
@@ -3921,11 +3957,11 @@
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>BROADBAND_PON</t>
+          <t>DIA</t>
         </is>
       </c>
       <c r="D29" s="5" t="n">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E29" s="13" t="inlineStr">
         <is>
@@ -3939,7 +3975,7 @@
       </c>
       <c r="G29" s="8" t="inlineStr">
         <is>
-          <t>Business dynamic fibre on a 24-month contract: StarHub S$109, Singtel S$118.</t>
+          <t>TeleGeography's survey-based 10 GigE DIA benchmark for Singapore. No circuit in the set uses it.</t>
         </is>
       </c>
       <c r="H29" s="9">
@@ -3951,103 +3987,97 @@
         <v/>
       </c>
       <c r="J29" s="10" t="n">
-        <v>109</v>
+        <v>4500</v>
       </c>
       <c r="K29" s="5" t="inlineStr">
         <is>
-          <t>SGD</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="L29" s="10" t="n">
-        <v>85.16</v>
-      </c>
-      <c r="M29" s="10" t="n">
-        <v>115</v>
-      </c>
+        <v>4500</v>
+      </c>
+      <c r="M29" s="10" t="n"/>
       <c r="N29" s="11">
         <f>IF(OR(L29="",M29=""),"",L29/M29)</f>
         <v/>
       </c>
       <c r="O29" s="5" t="inlineStr">
         <is>
-          <t>SEED</t>
+          <t>none - new tier</t>
         </is>
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t>single source; read from a snippet; re-prices lower tiers</t>
+          <t>single source; read from a snippet</t>
         </is>
       </c>
       <c r="Q29" s="3" t="inlineStr">
         <is>
-          <t>BROADBAND_PON 500 Mbps MRC business dynamic — Singapore (Singtel)</t>
+          <t>DIA 10000 Mbps (10 GigE) MRC — SG (TeleGeography 2026)</t>
         </is>
       </c>
       <c r="R29" s="5" t="inlineStr">
         <is>
-          <t>DollarsAndSense.sg; AGGREGATOR/SNIPPET_ONLY</t>
+          <t>TeleGeography; TRADE_PRESS/SNIPPET_ONLY</t>
         </is>
       </c>
       <c r="S29" s="3" t="inlineStr">
         <is>
-          <t>Singtel · $118 · $178 [for 500Mbps and 1Gbps dynamic broadband, 24-month contract]</t>
+          <t>$4,500 for 10 GigE</t>
         </is>
       </c>
       <c r="T29" s="5" t="inlineStr">
         <is>
-          <t>https://dollarsandsense.sg/price-guide-to-business-broadband-plans-for-offices-in-singapore/</t>
+          <t>https://resources.telegeography.com/dia-pricing-in-asia-and-oceania</t>
         </is>
       </c>
       <c r="U29" s="5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="V29" s="5" t="inlineStr">
         <is>
-          <t>dbs</t>
+          <t>maersk</t>
         </is>
       </c>
       <c r="W29" s="12" t="n">
-        <v>-2199.09195</v>
+        <v>0</v>
       </c>
       <c r="X29" s="5" t="n">
-        <v>36</v>
-      </c>
-      <c r="Y29" s="3" t="inlineStr">
-        <is>
-          <t>dbs -2,199</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Y29" s="3" t="inlineStr"/>
       <c r="Z29" s="3" t="inlineStr">
         <is>
-          <t>250 Mbps at 91 &gt; 500 Mbps at 85 USD</t>
+          <t>no</t>
         </is>
       </c>
       <c r="AA29" s="3" t="inlineStr">
         <is>
-          <t>dbs 118 SGD; dbs 109 SGD</t>
+          <t>dbs 4500 USD; maersk 4500 USD</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>SG-BROADBAND_PON-1000-researched</t>
+          <t>US-BROADBAND_HFC-100-researched</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>BROADBAND_PON</t>
+          <t>BROADBAND_HFC</t>
         </is>
       </c>
       <c r="D30" s="5" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="E30" s="13" t="inlineStr">
         <is>
@@ -4061,30 +4091,28 @@
       </c>
       <c r="G30" s="8" t="inlineStr">
         <is>
-          <t>Business dynamic fibre on a 24-month contract: Singtel S$178, StarHub S$174.</t>
-        </is>
-      </c>
-      <c r="H30" s="9">
-        <f>J30*0.75</f>
-        <v/>
-      </c>
-      <c r="I30" s="9">
-        <f>J30*1.25</f>
-        <v/>
+          <t>Lightyear transaction dataset, median of US business broadband at 100 Mbps; the band is its 10th-90th percentile.</t>
+        </is>
+      </c>
+      <c r="H30" s="9" t="n">
+        <v>60</v>
+      </c>
+      <c r="I30" s="9" t="n">
+        <v>175</v>
       </c>
       <c r="J30" s="10" t="n">
-        <v>178</v>
+        <v>100</v>
       </c>
       <c r="K30" s="5" t="inlineStr">
         <is>
-          <t>SGD</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="L30" s="10" t="n">
-        <v>139.06</v>
+        <v>100</v>
       </c>
       <c r="M30" s="10" t="n">
-        <v>149</v>
+        <v>120</v>
       </c>
       <c r="N30" s="11">
         <f>IF(OR(L30="",M30=""),"",L30/M30)</f>
@@ -4097,79 +4125,79 @@
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t>single source; read from a snippet; re-prices lower tiers</t>
+          <t>re-prices lower tiers</t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
         <is>
-          <t>BROADBAND_PON 1000 Mbps MRC business dynamic — Singapore (Singtel)</t>
+          <t>BROADBAND_HFC 100 Mbps MRC median</t>
         </is>
       </c>
       <c r="R30" s="5" t="inlineStr">
         <is>
-          <t>DollarsAndSense.sg; AGGREGATOR/SNIPPET_ONLY</t>
+          <t>Lightyear; AGGREGATOR/FULL_PAGE</t>
         </is>
       </c>
       <c r="S30" s="3" t="inlineStr">
         <is>
-          <t>Singtel · $118 · $178 [for 500Mbps and 1Gbps dynamic broadband, 24-month contract]</t>
+          <t>100 Mbps | $60 | $100 | $175</t>
         </is>
       </c>
       <c r="T30" s="5" t="inlineStr">
         <is>
-          <t>https://dollarsandsense.sg/price-guide-to-business-broadband-plans-for-offices-in-singapore/</t>
+          <t>https://lightyear.ai/resources/dedicated-internet-access-dia-ultimate-pricing-guide</t>
         </is>
       </c>
       <c r="U30" s="5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025-2026</t>
         </is>
       </c>
       <c r="V30" s="5" t="inlineStr">
         <is>
-          <t>dbs</t>
+          <t>ahold-delhaize</t>
         </is>
       </c>
       <c r="W30" s="12" t="n">
-        <v>-320.98946125</v>
+        <v>-6522.79808</v>
       </c>
       <c r="X30" s="5" t="n">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t>novartis -321</t>
+          <t>maersk -3,696; ahold-delhaize -2,174; fresenius -435</t>
         </is>
       </c>
       <c r="Z30" s="3" t="inlineStr">
         <is>
-          <t>250 Mbps at 91 &gt; 500 Mbps at 85 USD</t>
+          <t>250 Mbps at 162 &gt; 500 Mbps at 110 USD</t>
         </is>
       </c>
       <c r="AA30" s="3" t="inlineStr">
         <is>
-          <t>dbs 178 SGD; dbs 53.89 SGD</t>
+          <t>ahold-delhaize 100 USD; ups 100 USD</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>SG-DIA-10000-researched</t>
+          <t>US-BROADBAND_HFC-500-researched</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>DIA</t>
+          <t>BROADBAND_HFC</t>
         </is>
       </c>
       <c r="D31" s="5" t="n">
-        <v>10000</v>
+        <v>500</v>
       </c>
       <c r="E31" s="13" t="inlineStr">
         <is>
@@ -4183,19 +4211,17 @@
       </c>
       <c r="G31" s="8" t="inlineStr">
         <is>
-          <t>TeleGeography's survey-based 10 GigE DIA benchmark for Singapore. No circuit in the set uses it.</t>
-        </is>
-      </c>
-      <c r="H31" s="9">
-        <f>J31*0.75</f>
-        <v/>
-      </c>
-      <c r="I31" s="9">
-        <f>J31*1.25</f>
-        <v/>
+          <t>Lightyear transaction dataset, median at 500 Mbps; the band is its 10th-90th percentile.</t>
+        </is>
+      </c>
+      <c r="H31" s="9" t="n">
+        <v>65</v>
+      </c>
+      <c r="I31" s="9" t="n">
+        <v>212</v>
       </c>
       <c r="J31" s="10" t="n">
-        <v>4500</v>
+        <v>110</v>
       </c>
       <c r="K31" s="5" t="inlineStr">
         <is>
@@ -4203,75 +4229,81 @@
         </is>
       </c>
       <c r="L31" s="10" t="n">
-        <v>4500</v>
-      </c>
-      <c r="M31" s="10" t="n"/>
+        <v>110</v>
+      </c>
+      <c r="M31" s="10" t="n">
+        <v>208</v>
+      </c>
       <c r="N31" s="11">
         <f>IF(OR(L31="",M31=""),"",L31/M31)</f>
         <v/>
       </c>
       <c r="O31" s="5" t="inlineStr">
         <is>
-          <t>none - new tier</t>
+          <t>SEED</t>
         </is>
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t>single source; read from a snippet</t>
+          <t>re-prices lower tiers</t>
         </is>
       </c>
       <c r="Q31" s="3" t="inlineStr">
         <is>
-          <t>DIA 10000 Mbps (10 GigE) MRC — SG (TeleGeography 2026)</t>
+          <t>BROADBAND_HFC/PON 500 Mbps MRC median</t>
         </is>
       </c>
       <c r="R31" s="5" t="inlineStr">
         <is>
-          <t>TeleGeography; TRADE_PRESS/SNIPPET_ONLY</t>
+          <t>Lightyear; AGGREGATOR/FULL_PAGE</t>
         </is>
       </c>
       <c r="S31" s="3" t="inlineStr">
         <is>
-          <t>$4,500 for 10 GigE</t>
+          <t>500 Mbps | $65 | $110 | $212</t>
         </is>
       </c>
       <c r="T31" s="5" t="inlineStr">
         <is>
-          <t>https://resources.telegeography.com/dia-pricing-in-asia-and-oceania</t>
+          <t>https://lightyear.ai/resources/dedicated-internet-access-dia-ultimate-pricing-guide</t>
         </is>
       </c>
       <c r="U31" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025-2026</t>
         </is>
       </c>
       <c r="V31" s="5" t="inlineStr">
         <is>
-          <t>maersk</t>
+          <t>ahold-delhaize</t>
         </is>
       </c>
       <c r="W31" s="12" t="n">
-        <v>0</v>
+        <v>-13448332.818288</v>
       </c>
       <c r="X31" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y31" s="3" t="inlineStr"/>
+        <v>17371</v>
+      </c>
+      <c r="Y31" s="3" t="inlineStr">
+        <is>
+          <t>mcdonalds -11,026,179; ahold-delhaize -1,096,373; ups -653,236</t>
+        </is>
+      </c>
       <c r="Z31" s="3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>250 Mbps at 162 &gt; 500 Mbps at 110 USD</t>
         </is>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
-          <t>dbs 4500 USD; maersk 4500 USD</t>
+          <t>ahold-delhaize 110 USD; simmons-bank 100 USD</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>US-BROADBAND_HFC-100-researched</t>
+          <t>US-BROADBAND_HFC-1000-researched</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
@@ -4285,7 +4317,7 @@
         </is>
       </c>
       <c r="D32" s="5" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="E32" s="13" t="inlineStr">
         <is>
@@ -4299,17 +4331,17 @@
       </c>
       <c r="G32" s="8" t="inlineStr">
         <is>
-          <t>Lightyear transaction dataset, median of US business broadband at 100 Mbps; the band is its 10th-90th percentile.</t>
+          <t>Lightyear transaction dataset, median at 1 Gbps; the band is its 10th-90th percentile.</t>
         </is>
       </c>
       <c r="H32" s="9" t="n">
-        <v>60</v>
+        <v>124</v>
       </c>
       <c r="I32" s="9" t="n">
-        <v>175</v>
+        <v>330</v>
       </c>
       <c r="J32" s="10" t="n">
-        <v>100</v>
+        <v>184</v>
       </c>
       <c r="K32" s="5" t="inlineStr">
         <is>
@@ -4317,10 +4349,10 @@
         </is>
       </c>
       <c r="L32" s="10" t="n">
-        <v>100</v>
+        <v>184</v>
       </c>
       <c r="M32" s="10" t="n">
-        <v>120</v>
+        <v>264</v>
       </c>
       <c r="N32" s="11">
         <f>IF(OR(L32="",M32=""),"",L32/M32)</f>
@@ -4338,7 +4370,7 @@
       </c>
       <c r="Q32" s="3" t="inlineStr">
         <is>
-          <t>BROADBAND_HFC 100 Mbps MRC median</t>
+          <t>BROADBAND_HFC/PON 1 Gbps MRC median</t>
         </is>
       </c>
       <c r="R32" s="5" t="inlineStr">
@@ -4348,7 +4380,7 @@
       </c>
       <c r="S32" s="3" t="inlineStr">
         <is>
-          <t>100 Mbps | $60 | $100 | $175</t>
+          <t>1 Gbps | $124 | $184 | $330</t>
         </is>
       </c>
       <c r="T32" s="5" t="inlineStr">
@@ -4367,16 +4399,12 @@
         </is>
       </c>
       <c r="W32" s="12" t="n">
-        <v>-6522.79808</v>
+        <v>0</v>
       </c>
       <c r="X32" s="5" t="n">
-        <v>30</v>
-      </c>
-      <c r="Y32" s="3" t="inlineStr">
-        <is>
-          <t>maersk -3,696; ahold-delhaize -2,174; fresenius -435</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Y32" s="3" t="inlineStr"/>
       <c r="Z32" s="3" t="inlineStr">
         <is>
           <t>250 Mbps at 162 &gt; 500 Mbps at 110 USD</t>
@@ -4384,14 +4412,14 @@
       </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
-          <t>ahold-delhaize 100 USD; ups 100 USD</t>
+          <t>ahold-delhaize 184 USD; simmons-bank 115 USD; ups 184 USD</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>US-BROADBAND_HFC-500-researched</t>
+          <t>US-BROADBAND_PON-100-researched</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
@@ -4401,11 +4429,11 @@
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>BROADBAND_HFC</t>
+          <t>BROADBAND_PON</t>
         </is>
       </c>
       <c r="D33" s="5" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="E33" s="13" t="inlineStr">
         <is>
@@ -4419,17 +4447,17 @@
       </c>
       <c r="G33" s="8" t="inlineStr">
         <is>
-          <t>Lightyear transaction dataset, median at 500 Mbps; the band is its 10th-90th percentile.</t>
+          <t>Lightyear transaction dataset, median at 100 Mbps (HFC and PON together); the band is its 10th-90th percentile.</t>
         </is>
       </c>
       <c r="H33" s="9" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="I33" s="9" t="n">
-        <v>212</v>
+        <v>175</v>
       </c>
       <c r="J33" s="10" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="K33" s="5" t="inlineStr">
         <is>
@@ -4437,10 +4465,10 @@
         </is>
       </c>
       <c r="L33" s="10" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="M33" s="10" t="n">
-        <v>208</v>
+        <v>85</v>
       </c>
       <c r="N33" s="11">
         <f>IF(OR(L33="",M33=""),"",L33/M33)</f>
@@ -4453,22 +4481,22 @@
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
-          <t>re-prices lower tiers</t>
+          <t>single source; read from a snippet; re-prices lower tiers</t>
         </is>
       </c>
       <c r="Q33" s="3" t="inlineStr">
         <is>
-          <t>BROADBAND_HFC/PON 500 Mbps MRC median</t>
+          <t>BROADBAND_PON/HFC 100 Mbps MRC – US business</t>
         </is>
       </c>
       <c r="R33" s="5" t="inlineStr">
         <is>
-          <t>Lightyear; AGGREGATOR/FULL_PAGE</t>
+          <t>Lightyear; AGGREGATOR/SNIPPET_ONLY</t>
         </is>
       </c>
       <c r="S33" s="3" t="inlineStr">
         <is>
-          <t>500 Mbps | $65 | $110 | $212</t>
+          <t>100 Mbps | $60 | $100 | $175 — Last 12 Months Broadband Pricing ($MRC) by Bandwidth Tier</t>
         </is>
       </c>
       <c r="T33" s="5" t="inlineStr">
@@ -4483,35 +4511,35 @@
       </c>
       <c r="V33" s="5" t="inlineStr">
         <is>
-          <t>ahold-delhaize</t>
+          <t>volkswagen</t>
         </is>
       </c>
       <c r="W33" s="12" t="n">
-        <v>-13448332.818288</v>
+        <v>290896.36184</v>
       </c>
       <c r="X33" s="5" t="n">
-        <v>17371</v>
+        <v>1770</v>
       </c>
       <c r="Y33" s="3" t="inlineStr">
         <is>
-          <t>mcdonalds -11,026,179; ahold-delhaize -1,096,373; ups -653,236</t>
+          <t>toyota +1,756; danone +2,107; bayer +3,512</t>
         </is>
       </c>
       <c r="Z33" s="3" t="inlineStr">
         <is>
-          <t>250 Mbps at 162 &gt; 500 Mbps at 110 USD</t>
+          <t>250 Mbps at 114 &gt; 500 Mbps at 99 USD</t>
         </is>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
-          <t>ahold-delhaize 110 USD; simmons-bank 100 USD</t>
+          <t>volkswagen 100 USD</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>US-BROADBAND_HFC-1000-researched</t>
+          <t>US-BROADBAND_PON-500-researched</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
@@ -4521,11 +4549,11 @@
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>BROADBAND_HFC</t>
+          <t>BROADBAND_PON</t>
         </is>
       </c>
       <c r="D34" s="5" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="E34" s="13" t="inlineStr">
         <is>
@@ -4539,17 +4567,19 @@
       </c>
       <c r="G34" s="8" t="inlineStr">
         <is>
-          <t>Lightyear transaction dataset, median at 1 Gbps; the band is its 10th-90th percentile.</t>
-        </is>
-      </c>
-      <c r="H34" s="9" t="n">
-        <v>124</v>
-      </c>
-      <c r="I34" s="9" t="n">
-        <v>330</v>
+          <t>Verizon Fios Business 500 at $99, consistent with the Lightyear 500 Mbps median of $110.</t>
+        </is>
+      </c>
+      <c r="H34" s="9">
+        <f>J34*0.75</f>
+        <v/>
+      </c>
+      <c r="I34" s="9">
+        <f>J34*1.25</f>
+        <v/>
       </c>
       <c r="J34" s="10" t="n">
-        <v>184</v>
+        <v>99</v>
       </c>
       <c r="K34" s="5" t="inlineStr">
         <is>
@@ -4557,10 +4587,10 @@
         </is>
       </c>
       <c r="L34" s="10" t="n">
-        <v>184</v>
+        <v>99</v>
       </c>
       <c r="M34" s="10" t="n">
-        <v>264</v>
+        <v>145</v>
       </c>
       <c r="N34" s="11">
         <f>IF(OR(L34="",M34=""),"",L34/M34)</f>
@@ -4573,61 +4603,65 @@
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
-          <t>re-prices lower tiers</t>
+          <t>single source; read from a snippet; re-prices lower tiers</t>
         </is>
       </c>
       <c r="Q34" s="3" t="inlineStr">
         <is>
-          <t>BROADBAND_HFC/PON 1 Gbps MRC median</t>
+          <t>BROADBAND_PON 500 Mbps MRC – US, Verizon Fios Business</t>
         </is>
       </c>
       <c r="R34" s="5" t="inlineStr">
         <is>
-          <t>Lightyear; AGGREGATOR/FULL_PAGE</t>
+          <t>highspeedinternet.com (Verizon published tariff); AGGREGATOR/SNIPPET_ONLY</t>
         </is>
       </c>
       <c r="S34" s="3" t="inlineStr">
         <is>
-          <t>1 Gbps | $124 | $184 | $330</t>
+          <t>Verizon Business Fios 500 | $99/mo. | Up to 500Mbps | Fiber</t>
         </is>
       </c>
       <c r="T34" s="5" t="inlineStr">
         <is>
-          <t>https://lightyear.ai/resources/dedicated-internet-access-dia-ultimate-pricing-guide</t>
+          <t>https://www.highspeedinternet.com/resources/business-internet-guide</t>
         </is>
       </c>
       <c r="U34" s="5" t="inlineStr">
         <is>
-          <t>2025-2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="V34" s="5" t="inlineStr">
         <is>
-          <t>ahold-delhaize</t>
+          <t>bayer</t>
         </is>
       </c>
       <c r="W34" s="12" t="n">
-        <v>0</v>
+        <v>-77962.3674245</v>
       </c>
       <c r="X34" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y34" s="3" t="inlineStr"/>
+        <v>243</v>
+      </c>
+      <c r="Y34" s="3" t="inlineStr">
+        <is>
+          <t>simmons-bank -20,511; basf -13,372; siemens -11,391</t>
+        </is>
+      </c>
       <c r="Z34" s="3" t="inlineStr">
         <is>
-          <t>250 Mbps at 162 &gt; 500 Mbps at 110 USD</t>
+          <t>250 Mbps at 114 &gt; 500 Mbps at 99 USD</t>
         </is>
       </c>
       <c r="AA34" s="3" t="inlineStr">
         <is>
-          <t>ahold-delhaize 184 USD; simmons-bank 115 USD; ups 184 USD</t>
+          <t>bayer 99 USD</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>US-BROADBAND_PON-100-researched</t>
+          <t>US-DIA-100-researched</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
@@ -4637,7 +4671,7 @@
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>BROADBAND_PON</t>
+          <t>DIA</t>
         </is>
       </c>
       <c r="D35" s="5" t="n">
@@ -4655,17 +4689,17 @@
       </c>
       <c r="G35" s="8" t="inlineStr">
         <is>
-          <t>Lightyear transaction dataset, median at 100 Mbps (HFC and PON together); the band is its 10th-90th percentile.</t>
+          <t>Lightyear 36-month DIA median at 100 Mbps; the band is its 10th-90th percentile.</t>
         </is>
       </c>
       <c r="H35" s="9" t="n">
-        <v>60</v>
+        <v>333</v>
       </c>
       <c r="I35" s="9" t="n">
-        <v>175</v>
+        <v>641</v>
       </c>
       <c r="J35" s="10" t="n">
-        <v>100</v>
+        <v>492</v>
       </c>
       <c r="K35" s="5" t="inlineStr">
         <is>
@@ -4673,10 +4707,10 @@
         </is>
       </c>
       <c r="L35" s="10" t="n">
-        <v>100</v>
+        <v>492</v>
       </c>
       <c r="M35" s="10" t="n">
-        <v>85</v>
+        <v>480</v>
       </c>
       <c r="N35" s="11">
         <f>IF(OR(L35="",M35=""),"",L35/M35)</f>
@@ -4689,22 +4723,22 @@
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
-          <t>single source; read from a snippet; re-prices lower tiers</t>
+          <t>read from a snippet; re-prices lower tiers</t>
         </is>
       </c>
       <c r="Q35" s="3" t="inlineStr">
         <is>
-          <t>BROADBAND_PON/HFC 100 Mbps MRC – US business</t>
+          <t>DIA 100 Mbps MRC – US (Lightyear dataset, 36-month, median)</t>
         </is>
       </c>
       <c r="R35" s="5" t="inlineStr">
         <is>
-          <t>Lightyear; AGGREGATOR/SNIPPET_ONLY</t>
+          <t>Lightyear.ai; AGGREGATOR/SNIPPET_ONLY</t>
         </is>
       </c>
       <c r="S35" s="3" t="inlineStr">
         <is>
-          <t>100 Mbps | $60 | $100 | $175 — Last 12 Months Broadband Pricing ($MRC) by Bandwidth Tier</t>
+          <t>Median DIA MRC 36-month: 100 Mbps $492, 1 Gbps $901, 10 Gbps $1,987 (US, mixed geo/ISP)</t>
         </is>
       </c>
       <c r="T35" s="5" t="inlineStr">
@@ -4719,35 +4753,35 @@
       </c>
       <c r="V35" s="5" t="inlineStr">
         <is>
-          <t>volkswagen</t>
+          <t>abb</t>
         </is>
       </c>
       <c r="W35" s="12" t="n">
-        <v>290896.36184</v>
+        <v>418650.656</v>
       </c>
       <c r="X35" s="5" t="n">
-        <v>1770</v>
+        <v>2670</v>
       </c>
       <c r="Y35" s="3" t="inlineStr">
         <is>
-          <t>toyota +1,756; danone +2,107; bayer +3,512</t>
+          <t>victorias-secret +314; ahold-delhaize +3,920; maersk +6,272</t>
         </is>
       </c>
       <c r="Z35" s="3" t="inlineStr">
         <is>
-          <t>250 Mbps at 114 &gt; 500 Mbps at 99 USD</t>
+          <t>500 Mbps at 1242 &gt; 1000 Mbps at 901 USD</t>
         </is>
       </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
-          <t>volkswagen 100 USD</t>
+          <t>abb 492 USD; ahold-delhaize 333 USD; ahold-delhaize 492 USD; ahold-delhaize 641 USD; basf 492 USD; basf 625 USD; bayer 492 USD; fresenius 492 USD</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>US-BROADBAND_PON-500-researched</t>
+          <t>US-DIA-1000-researched</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
@@ -4757,11 +4791,11 @@
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>BROADBAND_PON</t>
+          <t>DIA</t>
         </is>
       </c>
       <c r="D36" s="5" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="E36" s="13" t="inlineStr">
         <is>
@@ -4775,19 +4809,17 @@
       </c>
       <c r="G36" s="8" t="inlineStr">
         <is>
-          <t>Verizon Fios Business 500 at $99, consistent with the Lightyear 500 Mbps median of $110.</t>
-        </is>
-      </c>
-      <c r="H36" s="9">
-        <f>J36*0.75</f>
-        <v/>
-      </c>
-      <c r="I36" s="9">
-        <f>J36*1.25</f>
-        <v/>
+          <t>Lightyear 36-month DIA median at 1 Gbps; the band is its 10th-90th percentile.</t>
+        </is>
+      </c>
+      <c r="H36" s="9" t="n">
+        <v>600</v>
+      </c>
+      <c r="I36" s="9" t="n">
+        <v>1312</v>
       </c>
       <c r="J36" s="10" t="n">
-        <v>99</v>
+        <v>901</v>
       </c>
       <c r="K36" s="5" t="inlineStr">
         <is>
@@ -4795,10 +4827,10 @@
         </is>
       </c>
       <c r="L36" s="10" t="n">
-        <v>99</v>
+        <v>901</v>
       </c>
       <c r="M36" s="10" t="n">
-        <v>145</v>
+        <v>1350</v>
       </c>
       <c r="N36" s="11">
         <f>IF(OR(L36="",M36=""),"",L36/M36)</f>
@@ -4811,65 +4843,65 @@
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
-          <t>single source; read from a snippet; re-prices lower tiers</t>
+          <t>read from a snippet; re-prices lower tiers</t>
         </is>
       </c>
       <c r="Q36" s="3" t="inlineStr">
         <is>
-          <t>BROADBAND_PON 500 Mbps MRC – US, Verizon Fios Business</t>
+          <t>DIA 1000 Mbps MRC – US (Lightyear dataset, 36-month, median)</t>
         </is>
       </c>
       <c r="R36" s="5" t="inlineStr">
         <is>
-          <t>highspeedinternet.com (Verizon published tariff); AGGREGATOR/SNIPPET_ONLY</t>
+          <t>Lightyear.ai; AGGREGATOR/SNIPPET_ONLY</t>
         </is>
       </c>
       <c r="S36" s="3" t="inlineStr">
         <is>
-          <t>Verizon Business Fios 500 | $99/mo. | Up to 500Mbps | Fiber</t>
+          <t>Median DIA 1 Gbps $901/month (US, 36-month, 10th pct $600, 90th pct $1,312)</t>
         </is>
       </c>
       <c r="T36" s="5" t="inlineStr">
         <is>
-          <t>https://www.highspeedinternet.com/resources/business-internet-guide</t>
+          <t>https://lightyear.ai/resources/dedicated-internet-access-dia-ultimate-pricing-guide</t>
         </is>
       </c>
       <c r="U36" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025-2026</t>
         </is>
       </c>
       <c r="V36" s="5" t="inlineStr">
         <is>
-          <t>bayer</t>
+          <t>abb</t>
         </is>
       </c>
       <c r="W36" s="12" t="n">
-        <v>-77962.3674245</v>
+        <v>-1331147.0734</v>
       </c>
       <c r="X36" s="5" t="n">
-        <v>243</v>
+        <v>399</v>
       </c>
       <c r="Y36" s="3" t="inlineStr">
         <is>
-          <t>simmons-bank -20,511; basf -13,372; siemens -11,391</t>
+          <t>simmons-bank -537,948; siemens -314,464; nestle -84,483</t>
         </is>
       </c>
       <c r="Z36" s="3" t="inlineStr">
         <is>
-          <t>250 Mbps at 114 &gt; 500 Mbps at 99 USD</t>
+          <t>500 Mbps at 1242 &gt; 1000 Mbps at 901 USD</t>
         </is>
       </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
-          <t>bayer 99 USD</t>
+          <t>abb 901 USD; ahold-delhaize 600 USD; ahold-delhaize 901 USD; ahold-delhaize 1312 USD; basf 901 USD; basf 1070 USD; bayer 901 USD; fresenius 901 USD</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>US-DIA-100-researched</t>
+          <t>US-DIA-10000-researched</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
@@ -4883,7 +4915,7 @@
         </is>
       </c>
       <c r="D37" s="5" t="n">
-        <v>100</v>
+        <v>10000</v>
       </c>
       <c r="E37" s="13" t="inlineStr">
         <is>
@@ -4897,17 +4929,17 @@
       </c>
       <c r="G37" s="8" t="inlineStr">
         <is>
-          <t>Lightyear 36-month DIA median at 100 Mbps; the band is its 10th-90th percentile.</t>
+          <t>Lightyear 36-month DIA median at 10 Gbps; the band is its 10th-90th percentile. Approved on 13 Oct, and lost to a re-promotion.</t>
         </is>
       </c>
       <c r="H37" s="9" t="n">
-        <v>333</v>
+        <v>1175</v>
       </c>
       <c r="I37" s="9" t="n">
-        <v>641</v>
+        <v>2853</v>
       </c>
       <c r="J37" s="10" t="n">
-        <v>492</v>
+        <v>1987</v>
       </c>
       <c r="K37" s="5" t="inlineStr">
         <is>
@@ -4915,18 +4947,16 @@
         </is>
       </c>
       <c r="L37" s="10" t="n">
-        <v>492</v>
-      </c>
-      <c r="M37" s="10" t="n">
-        <v>480</v>
-      </c>
+        <v>1987</v>
+      </c>
+      <c r="M37" s="10" t="n"/>
       <c r="N37" s="11">
         <f>IF(OR(L37="",M37=""),"",L37/M37)</f>
         <v/>
       </c>
       <c r="O37" s="5" t="inlineStr">
         <is>
-          <t>SEED</t>
+          <t>none - new tier</t>
         </is>
       </c>
       <c r="P37" s="3" t="inlineStr">
@@ -4936,7 +4966,7 @@
       </c>
       <c r="Q37" s="3" t="inlineStr">
         <is>
-          <t>DIA 100 Mbps MRC – US (Lightyear dataset, 36-month, median)</t>
+          <t>DIA 10000 Mbps MRC – US (Lightyear dataset, 36-month, median)</t>
         </is>
       </c>
       <c r="R37" s="5" t="inlineStr">
@@ -4946,7 +4976,7 @@
       </c>
       <c r="S37" s="3" t="inlineStr">
         <is>
-          <t>Median DIA MRC 36-month: 100 Mbps $492, 1 Gbps $901, 10 Gbps $1,987 (US, mixed geo/ISP)</t>
+          <t>Median DIA 10 Gbps $1,987/month (US, 36-month, 10th pct $1,175, 90th pct $2,853)</t>
         </is>
       </c>
       <c r="T37" s="5" t="inlineStr">
@@ -4965,16 +4995,12 @@
         </is>
       </c>
       <c r="W37" s="12" t="n">
-        <v>418650.656</v>
+        <v>0</v>
       </c>
       <c r="X37" s="5" t="n">
-        <v>2670</v>
-      </c>
-      <c r="Y37" s="3" t="inlineStr">
-        <is>
-          <t>victorias-secret +314; ahold-delhaize +3,920; maersk +6,272</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Y37" s="3" t="inlineStr"/>
       <c r="Z37" s="3" t="inlineStr">
         <is>
           <t>500 Mbps at 1242 &gt; 1000 Mbps at 901 USD</t>
@@ -4982,14 +5008,14 @@
       </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
-          <t>abb 492 USD; ahold-delhaize 333 USD; ahold-delhaize 492 USD; ahold-delhaize 641 USD; basf 492 USD; basf 625 USD; bayer 492 USD; fresenius 492 USD</t>
+          <t>abb 1987 USD; ahold-delhaize 1987 USD; bayer 1987 USD; fresenius 1987 USD; mcdonalds 1987 USD; siemens 1987 USD; simmons-bank 1987 USD; ups 1987 USD</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>US-DIA-1000-researched</t>
+          <t>US-ETHERNET-10000-researched</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
@@ -4999,11 +5025,11 @@
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>DIA</t>
+          <t>ETHERNET</t>
         </is>
       </c>
       <c r="D38" s="5" t="n">
-        <v>1000</v>
+        <v>10000</v>
       </c>
       <c r="E38" s="13" t="inlineStr">
         <is>
@@ -5017,17 +5043,17 @@
       </c>
       <c r="G38" s="8" t="inlineStr">
         <is>
-          <t>Lightyear 36-month DIA median at 1 Gbps; the band is its 10th-90th percentile.</t>
+          <t>Lightyear Ethernet private-line median at 10 Gbps; the band is its 10th-90th percentile.</t>
         </is>
       </c>
       <c r="H38" s="9" t="n">
-        <v>600</v>
+        <v>1244</v>
       </c>
       <c r="I38" s="9" t="n">
-        <v>1312</v>
+        <v>2157</v>
       </c>
       <c r="J38" s="10" t="n">
-        <v>901</v>
+        <v>1807</v>
       </c>
       <c r="K38" s="5" t="inlineStr">
         <is>
@@ -5035,10 +5061,10 @@
         </is>
       </c>
       <c r="L38" s="10" t="n">
-        <v>901</v>
+        <v>1807</v>
       </c>
       <c r="M38" s="10" t="n">
-        <v>1350</v>
+        <v>3450</v>
       </c>
       <c r="N38" s="11">
         <f>IF(OR(L38="",M38=""),"",L38/M38)</f>
@@ -5051,27 +5077,27 @@
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t>read from a snippet; re-prices lower tiers</t>
+          <t>floor; read from a snippet; re-prices lower tiers</t>
         </is>
       </c>
       <c r="Q38" s="3" t="inlineStr">
         <is>
-          <t>DIA 1000 Mbps MRC – US (Lightyear dataset, 36-month, median)</t>
+          <t>ETHERNET 10000 Mbps point-to-point MRC – US (Lightyear dataset)</t>
         </is>
       </c>
       <c r="R38" s="5" t="inlineStr">
         <is>
-          <t>Lightyear.ai; AGGREGATOR/SNIPPET_ONLY</t>
+          <t>lightyear.ai (Ethernet Private Line guide); TRADE_PRESS/SNIPPET_ONLY</t>
         </is>
       </c>
       <c r="S38" s="3" t="inlineStr">
         <is>
-          <t>Median DIA 1 Gbps $901/month (US, 36-month, 10th pct $600, 90th pct $1,312)</t>
+          <t>10 Gbps Point-to-Point (Ethernet): 10th pct $1,244, Median $1,807, 90th pct $2,157</t>
         </is>
       </c>
       <c r="T38" s="5" t="inlineStr">
         <is>
-          <t>https://lightyear.ai/resources/dedicated-internet-access-dia-ultimate-pricing-guide</t>
+          <t>https://lightyear.ai/blogs/ethernet-private-line-cost</t>
         </is>
       </c>
       <c r="U38" s="5" t="inlineStr">
@@ -5081,35 +5107,35 @@
       </c>
       <c r="V38" s="5" t="inlineStr">
         <is>
-          <t>abb</t>
+          <t>simmons-bank</t>
         </is>
       </c>
       <c r="W38" s="12" t="n">
-        <v>-1331147.0734</v>
+        <v>-32322.017413</v>
       </c>
       <c r="X38" s="5" t="n">
-        <v>399</v>
+        <v>2</v>
       </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
-          <t>simmons-bank -537,948; siemens -314,464; nestle -84,483</t>
+          <t>shell -32,322</t>
         </is>
       </c>
       <c r="Z38" s="3" t="inlineStr">
         <is>
-          <t>500 Mbps at 1242 &gt; 1000 Mbps at 901 USD</t>
+          <t>9000 Mbps at 3267 &gt; 10000 Mbps at 1807 USD</t>
         </is>
       </c>
       <c r="AA38" s="3" t="inlineStr">
         <is>
-          <t>abb 901 USD; ahold-delhaize 600 USD; ahold-delhaize 901 USD; ahold-delhaize 1312 USD; basf 901 USD; basf 1070 USD; bayer 901 USD; fresenius 901 USD</t>
+          <t>simmons-bank 1807 USD</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>US-DIA-10000-researched</t>
+          <t>US-MPLS-1000-researched</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
@@ -5119,11 +5145,11 @@
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>DIA</t>
+          <t>MPLS</t>
         </is>
       </c>
       <c r="D39" s="5" t="n">
-        <v>10000</v>
+        <v>1000</v>
       </c>
       <c r="E39" s="13" t="inlineStr">
         <is>
@@ -5137,17 +5163,19 @@
       </c>
       <c r="G39" s="8" t="inlineStr">
         <is>
-          <t>Lightyear 36-month DIA median at 10 Gbps; the band is its 10th-90th percentile. Approved on 13 Oct, and lost to a re-promotion.</t>
-        </is>
-      </c>
-      <c r="H39" s="9" t="n">
-        <v>1175</v>
-      </c>
-      <c r="I39" s="9" t="n">
-        <v>2853</v>
+          <t>Lightyear median for an all-inclusive managed MPLS service at 1 Gbps. Approved on 13 Oct, and lost to a re-promotion.</t>
+        </is>
+      </c>
+      <c r="H39" s="9">
+        <f>J39*0.75</f>
+        <v/>
+      </c>
+      <c r="I39" s="9">
+        <f>J39*1.25</f>
+        <v/>
       </c>
       <c r="J39" s="10" t="n">
-        <v>1987</v>
+        <v>1439</v>
       </c>
       <c r="K39" s="5" t="inlineStr">
         <is>
@@ -5155,7 +5183,7 @@
         </is>
       </c>
       <c r="L39" s="10" t="n">
-        <v>1987</v>
+        <v>1439</v>
       </c>
       <c r="M39" s="10" t="n"/>
       <c r="N39" s="11">
@@ -5169,37 +5197,37 @@
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
-          <t>read from a snippet; re-prices lower tiers</t>
+          <t>single source; read from a snippet</t>
         </is>
       </c>
       <c r="Q39" s="3" t="inlineStr">
         <is>
-          <t>DIA 10000 Mbps MRC – US (Lightyear dataset, 36-month, median)</t>
+          <t>MPLS 1000Mbps MRC</t>
         </is>
       </c>
       <c r="R39" s="5" t="inlineStr">
         <is>
-          <t>Lightyear.ai; AGGREGATOR/SNIPPET_ONLY</t>
+          <t>Lightyear; AGGREGATOR/SNIPPET_ONLY</t>
         </is>
       </c>
       <c r="S39" s="3" t="inlineStr">
         <is>
-          <t>Median DIA 10 Gbps $1,987/month (US, 36-month, 10th pct $1,175, 90th pct $2,853)</t>
+          <t>MPLS | $1,439 | $17,268 | All-inclusive managed service (1 Gbps)</t>
         </is>
       </c>
       <c r="T39" s="5" t="inlineStr">
         <is>
-          <t>https://lightyear.ai/resources/dedicated-internet-access-dia-ultimate-pricing-guide</t>
+          <t>https://lightyear.ai/blogs/sd-wan-vs-mpls-cost-comparison</t>
         </is>
       </c>
       <c r="U39" s="5" t="inlineStr">
         <is>
-          <t>2025-2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="V39" s="5" t="inlineStr">
         <is>
-          <t>abb</t>
+          <t>toyota</t>
         </is>
       </c>
       <c r="W39" s="12" t="n">
@@ -5211,68 +5239,70 @@
       <c r="Y39" s="3" t="inlineStr"/>
       <c r="Z39" s="3" t="inlineStr">
         <is>
-          <t>500 Mbps at 1242 &gt; 1000 Mbps at 901 USD</t>
+          <t>no</t>
         </is>
       </c>
       <c r="AA39" s="3" t="inlineStr">
         <is>
-          <t>abb 1987 USD; ahold-delhaize 1987 USD; bayer 1987 USD; fresenius 1987 USD; mcdonalds 1987 USD; siemens 1987 USD; simmons-bank 1987 USD; ups 1987 USD</t>
+          <t>abb 1439 USD; basf 1439 USD; bayer 1439 USD; maersk 1439 USD; mcdonalds 1439 USD; siemens 1439 USD; simmons-bank 1439 USD; toyota 1439 USD</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>US-ETHERNET-10000-researched</t>
+          <t>AU-DIA-1000-researched</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>ETHERNET</t>
+          <t>DIA</t>
         </is>
       </c>
       <c r="D40" s="5" t="n">
-        <v>10000</v>
-      </c>
-      <c r="E40" s="13" t="inlineStr">
-        <is>
-          <t>approved by Christian Bartosch</t>
+        <v>1000</v>
+      </c>
+      <c r="E40" s="14" t="inlineStr">
+        <is>
+          <t>revoked by Christian Bartosch</t>
         </is>
       </c>
       <c r="F40" s="7" t="inlineStr">
         <is>
-          <t>Approve</t>
+          <t>Reject</t>
         </is>
       </c>
       <c r="G40" s="8" t="inlineStr">
         <is>
-          <t>Lightyear Ethernet private-line median at 10 Gbps; the band is its 10th-90th percentile.</t>
-        </is>
-      </c>
-      <c r="H40" s="9" t="n">
-        <v>1244</v>
-      </c>
-      <c r="I40" s="9" t="n">
-        <v>2157</v>
+          <t>An on-net data-centre DIA price (Nexthop), not site access. The same research cites A$2,500-8,000 for enterprise dedicated fibre.</t>
+        </is>
+      </c>
+      <c r="H40" s="9">
+        <f>J40*0.75</f>
+        <v/>
+      </c>
+      <c r="I40" s="9">
+        <f>J40*1.25</f>
+        <v/>
       </c>
       <c r="J40" s="10" t="n">
-        <v>1807</v>
+        <v>499</v>
       </c>
       <c r="K40" s="5" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>AUD</t>
         </is>
       </c>
       <c r="L40" s="10" t="n">
-        <v>1807</v>
+        <v>337.16</v>
       </c>
       <c r="M40" s="10" t="n">
-        <v>3450</v>
+        <v>1750</v>
       </c>
       <c r="N40" s="11">
         <f>IF(OR(L40="",M40=""),"",L40/M40)</f>
@@ -5285,93 +5315,81 @@
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
-          <t>floor; read from a snippet; re-prices lower tiers</t>
-        </is>
-      </c>
-      <c r="Q40" s="3" t="inlineStr">
-        <is>
-          <t>ETHERNET 10000 Mbps point-to-point MRC – US (Lightyear dataset)</t>
-        </is>
-      </c>
+          <t>consumer; single source; re-prices lower tiers</t>
+        </is>
+      </c>
+      <c r="Q40" s="3" t="inlineStr"/>
       <c r="R40" s="5" t="inlineStr">
         <is>
-          <t>lightyear.ai (Ethernet Private Line guide); TRADE_PRESS/SNIPPET_ONLY</t>
+          <t>run narrative (the disposition was replaced)</t>
         </is>
       </c>
       <c r="S40" s="3" t="inlineStr">
         <is>
-          <t>10 Gbps Point-to-Point (Ethernet): 10th pct $1,244, Median $1,807, 90th pct $2,157</t>
-        </is>
-      </c>
-      <c r="T40" s="5" t="inlineStr">
-        <is>
-          <t>https://lightyear.ai/blogs/ethernet-private-line-cost</t>
-        </is>
-      </c>
+          <t xml:space="preserve"> not retail MRCs. Residential NBN (consumer, ACCC June 2025): 100 Mbps median advertised price ~A$65-80/mo (not enterprise). AU DIA (Dedicated Internet Access – direct fibre): Nexthop AU lists 1 Gbps datacenter DIA at A$499/mo (24-month, on-net); Vocus Fast Fibre (direct fibre, enterprise) from A$339/mo excl. GST for 250 Mbps+. AyeTech 2026 guide cites enterprise dedicated fibre 1</t>
+        </is>
+      </c>
+      <c r="T40" s="5" t="inlineStr"/>
       <c r="U40" s="5" t="inlineStr">
         <is>
-          <t>2025-2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="V40" s="5" t="inlineStr">
         <is>
-          <t>simmons-bank</t>
+          <t>woolworths</t>
         </is>
       </c>
       <c r="W40" s="12" t="n">
-        <v>-32322.017413</v>
+        <v>-416627.1182432433</v>
       </c>
       <c r="X40" s="5" t="n">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="Y40" s="3" t="inlineStr">
         <is>
-          <t>shell -32,322</t>
+          <t>woolworths -416,627</t>
         </is>
       </c>
       <c r="Z40" s="3" t="inlineStr">
         <is>
-          <t>9000 Mbps at 3267 &gt; 10000 Mbps at 1807 USD</t>
-        </is>
-      </c>
-      <c r="AA40" s="3" t="inlineStr">
-        <is>
-          <t>simmons-bank 1807 USD</t>
-        </is>
-      </c>
+          <t>500 Mbps at 1610 &gt; 1000 Mbps at 337 USD</t>
+        </is>
+      </c>
+      <c r="AA40" s="3" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>US-MPLS-1000-researched</t>
+          <t>DE-BROADBAND_PON-75-researched</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>MPLS</t>
+          <t>BROADBAND_PON</t>
         </is>
       </c>
       <c r="D41" s="5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="E41" s="13" t="inlineStr">
-        <is>
-          <t>approved by Christian Bartosch</t>
+        <v>75</v>
+      </c>
+      <c r="E41" s="14" t="inlineStr">
+        <is>
+          <t>revoked by Christian Bartosch</t>
         </is>
       </c>
       <c r="F41" s="7" t="inlineStr">
         <is>
-          <t>Approve</t>
+          <t>Reject</t>
         </is>
       </c>
       <c r="G41" s="8" t="inlineStr">
         <is>
-          <t>Lightyear median for an all-inclusive managed MPLS service at 1 Gbps. Approved on 13 Oct, and lost to a re-promotion.</t>
+          <t>A wholesale bitstream price cap for subsidised networks (BMDV L2-BSA). A business pays the retail price on top of it.</t>
         </is>
       </c>
       <c r="H41" s="9">
@@ -5383,15 +5401,15 @@
         <v/>
       </c>
       <c r="J41" s="10" t="n">
-        <v>1439</v>
+        <v>19.22</v>
       </c>
       <c r="K41" s="5" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="L41" s="10" t="n">
-        <v>1439</v>
+        <v>22.06</v>
       </c>
       <c r="M41" s="10" t="n"/>
       <c r="N41" s="11">
@@ -5405,37 +5423,37 @@
       </c>
       <c r="P41" s="3" t="inlineStr">
         <is>
-          <t>single source; read from a snippet</t>
+          <t>wholesale; read from a snippet; re-prices lower tiers</t>
         </is>
       </c>
       <c r="Q41" s="3" t="inlineStr">
         <is>
-          <t>MPLS 1000Mbps MRC</t>
+          <t>DE BROADBAND_PON wholesale bitstream L2-BSA 50-99 Mbps MRC (regulatory price cap)</t>
         </is>
       </c>
       <c r="R41" s="5" t="inlineStr">
         <is>
-          <t>Lightyear; AGGREGATOR/SNIPPET_ONLY</t>
+          <t>BMDV / Bundesnetzagentur (German Federal Ministry for Digital Affairs); REGULATOR/SNIPPET_ONLY</t>
         </is>
       </c>
       <c r="S41" s="3" t="inlineStr">
         <is>
-          <t>MPLS | $1,439 | $17,268 | All-inclusive managed service (1 Gbps)</t>
+          <t>50 – 99 Mbit/s … L2-BSA Überlassungsentgelt … 19,22 €</t>
         </is>
       </c>
       <c r="T41" s="5" t="inlineStr">
         <is>
-          <t>https://lightyear.ai/blogs/sd-wan-vs-mpls-cost-comparison</t>
+          <t>https://www.bmv.de/SharedDocs/DE/Anlage/DG/vorleistungspreise.pdf?__blob=publicationFile</t>
         </is>
       </c>
       <c r="U41" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="V41" s="5" t="inlineStr">
         <is>
-          <t>toyota</t>
+          <t>fresenius</t>
         </is>
       </c>
       <c r="W41" s="12" t="n">
@@ -5447,33 +5465,33 @@
       <c r="Y41" s="3" t="inlineStr"/>
       <c r="Z41" s="3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>50 Mbps at 64 &gt; 75 Mbps at 22 USD</t>
         </is>
       </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
-          <t>abb 1439 USD; basf 1439 USD; bayer 1439 USD; maersk 1439 USD; mcdonalds 1439 USD; siemens 1439 USD; simmons-bank 1439 USD; toyota 1439 USD</t>
+          <t>fresenius 19.22 EUR</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>AU-DIA-1000-researched</t>
+          <t>DE-BROADBAND_PON-150-researched</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>DIA</t>
+          <t>BROADBAND_PON</t>
         </is>
       </c>
       <c r="D42" s="5" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="E42" s="14" t="inlineStr">
         <is>
@@ -5487,7 +5505,7 @@
       </c>
       <c r="G42" s="8" t="inlineStr">
         <is>
-          <t>An on-net data-centre DIA price (Nexthop), not site access. The same research cites A$2,500-8,000 for enterprise dedicated fibre.</t>
+          <t>A wholesale bitstream price cap for subsidised networks (BMDV L2-BSA). A business pays the retail price on top of it.</t>
         </is>
       </c>
       <c r="H42" s="9">
@@ -5499,77 +5517,83 @@
         <v/>
       </c>
       <c r="J42" s="10" t="n">
-        <v>499</v>
+        <v>21.55</v>
       </c>
       <c r="K42" s="5" t="inlineStr">
         <is>
-          <t>AUD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="L42" s="10" t="n">
-        <v>337.16</v>
-      </c>
-      <c r="M42" s="10" t="n">
-        <v>1750</v>
-      </c>
+        <v>24.74</v>
+      </c>
+      <c r="M42" s="10" t="n"/>
       <c r="N42" s="11">
         <f>IF(OR(L42="",M42=""),"",L42/M42)</f>
         <v/>
       </c>
       <c r="O42" s="5" t="inlineStr">
         <is>
-          <t>SEED</t>
+          <t>none - new tier</t>
         </is>
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
-          <t>consumer; single source; re-prices lower tiers</t>
-        </is>
-      </c>
-      <c r="Q42" s="3" t="inlineStr"/>
+          <t>wholesale; read from a snippet; re-prices lower tiers</t>
+        </is>
+      </c>
+      <c r="Q42" s="3" t="inlineStr">
+        <is>
+          <t>DE BROADBAND_PON wholesale bitstream L2-BSA 100-199 Mbps MRC (regulatory price cap)</t>
+        </is>
+      </c>
       <c r="R42" s="5" t="inlineStr">
         <is>
-          <t>run narrative (the disposition was replaced)</t>
+          <t>BMDV / Bundesnetzagentur; REGULATOR/SNIPPET_ONLY</t>
         </is>
       </c>
       <c r="S42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> not retail MRCs. Residential NBN (consumer, ACCC June 2025): 100 Mbps median advertised price ~A$65-80/mo (not enterprise). AU DIA (Dedicated Internet Access – direct fibre): Nexthop AU lists 1 Gbps datacenter DIA at A$499/mo (24-month, on-net); Vocus Fast Fibre (direct fibre, enterprise) from A$339/mo excl. GST for 250 Mbps+. AyeTech 2026 guide cites enterprise dedicated fibre 1</t>
-        </is>
-      </c>
-      <c r="T42" s="5" t="inlineStr"/>
+          <t>100 – 199 Mbit/s … L2-BSA … 21,55 €</t>
+        </is>
+      </c>
+      <c r="T42" s="5" t="inlineStr">
+        <is>
+          <t>https://www.bmv.de/SharedDocs/DE/Anlage/DG/vorleistungspreise.pdf?__blob=publicationFile</t>
+        </is>
+      </c>
       <c r="U42" s="5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="V42" s="5" t="inlineStr">
         <is>
-          <t>woolworths</t>
+          <t>fresenius</t>
         </is>
       </c>
       <c r="W42" s="12" t="n">
-        <v>-416627.1182432433</v>
+        <v>0</v>
       </c>
       <c r="X42" s="5" t="n">
-        <v>30</v>
-      </c>
-      <c r="Y42" s="3" t="inlineStr">
-        <is>
-          <t>woolworths -416,627</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Y42" s="3" t="inlineStr"/>
       <c r="Z42" s="3" t="inlineStr">
         <is>
-          <t>500 Mbps at 1610 &gt; 1000 Mbps at 337 USD</t>
-        </is>
-      </c>
-      <c r="AA42" s="3" t="inlineStr"/>
+          <t>100 Mbps at 78 &gt; 150 Mbps at 25 USD</t>
+        </is>
+      </c>
+      <c r="AA42" s="3" t="inlineStr">
+        <is>
+          <t>fresenius 21.55 EUR</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>DE-BROADBAND_PON-75-researched</t>
+          <t>DE-BROADBAND_PON-750-researched</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
@@ -5583,7 +5607,7 @@
         </is>
       </c>
       <c r="D43" s="5" t="n">
-        <v>75</v>
+        <v>750</v>
       </c>
       <c r="E43" s="14" t="inlineStr">
         <is>
@@ -5609,7 +5633,7 @@
         <v/>
       </c>
       <c r="J43" s="10" t="n">
-        <v>19.22</v>
+        <v>30.74</v>
       </c>
       <c r="K43" s="5" t="inlineStr">
         <is>
@@ -5617,7 +5641,7 @@
         </is>
       </c>
       <c r="L43" s="10" t="n">
-        <v>22.06</v>
+        <v>35.29</v>
       </c>
       <c r="M43" s="10" t="n"/>
       <c r="N43" s="11">
@@ -5636,17 +5660,17 @@
       </c>
       <c r="Q43" s="3" t="inlineStr">
         <is>
-          <t>DE BROADBAND_PON wholesale bitstream L2-BSA 50-99 Mbps MRC (regulatory price cap)</t>
+          <t>DE BROADBAND_PON wholesale bitstream L2-BSA 500-999 Mbps MRC (regulatory price cap)</t>
         </is>
       </c>
       <c r="R43" s="5" t="inlineStr">
         <is>
-          <t>BMDV / Bundesnetzagentur (German Federal Ministry for Digital Affairs); REGULATOR/SNIPPET_ONLY</t>
+          <t>BMDV / Bundesnetzagentur; REGULATOR/SNIPPET_ONLY</t>
         </is>
       </c>
       <c r="S43" s="3" t="inlineStr">
         <is>
-          <t>50 – 99 Mbit/s … L2-BSA Überlassungsentgelt … 19,22 €</t>
+          <t>500 – 999 Mbit/s … L2-BSA … 30,74 €</t>
         </is>
       </c>
       <c r="T43" s="5" t="inlineStr">
@@ -5665,27 +5689,31 @@
         </is>
       </c>
       <c r="W43" s="12" t="n">
-        <v>0</v>
+        <v>-131200.10221975</v>
       </c>
       <c r="X43" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y43" s="3" t="inlineStr"/>
+        <v>126</v>
+      </c>
+      <c r="Y43" s="3" t="inlineStr">
+        <is>
+          <t>basf -38,527; siemens -29,156; volkswagen -29,156</t>
+        </is>
+      </c>
       <c r="Z43" s="3" t="inlineStr">
         <is>
-          <t>50 Mbps at 64 &gt; 75 Mbps at 22 USD</t>
+          <t>500 Mbps at 132 &gt; 750 Mbps at 35 USD</t>
         </is>
       </c>
       <c r="AA43" s="3" t="inlineStr">
         <is>
-          <t>fresenius 19.22 EUR</t>
+          <t>fresenius 30.74 EUR</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>DE-BROADBAND_PON-150-researched</t>
+          <t>DE-BROADBAND_PON-1000-researched</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
@@ -5699,7 +5727,7 @@
         </is>
       </c>
       <c r="D44" s="5" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="E44" s="14" t="inlineStr">
         <is>
@@ -5713,7 +5741,7 @@
       </c>
       <c r="G44" s="8" t="inlineStr">
         <is>
-          <t>A wholesale bitstream price cap for subsidised networks (BMDV L2-BSA). A business pays the retail price on top of it.</t>
+          <t>A wholesale bitstream price cap for subsidised networks (BMDV L2-BSA). The source itself says retail will be higher after the margin stack.</t>
         </is>
       </c>
       <c r="H44" s="9">
@@ -5725,7 +5753,7 @@
         <v/>
       </c>
       <c r="J44" s="10" t="n">
-        <v>21.55</v>
+        <v>41.97</v>
       </c>
       <c r="K44" s="5" t="inlineStr">
         <is>
@@ -5733,16 +5761,18 @@
         </is>
       </c>
       <c r="L44" s="10" t="n">
-        <v>24.74</v>
-      </c>
-      <c r="M44" s="10" t="n"/>
+        <v>48.18</v>
+      </c>
+      <c r="M44" s="10" t="n">
+        <v>171</v>
+      </c>
       <c r="N44" s="11">
         <f>IF(OR(L44="",M44=""),"",L44/M44)</f>
         <v/>
       </c>
       <c r="O44" s="5" t="inlineStr">
         <is>
-          <t>none - new tier</t>
+          <t>SEED</t>
         </is>
       </c>
       <c r="P44" s="3" t="inlineStr">
@@ -5752,7 +5782,7 @@
       </c>
       <c r="Q44" s="3" t="inlineStr">
         <is>
-          <t>DE BROADBAND_PON wholesale bitstream L2-BSA 100-199 Mbps MRC (regulatory price cap)</t>
+          <t>DE BROADBAND_PON wholesale bitstream L2-BSA 1000 Mbps MRC (regulatory price cap)</t>
         </is>
       </c>
       <c r="R44" s="5" t="inlineStr">
@@ -5762,7 +5792,7 @@
       </c>
       <c r="S44" s="3" t="inlineStr">
         <is>
-          <t>100 – 199 Mbit/s … L2-BSA … 21,55 €</t>
+          <t>1000 Mbit/s … L2-BSA … 41,97 €</t>
         </is>
       </c>
       <c r="T44" s="5" t="inlineStr">
@@ -5781,41 +5811,45 @@
         </is>
       </c>
       <c r="W44" s="12" t="n">
-        <v>0</v>
+        <v>-113710.9553765</v>
       </c>
       <c r="X44" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y44" s="3" t="inlineStr"/>
+        <v>126</v>
+      </c>
+      <c r="Y44" s="3" t="inlineStr">
+        <is>
+          <t>basf -33,391; siemens -25,269; volkswagen -25,269</t>
+        </is>
+      </c>
       <c r="Z44" s="3" t="inlineStr">
         <is>
-          <t>100 Mbps at 78 &gt; 150 Mbps at 25 USD</t>
+          <t>500 Mbps at 132 &gt; 1000 Mbps at 48 USD</t>
         </is>
       </c>
       <c r="AA44" s="3" t="inlineStr">
         <is>
-          <t>fresenius 21.55 EUR</t>
+          <t>fresenius 41.97 EUR</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>DE-BROADBAND_PON-750-researched</t>
+          <t>ES-DIA-600-researched</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>BROADBAND_PON</t>
+          <t>DIA</t>
         </is>
       </c>
       <c r="D45" s="5" t="n">
-        <v>750</v>
+        <v>600</v>
       </c>
       <c r="E45" s="14" t="inlineStr">
         <is>
@@ -5829,7 +5863,7 @@
       </c>
       <c r="G45" s="8" t="inlineStr">
         <is>
-          <t>A wholesale bitstream price cap for subsidised networks (BMDV L2-BSA). A business pays the retail price on top of it.</t>
+          <t>Rejected against a second Spanish source: a multi-network (3Net) circuit marked approximate pending a site survey, about twice Kompara's EUR 400-600 for 500 Mbps dedicated fibre. No circuit in the set uses it.</t>
         </is>
       </c>
       <c r="H45" s="9">
@@ -5841,7 +5875,7 @@
         <v/>
       </c>
       <c r="J45" s="10" t="n">
-        <v>30.74</v>
+        <v>1100</v>
       </c>
       <c r="K45" s="5" t="inlineStr">
         <is>
@@ -5849,7 +5883,7 @@
         </is>
       </c>
       <c r="L45" s="10" t="n">
-        <v>35.29</v>
+        <v>1262.77</v>
       </c>
       <c r="M45" s="10" t="n"/>
       <c r="N45" s="11">
@@ -5863,75 +5897,55 @@
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
-          <t>wholesale; read from a snippet; re-prices lower tiers</t>
-        </is>
-      </c>
-      <c r="Q45" s="3" t="inlineStr">
-        <is>
-          <t>DE BROADBAND_PON wholesale bitstream L2-BSA 500-999 Mbps MRC (regulatory price cap)</t>
-        </is>
-      </c>
+          <t>single source; untraceable</t>
+        </is>
+      </c>
+      <c r="Q45" s="3" t="inlineStr"/>
       <c r="R45" s="5" t="inlineStr">
         <is>
-          <t>BMDV / Bundesnetzagentur; REGULATOR/SNIPPET_ONLY</t>
-        </is>
-      </c>
-      <c r="S45" s="3" t="inlineStr">
-        <is>
-          <t>500 – 999 Mbit/s … L2-BSA … 30,74 €</t>
-        </is>
-      </c>
-      <c r="T45" s="5" t="inlineStr">
-        <is>
-          <t>https://www.bmv.de/SharedDocs/DE/Anlage/DG/vorleistungspreise.pdf?__blob=publicationFile</t>
-        </is>
-      </c>
+          <t>run narrative (the disposition was replaced)</t>
+        </is>
+      </c>
+      <c r="S45" s="3" t="inlineStr"/>
+      <c r="T45" s="5" t="inlineStr"/>
       <c r="U45" s="5" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="V45" s="5" t="inlineStr">
         <is>
-          <t>fresenius</t>
+          <t>carrefour</t>
         </is>
       </c>
       <c r="W45" s="12" t="n">
-        <v>-131200.10221975</v>
+        <v>0</v>
       </c>
       <c r="X45" s="5" t="n">
-        <v>126</v>
-      </c>
-      <c r="Y45" s="3" t="inlineStr">
-        <is>
-          <t>basf -38,527; siemens -29,156; volkswagen -29,156</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Y45" s="3" t="inlineStr"/>
       <c r="Z45" s="3" t="inlineStr">
         <is>
-          <t>500 Mbps at 132 &gt; 750 Mbps at 35 USD</t>
-        </is>
-      </c>
-      <c r="AA45" s="3" t="inlineStr">
-        <is>
-          <t>fresenius 30.74 EUR</t>
-        </is>
-      </c>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="AA45" s="3" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>DE-BROADBAND_PON-1000-researched</t>
+          <t>ES-DIA-1000-researched</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>BROADBAND_PON</t>
+          <t>DIA</t>
         </is>
       </c>
       <c r="D46" s="5" t="n">
@@ -5949,7 +5963,7 @@
       </c>
       <c r="G46" s="8" t="inlineStr">
         <is>
-          <t>A wholesale bitstream price cap for subsidised networks (BMDV L2-BSA). The source itself says retail will be higher after the margin stack.</t>
+          <t>Rejected against a second Spanish source: Kompara's 2026 market range for 1 Gbps dedicated fibre is EUR 700-1,200, and Direct Telecom's own page also lists a 1 Gbps dedicated circuit at EUR 1,860 - EUR 449 is the cheaper of its two figures. The seed it would replace, EUR 1,132, sits inside the range.</t>
         </is>
       </c>
       <c r="H46" s="9">
@@ -5961,7 +5975,7 @@
         <v/>
       </c>
       <c r="J46" s="10" t="n">
-        <v>41.97</v>
+        <v>449</v>
       </c>
       <c r="K46" s="5" t="inlineStr">
         <is>
@@ -5969,10 +5983,10 @@
         </is>
       </c>
       <c r="L46" s="10" t="n">
-        <v>48.18</v>
+        <v>515.4400000000001</v>
       </c>
       <c r="M46" s="10" t="n">
-        <v>171</v>
+        <v>1300</v>
       </c>
       <c r="N46" s="11">
         <f>IF(OR(L46="",M46=""),"",L46/M46)</f>
@@ -5985,60 +5999,48 @@
       </c>
       <c r="P46" s="3" t="inlineStr">
         <is>
-          <t>wholesale; read from a snippet; re-prices lower tiers</t>
-        </is>
-      </c>
-      <c r="Q46" s="3" t="inlineStr">
-        <is>
-          <t>DE BROADBAND_PON wholesale bitstream L2-BSA 1000 Mbps MRC (regulatory price cap)</t>
-        </is>
-      </c>
+          <t>single source; re-prices lower tiers</t>
+        </is>
+      </c>
+      <c r="Q46" s="3" t="inlineStr"/>
       <c r="R46" s="5" t="inlineStr">
         <is>
-          <t>BMDV / Bundesnetzagentur; REGULATOR/SNIPPET_ONLY</t>
+          <t>run narrative (the disposition was replaced)</t>
         </is>
       </c>
       <c r="S46" s="3" t="inlineStr">
         <is>
-          <t>1000 Mbit/s … L2-BSA … 41,97 €</t>
-        </is>
-      </c>
-      <c r="T46" s="5" t="inlineStr">
-        <is>
-          <t>https://www.bmv.de/SharedDocs/DE/Anlage/DG/vorleistungspreise.pdf?__blob=publicationFile</t>
-        </is>
-      </c>
+          <t>ional players plus resellers. Telefónica Global Solutions offers DIA on its own Tier 1 global infrastructure. A domestic reseller (Direct Telecom) lists 100/100 Mbps DIA at €159.99/month and 1 Gbps dedicated circuit at €449/month (2025 prices). Telefónica and MasOrange are exploring acquisition of Vodafone España (as of mid-2025); if completed this would reduce the market to three</t>
+        </is>
+      </c>
+      <c r="T46" s="5" t="inlineStr"/>
       <c r="U46" s="5" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="V46" s="5" t="inlineStr">
         <is>
-          <t>fresenius</t>
+          <t>inditex</t>
         </is>
       </c>
       <c r="W46" s="12" t="n">
-        <v>-113710.9553765</v>
+        <v>-229632.48</v>
       </c>
       <c r="X46" s="5" t="n">
-        <v>126</v>
+        <v>28</v>
       </c>
       <c r="Y46" s="3" t="inlineStr">
         <is>
-          <t>basf -33,391; siemens -25,269; volkswagen -25,269</t>
+          <t>iberdrola -164,023; volkswagen -65,609</t>
         </is>
       </c>
       <c r="Z46" s="3" t="inlineStr">
         <is>
-          <t>500 Mbps at 132 &gt; 1000 Mbps at 48 USD</t>
-        </is>
-      </c>
-      <c r="AA46" s="3" t="inlineStr">
-        <is>
-          <t>fresenius 41.97 EUR</t>
-        </is>
-      </c>
+          <t>500 Mbps at 1196 &gt; 1000 Mbps at 515 USD</t>
+        </is>
+      </c>
+      <c r="AA46" s="3" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
@@ -7898,14 +7900,14 @@
       </c>
       <c r="D8" s="15" t="inlineStr">
         <is>
-          <t>100, 600, 1000</t>
+          <t>100</t>
         </is>
       </c>
       <c r="E8" s="16" t="n">
         <v>0</v>
       </c>
       <c r="F8" s="16" t="n">
-        <v>-19766167.74</v>
+        <v>-2357511.18</v>
       </c>
     </row>
     <row r="9">
@@ -8768,7 +8770,7 @@
         <v/>
       </c>
       <c r="E13" s="16" t="n">
-        <v>-202377.53</v>
+        <v>-38354.33</v>
       </c>
     </row>
     <row r="14">
@@ -8938,7 +8940,7 @@
         </is>
       </c>
       <c r="B22" s="16" t="n">
-        <v>30527838.53</v>
+        <v>17697685.39</v>
       </c>
       <c r="C22" s="16" t="n">
         <v>-57957.48</v>
@@ -8948,7 +8950,7 @@
         <v/>
       </c>
       <c r="E22" s="16" t="n">
-        <v>-14871319.67</v>
+        <v>-2041166.52</v>
       </c>
     </row>
     <row r="23">
@@ -8968,7 +8970,7 @@
         <v/>
       </c>
       <c r="E23" s="16" t="n">
-        <v>-66545.99000000001</v>
+        <v>-936.71</v>
       </c>
     </row>
     <row r="24">
@@ -9278,7 +9280,7 @@
         </is>
       </c>
       <c r="B39" s="16" t="n">
-        <v>39900513.72</v>
+        <v>39782444.83</v>
       </c>
       <c r="C39" s="16" t="n">
         <v>0</v>
@@ -9288,7 +9290,7 @@
         <v/>
       </c>
       <c r="E39" s="16" t="n">
-        <v>-134271.72</v>
+        <v>-16202.83</v>
       </c>
     </row>
     <row r="40">
@@ -9378,7 +9380,7 @@
         </is>
       </c>
       <c r="B44" s="16" t="n">
-        <v>37430393.58</v>
+        <v>33199591.55</v>
       </c>
       <c r="C44" s="16" t="n">
         <v>635912.58</v>
@@ -9388,7 +9390,7 @@
         <v/>
       </c>
       <c r="E44" s="16" t="n">
-        <v>-4811403.3</v>
+        <v>-580601.26</v>
       </c>
     </row>
   </sheetData>

--- a/docs/price-review.xlsx
+++ b/docs/price-review.xlsx
@@ -542,7 +542,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>Every researched price on the rate card - 28 approved, 21 revoked, 10 undecided - beside the rate it would replace, with its evidence and what its approval does to the sample baselines.</t>
+          <t>Every researched price on the rate card - 28 approved, 25 revoked, 6 undecided - beside the rate it would replace, with its evidence and what its approval does to the sample baselines.</t>
         </is>
       </c>
     </row>
@@ -1123,12 +1123,12 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>GB-DIA-100-researched</t>
+          <t>SG-DIA-100-researched</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="G5" s="8" t="inlineStr">
         <is>
-          <t>Virgin's 'packages start at' floor. The seed it would replace is survey-sourced (grade C) and sits inside the GBP 175-320 range the same research quotes.</t>
+          <t>Published on SPTel's promotion page (valid to 31 Dec 2026). No circuit in the set uses it.</t>
         </is>
       </c>
       <c r="H5" s="9">
@@ -1163,18 +1163,18 @@
         <v/>
       </c>
       <c r="J5" s="10" t="n">
-        <v>185</v>
+        <v>312</v>
       </c>
       <c r="K5" s="5" t="inlineStr">
         <is>
-          <t>GBP</t>
+          <t>SGD</t>
         </is>
       </c>
       <c r="L5" s="10" t="n">
-        <v>247.89</v>
+        <v>243.75</v>
       </c>
       <c r="M5" s="10" t="n">
-        <v>335</v>
+        <v>660</v>
       </c>
       <c r="N5" s="11">
         <f>IF(OR(L5="",M5=""),"",L5/M5)</f>
@@ -1187,50 +1187,46 @@
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t>floor; read from a snippet</t>
+          <t>single source; read from a snippet</t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr">
         <is>
-          <t>GB DIA 100 Mbps MRC – Virgin Media Business published tariff</t>
+          <t>DIA 100 Mbps MRC — Singapore (SPTel enterprise tariff)</t>
         </is>
       </c>
       <c r="R5" s="5" t="inlineStr">
         <is>
-          <t>Virgin Media Business; COMPANY_PUBLISHED/SNIPPET_ONLY</t>
+          <t>SPTel; COMPANY_PUBLISHED/SNIPPET_ONLY</t>
         </is>
       </c>
       <c r="S5" s="3" t="inlineStr">
         <is>
-          <t>Our packages start at £185 per month which provided 100Mbps upload and download speeds.</t>
+          <t>Enterprise Internet 100Mbps $312/mth (on 24-month contract)</t>
         </is>
       </c>
       <c r="T5" s="5" t="inlineStr">
         <is>
-          <t>https://www.virginmediabusiness.co.uk/connectivity/internet-access/leased-lines-for-business/</t>
+          <t>https://sptel.com/promotion/business-broadband-singapore/</t>
         </is>
       </c>
       <c r="U5" s="5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="V5" s="5" t="inlineStr">
         <is>
-          <t>unilever</t>
+          <t>dbs</t>
         </is>
       </c>
       <c r="W5" s="12" t="n">
-        <v>-2414090.918069141</v>
+        <v>0</v>
       </c>
       <c r="X5" s="5" t="n">
-        <v>2429</v>
-      </c>
-      <c r="Y5" s="3" t="inlineStr">
-        <is>
-          <t>nhs-england -1,121,155; saint-gobain -796,760; santander -280,459</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Y5" s="3" t="inlineStr"/>
       <c r="Z5" s="3" t="inlineStr">
         <is>
           <t>no</t>
@@ -1238,28 +1234,28 @@
       </c>
       <c r="AA5" s="3" t="inlineStr">
         <is>
-          <t>deutsche-post-dhl 206 GBP; eon 139 GBP; iberdrola 130 GBP; nhs-england 222 GBP; unilever 185 GBP</t>
+          <t>dbs 312 SGD; dbs 312 SGD</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>GB-DIA-500-researched</t>
+          <t>US-BROADBAND_PON-300-researched</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>DIA</t>
+          <t>BROADBAND_PON</t>
         </is>
       </c>
       <c r="D6" s="5" t="n">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
@@ -1273,7 +1269,7 @@
       </c>
       <c r="G6" s="8" t="inlineStr">
         <is>
-          <t>Vodafone 'from' GBP 257 on a 60-month term. The same research puts urban 500 Mbps at GBP 350-500 on 36 months.</t>
+          <t>AT&amp;T Business Fiber 300, inside AT&amp;T's footprint only. At $70 it is below the national median for 100 Mbps, and would price every US PON circuit up to 300 Mbps at it.</t>
         </is>
       </c>
       <c r="H6" s="9">
@@ -1285,94 +1281,92 @@
         <v/>
       </c>
       <c r="J6" s="10" t="n">
-        <v>257</v>
+        <v>70</v>
       </c>
       <c r="K6" s="5" t="inlineStr">
         <is>
-          <t>GBP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="L6" s="10" t="n">
-        <v>344.37</v>
-      </c>
-      <c r="M6" s="10" t="n">
-        <v>690</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="M6" s="10" t="n"/>
       <c r="N6" s="11">
         <f>IF(OR(L6="",M6=""),"",L6/M6)</f>
         <v/>
       </c>
       <c r="O6" s="5" t="inlineStr">
         <is>
-          <t>SEED</t>
+          <t>none - new tier</t>
         </is>
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t>floor; single source; re-prices lower tiers</t>
+          <t>read from a snippet; re-prices lower tiers</t>
         </is>
       </c>
       <c r="Q6" s="3" t="inlineStr">
         <is>
-          <t>DIA 500Mbps MRC – Vodafone Business published retail tariff</t>
+          <t>BROADBAND_PON 300 Mbps MRC – US (AT&amp;T Business Fiber published rate)</t>
         </is>
       </c>
       <c r="R6" s="5" t="inlineStr">
         <is>
-          <t>Vodafone Business; COMPANY_PUBLISHED/FULL_PAGE</t>
+          <t>business.org (AT&amp;T Business Internet Review 2026); AGGREGATOR/SNIPPET_ONLY</t>
         </is>
       </c>
       <c r="S6" s="3" t="inlineStr">
         <is>
-          <t>Vodafone Dedicated Internet Access (Managed) 500 Mbps Monthly price from £257 (ex. VAT) 60 months</t>
+          <t>Business Fiber 300: $70.00/mo</t>
         </is>
       </c>
       <c r="T6" s="5" t="inlineStr">
         <is>
-          <t>https://www.vodafone.co.uk/business/connectivity/data-connectivity/dedicated-internet-access</t>
+          <t>https://www.business.org/services/internet/att-business-internet-review/</t>
         </is>
       </c>
       <c r="U6" s="5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="V6" s="5" t="inlineStr">
         <is>
-          <t>nhs-england</t>
+          <t>simmons-bank</t>
         </is>
       </c>
       <c r="W6" s="12" t="n">
-        <v>-2330376.070015842</v>
+        <v>-75873.6111235</v>
       </c>
       <c r="X6" s="5" t="n">
-        <v>520</v>
+        <v>243</v>
       </c>
       <c r="Y6" s="3" t="inlineStr">
         <is>
-          <t>deutsche-post-dhl -1,892,302; royal-mail -272,780; ups -112,906</t>
+          <t>simmons-bank -39,654; basf -8,430; siemens -7,181</t>
         </is>
       </c>
       <c r="Z6" s="3" t="inlineStr">
         <is>
-          <t>300 Mbps at 600 &gt; 500 Mbps at 344 USD</t>
+          <t>250 Mbps at 114 &gt; 300 Mbps at 70 USD</t>
         </is>
       </c>
       <c r="AA6" s="3" t="inlineStr">
         <is>
-          <t>deutsche-post-dhl 243 GBP; nhs-england 257 GBP</t>
+          <t>simmons-bank 70 USD</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>GB-DIA-1000-researched</t>
+          <t>ZA-DIA-100-researched</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>ZA</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -1381,7 +1375,7 @@
         </is>
       </c>
       <c r="D7" s="5" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
@@ -1395,7 +1389,7 @@
       </c>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>CompareNet publishes a 1 Gbps symmetric leased-line floor of £195/month. Hold—not reject—because it is an aggregator 'from' price below the broader market range and needs address/term validation.</t>
+          <t>MWCom 'from around R8,000'; the same research gives R8,000-25,000 depending on distance and capacity.</t>
         </is>
       </c>
       <c r="H7" s="9">
@@ -1407,51 +1401,49 @@
         <v/>
       </c>
       <c r="J7" s="10" t="n">
-        <v>195</v>
+        <v>8000</v>
       </c>
       <c r="K7" s="5" t="inlineStr">
         <is>
-          <t>GBP</t>
+          <t>ZAR</t>
         </is>
       </c>
       <c r="L7" s="10" t="n">
-        <v>261.29</v>
-      </c>
-      <c r="M7" s="10" t="n">
-        <v>737</v>
-      </c>
+        <v>444.44</v>
+      </c>
+      <c r="M7" s="10" t="n"/>
       <c r="N7" s="11">
         <f>IF(OR(L7="",M7=""),"",L7/M7)</f>
         <v/>
       </c>
       <c r="O7" s="5" t="inlineStr">
         <is>
-          <t>SEED</t>
+          <t>none - new tier</t>
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t>floor; single source; read from a snippet; re-prices lower tiers</t>
+          <t>floor; read from a snippet</t>
         </is>
       </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t>GB enterprise leased line (DIA) monthly cost — 1 Gbps enterprise</t>
+          <t>DIA 100 Mbps MRC ZA (leased line / dedicated fibre)</t>
         </is>
       </c>
       <c r="R7" s="5" t="inlineStr">
         <is>
-          <t>ComparenetUK; AGGREGATOR/SNIPPET_ONLY</t>
+          <t>mwcom.co.za; COMPANY_PUBLISHED/SNIPPET_ONLY</t>
         </is>
       </c>
       <c r="S7" s="3" t="inlineStr">
         <is>
-          <t>1Gbps Symmetric — From £195/month, enterprise-grade with dedicated account manager</t>
+          <t>Leased lines start from around R8,000/mo for 100 Mbps symmetric.</t>
         </is>
       </c>
       <c r="T7" s="5" t="inlineStr">
         <is>
-          <t>https://comparenet.co.uk/dedicated-fibre-leased-lines</t>
+          <t>https://www.mwcom.co.za/business-internet-south-africa</t>
         </is>
       </c>
       <c r="U7" s="5" t="inlineStr">
@@ -1461,63 +1453,59 @@
       </c>
       <c r="V7" s="5" t="inlineStr">
         <is>
-          <t>iberdrola</t>
+          <t>not recorded</t>
         </is>
       </c>
       <c r="W7" s="12" t="n">
-        <v>-659380.2940418924</v>
+        <v>-16474.2432</v>
       </c>
       <c r="X7" s="5" t="n">
-        <v>133</v>
+        <v>1</v>
       </c>
       <c r="Y7" s="3" t="inlineStr">
         <is>
-          <t>nhs-england -183,990; siemens -119,345; network-rail -119,345</t>
+          <t>anglo-american -16,474</t>
         </is>
       </c>
       <c r="Z7" s="3" t="inlineStr">
         <is>
-          <t>500 Mbps at 690 &gt; 1000 Mbps at 261 USD</t>
-        </is>
-      </c>
-      <c r="AA7" s="3" t="inlineStr">
-        <is>
-          <t>deutsche-post-dhl 267 GBP; iberdrola 195 GBP; nhs-england 300 GBP</t>
-        </is>
-      </c>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="AA7" s="3" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>GB-DIA-10000-researched</t>
+          <t>AU-BROADBAND_HFC-250-researched</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>DIA</t>
+          <t>BROADBAND_HFC</t>
         </is>
       </c>
       <c r="D8" s="5" t="n">
-        <v>10000</v>
-      </c>
-      <c r="E8" s="6" t="inlineStr">
-        <is>
-          <t>undecided</t>
+        <v>250</v>
+      </c>
+      <c r="E8" s="13" t="inlineStr">
+        <is>
+          <t>approved by Christian Bartosch</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Approve</t>
         </is>
       </c>
       <c r="G8" s="8" t="inlineStr">
         <is>
-          <t>Spitfire publishes 10 Gbps symmetric leased-line pricing from £450/month. Hold—not reject—because it is a single-carrier floor that needs location, term and installation-cost validation.</t>
+          <t>Swoop's published standard business nbn 250/100 price of A$104/month. The introductory discount is excluded.</t>
         </is>
       </c>
       <c r="H8" s="9">
@@ -1529,111 +1517,105 @@
         <v/>
       </c>
       <c r="J8" s="10" t="n">
-        <v>450</v>
+        <v>104</v>
       </c>
       <c r="K8" s="5" t="inlineStr">
         <is>
-          <t>GBP</t>
+          <t>AUD</t>
         </is>
       </c>
       <c r="L8" s="10" t="n">
-        <v>602.97</v>
-      </c>
-      <c r="M8" s="10" t="n"/>
+        <v>70.27</v>
+      </c>
+      <c r="M8" s="10" t="n">
+        <v>155</v>
+      </c>
       <c r="N8" s="11">
         <f>IF(OR(L8="",M8=""),"",L8/M8)</f>
         <v/>
       </c>
       <c r="O8" s="5" t="inlineStr">
         <is>
-          <t>none - new tier</t>
+          <t>SEED</t>
         </is>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t>single source; read from a snippet; re-prices lower tiers</t>
-        </is>
-      </c>
-      <c r="Q8" s="3" t="inlineStr">
-        <is>
-          <t>DIA 10000Mbps MRC (Spitfire, retail)</t>
-        </is>
-      </c>
+          <t>single source; re-prices lower tiers</t>
+        </is>
+      </c>
+      <c r="Q8" s="3" t="inlineStr"/>
       <c r="R8" s="5" t="inlineStr">
         <is>
-          <t>Spitfire Networks — product page; COMPANY_PUBLISHED/SNIPPET_ONLY</t>
+          <t>run narrative (the disposition was replaced)</t>
         </is>
       </c>
       <c r="S8" s="3" t="inlineStr">
         <is>
-          <t>10 Gbps From: £450/month — 10Gbps Upload — 10Gbps Download</t>
-        </is>
-      </c>
-      <c r="T8" s="5" t="inlineStr">
-        <is>
-          <t>https://www.spitfire.co.uk/connectivity/fibre-ethernet-leased-line/</t>
-        </is>
-      </c>
+          <t>ise NBN (symmetric, SLA-backed) list prices in AUD excl. GST: 100/100 Mbps A$399/mo, 250/250 Mbps A$399/mo, 500/500 Mbps A$469/mo, 1000/1000 Mbps A$699/mo (36-month term). Swoop published business NBN prices: 250 Mbps A$104/mo (FTTP), 1000 Mbps A$129/mo (FTTP/HFC). Kookaburra Comms (trade press, 2026) cites typical published range A$400 for 100-250 Mbps to A$700-A$1,500 for 1 Gbps</t>
+        </is>
+      </c>
+      <c r="T8" s="5" t="inlineStr"/>
       <c r="U8" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="V8" s="5" t="inlineStr">
         <is>
-          <t>deutsche-post-dhl</t>
+          <t>woolworths</t>
         </is>
       </c>
       <c r="W8" s="12" t="n">
-        <v>0</v>
+        <v>-925814.4972972973</v>
       </c>
       <c r="X8" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y8" s="3" t="inlineStr"/>
+        <v>1130</v>
+      </c>
+      <c r="Y8" s="3" t="inlineStr">
+        <is>
+          <t>woolworths -925,814</t>
+        </is>
+      </c>
       <c r="Z8" s="3" t="inlineStr">
         <is>
-          <t>1000 Mbps at 737 &gt; 10000 Mbps at 603 USD</t>
-        </is>
-      </c>
-      <c r="AA8" s="3" t="inlineStr">
-        <is>
-          <t>deutsche-post-dhl 450 GBP</t>
-        </is>
-      </c>
+          <t>100 Mbps at 115 &gt; 250 Mbps at 70 USD; 1000 Mbps at 250 &gt; 2000 Mbps at 149 USD</t>
+        </is>
+      </c>
+      <c r="AA8" s="3" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>SG-DIA-100-researched</t>
+          <t>AU-BROADBAND_HFC-2000-researched</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>DIA</t>
+          <t>BROADBAND_HFC</t>
         </is>
       </c>
       <c r="D9" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="E9" s="6" t="inlineStr">
-        <is>
-          <t>undecided</t>
+        <v>2000</v>
+      </c>
+      <c r="E9" s="13" t="inlineStr">
+        <is>
+          <t>approved by Christian Bartosch</t>
         </is>
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Approve</t>
         </is>
       </c>
       <c r="G9" s="8" t="inlineStr">
         <is>
-          <t>Published on SPTel's promotion page (valid to 31 Dec 2026). No circuit in the set uses it.</t>
+          <t>Aussie Broadband business Hyperfast 2000, published; a trade guide puts business fibre plans at A$100-220.</t>
         </is>
       </c>
       <c r="H9" s="9">
@@ -1645,51 +1627,49 @@
         <v/>
       </c>
       <c r="J9" s="10" t="n">
-        <v>312</v>
+        <v>220</v>
       </c>
       <c r="K9" s="5" t="inlineStr">
         <is>
-          <t>SGD</t>
+          <t>AUD</t>
         </is>
       </c>
       <c r="L9" s="10" t="n">
-        <v>243.75</v>
-      </c>
-      <c r="M9" s="10" t="n">
-        <v>660</v>
-      </c>
+        <v>148.65</v>
+      </c>
+      <c r="M9" s="10" t="n"/>
       <c r="N9" s="11">
         <f>IF(OR(L9="",M9=""),"",L9/M9)</f>
         <v/>
       </c>
       <c r="O9" s="5" t="inlineStr">
         <is>
-          <t>SEED</t>
+          <t>none - new tier</t>
         </is>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t>single source; read from a snippet</t>
+          <t>read from a snippet; re-prices lower tiers</t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t>DIA 100 Mbps MRC — Singapore (SPTel enterprise tariff)</t>
+          <t>BROADBAND_HFC AU 2000Mbps MRC (Aussie Broadband Business Hyperfast HFC)</t>
         </is>
       </c>
       <c r="R9" s="5" t="inlineStr">
         <is>
-          <t>SPTel; COMPANY_PUBLISHED/SNIPPET_ONLY</t>
+          <t>Aussie Broadband / WhistleOut; AGGREGATOR/SNIPPET_ONLY</t>
         </is>
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t>Enterprise Internet 100Mbps $312/mth (on 24-month contract)</t>
+          <t>Aussie Broadband FTTP Business Hyperfast Plus 2000/500 Unlimited Data $220/mth</t>
         </is>
       </c>
       <c r="T9" s="5" t="inlineStr">
         <is>
-          <t>https://sptel.com/promotion/business-broadband-singapore/</t>
+          <t>https://www.whistleout.com.au/Broadband/Guides/NBN-business-plans-compared</t>
         </is>
       </c>
       <c r="U9" s="5" t="inlineStr">
@@ -1699,7 +1679,7 @@
       </c>
       <c r="V9" s="5" t="inlineStr">
         <is>
-          <t>dbs</t>
+          <t>woolworths</t>
         </is>
       </c>
       <c r="W9" s="12" t="n">
@@ -1711,24 +1691,24 @@
       <c r="Y9" s="3" t="inlineStr"/>
       <c r="Z9" s="3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>100 Mbps at 115 &gt; 250 Mbps at 70 USD; 1000 Mbps at 250 &gt; 2000 Mbps at 149 USD</t>
         </is>
       </c>
       <c r="AA9" s="3" t="inlineStr">
         <is>
-          <t>dbs 312 SGD; dbs 312 SGD</t>
+          <t>woolworths 220 AUD</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>US-BROADBAND_PON-300-researched</t>
+          <t>AU-BROADBAND_PON-250-researched</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -1737,21 +1717,21 @@
         </is>
       </c>
       <c r="D10" s="5" t="n">
-        <v>300</v>
-      </c>
-      <c r="E10" s="6" t="inlineStr">
-        <is>
-          <t>undecided</t>
+        <v>250</v>
+      </c>
+      <c r="E10" s="13" t="inlineStr">
+        <is>
+          <t>approved by Christian Bartosch</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Approve</t>
         </is>
       </c>
       <c r="G10" s="8" t="inlineStr">
         <is>
-          <t>AT&amp;T Business Fiber 300, inside AT&amp;T's footprint only. At $70 it is below the national median for 100 Mbps, and would price every US PON circuit up to 300 Mbps at it.</t>
+          <t>Aussie Broadband business FTTP 250/100, published by the provider and confirmed by an aggregator.</t>
         </is>
       </c>
       <c r="H10" s="9">
@@ -1763,49 +1743,51 @@
         <v/>
       </c>
       <c r="J10" s="10" t="n">
-        <v>70</v>
+        <v>114</v>
       </c>
       <c r="K10" s="5" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>AUD</t>
         </is>
       </c>
       <c r="L10" s="10" t="n">
-        <v>70</v>
-      </c>
-      <c r="M10" s="10" t="n"/>
+        <v>77.03</v>
+      </c>
+      <c r="M10" s="10" t="n">
+        <v>101</v>
+      </c>
       <c r="N10" s="11">
         <f>IF(OR(L10="",M10=""),"",L10/M10)</f>
         <v/>
       </c>
       <c r="O10" s="5" t="inlineStr">
         <is>
-          <t>none - new tier</t>
+          <t>SEED</t>
         </is>
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t>read from a snippet; re-prices lower tiers</t>
+          <t>read from a snippet</t>
         </is>
       </c>
       <c r="Q10" s="3" t="inlineStr">
         <is>
-          <t>BROADBAND_PON 300 Mbps MRC – US (AT&amp;T Business Fiber published rate)</t>
+          <t>BROADBAND_PON AU 250Mbps MRC (Aussie Broadband Business FTTP 250/100)</t>
         </is>
       </c>
       <c r="R10" s="5" t="inlineStr">
         <is>
-          <t>business.org (AT&amp;T Business Internet Review 2026); AGGREGATOR/SNIPPET_ONLY</t>
+          <t>Aussie Broadband Enterprise; COMPANY_PUBLISHED/SNIPPET_ONLY</t>
         </is>
       </c>
       <c r="S10" s="3" t="inlineStr">
         <is>
-          <t>Business Fiber 300: $70.00/mo</t>
+          <t>Superfast Plus 250/100 $114/month</t>
         </is>
       </c>
       <c r="T10" s="5" t="inlineStr">
         <is>
-          <t>https://www.business.org/services/internet/att-business-internet-review/</t>
+          <t>https://www.aussiebroadband.com.au/enterprise/internet/nbn-plans/</t>
         </is>
       </c>
       <c r="U10" s="5" t="inlineStr">
@@ -1815,63 +1797,59 @@
       </c>
       <c r="V10" s="5" t="inlineStr">
         <is>
-          <t>simmons-bank</t>
+          <t>woolworths</t>
         </is>
       </c>
       <c r="W10" s="12" t="n">
-        <v>-75873.6111235</v>
+        <v>0</v>
       </c>
       <c r="X10" s="5" t="n">
-        <v>243</v>
-      </c>
-      <c r="Y10" s="3" t="inlineStr">
-        <is>
-          <t>simmons-bank -39,654; basf -8,430; siemens -7,181</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Y10" s="3" t="inlineStr"/>
       <c r="Z10" s="3" t="inlineStr">
         <is>
-          <t>250 Mbps at 114 &gt; 300 Mbps at 70 USD</t>
+          <t>no</t>
         </is>
       </c>
       <c r="AA10" s="3" t="inlineStr">
         <is>
-          <t>simmons-bank 70 USD</t>
+          <t>woolworths 114 AUD</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>ZA-DIA-100-researched</t>
+          <t>AU-ETHERNET-250-researched</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>ZA</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>DIA</t>
+          <t>ETHERNET</t>
         </is>
       </c>
       <c r="D11" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="E11" s="6" t="inlineStr">
-        <is>
-          <t>undecided</t>
+        <v>250</v>
+      </c>
+      <c r="E11" s="13" t="inlineStr">
+        <is>
+          <t>approved by Christian Bartosch</t>
         </is>
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Approve</t>
         </is>
       </c>
       <c r="G11" s="8" t="inlineStr">
         <is>
-          <t>MWCom 'from around R8,000'; the same research gives R8,000-25,000 depending on distance and capacity.</t>
+          <t>NBN Enterprise Ethernet retail, ex GST, 36-month: Swoop and Vocus publish the same A$399.</t>
         </is>
       </c>
       <c r="H11" s="9">
@@ -1883,15 +1861,15 @@
         <v/>
       </c>
       <c r="J11" s="10" t="n">
-        <v>8000</v>
+        <v>399</v>
       </c>
       <c r="K11" s="5" t="inlineStr">
         <is>
-          <t>ZAR</t>
+          <t>AUD</t>
         </is>
       </c>
       <c r="L11" s="10" t="n">
-        <v>444.44</v>
+        <v>269.59</v>
       </c>
       <c r="M11" s="10" t="n"/>
       <c r="N11" s="11">
@@ -1905,27 +1883,27 @@
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t>floor; read from a snippet</t>
+          <t>wholesale; floor; read from a snippet</t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
-          <t>DIA 100 Mbps MRC ZA (leased line / dedicated fibre)</t>
+          <t>ETHERNET AU 250Mbps MRC (NBN Enterprise Ethernet retail, ex GST)</t>
         </is>
       </c>
       <c r="R11" s="5" t="inlineStr">
         <is>
-          <t>mwcom.co.za; COMPANY_PUBLISHED/SNIPPET_ONLY</t>
+          <t>Swoop; COMPANY_PUBLISHED/SNIPPET_ONLY</t>
         </is>
       </c>
       <c r="S11" s="3" t="inlineStr">
         <is>
-          <t>Leased lines start from around R8,000/mo for 100 Mbps symmetric.</t>
+          <t>Business Fibre 250/250 Mbps $399 per month</t>
         </is>
       </c>
       <c r="T11" s="5" t="inlineStr">
         <is>
-          <t>https://www.mwcom.co.za/business-internet-south-africa</t>
+          <t>https://www.swoop.com.au/business/enterprise-ethernet/</t>
         </is>
       </c>
       <c r="U11" s="5" t="inlineStr">
@@ -1935,18 +1913,18 @@
       </c>
       <c r="V11" s="5" t="inlineStr">
         <is>
-          <t>not recorded</t>
+          <t>woolworths</t>
         </is>
       </c>
       <c r="W11" s="12" t="n">
-        <v>-16474.2432</v>
+        <v>-2472.04054054054</v>
       </c>
       <c r="X11" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Y11" s="3" t="inlineStr">
         <is>
-          <t>anglo-american -16,474</t>
+          <t>woolworths -2,472</t>
         </is>
       </c>
       <c r="Z11" s="3" t="inlineStr">
@@ -1954,12 +1932,16 @@
           <t>no</t>
         </is>
       </c>
-      <c r="AA11" s="3" t="inlineStr"/>
+      <c r="AA11" s="3" t="inlineStr">
+        <is>
+          <t>woolworths 399 AUD</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>AU-BROADBAND_HFC-250-researched</t>
+          <t>AU-ETHERNET-500-researched</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
@@ -1969,11 +1951,11 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>BROADBAND_HFC</t>
+          <t>ETHERNET</t>
         </is>
       </c>
       <c r="D12" s="5" t="n">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="E12" s="13" t="inlineStr">
         <is>
@@ -1987,7 +1969,7 @@
       </c>
       <c r="G12" s="8" t="inlineStr">
         <is>
-          <t>Swoop's published standard business nbn 250/100 price of A$104/month. The introductory discount is excluded.</t>
+          <t>NBN Enterprise Ethernet retail, ex GST, 36-month: Vocus A$469, Swoop A$499.</t>
         </is>
       </c>
       <c r="H12" s="9">
@@ -1999,7 +1981,7 @@
         <v/>
       </c>
       <c r="J12" s="10" t="n">
-        <v>104</v>
+        <v>469</v>
       </c>
       <c r="K12" s="5" t="inlineStr">
         <is>
@@ -2007,10 +1989,10 @@
         </is>
       </c>
       <c r="L12" s="10" t="n">
-        <v>70.27</v>
+        <v>316.89</v>
       </c>
       <c r="M12" s="10" t="n">
-        <v>155</v>
+        <v>1288</v>
       </c>
       <c r="N12" s="11">
         <f>IF(OR(L12="",M12=""),"",L12/M12)</f>
@@ -2023,24 +2005,32 @@
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t>single source; re-prices lower tiers</t>
-        </is>
-      </c>
-      <c r="Q12" s="3" t="inlineStr"/>
+          <t>floor; read from a snippet</t>
+        </is>
+      </c>
+      <c r="Q12" s="3" t="inlineStr">
+        <is>
+          <t>ETHERNET AU 500Mbps MRC (NBN Enterprise Ethernet retail, ex GST)</t>
+        </is>
+      </c>
       <c r="R12" s="5" t="inlineStr">
         <is>
-          <t>run narrative (the disposition was replaced)</t>
+          <t>Vocus; COMPANY_PUBLISHED/SNIPPET_ONLY</t>
         </is>
       </c>
       <c r="S12" s="3" t="inlineStr">
         <is>
-          <t>ise NBN (symmetric, SLA-backed) list prices in AUD excl. GST: 100/100 Mbps A$399/mo, 250/250 Mbps A$399/mo, 500/500 Mbps A$469/mo, 1000/1000 Mbps A$699/mo (36-month term). Swoop published business NBN prices: 250 Mbps A$104/mo (FTTP), 1000 Mbps A$129/mo (FTTP/HFC). Kookaburra Comms (trade press, 2026) cites typical published range A$400 for 100-250 Mbps to A$700-A$1,500 for 1 Gbps</t>
-        </is>
-      </c>
-      <c r="T12" s="5" t="inlineStr"/>
+          <t>500/500Mbps Starting at $469 / per month (ex. GST)</t>
+        </is>
+      </c>
+      <c r="T12" s="5" t="inlineStr">
+        <is>
+          <t>https://www.vocus.com.au/enterprise/internet-and-networks/nbn-enterprise-ethernet</t>
+        </is>
+      </c>
       <c r="U12" s="5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="V12" s="5" t="inlineStr">
@@ -2049,27 +2039,27 @@
         </is>
       </c>
       <c r="W12" s="12" t="n">
-        <v>-925814.4972972973</v>
+        <v>0</v>
       </c>
       <c r="X12" s="5" t="n">
-        <v>1130</v>
-      </c>
-      <c r="Y12" s="3" t="inlineStr">
-        <is>
-          <t>woolworths -925,814</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Y12" s="3" t="inlineStr"/>
       <c r="Z12" s="3" t="inlineStr">
         <is>
-          <t>100 Mbps at 115 &gt; 250 Mbps at 70 USD; 1000 Mbps at 250 &gt; 2000 Mbps at 149 USD</t>
-        </is>
-      </c>
-      <c r="AA12" s="3" t="inlineStr"/>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="AA12" s="3" t="inlineStr">
+        <is>
+          <t>woolworths 469 AUD</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>AU-BROADBAND_HFC-2000-researched</t>
+          <t>AU-ETHERNET-1000-researched</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
@@ -2079,11 +2069,11 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>BROADBAND_HFC</t>
+          <t>ETHERNET</t>
         </is>
       </c>
       <c r="D13" s="5" t="n">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="E13" s="13" t="inlineStr">
         <is>
@@ -2097,7 +2087,7 @@
       </c>
       <c r="G13" s="8" t="inlineStr">
         <is>
-          <t>Aussie Broadband business Hyperfast 2000, published; a trade guide puts business fibre plans at A$100-220.</t>
+          <t>NBN Enterprise Ethernet retail, ex GST, 36-month: Swoop and Vocus A$699, Telstra via Telair A$659.</t>
         </is>
       </c>
       <c r="H13" s="9">
@@ -2109,7 +2099,7 @@
         <v/>
       </c>
       <c r="J13" s="10" t="n">
-        <v>220</v>
+        <v>699</v>
       </c>
       <c r="K13" s="5" t="inlineStr">
         <is>
@@ -2117,41 +2107,43 @@
         </is>
       </c>
       <c r="L13" s="10" t="n">
-        <v>148.65</v>
-      </c>
-      <c r="M13" s="10" t="n"/>
+        <v>472.3</v>
+      </c>
+      <c r="M13" s="10" t="n">
+        <v>1450</v>
+      </c>
       <c r="N13" s="11">
         <f>IF(OR(L13="",M13=""),"",L13/M13)</f>
         <v/>
       </c>
       <c r="O13" s="5" t="inlineStr">
         <is>
-          <t>none - new tier</t>
+          <t>SEED</t>
         </is>
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t>read from a snippet; re-prices lower tiers</t>
+          <t>floor; read from a snippet</t>
         </is>
       </c>
       <c r="Q13" s="3" t="inlineStr">
         <is>
-          <t>BROADBAND_HFC AU 2000Mbps MRC (Aussie Broadband Business Hyperfast HFC)</t>
+          <t>ETHERNET AU 1000Mbps MRC (NBN Enterprise Ethernet retail, ex GST)</t>
         </is>
       </c>
       <c r="R13" s="5" t="inlineStr">
         <is>
-          <t>Aussie Broadband / WhistleOut; AGGREGATOR/SNIPPET_ONLY</t>
+          <t>Swoop; COMPANY_PUBLISHED/SNIPPET_ONLY</t>
         </is>
       </c>
       <c r="S13" s="3" t="inlineStr">
         <is>
-          <t>Aussie Broadband FTTP Business Hyperfast Plus 2000/500 Unlimited Data $220/mth</t>
+          <t>Business Fibre 1000/1000 Mbps $699 per month</t>
         </is>
       </c>
       <c r="T13" s="5" t="inlineStr">
         <is>
-          <t>https://www.whistleout.com.au/Broadband/Guides/NBN-business-plans-compared</t>
+          <t>https://www.swoop.com.au/business/enterprise-ethernet/</t>
         </is>
       </c>
       <c r="U13" s="5" t="inlineStr">
@@ -2165,32 +2157,36 @@
         </is>
       </c>
       <c r="W13" s="12" t="n">
-        <v>0</v>
+        <v>-304559.635439</v>
       </c>
       <c r="X13" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y13" s="3" t="inlineStr"/>
+        <v>20</v>
+      </c>
+      <c r="Y13" s="3" t="inlineStr">
+        <is>
+          <t>rio-tinto -304,560</t>
+        </is>
+      </c>
       <c r="Z13" s="3" t="inlineStr">
         <is>
-          <t>100 Mbps at 115 &gt; 250 Mbps at 70 USD; 1000 Mbps at 250 &gt; 2000 Mbps at 149 USD</t>
+          <t>no</t>
         </is>
       </c>
       <c r="AA13" s="3" t="inlineStr">
         <is>
-          <t>woolworths 220 AUD</t>
+          <t>woolworths 699 AUD</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>AU-BROADBAND_PON-250-researched</t>
+          <t>BE-BROADBAND_PON-150-researched</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
@@ -2199,7 +2195,7 @@
         </is>
       </c>
       <c r="D14" s="5" t="n">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="E14" s="13" t="inlineStr">
         <is>
@@ -2213,7 +2209,7 @@
       </c>
       <c r="G14" s="8" t="inlineStr">
         <is>
-          <t>Aussie Broadband business FTTP 250/100, published by the provider and confirmed by an aggregator.</t>
+          <t>Proximus Business Go Fiber 150, the standard price after the 12-month promotion, ex VAT, read from the full page.</t>
         </is>
       </c>
       <c r="H14" s="9">
@@ -2225,61 +2221,59 @@
         <v/>
       </c>
       <c r="J14" s="10" t="n">
-        <v>114</v>
+        <v>60</v>
       </c>
       <c r="K14" s="5" t="inlineStr">
         <is>
-          <t>AUD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="L14" s="10" t="n">
-        <v>77.03</v>
-      </c>
-      <c r="M14" s="10" t="n">
-        <v>101</v>
-      </c>
+        <v>68.88</v>
+      </c>
+      <c r="M14" s="10" t="n"/>
       <c r="N14" s="11">
         <f>IF(OR(L14="",M14=""),"",L14/M14)</f>
         <v/>
       </c>
       <c r="O14" s="5" t="inlineStr">
         <is>
-          <t>SEED</t>
+          <t>none - new tier</t>
         </is>
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t>read from a snippet</t>
+          <t>promotional; single source</t>
         </is>
       </c>
       <c r="Q14" s="3" t="inlineStr">
         <is>
-          <t>BROADBAND_PON AU 250Mbps MRC (Aussie Broadband Business FTTP 250/100)</t>
+          <t>BROADBAND_PON 150 Mbps MRC (business shared fibre, Proximus Go Fiber)</t>
         </is>
       </c>
       <c r="R14" s="5" t="inlineStr">
         <is>
-          <t>Aussie Broadband Enterprise; COMPANY_PUBLISHED/SNIPPET_ONLY</t>
+          <t>Proximus (proximus.be); COMPANY_PUBLISHED/FULL_PAGE</t>
         </is>
       </c>
       <c r="S14" s="3" t="inlineStr">
         <is>
-          <t>Superfast Plus 250/100 $114/month</t>
+          <t>Business Internet Go Fiber 150 Mbps: €45/month during 12 months, then €60/month</t>
         </is>
       </c>
       <c r="T14" s="5" t="inlineStr">
         <is>
-          <t>https://www.aussiebroadband.com.au/enterprise/internet/nbn-plans/</t>
+          <t>https://www.proximus.be/en/business/internet-subscription</t>
         </is>
       </c>
       <c r="U14" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="V14" s="5" t="inlineStr">
         <is>
-          <t>woolworths</t>
+          <t>bnp-paribas</t>
         </is>
       </c>
       <c r="W14" s="12" t="n">
@@ -2296,28 +2290,28 @@
       </c>
       <c r="AA14" s="3" t="inlineStr">
         <is>
-          <t>woolworths 114 AUD</t>
+          <t>bnp-paribas 60 EUR</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>AU-ETHERNET-250-researched</t>
+          <t>FR-DIA-1000-researched</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>ETHERNET</t>
+          <t>DIA</t>
         </is>
       </c>
       <c r="D15" s="5" t="n">
-        <v>250</v>
+        <v>1000</v>
       </c>
       <c r="E15" s="13" t="inlineStr">
         <is>
@@ -2331,7 +2325,7 @@
       </c>
       <c r="G15" s="8" t="inlineStr">
         <is>
-          <t>NBN Enterprise Ethernet retail, ex GST, 36-month: Swoop and Vocus publish the same A$399.</t>
+          <t>Orange Business FTTO 1 Gbps, approximately EUR 1,200 per a trade-press snippet. It sits close to the seed (0.91x).</t>
         </is>
       </c>
       <c r="H15" s="9">
@@ -2343,101 +2337,103 @@
         <v/>
       </c>
       <c r="J15" s="10" t="n">
-        <v>399</v>
+        <v>1200</v>
       </c>
       <c r="K15" s="5" t="inlineStr">
         <is>
-          <t>AUD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="L15" s="10" t="n">
-        <v>269.59</v>
-      </c>
-      <c r="M15" s="10" t="n"/>
+        <v>1377.57</v>
+      </c>
+      <c r="M15" s="10" t="n">
+        <v>1520</v>
+      </c>
       <c r="N15" s="11">
         <f>IF(OR(L15="",M15=""),"",L15/M15)</f>
         <v/>
       </c>
       <c r="O15" s="5" t="inlineStr">
         <is>
-          <t>none - new tier</t>
+          <t>SEED</t>
         </is>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t>wholesale; floor; read from a snippet</t>
+          <t>single source; read from a snippet; re-prices lower tiers</t>
         </is>
       </c>
       <c r="Q15" s="3" t="inlineStr">
         <is>
-          <t>ETHERNET AU 250Mbps MRC (NBN Enterprise Ethernet retail, ex GST)</t>
+          <t>DIA 1000 Mbps MRC France (Orange Business FTTO dedicated fibre)</t>
         </is>
       </c>
       <c r="R15" s="5" t="inlineStr">
         <is>
-          <t>Swoop; COMPANY_PUBLISHED/SNIPPET_ONLY</t>
+          <t>myadsl.fr; TRADE_PRESS/SNIPPET_ONLY</t>
         </is>
       </c>
       <c r="S15" s="3" t="inlineStr">
         <is>
-          <t>Business Fibre 250/250 Mbps $399 per month</t>
+          <t>Offre intermédiaire: 1 Gb/s, SLA amélioré, support 24/7 – tarif mensuel approximatif: 1 200 €</t>
         </is>
       </c>
       <c r="T15" s="5" t="inlineStr">
         <is>
-          <t>https://www.swoop.com.au/business/enterprise-ethernet/</t>
+          <t>https://www.myadsl.fr/cout-ftto-orange-2025/</t>
         </is>
       </c>
       <c r="U15" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="V15" s="5" t="inlineStr">
         <is>
-          <t>woolworths</t>
+          <t>bnp-paribas</t>
         </is>
       </c>
       <c r="W15" s="12" t="n">
-        <v>-2472.04054054054</v>
+        <v>-106959.98274275</v>
       </c>
       <c r="X15" s="5" t="n">
-        <v>5</v>
+        <v>72</v>
       </c>
       <c r="Y15" s="3" t="inlineStr">
         <is>
-          <t>woolworths -2,472</t>
+          <t>bnp-paribas -29,777; siemens -26,800; capgemini -14,889</t>
         </is>
       </c>
       <c r="Z15" s="3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>500 Mbps at 1398 &gt; 1000 Mbps at 1378 USD</t>
         </is>
       </c>
       <c r="AA15" s="3" t="inlineStr">
         <is>
-          <t>woolworths 399 AUD</t>
+          <t>bnp-paribas ~1200 EUR</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>AU-ETHERNET-500-researched</t>
+          <t>GB-BROADBAND_HFC-200-researched</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>ETHERNET</t>
+          <t>BROADBAND_HFC</t>
         </is>
       </c>
       <c r="D16" s="5" t="n">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="E16" s="13" t="inlineStr">
         <is>
@@ -2451,7 +2447,7 @@
       </c>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>NBN Enterprise Ethernet retail, ex GST, 36-month: Vocus A$469, Swoop A$499.</t>
+          <t>Virgin Media Business Voom 200, published, ex VAT, 24-month.</t>
         </is>
       </c>
       <c r="H16" s="9">
@@ -2463,51 +2459,49 @@
         <v/>
       </c>
       <c r="J16" s="10" t="n">
-        <v>469</v>
+        <v>29.95</v>
       </c>
       <c r="K16" s="5" t="inlineStr">
         <is>
-          <t>AUD</t>
+          <t>GBP</t>
         </is>
       </c>
       <c r="L16" s="10" t="n">
-        <v>316.89</v>
-      </c>
-      <c r="M16" s="10" t="n">
-        <v>1288</v>
-      </c>
+        <v>40.13</v>
+      </c>
+      <c r="M16" s="10" t="n"/>
       <c r="N16" s="11">
         <f>IF(OR(L16="",M16=""),"",L16/M16)</f>
         <v/>
       </c>
       <c r="O16" s="5" t="inlineStr">
         <is>
-          <t>SEED</t>
+          <t>none - new tier</t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t>floor; read from a snippet</t>
+          <t>floor; read from a snippet; re-prices lower tiers</t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t>ETHERNET AU 500Mbps MRC (NBN Enterprise Ethernet retail, ex GST)</t>
+          <t>BROADBAND_HFC 200Mbps MRC (Virgin Media Business Voom 200)</t>
         </is>
       </c>
       <c r="R16" s="5" t="inlineStr">
         <is>
-          <t>Vocus; COMPANY_PUBLISHED/SNIPPET_ONLY</t>
+          <t>virginmediabusiness.co.uk; COMPANY_PUBLISHED/SNIPPET_ONLY</t>
         </is>
       </c>
       <c r="S16" s="3" t="inlineStr">
         <is>
-          <t>500/500Mbps Starting at $469 / per month (ex. GST)</t>
+          <t>Prices start from just £29.95 per month</t>
         </is>
       </c>
       <c r="T16" s="5" t="inlineStr">
         <is>
-          <t>https://www.vocus.com.au/enterprise/internet-and-networks/nbn-enterprise-ethernet</t>
+          <t>https://www.virginmediabusiness.co.uk/connectivity/internet-access/business-broadband/</t>
         </is>
       </c>
       <c r="U16" s="5" t="inlineStr">
@@ -2517,45 +2511,49 @@
       </c>
       <c r="V16" s="5" t="inlineStr">
         <is>
-          <t>woolworths</t>
+          <t>boots</t>
         </is>
       </c>
       <c r="W16" s="12" t="n">
-        <v>0</v>
+        <v>-421041.3935414713</v>
       </c>
       <c r="X16" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y16" s="3" t="inlineStr"/>
+        <v>5864</v>
+      </c>
+      <c r="Y16" s="3" t="inlineStr">
+        <is>
+          <t>tesco -269,489; boots -151,552</t>
+        </is>
+      </c>
       <c r="Z16" s="3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>100 Mbps at 80 &gt; 200 Mbps at 40 USD; 250 Mbps at 108 &gt; 400 Mbps at 47 USD; 500 Mbps at 140 &gt; 600 Mbps at 52 USD</t>
         </is>
       </c>
       <c r="AA16" s="3" t="inlineStr">
         <is>
-          <t>woolworths 469 AUD</t>
+          <t>boots 29.95 GBP</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>AU-ETHERNET-1000-researched</t>
+          <t>GB-BROADBAND_HFC-400-researched</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>ETHERNET</t>
+          <t>BROADBAND_HFC</t>
         </is>
       </c>
       <c r="D17" s="5" t="n">
-        <v>1000</v>
+        <v>400</v>
       </c>
       <c r="E17" s="13" t="inlineStr">
         <is>
@@ -2569,7 +2567,7 @@
       </c>
       <c r="G17" s="8" t="inlineStr">
         <is>
-          <t>NBN Enterprise Ethernet retail, ex GST, 36-month: Swoop and Vocus A$699, Telstra via Telair A$659.</t>
+          <t>Virgin Media Business Voom 400, published, ex VAT, 24-month.</t>
         </is>
       </c>
       <c r="H17" s="9">
@@ -2581,51 +2579,49 @@
         <v/>
       </c>
       <c r="J17" s="10" t="n">
-        <v>699</v>
+        <v>34.95</v>
       </c>
       <c r="K17" s="5" t="inlineStr">
         <is>
-          <t>AUD</t>
+          <t>GBP</t>
         </is>
       </c>
       <c r="L17" s="10" t="n">
-        <v>472.3</v>
-      </c>
-      <c r="M17" s="10" t="n">
-        <v>1450</v>
-      </c>
+        <v>46.83</v>
+      </c>
+      <c r="M17" s="10" t="n"/>
       <c r="N17" s="11">
         <f>IF(OR(L17="",M17=""),"",L17/M17)</f>
         <v/>
       </c>
       <c r="O17" s="5" t="inlineStr">
         <is>
-          <t>SEED</t>
+          <t>none - new tier</t>
         </is>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t>floor; read from a snippet</t>
+          <t>read from a snippet; re-prices lower tiers</t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr">
         <is>
-          <t>ETHERNET AU 1000Mbps MRC (NBN Enterprise Ethernet retail, ex GST)</t>
+          <t>BROADBAND_HFC 400Mbps MRC — Virgin Media Business Voom 400</t>
         </is>
       </c>
       <c r="R17" s="5" t="inlineStr">
         <is>
-          <t>Swoop; COMPANY_PUBLISHED/SNIPPET_ONLY</t>
+          <t>virginmediabusiness.co.uk; COMPANY_PUBLISHED/SNIPPET_ONLY</t>
         </is>
       </c>
       <c r="S17" s="3" t="inlineStr">
         <is>
-          <t>Business Fibre 1000/1000 Mbps $699 per month</t>
+          <t>Voom 400 | Download 400Mbps | £34.95 per month</t>
         </is>
       </c>
       <c r="T17" s="5" t="inlineStr">
         <is>
-          <t>https://www.swoop.com.au/business/enterprise-ethernet/</t>
+          <t>https://www.virginmediabusiness.co.uk/connectivity/internet-access/business-broadband/</t>
         </is>
       </c>
       <c r="U17" s="5" t="inlineStr">
@@ -2635,49 +2631,45 @@
       </c>
       <c r="V17" s="5" t="inlineStr">
         <is>
-          <t>woolworths</t>
+          <t>not recorded</t>
         </is>
       </c>
       <c r="W17" s="12" t="n">
-        <v>-304559.635439</v>
+        <v>-111641.2488303241</v>
       </c>
       <c r="X17" s="5" t="n">
-        <v>20</v>
+        <v>1916</v>
       </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
-          <t>rio-tinto -304,560</t>
+          <t>mcdonalds -87,810; deutsche-post-dhl -20,102; royal-mail -2,622</t>
         </is>
       </c>
       <c r="Z17" s="3" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="AA17" s="3" t="inlineStr">
-        <is>
-          <t>woolworths 699 AUD</t>
-        </is>
-      </c>
+          <t>100 Mbps at 80 &gt; 200 Mbps at 40 USD; 250 Mbps at 108 &gt; 400 Mbps at 47 USD; 500 Mbps at 140 &gt; 600 Mbps at 52 USD</t>
+        </is>
+      </c>
+      <c r="AA17" s="3" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>BE-BROADBAND_PON-150-researched</t>
+          <t>GB-BROADBAND_HFC-600-researched</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>BE</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>BROADBAND_PON</t>
+          <t>BROADBAND_HFC</t>
         </is>
       </c>
       <c r="D18" s="5" t="n">
-        <v>150</v>
+        <v>600</v>
       </c>
       <c r="E18" s="13" t="inlineStr">
         <is>
@@ -2691,7 +2683,7 @@
       </c>
       <c r="G18" s="8" t="inlineStr">
         <is>
-          <t>Proximus Business Go Fiber 150, the standard price after the 12-month promotion, ex VAT, read from the full page.</t>
+          <t>Virgin Media Business Voom 600, published, ex VAT, 24-month.</t>
         </is>
       </c>
       <c r="H18" s="9">
@@ -2703,15 +2695,15 @@
         <v/>
       </c>
       <c r="J18" s="10" t="n">
-        <v>60</v>
+        <v>38.95</v>
       </c>
       <c r="K18" s="5" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>GBP</t>
         </is>
       </c>
       <c r="L18" s="10" t="n">
-        <v>68.88</v>
+        <v>52.19</v>
       </c>
       <c r="M18" s="10" t="n"/>
       <c r="N18" s="11">
@@ -2725,37 +2717,37 @@
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t>promotional; single source</t>
+          <t>read from a snippet; re-prices lower tiers</t>
         </is>
       </c>
       <c r="Q18" s="3" t="inlineStr">
         <is>
-          <t>BROADBAND_PON 150 Mbps MRC (business shared fibre, Proximus Go Fiber)</t>
+          <t>BROADBAND_HFC 600Mbps MRC — Virgin Media Business Voom 600</t>
         </is>
       </c>
       <c r="R18" s="5" t="inlineStr">
         <is>
-          <t>Proximus (proximus.be); COMPANY_PUBLISHED/FULL_PAGE</t>
+          <t>virginmediabusiness.co.uk; COMPANY_PUBLISHED/SNIPPET_ONLY</t>
         </is>
       </c>
       <c r="S18" s="3" t="inlineStr">
         <is>
-          <t>Business Internet Go Fiber 150 Mbps: €45/month during 12 months, then €60/month</t>
+          <t>Voom 600 | Download 600Mbps | £38.95 per month</t>
         </is>
       </c>
       <c r="T18" s="5" t="inlineStr">
         <is>
-          <t>https://www.proximus.be/en/business/internet-subscription</t>
+          <t>https://www.virginmediabusiness.co.uk/connectivity/internet-access/business-broadband/</t>
         </is>
       </c>
       <c r="U18" s="5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="V18" s="5" t="inlineStr">
         <is>
-          <t>bnp-paribas</t>
+          <t>not recorded</t>
         </is>
       </c>
       <c r="W18" s="12" t="n">
@@ -2767,29 +2759,25 @@
       <c r="Y18" s="3" t="inlineStr"/>
       <c r="Z18" s="3" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="AA18" s="3" t="inlineStr">
-        <is>
-          <t>bnp-paribas 60 EUR</t>
-        </is>
-      </c>
+          <t>100 Mbps at 80 &gt; 200 Mbps at 40 USD; 250 Mbps at 108 &gt; 400 Mbps at 47 USD; 500 Mbps at 140 &gt; 600 Mbps at 52 USD</t>
+        </is>
+      </c>
+      <c r="AA18" s="3" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>FR-DIA-1000-researched</t>
+          <t>GB-BROADBAND_HFC-1000-researched</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>DIA</t>
+          <t>BROADBAND_HFC</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
@@ -2807,7 +2795,7 @@
       </c>
       <c r="G19" s="8" t="inlineStr">
         <is>
-          <t>Orange Business FTTO 1 Gbps, approximately EUR 1,200 per a trade-press snippet. It sits close to the seed (0.91x).</t>
+          <t>Virgin Media Business Voom Gig1, published, ex VAT, 24-month.</t>
         </is>
       </c>
       <c r="H19" s="9">
@@ -2819,18 +2807,18 @@
         <v/>
       </c>
       <c r="J19" s="10" t="n">
-        <v>1200</v>
+        <v>43.95</v>
       </c>
       <c r="K19" s="5" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>GBP</t>
         </is>
       </c>
       <c r="L19" s="10" t="n">
-        <v>1377.57</v>
+        <v>58.89</v>
       </c>
       <c r="M19" s="10" t="n">
-        <v>1520</v>
+        <v>176</v>
       </c>
       <c r="N19" s="11">
         <f>IF(OR(L19="",M19=""),"",L19/M19)</f>
@@ -2843,65 +2831,61 @@
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t>single source; read from a snippet; re-prices lower tiers</t>
+          <t>read from a snippet; re-prices lower tiers</t>
         </is>
       </c>
       <c r="Q19" s="3" t="inlineStr">
         <is>
-          <t>DIA 1000 Mbps MRC France (Orange Business FTTO dedicated fibre)</t>
+          <t>BROADBAND_HFC 1000Mbps MRC — Virgin Media Business Voom Gig1</t>
         </is>
       </c>
       <c r="R19" s="5" t="inlineStr">
         <is>
-          <t>myadsl.fr; TRADE_PRESS/SNIPPET_ONLY</t>
+          <t>virginmediabusiness.co.uk; COMPANY_PUBLISHED/SNIPPET_ONLY</t>
         </is>
       </c>
       <c r="S19" s="3" t="inlineStr">
         <is>
-          <t>Offre intermédiaire: 1 Gb/s, SLA amélioré, support 24/7 – tarif mensuel approximatif: 1 200 €</t>
+          <t>Voom Gig1 | Download 1000Mbps | £43.95 per month</t>
         </is>
       </c>
       <c r="T19" s="5" t="inlineStr">
         <is>
-          <t>https://www.myadsl.fr/cout-ftto-orange-2025/</t>
+          <t>https://www.virginmediabusiness.co.uk/connectivity/internet-access/business-broadband/</t>
         </is>
       </c>
       <c r="U19" s="5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="V19" s="5" t="inlineStr">
         <is>
-          <t>bnp-paribas</t>
+          <t>not recorded</t>
         </is>
       </c>
       <c r="W19" s="12" t="n">
-        <v>-106959.98274275</v>
+        <v>0</v>
       </c>
       <c r="X19" s="5" t="n">
-        <v>72</v>
-      </c>
-      <c r="Y19" s="3" t="inlineStr">
-        <is>
-          <t>bnp-paribas -29,777; siemens -26,800; capgemini -14,889</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Y19" s="3" t="inlineStr"/>
       <c r="Z19" s="3" t="inlineStr">
         <is>
-          <t>500 Mbps at 1398 &gt; 1000 Mbps at 1378 USD</t>
+          <t>100 Mbps at 80 &gt; 200 Mbps at 40 USD; 250 Mbps at 108 &gt; 400 Mbps at 47 USD; 500 Mbps at 140 &gt; 600 Mbps at 52 USD</t>
         </is>
       </c>
       <c r="AA19" s="3" t="inlineStr">
         <is>
-          <t>bnp-paribas ~1200 EUR</t>
+          <t>boots 53.95 GBP</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>GB-BROADBAND_HFC-200-researched</t>
+          <t>GB-BROADBAND_HFC-2000-researched</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
@@ -2915,7 +2899,7 @@
         </is>
       </c>
       <c r="D20" s="5" t="n">
-        <v>200</v>
+        <v>2000</v>
       </c>
       <c r="E20" s="13" t="inlineStr">
         <is>
@@ -2929,7 +2913,7 @@
       </c>
       <c r="G20" s="8" t="inlineStr">
         <is>
-          <t>Virgin Media Business Voom 200, published, ex VAT, 24-month.</t>
+          <t>Virgin Media Business Voom Gig2, published, ex VAT, 24-month.</t>
         </is>
       </c>
       <c r="H20" s="9">
@@ -2941,7 +2925,7 @@
         <v/>
       </c>
       <c r="J20" s="10" t="n">
-        <v>29.95</v>
+        <v>83.95</v>
       </c>
       <c r="K20" s="5" t="inlineStr">
         <is>
@@ -2949,7 +2933,7 @@
         </is>
       </c>
       <c r="L20" s="10" t="n">
-        <v>40.13</v>
+        <v>112.49</v>
       </c>
       <c r="M20" s="10" t="n"/>
       <c r="N20" s="11">
@@ -2963,29 +2947,21 @@
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t>floor; read from a snippet; re-prices lower tiers</t>
-        </is>
-      </c>
-      <c r="Q20" s="3" t="inlineStr">
-        <is>
-          <t>BROADBAND_HFC 200Mbps MRC (Virgin Media Business Voom 200)</t>
-        </is>
-      </c>
+          <t>floor; single source; re-prices lower tiers</t>
+        </is>
+      </c>
+      <c r="Q20" s="3" t="inlineStr"/>
       <c r="R20" s="5" t="inlineStr">
         <is>
-          <t>virginmediabusiness.co.uk; COMPANY_PUBLISHED/SNIPPET_ONLY</t>
+          <t>run narrative (the disposition was replaced)</t>
         </is>
       </c>
       <c r="S20" s="3" t="inlineStr">
         <is>
-          <t>Prices start from just £29.95 per month</t>
-        </is>
-      </c>
-      <c r="T20" s="5" t="inlineStr">
-        <is>
-          <t>https://www.virginmediabusiness.co.uk/connectivity/internet-access/business-broadband/</t>
-        </is>
-      </c>
+          <t>e DIA. (2) BROADBAND_HFC: Virgin Media Business publishes HFC/cable broadband: Voom 200 (200 Mbps) from £29.95/month, Voom 400 (400 Mbps) from £34.95/month, Voom Gig1 (1 Gbps) from £43.95/month, Voom Gig2 (2 Gbps) from £83.95/month, all ex-VAT 24-month contract, October 2026. New symmetric XGS-PON (BROADBAND_PON) Full Fibre X plans: 200 Mbps from £39.95/month, 1 Gbps from £53.95/mon</t>
+        </is>
+      </c>
+      <c r="T20" s="5" t="inlineStr"/>
       <c r="U20" s="5" t="inlineStr">
         <is>
           <t>2026</t>
@@ -2993,35 +2969,27 @@
       </c>
       <c r="V20" s="5" t="inlineStr">
         <is>
-          <t>boots</t>
+          <t>royal-mail</t>
         </is>
       </c>
       <c r="W20" s="12" t="n">
-        <v>-421041.3935414713</v>
+        <v>0</v>
       </c>
       <c r="X20" s="5" t="n">
-        <v>5864</v>
-      </c>
-      <c r="Y20" s="3" t="inlineStr">
-        <is>
-          <t>tesco -269,489; boots -151,552</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Y20" s="3" t="inlineStr"/>
       <c r="Z20" s="3" t="inlineStr">
         <is>
           <t>100 Mbps at 80 &gt; 200 Mbps at 40 USD; 250 Mbps at 108 &gt; 400 Mbps at 47 USD; 500 Mbps at 140 &gt; 600 Mbps at 52 USD</t>
         </is>
       </c>
-      <c r="AA20" s="3" t="inlineStr">
-        <is>
-          <t>boots 29.95 GBP</t>
-        </is>
-      </c>
+      <c r="AA20" s="3" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>GB-BROADBAND_HFC-400-researched</t>
+          <t>GB-BROADBAND_PON-100-researched</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
@@ -3031,11 +2999,11 @@
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>BROADBAND_HFC</t>
+          <t>BROADBAND_PON</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="E21" s="13" t="inlineStr">
         <is>
@@ -3049,7 +3017,7 @@
       </c>
       <c r="G21" s="8" t="inlineStr">
         <is>
-          <t>Virgin Media Business Voom 400, published, ex VAT, 24-month.</t>
+          <t>BT Business Full Fibre 100 at GBP 35 a month ex VAT, published (verified May 2026).</t>
         </is>
       </c>
       <c r="H21" s="9">
@@ -3061,7 +3029,7 @@
         <v/>
       </c>
       <c r="J21" s="10" t="n">
-        <v>34.95</v>
+        <v>35</v>
       </c>
       <c r="K21" s="5" t="inlineStr">
         <is>
@@ -3069,89 +3037,89 @@
         </is>
       </c>
       <c r="L21" s="10" t="n">
-        <v>46.83</v>
-      </c>
-      <c r="M21" s="10" t="n"/>
+        <v>46.9</v>
+      </c>
+      <c r="M21" s="10" t="n">
+        <v>70</v>
+      </c>
       <c r="N21" s="11">
         <f>IF(OR(L21="",M21=""),"",L21/M21)</f>
         <v/>
       </c>
       <c r="O21" s="5" t="inlineStr">
         <is>
-          <t>none - new tier</t>
+          <t>SEED</t>
         </is>
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
-          <t>read from a snippet; re-prices lower tiers</t>
-        </is>
-      </c>
-      <c r="Q21" s="3" t="inlineStr">
-        <is>
-          <t>BROADBAND_HFC 400Mbps MRC — Virgin Media Business Voom 400</t>
-        </is>
-      </c>
+          <t>floor; single source; re-prices lower tiers</t>
+        </is>
+      </c>
+      <c r="Q21" s="3" t="inlineStr"/>
       <c r="R21" s="5" t="inlineStr">
         <is>
-          <t>virginmediabusiness.co.uk; COMPANY_PUBLISHED/SNIPPET_ONLY</t>
+          <t>run narrative (the disposition was replaced)</t>
         </is>
       </c>
       <c r="S21" s="3" t="inlineStr">
         <is>
-          <t>Voom 400 | Download 400Mbps | £34.95 per month</t>
-        </is>
-      </c>
-      <c r="T21" s="5" t="inlineStr">
-        <is>
-          <t>https://www.virginmediabusiness.co.uk/connectivity/internet-access/business-broadband/</t>
-        </is>
-      </c>
+          <t xml:space="preserve"> €700–€1,300/month (≈USD 765–1,420). The model's assumed GB MPLS 100 Mbps of USD 750–1,250/month is within this band.
+**GB — BROADBAND_PON / HFC**
+BT Business published tariffs (verified May 2026): Full Fibre 100 Mbps £35/month ex-VAT; Full Fibre 500 Mbps £55/month; Full Fibre 900 Mbps £65/month. Virgin Media Business (cable/HFC): from £29.95/month. Vodafone Business entry-level</t>
+        </is>
+      </c>
+      <c r="T21" s="5" t="inlineStr"/>
       <c r="U21" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="V21" s="5" t="inlineStr">
         <is>
-          <t>not recorded</t>
+          <t>saint-gobain</t>
         </is>
       </c>
       <c r="W21" s="12" t="n">
-        <v>-111641.2488303241</v>
+        <v>-742283.2166248914</v>
       </c>
       <c r="X21" s="5" t="n">
-        <v>1916</v>
+        <v>2847</v>
       </c>
       <c r="Y21" s="3" t="inlineStr">
         <is>
-          <t>mcdonalds -87,810; deutsche-post-dhl -20,102; royal-mail -2,622</t>
+          <t>iberdrola -243,421; network-rail -216,375; nhs-england -161,315</t>
         </is>
       </c>
       <c r="Z21" s="3" t="inlineStr">
         <is>
-          <t>100 Mbps at 80 &gt; 200 Mbps at 40 USD; 250 Mbps at 108 &gt; 400 Mbps at 47 USD; 500 Mbps at 140 &gt; 600 Mbps at 52 USD</t>
-        </is>
-      </c>
-      <c r="AA21" s="3" t="inlineStr"/>
+          <t>50 Mbps at 58 &gt; 100 Mbps at 47 USD</t>
+        </is>
+      </c>
+      <c r="AA21" s="3" t="inlineStr">
+        <is>
+          <t>deutsche-post-dhl 29 GBP</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>GB-BROADBAND_HFC-600-researched</t>
+          <t>NL-DIA-200-researched</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>NL</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>BROADBAND_HFC</t>
+          <t>DIA</t>
         </is>
       </c>
       <c r="D22" s="5" t="n">
-        <v>600</v>
+        <v>200</v>
       </c>
       <c r="E22" s="13" t="inlineStr">
         <is>
@@ -3165,7 +3133,7 @@
       </c>
       <c r="G22" s="8" t="inlineStr">
         <is>
-          <t>Virgin Media Business Voom 600, published, ex VAT, 24-month.</t>
+          <t>Eurofiber DIA 200 from about EUR 348, as quoted by a broker; a carrier's indicative business price. No circuit in the set uses it.</t>
         </is>
       </c>
       <c r="H22" s="9">
@@ -3177,15 +3145,15 @@
         <v/>
       </c>
       <c r="J22" s="10" t="n">
-        <v>38.95</v>
+        <v>348</v>
       </c>
       <c r="K22" s="5" t="inlineStr">
         <is>
-          <t>GBP</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="L22" s="10" t="n">
-        <v>52.19</v>
+        <v>399.49</v>
       </c>
       <c r="M22" s="10" t="n"/>
       <c r="N22" s="11">
@@ -3199,37 +3167,37 @@
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
-          <t>read from a snippet; re-prices lower tiers</t>
+          <t>floor; single source; re-prices lower tiers</t>
         </is>
       </c>
       <c r="Q22" s="3" t="inlineStr">
         <is>
-          <t>BROADBAND_HFC 600Mbps MRC — Virgin Media Business Voom 600</t>
+          <t>DIA MRC 200 Mbps (NL, Eurofiber)</t>
         </is>
       </c>
       <c r="R22" s="5" t="inlineStr">
         <is>
-          <t>virginmediabusiness.co.uk; COMPANY_PUBLISHED/SNIPPET_ONLY</t>
+          <t>Connected Networks; COMPANY_PUBLISHED/FULL_PAGE</t>
         </is>
       </c>
       <c r="S22" s="3" t="inlineStr">
         <is>
-          <t>Voom 600 | Download 600Mbps | £38.95 per month</t>
+          <t>DIA pricing via Eurofiber starts from approximately €348/month for 200Mbps.</t>
         </is>
       </c>
       <c r="T22" s="5" t="inlineStr">
         <is>
-          <t>https://www.virginmediabusiness.co.uk/connectivity/internet-access/business-broadband/</t>
+          <t>https://www.connectednetworks.io/countries/holland-the-netherlands-business-internet-connectivity</t>
         </is>
       </c>
       <c r="U22" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="V22" s="5" t="inlineStr">
         <is>
-          <t>not recorded</t>
+          <t>ahold-delhaize</t>
         </is>
       </c>
       <c r="W22" s="12" t="n">
@@ -3241,29 +3209,33 @@
       <c r="Y22" s="3" t="inlineStr"/>
       <c r="Z22" s="3" t="inlineStr">
         <is>
-          <t>100 Mbps at 80 &gt; 200 Mbps at 40 USD; 250 Mbps at 108 &gt; 400 Mbps at 47 USD; 500 Mbps at 140 &gt; 600 Mbps at 52 USD</t>
-        </is>
-      </c>
-      <c r="AA22" s="3" t="inlineStr"/>
+          <t>100 Mbps at 500 &gt; 200 Mbps at 399 USD</t>
+        </is>
+      </c>
+      <c r="AA22" s="3" t="inlineStr">
+        <is>
+          <t>ahold-delhaize 348 EUR; deutsche-post-dhl 348 EUR; douglas 348 EUR; maersk 348 EUR; shell ~€348 EUR; shell 348 EUR; unilever 348 EUR; unilever 348 EUR</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>GB-BROADBAND_HFC-1000-researched</t>
+          <t>SG-BROADBAND_PON-500-researched</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>BROADBAND_HFC</t>
+          <t>BROADBAND_PON</t>
         </is>
       </c>
       <c r="D23" s="5" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="E23" s="13" t="inlineStr">
         <is>
@@ -3277,7 +3249,7 @@
       </c>
       <c r="G23" s="8" t="inlineStr">
         <is>
-          <t>Virgin Media Business Voom Gig1, published, ex VAT, 24-month.</t>
+          <t>Business dynamic fibre on a 24-month contract: StarHub S$109, Singtel S$118.</t>
         </is>
       </c>
       <c r="H23" s="9">
@@ -3289,18 +3261,18 @@
         <v/>
       </c>
       <c r="J23" s="10" t="n">
-        <v>43.95</v>
+        <v>109</v>
       </c>
       <c r="K23" s="5" t="inlineStr">
         <is>
-          <t>GBP</t>
+          <t>SGD</t>
         </is>
       </c>
       <c r="L23" s="10" t="n">
-        <v>58.89</v>
+        <v>85.16</v>
       </c>
       <c r="M23" s="10" t="n">
-        <v>176</v>
+        <v>115</v>
       </c>
       <c r="N23" s="11">
         <f>IF(OR(L23="",M23=""),"",L23/M23)</f>
@@ -3313,75 +3285,79 @@
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t>read from a snippet; re-prices lower tiers</t>
+          <t>single source; read from a snippet; re-prices lower tiers</t>
         </is>
       </c>
       <c r="Q23" s="3" t="inlineStr">
         <is>
-          <t>BROADBAND_HFC 1000Mbps MRC — Virgin Media Business Voom Gig1</t>
+          <t>BROADBAND_PON 500 Mbps MRC business dynamic — Singapore (Singtel)</t>
         </is>
       </c>
       <c r="R23" s="5" t="inlineStr">
         <is>
-          <t>virginmediabusiness.co.uk; COMPANY_PUBLISHED/SNIPPET_ONLY</t>
+          <t>DollarsAndSense.sg; AGGREGATOR/SNIPPET_ONLY</t>
         </is>
       </c>
       <c r="S23" s="3" t="inlineStr">
         <is>
-          <t>Voom Gig1 | Download 1000Mbps | £43.95 per month</t>
+          <t>Singtel · $118 · $178 [for 500Mbps and 1Gbps dynamic broadband, 24-month contract]</t>
         </is>
       </c>
       <c r="T23" s="5" t="inlineStr">
         <is>
-          <t>https://www.virginmediabusiness.co.uk/connectivity/internet-access/business-broadband/</t>
+          <t>https://dollarsandsense.sg/price-guide-to-business-broadband-plans-for-offices-in-singapore/</t>
         </is>
       </c>
       <c r="U23" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="V23" s="5" t="inlineStr">
         <is>
-          <t>not recorded</t>
+          <t>dbs</t>
         </is>
       </c>
       <c r="W23" s="12" t="n">
-        <v>0</v>
+        <v>-2199.09195</v>
       </c>
       <c r="X23" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y23" s="3" t="inlineStr"/>
+        <v>36</v>
+      </c>
+      <c r="Y23" s="3" t="inlineStr">
+        <is>
+          <t>dbs -2,199</t>
+        </is>
+      </c>
       <c r="Z23" s="3" t="inlineStr">
         <is>
-          <t>100 Mbps at 80 &gt; 200 Mbps at 40 USD; 250 Mbps at 108 &gt; 400 Mbps at 47 USD; 500 Mbps at 140 &gt; 600 Mbps at 52 USD</t>
+          <t>250 Mbps at 91 &gt; 500 Mbps at 85 USD</t>
         </is>
       </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
-          <t>boots 53.95 GBP</t>
+          <t>dbs 118 SGD; dbs 109 SGD</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>GB-BROADBAND_HFC-2000-researched</t>
+          <t>SG-BROADBAND_PON-1000-researched</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>BROADBAND_HFC</t>
+          <t>BROADBAND_PON</t>
         </is>
       </c>
       <c r="D24" s="5" t="n">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="E24" s="13" t="inlineStr">
         <is>
@@ -3395,7 +3371,7 @@
       </c>
       <c r="G24" s="8" t="inlineStr">
         <is>
-          <t>Virgin Media Business Voom Gig2, published, ex VAT, 24-month.</t>
+          <t>Business dynamic fibre on a 24-month contract: Singtel S$178, StarHub S$174.</t>
         </is>
       </c>
       <c r="H24" s="9">
@@ -3407,85 +3383,103 @@
         <v/>
       </c>
       <c r="J24" s="10" t="n">
-        <v>83.95</v>
+        <v>178</v>
       </c>
       <c r="K24" s="5" t="inlineStr">
         <is>
-          <t>GBP</t>
+          <t>SGD</t>
         </is>
       </c>
       <c r="L24" s="10" t="n">
-        <v>112.49</v>
-      </c>
-      <c r="M24" s="10" t="n"/>
+        <v>139.06</v>
+      </c>
+      <c r="M24" s="10" t="n">
+        <v>149</v>
+      </c>
       <c r="N24" s="11">
         <f>IF(OR(L24="",M24=""),"",L24/M24)</f>
         <v/>
       </c>
       <c r="O24" s="5" t="inlineStr">
         <is>
-          <t>none - new tier</t>
+          <t>SEED</t>
         </is>
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t>floor; single source; re-prices lower tiers</t>
-        </is>
-      </c>
-      <c r="Q24" s="3" t="inlineStr"/>
+          <t>single source; read from a snippet; re-prices lower tiers</t>
+        </is>
+      </c>
+      <c r="Q24" s="3" t="inlineStr">
+        <is>
+          <t>BROADBAND_PON 1000 Mbps MRC business dynamic — Singapore (Singtel)</t>
+        </is>
+      </c>
       <c r="R24" s="5" t="inlineStr">
         <is>
-          <t>run narrative (the disposition was replaced)</t>
+          <t>DollarsAndSense.sg; AGGREGATOR/SNIPPET_ONLY</t>
         </is>
       </c>
       <c r="S24" s="3" t="inlineStr">
         <is>
-          <t>e DIA. (2) BROADBAND_HFC: Virgin Media Business publishes HFC/cable broadband: Voom 200 (200 Mbps) from £29.95/month, Voom 400 (400 Mbps) from £34.95/month, Voom Gig1 (1 Gbps) from £43.95/month, Voom Gig2 (2 Gbps) from £83.95/month, all ex-VAT 24-month contract, October 2026. New symmetric XGS-PON (BROADBAND_PON) Full Fibre X plans: 200 Mbps from £39.95/month, 1 Gbps from £53.95/mon</t>
-        </is>
-      </c>
-      <c r="T24" s="5" t="inlineStr"/>
+          <t>Singtel · $118 · $178 [for 500Mbps and 1Gbps dynamic broadband, 24-month contract]</t>
+        </is>
+      </c>
+      <c r="T24" s="5" t="inlineStr">
+        <is>
+          <t>https://dollarsandsense.sg/price-guide-to-business-broadband-plans-for-offices-in-singapore/</t>
+        </is>
+      </c>
       <c r="U24" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="V24" s="5" t="inlineStr">
         <is>
-          <t>royal-mail</t>
+          <t>dbs</t>
         </is>
       </c>
       <c r="W24" s="12" t="n">
-        <v>0</v>
+        <v>-320.98946125</v>
       </c>
       <c r="X24" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y24" s="3" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="Y24" s="3" t="inlineStr">
+        <is>
+          <t>novartis -321</t>
+        </is>
+      </c>
       <c r="Z24" s="3" t="inlineStr">
         <is>
-          <t>100 Mbps at 80 &gt; 200 Mbps at 40 USD; 250 Mbps at 108 &gt; 400 Mbps at 47 USD; 500 Mbps at 140 &gt; 600 Mbps at 52 USD</t>
-        </is>
-      </c>
-      <c r="AA24" s="3" t="inlineStr"/>
+          <t>250 Mbps at 91 &gt; 500 Mbps at 85 USD</t>
+        </is>
+      </c>
+      <c r="AA24" s="3" t="inlineStr">
+        <is>
+          <t>dbs 178 SGD; dbs 53.89 SGD</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>GB-BROADBAND_PON-100-researched</t>
+          <t>SG-DIA-10000-researched</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>BROADBAND_PON</t>
+          <t>DIA</t>
         </is>
       </c>
       <c r="D25" s="5" t="n">
-        <v>100</v>
+        <v>10000</v>
       </c>
       <c r="E25" s="13" t="inlineStr">
         <is>
@@ -3499,7 +3493,7 @@
       </c>
       <c r="G25" s="8" t="inlineStr">
         <is>
-          <t>BT Business Full Fibre 100 at GBP 35 a month ex VAT, published (verified May 2026).</t>
+          <t>TeleGeography's survey-based 10 GigE DIA benchmark for Singapore. No circuit in the set uses it.</t>
         </is>
       </c>
       <c r="H25" s="9">
@@ -3511,97 +3505,97 @@
         <v/>
       </c>
       <c r="J25" s="10" t="n">
-        <v>35</v>
+        <v>4500</v>
       </c>
       <c r="K25" s="5" t="inlineStr">
         <is>
-          <t>GBP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="L25" s="10" t="n">
-        <v>46.9</v>
-      </c>
-      <c r="M25" s="10" t="n">
-        <v>70</v>
-      </c>
+        <v>4500</v>
+      </c>
+      <c r="M25" s="10" t="n"/>
       <c r="N25" s="11">
         <f>IF(OR(L25="",M25=""),"",L25/M25)</f>
         <v/>
       </c>
       <c r="O25" s="5" t="inlineStr">
         <is>
-          <t>SEED</t>
+          <t>none - new tier</t>
         </is>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t>floor; single source; re-prices lower tiers</t>
-        </is>
-      </c>
-      <c r="Q25" s="3" t="inlineStr"/>
+          <t>single source; read from a snippet</t>
+        </is>
+      </c>
+      <c r="Q25" s="3" t="inlineStr">
+        <is>
+          <t>DIA 10000 Mbps (10 GigE) MRC — SG (TeleGeography 2026)</t>
+        </is>
+      </c>
       <c r="R25" s="5" t="inlineStr">
         <is>
-          <t>run narrative (the disposition was replaced)</t>
+          <t>TeleGeography; TRADE_PRESS/SNIPPET_ONLY</t>
         </is>
       </c>
       <c r="S25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> €700–€1,300/month (≈USD 765–1,420). The model's assumed GB MPLS 100 Mbps of USD 750–1,250/month is within this band.
-**GB — BROADBAND_PON / HFC**
-BT Business published tariffs (verified May 2026): Full Fibre 100 Mbps £35/month ex-VAT; Full Fibre 500 Mbps £55/month; Full Fibre 900 Mbps £65/month. Virgin Media Business (cable/HFC): from £29.95/month. Vodafone Business entry-level</t>
-        </is>
-      </c>
-      <c r="T25" s="5" t="inlineStr"/>
+          <t>$4,500 for 10 GigE</t>
+        </is>
+      </c>
+      <c r="T25" s="5" t="inlineStr">
+        <is>
+          <t>https://resources.telegeography.com/dia-pricing-in-asia-and-oceania</t>
+        </is>
+      </c>
       <c r="U25" s="5" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="V25" s="5" t="inlineStr">
         <is>
-          <t>saint-gobain</t>
+          <t>maersk</t>
         </is>
       </c>
       <c r="W25" s="12" t="n">
-        <v>-742283.2166248914</v>
+        <v>0</v>
       </c>
       <c r="X25" s="5" t="n">
-        <v>2847</v>
-      </c>
-      <c r="Y25" s="3" t="inlineStr">
-        <is>
-          <t>iberdrola -243,421; network-rail -216,375; nhs-england -161,315</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Y25" s="3" t="inlineStr"/>
       <c r="Z25" s="3" t="inlineStr">
         <is>
-          <t>50 Mbps at 58 &gt; 100 Mbps at 47 USD</t>
+          <t>no</t>
         </is>
       </c>
       <c r="AA25" s="3" t="inlineStr">
         <is>
-          <t>deutsche-post-dhl 29 GBP</t>
+          <t>dbs 4500 USD; maersk 4500 USD</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>NL-DIA-200-researched</t>
+          <t>US-BROADBAND_HFC-100-researched</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>NL</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>DIA</t>
+          <t>BROADBAND_HFC</t>
         </is>
       </c>
       <c r="D26" s="5" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="E26" s="13" t="inlineStr">
         <is>
@@ -3615,66 +3609,66 @@
       </c>
       <c r="G26" s="8" t="inlineStr">
         <is>
-          <t>Eurofiber DIA 200 from about EUR 348, as quoted by a broker; a carrier's indicative business price. No circuit in the set uses it.</t>
-        </is>
-      </c>
-      <c r="H26" s="9">
-        <f>J26*0.75</f>
-        <v/>
-      </c>
-      <c r="I26" s="9">
-        <f>J26*1.25</f>
-        <v/>
+          <t>Lightyear transaction dataset, median of US business broadband at 100 Mbps; the band is its 10th-90th percentile.</t>
+        </is>
+      </c>
+      <c r="H26" s="9" t="n">
+        <v>60</v>
+      </c>
+      <c r="I26" s="9" t="n">
+        <v>175</v>
       </c>
       <c r="J26" s="10" t="n">
-        <v>348</v>
+        <v>100</v>
       </c>
       <c r="K26" s="5" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="L26" s="10" t="n">
-        <v>399.49</v>
-      </c>
-      <c r="M26" s="10" t="n"/>
+        <v>100</v>
+      </c>
+      <c r="M26" s="10" t="n">
+        <v>120</v>
+      </c>
       <c r="N26" s="11">
         <f>IF(OR(L26="",M26=""),"",L26/M26)</f>
         <v/>
       </c>
       <c r="O26" s="5" t="inlineStr">
         <is>
-          <t>none - new tier</t>
+          <t>SEED</t>
         </is>
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
-          <t>floor; single source; re-prices lower tiers</t>
+          <t>re-prices lower tiers</t>
         </is>
       </c>
       <c r="Q26" s="3" t="inlineStr">
         <is>
-          <t>DIA MRC 200 Mbps (NL, Eurofiber)</t>
+          <t>BROADBAND_HFC 100 Mbps MRC median</t>
         </is>
       </c>
       <c r="R26" s="5" t="inlineStr">
         <is>
-          <t>Connected Networks; COMPANY_PUBLISHED/FULL_PAGE</t>
+          <t>Lightyear; AGGREGATOR/FULL_PAGE</t>
         </is>
       </c>
       <c r="S26" s="3" t="inlineStr">
         <is>
-          <t>DIA pricing via Eurofiber starts from approximately €348/month for 200Mbps.</t>
+          <t>100 Mbps | $60 | $100 | $175</t>
         </is>
       </c>
       <c r="T26" s="5" t="inlineStr">
         <is>
-          <t>https://www.connectednetworks.io/countries/holland-the-netherlands-business-internet-connectivity</t>
+          <t>https://lightyear.ai/resources/dedicated-internet-access-dia-ultimate-pricing-guide</t>
         </is>
       </c>
       <c r="U26" s="5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025-2026</t>
         </is>
       </c>
       <c r="V26" s="5" t="inlineStr">
@@ -3683,37 +3677,41 @@
         </is>
       </c>
       <c r="W26" s="12" t="n">
-        <v>0</v>
+        <v>-6522.79808</v>
       </c>
       <c r="X26" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y26" s="3" t="inlineStr"/>
+        <v>30</v>
+      </c>
+      <c r="Y26" s="3" t="inlineStr">
+        <is>
+          <t>maersk -3,696; ahold-delhaize -2,174; fresenius -435</t>
+        </is>
+      </c>
       <c r="Z26" s="3" t="inlineStr">
         <is>
-          <t>100 Mbps at 500 &gt; 200 Mbps at 399 USD</t>
+          <t>250 Mbps at 162 &gt; 500 Mbps at 110 USD</t>
         </is>
       </c>
       <c r="AA26" s="3" t="inlineStr">
         <is>
-          <t>ahold-delhaize 348 EUR; deutsche-post-dhl 348 EUR; douglas 348 EUR; maersk 348 EUR; shell ~€348 EUR; shell 348 EUR; unilever 348 EUR; unilever 348 EUR</t>
+          <t>ahold-delhaize 100 USD; ups 100 USD</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>SG-BROADBAND_PON-500-researched</t>
+          <t>US-BROADBAND_HFC-500-researched</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>BROADBAND_PON</t>
+          <t>BROADBAND_HFC</t>
         </is>
       </c>
       <c r="D27" s="5" t="n">
@@ -3731,30 +3729,28 @@
       </c>
       <c r="G27" s="8" t="inlineStr">
         <is>
-          <t>Business dynamic fibre on a 24-month contract: StarHub S$109, Singtel S$118.</t>
-        </is>
-      </c>
-      <c r="H27" s="9">
-        <f>J27*0.75</f>
-        <v/>
-      </c>
-      <c r="I27" s="9">
-        <f>J27*1.25</f>
-        <v/>
+          <t>Lightyear transaction dataset, median at 500 Mbps; the band is its 10th-90th percentile.</t>
+        </is>
+      </c>
+      <c r="H27" s="9" t="n">
+        <v>65</v>
+      </c>
+      <c r="I27" s="9" t="n">
+        <v>212</v>
       </c>
       <c r="J27" s="10" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="K27" s="5" t="inlineStr">
         <is>
-          <t>SGD</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="L27" s="10" t="n">
-        <v>85.16</v>
+        <v>110</v>
       </c>
       <c r="M27" s="10" t="n">
-        <v>115</v>
+        <v>208</v>
       </c>
       <c r="N27" s="11">
         <f>IF(OR(L27="",M27=""),"",L27/M27)</f>
@@ -3767,75 +3763,75 @@
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
-          <t>single source; read from a snippet; re-prices lower tiers</t>
+          <t>re-prices lower tiers</t>
         </is>
       </c>
       <c r="Q27" s="3" t="inlineStr">
         <is>
-          <t>BROADBAND_PON 500 Mbps MRC business dynamic — Singapore (Singtel)</t>
+          <t>BROADBAND_HFC/PON 500 Mbps MRC median</t>
         </is>
       </c>
       <c r="R27" s="5" t="inlineStr">
         <is>
-          <t>DollarsAndSense.sg; AGGREGATOR/SNIPPET_ONLY</t>
+          <t>Lightyear; AGGREGATOR/FULL_PAGE</t>
         </is>
       </c>
       <c r="S27" s="3" t="inlineStr">
         <is>
-          <t>Singtel · $118 · $178 [for 500Mbps and 1Gbps dynamic broadband, 24-month contract]</t>
+          <t>500 Mbps | $65 | $110 | $212</t>
         </is>
       </c>
       <c r="T27" s="5" t="inlineStr">
         <is>
-          <t>https://dollarsandsense.sg/price-guide-to-business-broadband-plans-for-offices-in-singapore/</t>
+          <t>https://lightyear.ai/resources/dedicated-internet-access-dia-ultimate-pricing-guide</t>
         </is>
       </c>
       <c r="U27" s="5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025-2026</t>
         </is>
       </c>
       <c r="V27" s="5" t="inlineStr">
         <is>
-          <t>dbs</t>
+          <t>ahold-delhaize</t>
         </is>
       </c>
       <c r="W27" s="12" t="n">
-        <v>-2199.09195</v>
+        <v>-13448332.818288</v>
       </c>
       <c r="X27" s="5" t="n">
-        <v>36</v>
+        <v>17371</v>
       </c>
       <c r="Y27" s="3" t="inlineStr">
         <is>
-          <t>dbs -2,199</t>
+          <t>mcdonalds -11,026,179; ahold-delhaize -1,096,373; ups -653,236</t>
         </is>
       </c>
       <c r="Z27" s="3" t="inlineStr">
         <is>
-          <t>250 Mbps at 91 &gt; 500 Mbps at 85 USD</t>
+          <t>250 Mbps at 162 &gt; 500 Mbps at 110 USD</t>
         </is>
       </c>
       <c r="AA27" s="3" t="inlineStr">
         <is>
-          <t>dbs 118 SGD; dbs 109 SGD</t>
+          <t>ahold-delhaize 110 USD; simmons-bank 100 USD</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>SG-BROADBAND_PON-1000-researched</t>
+          <t>US-BROADBAND_HFC-1000-researched</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>BROADBAND_PON</t>
+          <t>BROADBAND_HFC</t>
         </is>
       </c>
       <c r="D28" s="5" t="n">
@@ -3853,30 +3849,28 @@
       </c>
       <c r="G28" s="8" t="inlineStr">
         <is>
-          <t>Business dynamic fibre on a 24-month contract: Singtel S$178, StarHub S$174.</t>
-        </is>
-      </c>
-      <c r="H28" s="9">
-        <f>J28*0.75</f>
-        <v/>
-      </c>
-      <c r="I28" s="9">
-        <f>J28*1.25</f>
-        <v/>
+          <t>Lightyear transaction dataset, median at 1 Gbps; the band is its 10th-90th percentile.</t>
+        </is>
+      </c>
+      <c r="H28" s="9" t="n">
+        <v>124</v>
+      </c>
+      <c r="I28" s="9" t="n">
+        <v>330</v>
       </c>
       <c r="J28" s="10" t="n">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="K28" s="5" t="inlineStr">
         <is>
-          <t>SGD</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="L28" s="10" t="n">
-        <v>139.06</v>
+        <v>184</v>
       </c>
       <c r="M28" s="10" t="n">
-        <v>149</v>
+        <v>264</v>
       </c>
       <c r="N28" s="11">
         <f>IF(OR(L28="",M28=""),"",L28/M28)</f>
@@ -3889,79 +3883,75 @@
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t>single source; read from a snippet; re-prices lower tiers</t>
+          <t>re-prices lower tiers</t>
         </is>
       </c>
       <c r="Q28" s="3" t="inlineStr">
         <is>
-          <t>BROADBAND_PON 1000 Mbps MRC business dynamic — Singapore (Singtel)</t>
+          <t>BROADBAND_HFC/PON 1 Gbps MRC median</t>
         </is>
       </c>
       <c r="R28" s="5" t="inlineStr">
         <is>
-          <t>DollarsAndSense.sg; AGGREGATOR/SNIPPET_ONLY</t>
+          <t>Lightyear; AGGREGATOR/FULL_PAGE</t>
         </is>
       </c>
       <c r="S28" s="3" t="inlineStr">
         <is>
-          <t>Singtel · $118 · $178 [for 500Mbps and 1Gbps dynamic broadband, 24-month contract]</t>
+          <t>1 Gbps | $124 | $184 | $330</t>
         </is>
       </c>
       <c r="T28" s="5" t="inlineStr">
         <is>
-          <t>https://dollarsandsense.sg/price-guide-to-business-broadband-plans-for-offices-in-singapore/</t>
+          <t>https://lightyear.ai/resources/dedicated-internet-access-dia-ultimate-pricing-guide</t>
         </is>
       </c>
       <c r="U28" s="5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025-2026</t>
         </is>
       </c>
       <c r="V28" s="5" t="inlineStr">
         <is>
-          <t>dbs</t>
+          <t>ahold-delhaize</t>
         </is>
       </c>
       <c r="W28" s="12" t="n">
-        <v>-320.98946125</v>
+        <v>0</v>
       </c>
       <c r="X28" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y28" s="3" t="inlineStr">
-        <is>
-          <t>novartis -321</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Y28" s="3" t="inlineStr"/>
       <c r="Z28" s="3" t="inlineStr">
         <is>
-          <t>250 Mbps at 91 &gt; 500 Mbps at 85 USD</t>
+          <t>250 Mbps at 162 &gt; 500 Mbps at 110 USD</t>
         </is>
       </c>
       <c r="AA28" s="3" t="inlineStr">
         <is>
-          <t>dbs 178 SGD; dbs 53.89 SGD</t>
+          <t>ahold-delhaize 184 USD; simmons-bank 115 USD; ups 184 USD</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>SG-DIA-10000-researched</t>
+          <t>US-BROADBAND_PON-100-researched</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>DIA</t>
+          <t>BROADBAND_PON</t>
         </is>
       </c>
       <c r="D29" s="5" t="n">
-        <v>10000</v>
+        <v>100</v>
       </c>
       <c r="E29" s="13" t="inlineStr">
         <is>
@@ -3975,19 +3965,17 @@
       </c>
       <c r="G29" s="8" t="inlineStr">
         <is>
-          <t>TeleGeography's survey-based 10 GigE DIA benchmark for Singapore. No circuit in the set uses it.</t>
-        </is>
-      </c>
-      <c r="H29" s="9">
-        <f>J29*0.75</f>
-        <v/>
-      </c>
-      <c r="I29" s="9">
-        <f>J29*1.25</f>
-        <v/>
+          <t>Lightyear transaction dataset, median at 100 Mbps (HFC and PON together); the band is its 10th-90th percentile.</t>
+        </is>
+      </c>
+      <c r="H29" s="9" t="n">
+        <v>60</v>
+      </c>
+      <c r="I29" s="9" t="n">
+        <v>175</v>
       </c>
       <c r="J29" s="10" t="n">
-        <v>4500</v>
+        <v>100</v>
       </c>
       <c r="K29" s="5" t="inlineStr">
         <is>
@@ -3995,75 +3983,81 @@
         </is>
       </c>
       <c r="L29" s="10" t="n">
-        <v>4500</v>
-      </c>
-      <c r="M29" s="10" t="n"/>
+        <v>100</v>
+      </c>
+      <c r="M29" s="10" t="n">
+        <v>85</v>
+      </c>
       <c r="N29" s="11">
         <f>IF(OR(L29="",M29=""),"",L29/M29)</f>
         <v/>
       </c>
       <c r="O29" s="5" t="inlineStr">
         <is>
-          <t>none - new tier</t>
+          <t>SEED</t>
         </is>
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t>single source; read from a snippet</t>
+          <t>single source; read from a snippet; re-prices lower tiers</t>
         </is>
       </c>
       <c r="Q29" s="3" t="inlineStr">
         <is>
-          <t>DIA 10000 Mbps (10 GigE) MRC — SG (TeleGeography 2026)</t>
+          <t>BROADBAND_PON/HFC 100 Mbps MRC – US business</t>
         </is>
       </c>
       <c r="R29" s="5" t="inlineStr">
         <is>
-          <t>TeleGeography; TRADE_PRESS/SNIPPET_ONLY</t>
+          <t>Lightyear; AGGREGATOR/SNIPPET_ONLY</t>
         </is>
       </c>
       <c r="S29" s="3" t="inlineStr">
         <is>
-          <t>$4,500 for 10 GigE</t>
+          <t>100 Mbps | $60 | $100 | $175 — Last 12 Months Broadband Pricing ($MRC) by Bandwidth Tier</t>
         </is>
       </c>
       <c r="T29" s="5" t="inlineStr">
         <is>
-          <t>https://resources.telegeography.com/dia-pricing-in-asia-and-oceania</t>
+          <t>https://lightyear.ai/resources/dedicated-internet-access-dia-ultimate-pricing-guide</t>
         </is>
       </c>
       <c r="U29" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025-2026</t>
         </is>
       </c>
       <c r="V29" s="5" t="inlineStr">
         <is>
-          <t>maersk</t>
+          <t>volkswagen</t>
         </is>
       </c>
       <c r="W29" s="12" t="n">
-        <v>0</v>
+        <v>290896.36184</v>
       </c>
       <c r="X29" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y29" s="3" t="inlineStr"/>
+        <v>1770</v>
+      </c>
+      <c r="Y29" s="3" t="inlineStr">
+        <is>
+          <t>toyota +1,756; danone +2,107; bayer +3,512</t>
+        </is>
+      </c>
       <c r="Z29" s="3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>250 Mbps at 114 &gt; 500 Mbps at 99 USD</t>
         </is>
       </c>
       <c r="AA29" s="3" t="inlineStr">
         <is>
-          <t>dbs 4500 USD; maersk 4500 USD</t>
+          <t>volkswagen 100 USD</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>US-BROADBAND_HFC-100-researched</t>
+          <t>US-BROADBAND_PON-500-researched</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
@@ -4073,11 +4067,11 @@
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>BROADBAND_HFC</t>
+          <t>BROADBAND_PON</t>
         </is>
       </c>
       <c r="D30" s="5" t="n">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="E30" s="13" t="inlineStr">
         <is>
@@ -4091,17 +4085,19 @@
       </c>
       <c r="G30" s="8" t="inlineStr">
         <is>
-          <t>Lightyear transaction dataset, median of US business broadband at 100 Mbps; the band is its 10th-90th percentile.</t>
-        </is>
-      </c>
-      <c r="H30" s="9" t="n">
-        <v>60</v>
-      </c>
-      <c r="I30" s="9" t="n">
-        <v>175</v>
+          <t>Verizon Fios Business 500 at $99, consistent with the Lightyear 500 Mbps median of $110.</t>
+        </is>
+      </c>
+      <c r="H30" s="9">
+        <f>J30*0.75</f>
+        <v/>
+      </c>
+      <c r="I30" s="9">
+        <f>J30*1.25</f>
+        <v/>
       </c>
       <c r="J30" s="10" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="K30" s="5" t="inlineStr">
         <is>
@@ -4109,10 +4105,10 @@
         </is>
       </c>
       <c r="L30" s="10" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="M30" s="10" t="n">
-        <v>120</v>
+        <v>145</v>
       </c>
       <c r="N30" s="11">
         <f>IF(OR(L30="",M30=""),"",L30/M30)</f>
@@ -4125,65 +4121,65 @@
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t>re-prices lower tiers</t>
+          <t>single source; read from a snippet; re-prices lower tiers</t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
         <is>
-          <t>BROADBAND_HFC 100 Mbps MRC median</t>
+          <t>BROADBAND_PON 500 Mbps MRC – US, Verizon Fios Business</t>
         </is>
       </c>
       <c r="R30" s="5" t="inlineStr">
         <is>
-          <t>Lightyear; AGGREGATOR/FULL_PAGE</t>
+          <t>highspeedinternet.com (Verizon published tariff); AGGREGATOR/SNIPPET_ONLY</t>
         </is>
       </c>
       <c r="S30" s="3" t="inlineStr">
         <is>
-          <t>100 Mbps | $60 | $100 | $175</t>
+          <t>Verizon Business Fios 500 | $99/mo. | Up to 500Mbps | Fiber</t>
         </is>
       </c>
       <c r="T30" s="5" t="inlineStr">
         <is>
-          <t>https://lightyear.ai/resources/dedicated-internet-access-dia-ultimate-pricing-guide</t>
+          <t>https://www.highspeedinternet.com/resources/business-internet-guide</t>
         </is>
       </c>
       <c r="U30" s="5" t="inlineStr">
         <is>
-          <t>2025-2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="V30" s="5" t="inlineStr">
         <is>
-          <t>ahold-delhaize</t>
+          <t>bayer</t>
         </is>
       </c>
       <c r="W30" s="12" t="n">
-        <v>-6522.79808</v>
+        <v>-77962.3674245</v>
       </c>
       <c r="X30" s="5" t="n">
-        <v>30</v>
+        <v>243</v>
       </c>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t>maersk -3,696; ahold-delhaize -2,174; fresenius -435</t>
+          <t>simmons-bank -20,511; basf -13,372; siemens -11,391</t>
         </is>
       </c>
       <c r="Z30" s="3" t="inlineStr">
         <is>
-          <t>250 Mbps at 162 &gt; 500 Mbps at 110 USD</t>
+          <t>250 Mbps at 114 &gt; 500 Mbps at 99 USD</t>
         </is>
       </c>
       <c r="AA30" s="3" t="inlineStr">
         <is>
-          <t>ahold-delhaize 100 USD; ups 100 USD</t>
+          <t>bayer 99 USD</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>US-BROADBAND_HFC-500-researched</t>
+          <t>US-DIA-100-researched</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
@@ -4193,11 +4189,11 @@
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>BROADBAND_HFC</t>
+          <t>DIA</t>
         </is>
       </c>
       <c r="D31" s="5" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="E31" s="13" t="inlineStr">
         <is>
@@ -4211,17 +4207,17 @@
       </c>
       <c r="G31" s="8" t="inlineStr">
         <is>
-          <t>Lightyear transaction dataset, median at 500 Mbps; the band is its 10th-90th percentile.</t>
+          <t>Lightyear 36-month DIA median at 100 Mbps; the band is its 10th-90th percentile.</t>
         </is>
       </c>
       <c r="H31" s="9" t="n">
-        <v>65</v>
+        <v>333</v>
       </c>
       <c r="I31" s="9" t="n">
-        <v>212</v>
+        <v>641</v>
       </c>
       <c r="J31" s="10" t="n">
-        <v>110</v>
+        <v>492</v>
       </c>
       <c r="K31" s="5" t="inlineStr">
         <is>
@@ -4229,10 +4225,10 @@
         </is>
       </c>
       <c r="L31" s="10" t="n">
-        <v>110</v>
+        <v>492</v>
       </c>
       <c r="M31" s="10" t="n">
-        <v>208</v>
+        <v>480</v>
       </c>
       <c r="N31" s="11">
         <f>IF(OR(L31="",M31=""),"",L31/M31)</f>
@@ -4245,22 +4241,22 @@
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t>re-prices lower tiers</t>
+          <t>read from a snippet; re-prices lower tiers</t>
         </is>
       </c>
       <c r="Q31" s="3" t="inlineStr">
         <is>
-          <t>BROADBAND_HFC/PON 500 Mbps MRC median</t>
+          <t>DIA 100 Mbps MRC – US (Lightyear dataset, 36-month, median)</t>
         </is>
       </c>
       <c r="R31" s="5" t="inlineStr">
         <is>
-          <t>Lightyear; AGGREGATOR/FULL_PAGE</t>
+          <t>Lightyear.ai; AGGREGATOR/SNIPPET_ONLY</t>
         </is>
       </c>
       <c r="S31" s="3" t="inlineStr">
         <is>
-          <t>500 Mbps | $65 | $110 | $212</t>
+          <t>Median DIA MRC 36-month: 100 Mbps $492, 1 Gbps $901, 10 Gbps $1,987 (US, mixed geo/ISP)</t>
         </is>
       </c>
       <c r="T31" s="5" t="inlineStr">
@@ -4275,35 +4271,35 @@
       </c>
       <c r="V31" s="5" t="inlineStr">
         <is>
-          <t>ahold-delhaize</t>
+          <t>abb</t>
         </is>
       </c>
       <c r="W31" s="12" t="n">
-        <v>-13448332.818288</v>
+        <v>418650.656</v>
       </c>
       <c r="X31" s="5" t="n">
-        <v>17371</v>
+        <v>2670</v>
       </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t>mcdonalds -11,026,179; ahold-delhaize -1,096,373; ups -653,236</t>
+          <t>victorias-secret +314; ahold-delhaize +3,920; maersk +6,272</t>
         </is>
       </c>
       <c r="Z31" s="3" t="inlineStr">
         <is>
-          <t>250 Mbps at 162 &gt; 500 Mbps at 110 USD</t>
+          <t>500 Mbps at 1242 &gt; 1000 Mbps at 901 USD</t>
         </is>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
-          <t>ahold-delhaize 110 USD; simmons-bank 100 USD</t>
+          <t>abb 492 USD; ahold-delhaize 333 USD; ahold-delhaize 492 USD; ahold-delhaize 641 USD; basf 492 USD; basf 625 USD; bayer 492 USD; fresenius 492 USD</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>US-BROADBAND_HFC-1000-researched</t>
+          <t>US-DIA-1000-researched</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
@@ -4313,7 +4309,7 @@
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>BROADBAND_HFC</t>
+          <t>DIA</t>
         </is>
       </c>
       <c r="D32" s="5" t="n">
@@ -4331,17 +4327,17 @@
       </c>
       <c r="G32" s="8" t="inlineStr">
         <is>
-          <t>Lightyear transaction dataset, median at 1 Gbps; the band is its 10th-90th percentile.</t>
+          <t>Lightyear 36-month DIA median at 1 Gbps; the band is its 10th-90th percentile.</t>
         </is>
       </c>
       <c r="H32" s="9" t="n">
-        <v>124</v>
+        <v>600</v>
       </c>
       <c r="I32" s="9" t="n">
-        <v>330</v>
+        <v>1312</v>
       </c>
       <c r="J32" s="10" t="n">
-        <v>184</v>
+        <v>901</v>
       </c>
       <c r="K32" s="5" t="inlineStr">
         <is>
@@ -4349,10 +4345,10 @@
         </is>
       </c>
       <c r="L32" s="10" t="n">
-        <v>184</v>
+        <v>901</v>
       </c>
       <c r="M32" s="10" t="n">
-        <v>264</v>
+        <v>1350</v>
       </c>
       <c r="N32" s="11">
         <f>IF(OR(L32="",M32=""),"",L32/M32)</f>
@@ -4365,22 +4361,22 @@
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
-          <t>re-prices lower tiers</t>
+          <t>read from a snippet; re-prices lower tiers</t>
         </is>
       </c>
       <c r="Q32" s="3" t="inlineStr">
         <is>
-          <t>BROADBAND_HFC/PON 1 Gbps MRC median</t>
+          <t>DIA 1000 Mbps MRC – US (Lightyear dataset, 36-month, median)</t>
         </is>
       </c>
       <c r="R32" s="5" t="inlineStr">
         <is>
-          <t>Lightyear; AGGREGATOR/FULL_PAGE</t>
+          <t>Lightyear.ai; AGGREGATOR/SNIPPET_ONLY</t>
         </is>
       </c>
       <c r="S32" s="3" t="inlineStr">
         <is>
-          <t>1 Gbps | $124 | $184 | $330</t>
+          <t>Median DIA 1 Gbps $901/month (US, 36-month, 10th pct $600, 90th pct $1,312)</t>
         </is>
       </c>
       <c r="T32" s="5" t="inlineStr">
@@ -4395,31 +4391,35 @@
       </c>
       <c r="V32" s="5" t="inlineStr">
         <is>
-          <t>ahold-delhaize</t>
+          <t>abb</t>
         </is>
       </c>
       <c r="W32" s="12" t="n">
-        <v>0</v>
+        <v>-1331147.0734</v>
       </c>
       <c r="X32" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y32" s="3" t="inlineStr"/>
+        <v>399</v>
+      </c>
+      <c r="Y32" s="3" t="inlineStr">
+        <is>
+          <t>simmons-bank -537,948; siemens -314,464; nestle -84,483</t>
+        </is>
+      </c>
       <c r="Z32" s="3" t="inlineStr">
         <is>
-          <t>250 Mbps at 162 &gt; 500 Mbps at 110 USD</t>
+          <t>500 Mbps at 1242 &gt; 1000 Mbps at 901 USD</t>
         </is>
       </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
-          <t>ahold-delhaize 184 USD; simmons-bank 115 USD; ups 184 USD</t>
+          <t>abb 901 USD; ahold-delhaize 600 USD; ahold-delhaize 901 USD; ahold-delhaize 1312 USD; basf 901 USD; basf 1070 USD; bayer 901 USD; fresenius 901 USD</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>US-BROADBAND_PON-100-researched</t>
+          <t>US-DIA-10000-researched</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
@@ -4429,11 +4429,11 @@
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>BROADBAND_PON</t>
+          <t>DIA</t>
         </is>
       </c>
       <c r="D33" s="5" t="n">
-        <v>100</v>
+        <v>10000</v>
       </c>
       <c r="E33" s="13" t="inlineStr">
         <is>
@@ -4447,17 +4447,17 @@
       </c>
       <c r="G33" s="8" t="inlineStr">
         <is>
-          <t>Lightyear transaction dataset, median at 100 Mbps (HFC and PON together); the band is its 10th-90th percentile.</t>
+          <t>Lightyear 36-month DIA median at 10 Gbps; the band is its 10th-90th percentile. Approved on 13 Oct, and lost to a re-promotion.</t>
         </is>
       </c>
       <c r="H33" s="9" t="n">
-        <v>60</v>
+        <v>1175</v>
       </c>
       <c r="I33" s="9" t="n">
-        <v>175</v>
+        <v>2853</v>
       </c>
       <c r="J33" s="10" t="n">
-        <v>100</v>
+        <v>1987</v>
       </c>
       <c r="K33" s="5" t="inlineStr">
         <is>
@@ -4465,38 +4465,36 @@
         </is>
       </c>
       <c r="L33" s="10" t="n">
-        <v>100</v>
-      </c>
-      <c r="M33" s="10" t="n">
-        <v>85</v>
-      </c>
+        <v>1987</v>
+      </c>
+      <c r="M33" s="10" t="n"/>
       <c r="N33" s="11">
         <f>IF(OR(L33="",M33=""),"",L33/M33)</f>
         <v/>
       </c>
       <c r="O33" s="5" t="inlineStr">
         <is>
-          <t>SEED</t>
+          <t>none - new tier</t>
         </is>
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
-          <t>single source; read from a snippet; re-prices lower tiers</t>
+          <t>read from a snippet; re-prices lower tiers</t>
         </is>
       </c>
       <c r="Q33" s="3" t="inlineStr">
         <is>
-          <t>BROADBAND_PON/HFC 100 Mbps MRC – US business</t>
+          <t>DIA 10000 Mbps MRC – US (Lightyear dataset, 36-month, median)</t>
         </is>
       </c>
       <c r="R33" s="5" t="inlineStr">
         <is>
-          <t>Lightyear; AGGREGATOR/SNIPPET_ONLY</t>
+          <t>Lightyear.ai; AGGREGATOR/SNIPPET_ONLY</t>
         </is>
       </c>
       <c r="S33" s="3" t="inlineStr">
         <is>
-          <t>100 Mbps | $60 | $100 | $175 — Last 12 Months Broadband Pricing ($MRC) by Bandwidth Tier</t>
+          <t>Median DIA 10 Gbps $1,987/month (US, 36-month, 10th pct $1,175, 90th pct $2,853)</t>
         </is>
       </c>
       <c r="T33" s="5" t="inlineStr">
@@ -4511,35 +4509,31 @@
       </c>
       <c r="V33" s="5" t="inlineStr">
         <is>
-          <t>volkswagen</t>
+          <t>abb</t>
         </is>
       </c>
       <c r="W33" s="12" t="n">
-        <v>290896.36184</v>
+        <v>0</v>
       </c>
       <c r="X33" s="5" t="n">
-        <v>1770</v>
-      </c>
-      <c r="Y33" s="3" t="inlineStr">
-        <is>
-          <t>toyota +1,756; danone +2,107; bayer +3,512</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Y33" s="3" t="inlineStr"/>
       <c r="Z33" s="3" t="inlineStr">
         <is>
-          <t>250 Mbps at 114 &gt; 500 Mbps at 99 USD</t>
+          <t>500 Mbps at 1242 &gt; 1000 Mbps at 901 USD</t>
         </is>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
-          <t>volkswagen 100 USD</t>
+          <t>abb 1987 USD; ahold-delhaize 1987 USD; bayer 1987 USD; fresenius 1987 USD; mcdonalds 1987 USD; siemens 1987 USD; simmons-bank 1987 USD; ups 1987 USD</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>US-BROADBAND_PON-500-researched</t>
+          <t>US-ETHERNET-10000-researched</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
@@ -4549,11 +4543,11 @@
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>BROADBAND_PON</t>
+          <t>ETHERNET</t>
         </is>
       </c>
       <c r="D34" s="5" t="n">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E34" s="13" t="inlineStr">
         <is>
@@ -4567,19 +4561,17 @@
       </c>
       <c r="G34" s="8" t="inlineStr">
         <is>
-          <t>Verizon Fios Business 500 at $99, consistent with the Lightyear 500 Mbps median of $110.</t>
-        </is>
-      </c>
-      <c r="H34" s="9">
-        <f>J34*0.75</f>
-        <v/>
-      </c>
-      <c r="I34" s="9">
-        <f>J34*1.25</f>
-        <v/>
+          <t>Lightyear Ethernet private-line median at 10 Gbps; the band is its 10th-90th percentile.</t>
+        </is>
+      </c>
+      <c r="H34" s="9" t="n">
+        <v>1244</v>
+      </c>
+      <c r="I34" s="9" t="n">
+        <v>2157</v>
       </c>
       <c r="J34" s="10" t="n">
-        <v>99</v>
+        <v>1807</v>
       </c>
       <c r="K34" s="5" t="inlineStr">
         <is>
@@ -4587,10 +4579,10 @@
         </is>
       </c>
       <c r="L34" s="10" t="n">
-        <v>99</v>
+        <v>1807</v>
       </c>
       <c r="M34" s="10" t="n">
-        <v>145</v>
+        <v>3450</v>
       </c>
       <c r="N34" s="11">
         <f>IF(OR(L34="",M34=""),"",L34/M34)</f>
@@ -4603,65 +4595,65 @@
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
-          <t>single source; read from a snippet; re-prices lower tiers</t>
+          <t>floor; read from a snippet; re-prices lower tiers</t>
         </is>
       </c>
       <c r="Q34" s="3" t="inlineStr">
         <is>
-          <t>BROADBAND_PON 500 Mbps MRC – US, Verizon Fios Business</t>
+          <t>ETHERNET 10000 Mbps point-to-point MRC – US (Lightyear dataset)</t>
         </is>
       </c>
       <c r="R34" s="5" t="inlineStr">
         <is>
-          <t>highspeedinternet.com (Verizon published tariff); AGGREGATOR/SNIPPET_ONLY</t>
+          <t>lightyear.ai (Ethernet Private Line guide); TRADE_PRESS/SNIPPET_ONLY</t>
         </is>
       </c>
       <c r="S34" s="3" t="inlineStr">
         <is>
-          <t>Verizon Business Fios 500 | $99/mo. | Up to 500Mbps | Fiber</t>
+          <t>10 Gbps Point-to-Point (Ethernet): 10th pct $1,244, Median $1,807, 90th pct $2,157</t>
         </is>
       </c>
       <c r="T34" s="5" t="inlineStr">
         <is>
-          <t>https://www.highspeedinternet.com/resources/business-internet-guide</t>
+          <t>https://lightyear.ai/blogs/ethernet-private-line-cost</t>
         </is>
       </c>
       <c r="U34" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025-2026</t>
         </is>
       </c>
       <c r="V34" s="5" t="inlineStr">
         <is>
-          <t>bayer</t>
+          <t>simmons-bank</t>
         </is>
       </c>
       <c r="W34" s="12" t="n">
-        <v>-77962.3674245</v>
+        <v>-32322.017413</v>
       </c>
       <c r="X34" s="5" t="n">
-        <v>243</v>
+        <v>2</v>
       </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t>simmons-bank -20,511; basf -13,372; siemens -11,391</t>
+          <t>shell -32,322</t>
         </is>
       </c>
       <c r="Z34" s="3" t="inlineStr">
         <is>
-          <t>250 Mbps at 114 &gt; 500 Mbps at 99 USD</t>
+          <t>9000 Mbps at 3267 &gt; 10000 Mbps at 1807 USD</t>
         </is>
       </c>
       <c r="AA34" s="3" t="inlineStr">
         <is>
-          <t>bayer 99 USD</t>
+          <t>simmons-bank 1807 USD</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>US-DIA-100-researched</t>
+          <t>US-MPLS-1000-researched</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
@@ -4671,11 +4663,11 @@
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>DIA</t>
+          <t>MPLS</t>
         </is>
       </c>
       <c r="D35" s="5" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="E35" s="13" t="inlineStr">
         <is>
@@ -4689,17 +4681,19 @@
       </c>
       <c r="G35" s="8" t="inlineStr">
         <is>
-          <t>Lightyear 36-month DIA median at 100 Mbps; the band is its 10th-90th percentile.</t>
-        </is>
-      </c>
-      <c r="H35" s="9" t="n">
-        <v>333</v>
-      </c>
-      <c r="I35" s="9" t="n">
-        <v>641</v>
+          <t>Lightyear median for an all-inclusive managed MPLS service at 1 Gbps. Approved on 13 Oct, and lost to a re-promotion.</t>
+        </is>
+      </c>
+      <c r="H35" s="9">
+        <f>J35*0.75</f>
+        <v/>
+      </c>
+      <c r="I35" s="9">
+        <f>J35*1.25</f>
+        <v/>
       </c>
       <c r="J35" s="10" t="n">
-        <v>492</v>
+        <v>1439</v>
       </c>
       <c r="K35" s="5" t="inlineStr">
         <is>
@@ -4707,86 +4701,80 @@
         </is>
       </c>
       <c r="L35" s="10" t="n">
-        <v>492</v>
-      </c>
-      <c r="M35" s="10" t="n">
-        <v>480</v>
-      </c>
+        <v>1439</v>
+      </c>
+      <c r="M35" s="10" t="n"/>
       <c r="N35" s="11">
         <f>IF(OR(L35="",M35=""),"",L35/M35)</f>
         <v/>
       </c>
       <c r="O35" s="5" t="inlineStr">
         <is>
-          <t>SEED</t>
+          <t>none - new tier</t>
         </is>
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
-          <t>read from a snippet; re-prices lower tiers</t>
+          <t>single source; read from a snippet</t>
         </is>
       </c>
       <c r="Q35" s="3" t="inlineStr">
         <is>
-          <t>DIA 100 Mbps MRC – US (Lightyear dataset, 36-month, median)</t>
+          <t>MPLS 1000Mbps MRC</t>
         </is>
       </c>
       <c r="R35" s="5" t="inlineStr">
         <is>
-          <t>Lightyear.ai; AGGREGATOR/SNIPPET_ONLY</t>
+          <t>Lightyear; AGGREGATOR/SNIPPET_ONLY</t>
         </is>
       </c>
       <c r="S35" s="3" t="inlineStr">
         <is>
-          <t>Median DIA MRC 36-month: 100 Mbps $492, 1 Gbps $901, 10 Gbps $1,987 (US, mixed geo/ISP)</t>
+          <t>MPLS | $1,439 | $17,268 | All-inclusive managed service (1 Gbps)</t>
         </is>
       </c>
       <c r="T35" s="5" t="inlineStr">
         <is>
-          <t>https://lightyear.ai/resources/dedicated-internet-access-dia-ultimate-pricing-guide</t>
+          <t>https://lightyear.ai/blogs/sd-wan-vs-mpls-cost-comparison</t>
         </is>
       </c>
       <c r="U35" s="5" t="inlineStr">
         <is>
-          <t>2025-2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="V35" s="5" t="inlineStr">
         <is>
-          <t>abb</t>
+          <t>toyota</t>
         </is>
       </c>
       <c r="W35" s="12" t="n">
-        <v>418650.656</v>
+        <v>0</v>
       </c>
       <c r="X35" s="5" t="n">
-        <v>2670</v>
-      </c>
-      <c r="Y35" s="3" t="inlineStr">
-        <is>
-          <t>victorias-secret +314; ahold-delhaize +3,920; maersk +6,272</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Y35" s="3" t="inlineStr"/>
       <c r="Z35" s="3" t="inlineStr">
         <is>
-          <t>500 Mbps at 1242 &gt; 1000 Mbps at 901 USD</t>
+          <t>no</t>
         </is>
       </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
-          <t>abb 492 USD; ahold-delhaize 333 USD; ahold-delhaize 492 USD; ahold-delhaize 641 USD; basf 492 USD; basf 625 USD; bayer 492 USD; fresenius 492 USD</t>
+          <t>abb 1439 USD; basf 1439 USD; bayer 1439 USD; maersk 1439 USD; mcdonalds 1439 USD; siemens 1439 USD; simmons-bank 1439 USD; toyota 1439 USD</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>US-DIA-1000-researched</t>
+          <t>AU-DIA-1000-researched</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
@@ -4797,40 +4785,42 @@
       <c r="D36" s="5" t="n">
         <v>1000</v>
       </c>
-      <c r="E36" s="13" t="inlineStr">
-        <is>
-          <t>approved by Christian Bartosch</t>
+      <c r="E36" s="14" t="inlineStr">
+        <is>
+          <t>revoked by Christian Bartosch</t>
         </is>
       </c>
       <c r="F36" s="7" t="inlineStr">
         <is>
-          <t>Approve</t>
+          <t>Reject</t>
         </is>
       </c>
       <c r="G36" s="8" t="inlineStr">
         <is>
-          <t>Lightyear 36-month DIA median at 1 Gbps; the band is its 10th-90th percentile.</t>
-        </is>
-      </c>
-      <c r="H36" s="9" t="n">
-        <v>600</v>
-      </c>
-      <c r="I36" s="9" t="n">
-        <v>1312</v>
+          <t>An on-net data-centre DIA price (Nexthop), not site access. The same research cites A$2,500-8,000 for enterprise dedicated fibre.</t>
+        </is>
+      </c>
+      <c r="H36" s="9">
+        <f>J36*0.75</f>
+        <v/>
+      </c>
+      <c r="I36" s="9">
+        <f>J36*1.25</f>
+        <v/>
       </c>
       <c r="J36" s="10" t="n">
-        <v>901</v>
+        <v>499</v>
       </c>
       <c r="K36" s="5" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>AUD</t>
         </is>
       </c>
       <c r="L36" s="10" t="n">
-        <v>901</v>
+        <v>337.16</v>
       </c>
       <c r="M36" s="10" t="n">
-        <v>1350</v>
+        <v>1750</v>
       </c>
       <c r="N36" s="11">
         <f>IF(OR(L36="",M36=""),"",L36/M36)</f>
@@ -4843,111 +4833,101 @@
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
-          <t>read from a snippet; re-prices lower tiers</t>
-        </is>
-      </c>
-      <c r="Q36" s="3" t="inlineStr">
-        <is>
-          <t>DIA 1000 Mbps MRC – US (Lightyear dataset, 36-month, median)</t>
-        </is>
-      </c>
+          <t>consumer; single source; re-prices lower tiers</t>
+        </is>
+      </c>
+      <c r="Q36" s="3" t="inlineStr"/>
       <c r="R36" s="5" t="inlineStr">
         <is>
-          <t>Lightyear.ai; AGGREGATOR/SNIPPET_ONLY</t>
+          <t>run narrative (the disposition was replaced)</t>
         </is>
       </c>
       <c r="S36" s="3" t="inlineStr">
         <is>
-          <t>Median DIA 1 Gbps $901/month (US, 36-month, 10th pct $600, 90th pct $1,312)</t>
-        </is>
-      </c>
-      <c r="T36" s="5" t="inlineStr">
-        <is>
-          <t>https://lightyear.ai/resources/dedicated-internet-access-dia-ultimate-pricing-guide</t>
-        </is>
-      </c>
+          <t xml:space="preserve"> not retail MRCs. Residential NBN (consumer, ACCC June 2025): 100 Mbps median advertised price ~A$65-80/mo (not enterprise). AU DIA (Dedicated Internet Access – direct fibre): Nexthop AU lists 1 Gbps datacenter DIA at A$499/mo (24-month, on-net); Vocus Fast Fibre (direct fibre, enterprise) from A$339/mo excl. GST for 250 Mbps+. AyeTech 2026 guide cites enterprise dedicated fibre 1</t>
+        </is>
+      </c>
+      <c r="T36" s="5" t="inlineStr"/>
       <c r="U36" s="5" t="inlineStr">
         <is>
-          <t>2025-2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="V36" s="5" t="inlineStr">
         <is>
-          <t>abb</t>
+          <t>woolworths</t>
         </is>
       </c>
       <c r="W36" s="12" t="n">
-        <v>-1331147.0734</v>
+        <v>-416627.1182432433</v>
       </c>
       <c r="X36" s="5" t="n">
-        <v>399</v>
+        <v>30</v>
       </c>
       <c r="Y36" s="3" t="inlineStr">
         <is>
-          <t>simmons-bank -537,948; siemens -314,464; nestle -84,483</t>
+          <t>woolworths -416,627</t>
         </is>
       </c>
       <c r="Z36" s="3" t="inlineStr">
         <is>
-          <t>500 Mbps at 1242 &gt; 1000 Mbps at 901 USD</t>
-        </is>
-      </c>
-      <c r="AA36" s="3" t="inlineStr">
-        <is>
-          <t>abb 901 USD; ahold-delhaize 600 USD; ahold-delhaize 901 USD; ahold-delhaize 1312 USD; basf 901 USD; basf 1070 USD; bayer 901 USD; fresenius 901 USD</t>
-        </is>
-      </c>
+          <t>500 Mbps at 1610 &gt; 1000 Mbps at 337 USD</t>
+        </is>
+      </c>
+      <c r="AA36" s="3" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>US-DIA-10000-researched</t>
+          <t>DE-BROADBAND_PON-75-researched</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>DIA</t>
+          <t>BROADBAND_PON</t>
         </is>
       </c>
       <c r="D37" s="5" t="n">
-        <v>10000</v>
-      </c>
-      <c r="E37" s="13" t="inlineStr">
-        <is>
-          <t>approved by Christian Bartosch</t>
+        <v>75</v>
+      </c>
+      <c r="E37" s="14" t="inlineStr">
+        <is>
+          <t>revoked by Christian Bartosch</t>
         </is>
       </c>
       <c r="F37" s="7" t="inlineStr">
         <is>
-          <t>Approve</t>
+          <t>Reject</t>
         </is>
       </c>
       <c r="G37" s="8" t="inlineStr">
         <is>
-          <t>Lightyear 36-month DIA median at 10 Gbps; the band is its 10th-90th percentile. Approved on 13 Oct, and lost to a re-promotion.</t>
-        </is>
-      </c>
-      <c r="H37" s="9" t="n">
-        <v>1175</v>
-      </c>
-      <c r="I37" s="9" t="n">
-        <v>2853</v>
+          <t>A wholesale bitstream price cap for subsidised networks (BMDV L2-BSA). A business pays the retail price on top of it.</t>
+        </is>
+      </c>
+      <c r="H37" s="9">
+        <f>J37*0.75</f>
+        <v/>
+      </c>
+      <c r="I37" s="9">
+        <f>J37*1.25</f>
+        <v/>
       </c>
       <c r="J37" s="10" t="n">
-        <v>1987</v>
+        <v>19.22</v>
       </c>
       <c r="K37" s="5" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="L37" s="10" t="n">
-        <v>1987</v>
+        <v>22.06</v>
       </c>
       <c r="M37" s="10" t="n"/>
       <c r="N37" s="11">
@@ -4961,37 +4941,37 @@
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t>read from a snippet; re-prices lower tiers</t>
+          <t>wholesale; read from a snippet; re-prices lower tiers</t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
         <is>
-          <t>DIA 10000 Mbps MRC – US (Lightyear dataset, 36-month, median)</t>
+          <t>DE BROADBAND_PON wholesale bitstream L2-BSA 50-99 Mbps MRC (regulatory price cap)</t>
         </is>
       </c>
       <c r="R37" s="5" t="inlineStr">
         <is>
-          <t>Lightyear.ai; AGGREGATOR/SNIPPET_ONLY</t>
+          <t>BMDV / Bundesnetzagentur (German Federal Ministry for Digital Affairs); REGULATOR/SNIPPET_ONLY</t>
         </is>
       </c>
       <c r="S37" s="3" t="inlineStr">
         <is>
-          <t>Median DIA 10 Gbps $1,987/month (US, 36-month, 10th pct $1,175, 90th pct $2,853)</t>
+          <t>50 – 99 Mbit/s … L2-BSA Überlassungsentgelt … 19,22 €</t>
         </is>
       </c>
       <c r="T37" s="5" t="inlineStr">
         <is>
-          <t>https://lightyear.ai/resources/dedicated-internet-access-dia-ultimate-pricing-guide</t>
+          <t>https://www.bmv.de/SharedDocs/DE/Anlage/DG/vorleistungspreise.pdf?__blob=publicationFile</t>
         </is>
       </c>
       <c r="U37" s="5" t="inlineStr">
         <is>
-          <t>2025-2026</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="V37" s="5" t="inlineStr">
         <is>
-          <t>abb</t>
+          <t>fresenius</t>
         </is>
       </c>
       <c r="W37" s="12" t="n">
@@ -5003,167 +4983,163 @@
       <c r="Y37" s="3" t="inlineStr"/>
       <c r="Z37" s="3" t="inlineStr">
         <is>
-          <t>500 Mbps at 1242 &gt; 1000 Mbps at 901 USD</t>
+          <t>50 Mbps at 64 &gt; 75 Mbps at 22 USD</t>
         </is>
       </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
-          <t>abb 1987 USD; ahold-delhaize 1987 USD; bayer 1987 USD; fresenius 1987 USD; mcdonalds 1987 USD; siemens 1987 USD; simmons-bank 1987 USD; ups 1987 USD</t>
+          <t>fresenius 19.22 EUR</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>US-ETHERNET-10000-researched</t>
+          <t>DE-BROADBAND_PON-150-researched</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>ETHERNET</t>
+          <t>BROADBAND_PON</t>
         </is>
       </c>
       <c r="D38" s="5" t="n">
-        <v>10000</v>
-      </c>
-      <c r="E38" s="13" t="inlineStr">
-        <is>
-          <t>approved by Christian Bartosch</t>
+        <v>150</v>
+      </c>
+      <c r="E38" s="14" t="inlineStr">
+        <is>
+          <t>revoked by Christian Bartosch</t>
         </is>
       </c>
       <c r="F38" s="7" t="inlineStr">
         <is>
-          <t>Approve</t>
+          <t>Reject</t>
         </is>
       </c>
       <c r="G38" s="8" t="inlineStr">
         <is>
-          <t>Lightyear Ethernet private-line median at 10 Gbps; the band is its 10th-90th percentile.</t>
-        </is>
-      </c>
-      <c r="H38" s="9" t="n">
-        <v>1244</v>
-      </c>
-      <c r="I38" s="9" t="n">
-        <v>2157</v>
+          <t>A wholesale bitstream price cap for subsidised networks (BMDV L2-BSA). A business pays the retail price on top of it.</t>
+        </is>
+      </c>
+      <c r="H38" s="9">
+        <f>J38*0.75</f>
+        <v/>
+      </c>
+      <c r="I38" s="9">
+        <f>J38*1.25</f>
+        <v/>
       </c>
       <c r="J38" s="10" t="n">
-        <v>1807</v>
+        <v>21.55</v>
       </c>
       <c r="K38" s="5" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="L38" s="10" t="n">
-        <v>1807</v>
-      </c>
-      <c r="M38" s="10" t="n">
-        <v>3450</v>
-      </c>
+        <v>24.74</v>
+      </c>
+      <c r="M38" s="10" t="n"/>
       <c r="N38" s="11">
         <f>IF(OR(L38="",M38=""),"",L38/M38)</f>
         <v/>
       </c>
       <c r="O38" s="5" t="inlineStr">
         <is>
-          <t>SEED</t>
+          <t>none - new tier</t>
         </is>
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t>floor; read from a snippet; re-prices lower tiers</t>
+          <t>wholesale; read from a snippet; re-prices lower tiers</t>
         </is>
       </c>
       <c r="Q38" s="3" t="inlineStr">
         <is>
-          <t>ETHERNET 10000 Mbps point-to-point MRC – US (Lightyear dataset)</t>
+          <t>DE BROADBAND_PON wholesale bitstream L2-BSA 100-199 Mbps MRC (regulatory price cap)</t>
         </is>
       </c>
       <c r="R38" s="5" t="inlineStr">
         <is>
-          <t>lightyear.ai (Ethernet Private Line guide); TRADE_PRESS/SNIPPET_ONLY</t>
+          <t>BMDV / Bundesnetzagentur; REGULATOR/SNIPPET_ONLY</t>
         </is>
       </c>
       <c r="S38" s="3" t="inlineStr">
         <is>
-          <t>10 Gbps Point-to-Point (Ethernet): 10th pct $1,244, Median $1,807, 90th pct $2,157</t>
+          <t>100 – 199 Mbit/s … L2-BSA … 21,55 €</t>
         </is>
       </c>
       <c r="T38" s="5" t="inlineStr">
         <is>
-          <t>https://lightyear.ai/blogs/ethernet-private-line-cost</t>
+          <t>https://www.bmv.de/SharedDocs/DE/Anlage/DG/vorleistungspreise.pdf?__blob=publicationFile</t>
         </is>
       </c>
       <c r="U38" s="5" t="inlineStr">
         <is>
-          <t>2025-2026</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="V38" s="5" t="inlineStr">
         <is>
-          <t>simmons-bank</t>
+          <t>fresenius</t>
         </is>
       </c>
       <c r="W38" s="12" t="n">
-        <v>-32322.017413</v>
+        <v>0</v>
       </c>
       <c r="X38" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y38" s="3" t="inlineStr">
-        <is>
-          <t>shell -32,322</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Y38" s="3" t="inlineStr"/>
       <c r="Z38" s="3" t="inlineStr">
         <is>
-          <t>9000 Mbps at 3267 &gt; 10000 Mbps at 1807 USD</t>
+          <t>100 Mbps at 78 &gt; 150 Mbps at 25 USD</t>
         </is>
       </c>
       <c r="AA38" s="3" t="inlineStr">
         <is>
-          <t>simmons-bank 1807 USD</t>
+          <t>fresenius 21.55 EUR</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>US-MPLS-1000-researched</t>
+          <t>DE-BROADBAND_PON-750-researched</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>MPLS</t>
+          <t>BROADBAND_PON</t>
         </is>
       </c>
       <c r="D39" s="5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="E39" s="13" t="inlineStr">
-        <is>
-          <t>approved by Christian Bartosch</t>
+        <v>750</v>
+      </c>
+      <c r="E39" s="14" t="inlineStr">
+        <is>
+          <t>revoked by Christian Bartosch</t>
         </is>
       </c>
       <c r="F39" s="7" t="inlineStr">
         <is>
-          <t>Approve</t>
+          <t>Reject</t>
         </is>
       </c>
       <c r="G39" s="8" t="inlineStr">
         <is>
-          <t>Lightyear median for an all-inclusive managed MPLS service at 1 Gbps. Approved on 13 Oct, and lost to a re-promotion.</t>
+          <t>A wholesale bitstream price cap for subsidised networks (BMDV L2-BSA). A business pays the retail price on top of it.</t>
         </is>
       </c>
       <c r="H39" s="9">
@@ -5175,15 +5151,15 @@
         <v/>
       </c>
       <c r="J39" s="10" t="n">
-        <v>1439</v>
+        <v>30.74</v>
       </c>
       <c r="K39" s="5" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="L39" s="10" t="n">
-        <v>1439</v>
+        <v>35.29</v>
       </c>
       <c r="M39" s="10" t="n"/>
       <c r="N39" s="11">
@@ -5197,71 +5173,75 @@
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
-          <t>single source; read from a snippet</t>
+          <t>wholesale; read from a snippet; re-prices lower tiers</t>
         </is>
       </c>
       <c r="Q39" s="3" t="inlineStr">
         <is>
-          <t>MPLS 1000Mbps MRC</t>
+          <t>DE BROADBAND_PON wholesale bitstream L2-BSA 500-999 Mbps MRC (regulatory price cap)</t>
         </is>
       </c>
       <c r="R39" s="5" t="inlineStr">
         <is>
-          <t>Lightyear; AGGREGATOR/SNIPPET_ONLY</t>
+          <t>BMDV / Bundesnetzagentur; REGULATOR/SNIPPET_ONLY</t>
         </is>
       </c>
       <c r="S39" s="3" t="inlineStr">
         <is>
-          <t>MPLS | $1,439 | $17,268 | All-inclusive managed service (1 Gbps)</t>
+          <t>500 – 999 Mbit/s … L2-BSA … 30,74 €</t>
         </is>
       </c>
       <c r="T39" s="5" t="inlineStr">
         <is>
-          <t>https://lightyear.ai/blogs/sd-wan-vs-mpls-cost-comparison</t>
+          <t>https://www.bmv.de/SharedDocs/DE/Anlage/DG/vorleistungspreise.pdf?__blob=publicationFile</t>
         </is>
       </c>
       <c r="U39" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="V39" s="5" t="inlineStr">
         <is>
-          <t>toyota</t>
+          <t>fresenius</t>
         </is>
       </c>
       <c r="W39" s="12" t="n">
-        <v>0</v>
+        <v>-131200.10221975</v>
       </c>
       <c r="X39" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y39" s="3" t="inlineStr"/>
+        <v>126</v>
+      </c>
+      <c r="Y39" s="3" t="inlineStr">
+        <is>
+          <t>basf -38,527; siemens -29,156; volkswagen -29,156</t>
+        </is>
+      </c>
       <c r="Z39" s="3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>500 Mbps at 132 &gt; 750 Mbps at 35 USD</t>
         </is>
       </c>
       <c r="AA39" s="3" t="inlineStr">
         <is>
-          <t>abb 1439 USD; basf 1439 USD; bayer 1439 USD; maersk 1439 USD; mcdonalds 1439 USD; siemens 1439 USD; simmons-bank 1439 USD; toyota 1439 USD</t>
+          <t>fresenius 30.74 EUR</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>AU-DIA-1000-researched</t>
+          <t>DE-BROADBAND_PON-1000-researched</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>DIA</t>
+          <t>BROADBAND_PON</t>
         </is>
       </c>
       <c r="D40" s="5" t="n">
@@ -5279,7 +5259,7 @@
       </c>
       <c r="G40" s="8" t="inlineStr">
         <is>
-          <t>An on-net data-centre DIA price (Nexthop), not site access. The same research cites A$2,500-8,000 for enterprise dedicated fibre.</t>
+          <t>A wholesale bitstream price cap for subsidised networks (BMDV L2-BSA). The source itself says retail will be higher after the margin stack.</t>
         </is>
       </c>
       <c r="H40" s="9">
@@ -5291,18 +5271,18 @@
         <v/>
       </c>
       <c r="J40" s="10" t="n">
-        <v>499</v>
+        <v>41.97</v>
       </c>
       <c r="K40" s="5" t="inlineStr">
         <is>
-          <t>AUD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="L40" s="10" t="n">
-        <v>337.16</v>
+        <v>48.18</v>
       </c>
       <c r="M40" s="10" t="n">
-        <v>1750</v>
+        <v>171</v>
       </c>
       <c r="N40" s="11">
         <f>IF(OR(L40="",M40=""),"",L40/M40)</f>
@@ -5315,67 +5295,79 @@
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
-          <t>consumer; single source; re-prices lower tiers</t>
-        </is>
-      </c>
-      <c r="Q40" s="3" t="inlineStr"/>
+          <t>wholesale; read from a snippet; re-prices lower tiers</t>
+        </is>
+      </c>
+      <c r="Q40" s="3" t="inlineStr">
+        <is>
+          <t>DE BROADBAND_PON wholesale bitstream L2-BSA 1000 Mbps MRC (regulatory price cap)</t>
+        </is>
+      </c>
       <c r="R40" s="5" t="inlineStr">
         <is>
-          <t>run narrative (the disposition was replaced)</t>
+          <t>BMDV / Bundesnetzagentur; REGULATOR/SNIPPET_ONLY</t>
         </is>
       </c>
       <c r="S40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> not retail MRCs. Residential NBN (consumer, ACCC June 2025): 100 Mbps median advertised price ~A$65-80/mo (not enterprise). AU DIA (Dedicated Internet Access – direct fibre): Nexthop AU lists 1 Gbps datacenter DIA at A$499/mo (24-month, on-net); Vocus Fast Fibre (direct fibre, enterprise) from A$339/mo excl. GST for 250 Mbps+. AyeTech 2026 guide cites enterprise dedicated fibre 1</t>
-        </is>
-      </c>
-      <c r="T40" s="5" t="inlineStr"/>
+          <t>1000 Mbit/s … L2-BSA … 41,97 €</t>
+        </is>
+      </c>
+      <c r="T40" s="5" t="inlineStr">
+        <is>
+          <t>https://www.bmv.de/SharedDocs/DE/Anlage/DG/vorleistungspreise.pdf?__blob=publicationFile</t>
+        </is>
+      </c>
       <c r="U40" s="5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="V40" s="5" t="inlineStr">
         <is>
-          <t>woolworths</t>
+          <t>fresenius</t>
         </is>
       </c>
       <c r="W40" s="12" t="n">
-        <v>-416627.1182432433</v>
+        <v>-113710.9553765</v>
       </c>
       <c r="X40" s="5" t="n">
-        <v>30</v>
+        <v>126</v>
       </c>
       <c r="Y40" s="3" t="inlineStr">
         <is>
-          <t>woolworths -416,627</t>
+          <t>basf -33,391; siemens -25,269; volkswagen -25,269</t>
         </is>
       </c>
       <c r="Z40" s="3" t="inlineStr">
         <is>
-          <t>500 Mbps at 1610 &gt; 1000 Mbps at 337 USD</t>
-        </is>
-      </c>
-      <c r="AA40" s="3" t="inlineStr"/>
+          <t>500 Mbps at 132 &gt; 1000 Mbps at 48 USD</t>
+        </is>
+      </c>
+      <c r="AA40" s="3" t="inlineStr">
+        <is>
+          <t>fresenius 41.97 EUR</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>DE-BROADBAND_PON-75-researched</t>
+          <t>ES-DIA-600-researched</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>BROADBAND_PON</t>
+          <t>DIA</t>
         </is>
       </c>
       <c r="D41" s="5" t="n">
-        <v>75</v>
+        <v>600</v>
       </c>
       <c r="E41" s="14" t="inlineStr">
         <is>
@@ -5389,7 +5381,7 @@
       </c>
       <c r="G41" s="8" t="inlineStr">
         <is>
-          <t>A wholesale bitstream price cap for subsidised networks (BMDV L2-BSA). A business pays the retail price on top of it.</t>
+          <t>Rejected against a second Spanish source: a multi-network (3Net) circuit marked approximate pending a site survey, about twice Kompara's EUR 400-600 for 500 Mbps dedicated fibre. No circuit in the set uses it.</t>
         </is>
       </c>
       <c r="H41" s="9">
@@ -5401,7 +5393,7 @@
         <v/>
       </c>
       <c r="J41" s="10" t="n">
-        <v>19.22</v>
+        <v>1100</v>
       </c>
       <c r="K41" s="5" t="inlineStr">
         <is>
@@ -5409,7 +5401,7 @@
         </is>
       </c>
       <c r="L41" s="10" t="n">
-        <v>22.06</v>
+        <v>1262.77</v>
       </c>
       <c r="M41" s="10" t="n"/>
       <c r="N41" s="11">
@@ -5423,37 +5415,25 @@
       </c>
       <c r="P41" s="3" t="inlineStr">
         <is>
-          <t>wholesale; read from a snippet; re-prices lower tiers</t>
-        </is>
-      </c>
-      <c r="Q41" s="3" t="inlineStr">
-        <is>
-          <t>DE BROADBAND_PON wholesale bitstream L2-BSA 50-99 Mbps MRC (regulatory price cap)</t>
-        </is>
-      </c>
+          <t>single source; untraceable</t>
+        </is>
+      </c>
+      <c r="Q41" s="3" t="inlineStr"/>
       <c r="R41" s="5" t="inlineStr">
         <is>
-          <t>BMDV / Bundesnetzagentur (German Federal Ministry for Digital Affairs); REGULATOR/SNIPPET_ONLY</t>
-        </is>
-      </c>
-      <c r="S41" s="3" t="inlineStr">
-        <is>
-          <t>50 – 99 Mbit/s … L2-BSA Überlassungsentgelt … 19,22 €</t>
-        </is>
-      </c>
-      <c r="T41" s="5" t="inlineStr">
-        <is>
-          <t>https://www.bmv.de/SharedDocs/DE/Anlage/DG/vorleistungspreise.pdf?__blob=publicationFile</t>
-        </is>
-      </c>
+          <t>run narrative (the disposition was replaced)</t>
+        </is>
+      </c>
+      <c r="S41" s="3" t="inlineStr"/>
+      <c r="T41" s="5" t="inlineStr"/>
       <c r="U41" s="5" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="V41" s="5" t="inlineStr">
         <is>
-          <t>fresenius</t>
+          <t>carrefour</t>
         </is>
       </c>
       <c r="W41" s="12" t="n">
@@ -5465,33 +5445,29 @@
       <c r="Y41" s="3" t="inlineStr"/>
       <c r="Z41" s="3" t="inlineStr">
         <is>
-          <t>50 Mbps at 64 &gt; 75 Mbps at 22 USD</t>
-        </is>
-      </c>
-      <c r="AA41" s="3" t="inlineStr">
-        <is>
-          <t>fresenius 19.22 EUR</t>
-        </is>
-      </c>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="AA41" s="3" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>DE-BROADBAND_PON-150-researched</t>
+          <t>ES-DIA-1000-researched</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>BROADBAND_PON</t>
+          <t>DIA</t>
         </is>
       </c>
       <c r="D42" s="5" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="E42" s="14" t="inlineStr">
         <is>
@@ -5505,7 +5481,7 @@
       </c>
       <c r="G42" s="8" t="inlineStr">
         <is>
-          <t>A wholesale bitstream price cap for subsidised networks (BMDV L2-BSA). A business pays the retail price on top of it.</t>
+          <t>Rejected against a second Spanish source: Kompara's 2026 market range for 1 Gbps dedicated fibre is EUR 700-1,200, and Direct Telecom's own page also lists a 1 Gbps dedicated circuit at EUR 1,860 - EUR 449 is the cheaper of its two figures. The seed it would replace, EUR 1,132, sits inside the range.</t>
         </is>
       </c>
       <c r="H42" s="9">
@@ -5517,7 +5493,7 @@
         <v/>
       </c>
       <c r="J42" s="10" t="n">
-        <v>21.55</v>
+        <v>449</v>
       </c>
       <c r="K42" s="5" t="inlineStr">
         <is>
@@ -5525,80 +5501,74 @@
         </is>
       </c>
       <c r="L42" s="10" t="n">
-        <v>24.74</v>
-      </c>
-      <c r="M42" s="10" t="n"/>
+        <v>515.4400000000001</v>
+      </c>
+      <c r="M42" s="10" t="n">
+        <v>1300</v>
+      </c>
       <c r="N42" s="11">
         <f>IF(OR(L42="",M42=""),"",L42/M42)</f>
         <v/>
       </c>
       <c r="O42" s="5" t="inlineStr">
         <is>
-          <t>none - new tier</t>
+          <t>SEED</t>
         </is>
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
-          <t>wholesale; read from a snippet; re-prices lower tiers</t>
-        </is>
-      </c>
-      <c r="Q42" s="3" t="inlineStr">
-        <is>
-          <t>DE BROADBAND_PON wholesale bitstream L2-BSA 100-199 Mbps MRC (regulatory price cap)</t>
-        </is>
-      </c>
+          <t>single source; re-prices lower tiers</t>
+        </is>
+      </c>
+      <c r="Q42" s="3" t="inlineStr"/>
       <c r="R42" s="5" t="inlineStr">
         <is>
-          <t>BMDV / Bundesnetzagentur; REGULATOR/SNIPPET_ONLY</t>
+          <t>run narrative (the disposition was replaced)</t>
         </is>
       </c>
       <c r="S42" s="3" t="inlineStr">
         <is>
-          <t>100 – 199 Mbit/s … L2-BSA … 21,55 €</t>
-        </is>
-      </c>
-      <c r="T42" s="5" t="inlineStr">
-        <is>
-          <t>https://www.bmv.de/SharedDocs/DE/Anlage/DG/vorleistungspreise.pdf?__blob=publicationFile</t>
-        </is>
-      </c>
+          <t>ional players plus resellers. Telefónica Global Solutions offers DIA on its own Tier 1 global infrastructure. A domestic reseller (Direct Telecom) lists 100/100 Mbps DIA at €159.99/month and 1 Gbps dedicated circuit at €449/month (2025 prices). Telefónica and MasOrange are exploring acquisition of Vodafone España (as of mid-2025); if completed this would reduce the market to three</t>
+        </is>
+      </c>
+      <c r="T42" s="5" t="inlineStr"/>
       <c r="U42" s="5" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="V42" s="5" t="inlineStr">
         <is>
-          <t>fresenius</t>
+          <t>inditex</t>
         </is>
       </c>
       <c r="W42" s="12" t="n">
-        <v>0</v>
+        <v>-229632.48</v>
       </c>
       <c r="X42" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y42" s="3" t="inlineStr"/>
+        <v>28</v>
+      </c>
+      <c r="Y42" s="3" t="inlineStr">
+        <is>
+          <t>iberdrola -164,023; volkswagen -65,609</t>
+        </is>
+      </c>
       <c r="Z42" s="3" t="inlineStr">
         <is>
-          <t>100 Mbps at 78 &gt; 150 Mbps at 25 USD</t>
-        </is>
-      </c>
-      <c r="AA42" s="3" t="inlineStr">
-        <is>
-          <t>fresenius 21.55 EUR</t>
-        </is>
-      </c>
+          <t>500 Mbps at 1196 &gt; 1000 Mbps at 515 USD</t>
+        </is>
+      </c>
+      <c r="AA42" s="3" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>DE-BROADBAND_PON-750-researched</t>
+          <t>FR-BROADBAND_PON-100-researched</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
@@ -5607,7 +5577,7 @@
         </is>
       </c>
       <c r="D43" s="5" t="n">
-        <v>750</v>
+        <v>100</v>
       </c>
       <c r="E43" s="14" t="inlineStr">
         <is>
@@ -5621,7 +5591,7 @@
       </c>
       <c r="G43" s="8" t="inlineStr">
         <is>
-          <t>A wholesale bitstream price cap for subsidised networks (BMDV L2-BSA). A business pays the retail price on top of it.</t>
+          <t>ARCEP's cheapest consumer double-play range, incl. VAT, not a business tariff.</t>
         </is>
       </c>
       <c r="H43" s="9">
@@ -5633,7 +5603,7 @@
         <v/>
       </c>
       <c r="J43" s="10" t="n">
-        <v>30.74</v>
+        <v>26.12</v>
       </c>
       <c r="K43" s="5" t="inlineStr">
         <is>
@@ -5641,93 +5611,95 @@
         </is>
       </c>
       <c r="L43" s="10" t="n">
-        <v>35.29</v>
-      </c>
-      <c r="M43" s="10" t="n"/>
+        <v>29.99</v>
+      </c>
+      <c r="M43" s="10" t="n">
+        <v>68</v>
+      </c>
       <c r="N43" s="11">
         <f>IF(OR(L43="",M43=""),"",L43/M43)</f>
         <v/>
       </c>
       <c r="O43" s="5" t="inlineStr">
         <is>
-          <t>none - new tier</t>
+          <t>SEED</t>
         </is>
       </c>
       <c r="P43" s="3" t="inlineStr">
         <is>
-          <t>wholesale; read from a snippet; re-prices lower tiers</t>
+          <t>consumer; single source; read from a snippet; re-prices lower tiers</t>
         </is>
       </c>
       <c r="Q43" s="3" t="inlineStr">
         <is>
-          <t>DE BROADBAND_PON wholesale bitstream L2-BSA 500-999 Mbps MRC (regulatory price cap)</t>
+          <t>BROADBAND_PON France cheapest FttH/coaxial consumer double-play plan</t>
         </is>
       </c>
       <c r="R43" s="5" t="inlineStr">
         <is>
-          <t>BMDV / Bundesnetzagentur; REGULATOR/SNIPPET_ONLY</t>
+          <t>ARCEP; REGULATOR/SNIPPET_ONLY</t>
         </is>
       </c>
       <c r="S43" s="3" t="inlineStr">
         <is>
-          <t>500 – 999 Mbit/s … L2-BSA … 30,74 €</t>
+          <t>Les tarifs mensuels des offres FttH ou avec terminaison coaxiale les moins chères sont compris, en juin 2025, entre 20 € et 36 € TTC</t>
         </is>
       </c>
       <c r="T43" s="5" t="inlineStr">
         <is>
-          <t>https://www.bmv.de/SharedDocs/DE/Anlage/DG/vorleistungspreise.pdf?__blob=publicationFile</t>
+          <t>https://www.arcep.fr/uploads/tx_gspublication/etude-tarifs-services-fixes-France-evolution-2015-2025_janv2026.pdf</t>
         </is>
       </c>
       <c r="U43" s="5" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="V43" s="5" t="inlineStr">
         <is>
-          <t>fresenius</t>
+          <t>air-france-klm</t>
         </is>
       </c>
       <c r="W43" s="12" t="n">
-        <v>-131200.10221975</v>
+        <v>-723966.3278903649</v>
       </c>
       <c r="X43" s="5" t="n">
-        <v>126</v>
+        <v>1784</v>
       </c>
       <c r="Y43" s="3" t="inlineStr">
         <is>
-          <t>basf -38,527; siemens -29,156; volkswagen -29,156</t>
+          <t>bnp-paribas -509,835; heidelberg-materials -93,018; allianz -69,541</t>
         </is>
       </c>
       <c r="Z43" s="3" t="inlineStr">
         <is>
-          <t>500 Mbps at 132 &gt; 750 Mbps at 35 USD</t>
+          <t>50 Mbps at 56 &gt; 100 Mbps at 30 USD</t>
         </is>
       </c>
       <c r="AA43" s="3" t="inlineStr">
         <is>
-          <t>fresenius 30.74 EUR</t>
+          <t>air-france-klm 20 EUR; air-france-klm 36 EUR; air-france-klm 26.12 EUR</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>DE-BROADBAND_PON-1000-researched</t>
+          <t>GB-BROADBAND_HFC-100-researched</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>BROADBAND_PON</t>
+          <t>BROADBAND_HFC</t>
         </is>
       </c>
       <c r="D44" s="5" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="E44" s="14" t="inlineStr">
         <is>
@@ -5741,7 +5713,7 @@
       </c>
       <c r="G44" s="8" t="inlineStr">
         <is>
-          <t>A wholesale bitstream price cap for subsidised networks (BMDV L2-BSA). The source itself says retail will be higher after the margin stack.</t>
+          <t>The Voom 200 price, filed at 100 Mbps as the closest available. GB HFC 200 already carries it.</t>
         </is>
       </c>
       <c r="H44" s="9">
@@ -5753,18 +5725,18 @@
         <v/>
       </c>
       <c r="J44" s="10" t="n">
-        <v>41.97</v>
+        <v>29.95</v>
       </c>
       <c r="K44" s="5" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>GBP</t>
         </is>
       </c>
       <c r="L44" s="10" t="n">
-        <v>48.18</v>
+        <v>40.13</v>
       </c>
       <c r="M44" s="10" t="n">
-        <v>171</v>
+        <v>80</v>
       </c>
       <c r="N44" s="11">
         <f>IF(OR(L44="",M44=""),"",L44/M44)</f>
@@ -5777,79 +5749,79 @@
       </c>
       <c r="P44" s="3" t="inlineStr">
         <is>
-          <t>wholesale; read from a snippet; re-prices lower tiers</t>
+          <t>single source; read from a snippet; re-prices lower tiers</t>
         </is>
       </c>
       <c r="Q44" s="3" t="inlineStr">
         <is>
-          <t>DE BROADBAND_PON wholesale bitstream L2-BSA 1000 Mbps MRC (regulatory price cap)</t>
+          <t>BROADBAND_HFC 100Mbps MRC</t>
         </is>
       </c>
       <c r="R44" s="5" t="inlineStr">
         <is>
-          <t>BMDV / Bundesnetzagentur; REGULATOR/SNIPPET_ONLY</t>
+          <t>Amvia (citing Virgin Media Business); AGGREGATOR/SNIPPET_ONLY</t>
         </is>
       </c>
       <c r="S44" s="3" t="inlineStr">
         <is>
-          <t>1000 Mbit/s … L2-BSA … 41,97 €</t>
+          <t>Virgin Media Business £29.95/mo ex VAT (Voom 200) 24 months</t>
         </is>
       </c>
       <c r="T44" s="5" t="inlineStr">
         <is>
-          <t>https://www.bmv.de/SharedDocs/DE/Anlage/DG/vorleistungspreise.pdf?__blob=publicationFile</t>
+          <t>https://amvia.co.uk/compare/business-broadband</t>
         </is>
       </c>
       <c r="U44" s="5" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="V44" s="5" t="inlineStr">
         <is>
-          <t>fresenius</t>
+          <t>siemens</t>
         </is>
       </c>
       <c r="W44" s="12" t="n">
-        <v>-113710.9553765</v>
+        <v>-200926.0855755058</v>
       </c>
       <c r="X44" s="5" t="n">
-        <v>126</v>
+        <v>464</v>
       </c>
       <c r="Y44" s="3" t="inlineStr">
         <is>
-          <t>basf -33,391; siemens -25,269; volkswagen -25,269</t>
+          <t>saint-gobain -174,237; nhs-england -7,802; network-rail -7,368</t>
         </is>
       </c>
       <c r="Z44" s="3" t="inlineStr">
         <is>
-          <t>500 Mbps at 132 &gt; 1000 Mbps at 48 USD</t>
+          <t>50 Mbps at 65 &gt; 100 Mbps at 40 USD; 250 Mbps at 108 &gt; 400 Mbps at 47 USD; 500 Mbps at 140 &gt; 600 Mbps at 52 USD</t>
         </is>
       </c>
       <c r="AA44" s="3" t="inlineStr">
         <is>
-          <t>fresenius 41.97 EUR</t>
+          <t>siemens ~29.95 GBP</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>ES-DIA-600-researched</t>
+          <t>GB-BROADBAND_HFC-500-researched</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>DIA</t>
+          <t>BROADBAND_HFC</t>
         </is>
       </c>
       <c r="D45" s="5" t="n">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="E45" s="14" t="inlineStr">
         <is>
@@ -5863,7 +5835,7 @@
       </c>
       <c r="G45" s="8" t="inlineStr">
         <is>
-          <t>Rejected against a second Spanish source: a multi-network (3Net) circuit marked approximate pending a site survey, about twice Kompara's EUR 400-600 for 500 Mbps dedicated fibre. No circuit in the set uses it.</t>
+          <t>BT Business Full Fibre 500 at GBP 55 is a fibre (PON) tariff filed under cable (HFC). Virgin's cable range has no 500 tier.</t>
         </is>
       </c>
       <c r="H45" s="9">
@@ -5875,29 +5847,31 @@
         <v/>
       </c>
       <c r="J45" s="10" t="n">
-        <v>1100</v>
+        <v>55</v>
       </c>
       <c r="K45" s="5" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>GBP</t>
         </is>
       </c>
       <c r="L45" s="10" t="n">
-        <v>1262.77</v>
-      </c>
-      <c r="M45" s="10" t="n"/>
+        <v>73.7</v>
+      </c>
+      <c r="M45" s="10" t="n">
+        <v>140</v>
+      </c>
       <c r="N45" s="11">
         <f>IF(OR(L45="",M45=""),"",L45/M45)</f>
         <v/>
       </c>
       <c r="O45" s="5" t="inlineStr">
         <is>
-          <t>none - new tier</t>
+          <t>SEED</t>
         </is>
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
-          <t>single source; untraceable</t>
+          <t>floor; single source; re-prices lower tiers</t>
         </is>
       </c>
       <c r="Q45" s="3" t="inlineStr"/>
@@ -5906,498 +5880,524 @@
           <t>run narrative (the disposition was replaced)</t>
         </is>
       </c>
-      <c r="S45" s="3" t="inlineStr"/>
-      <c r="T45" s="5" t="inlineStr"/>
-      <c r="U45" s="5" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="V45" s="5" t="inlineStr">
-        <is>
-          <t>carrefour</t>
-        </is>
-      </c>
-      <c r="W45" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="X45" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y45" s="3" t="inlineStr"/>
-      <c r="Z45" s="3" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="AA45" s="3" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="5" t="inlineStr">
-        <is>
-          <t>ES-DIA-1000-researched</t>
-        </is>
-      </c>
-      <c r="B46" s="5" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="C46" s="5" t="inlineStr">
-        <is>
-          <t>DIA</t>
-        </is>
-      </c>
-      <c r="D46" s="5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="E46" s="14" t="inlineStr">
-        <is>
-          <t>revoked by Christian Bartosch</t>
-        </is>
-      </c>
-      <c r="F46" s="7" t="inlineStr">
-        <is>
-          <t>Reject</t>
-        </is>
-      </c>
-      <c r="G46" s="8" t="inlineStr">
-        <is>
-          <t>Rejected against a second Spanish source: Kompara's 2026 market range for 1 Gbps dedicated fibre is EUR 700-1,200, and Direct Telecom's own page also lists a 1 Gbps dedicated circuit at EUR 1,860 - EUR 449 is the cheaper of its two figures. The seed it would replace, EUR 1,132, sits inside the range.</t>
-        </is>
-      </c>
-      <c r="H46" s="9">
-        <f>J46*0.75</f>
-        <v/>
-      </c>
-      <c r="I46" s="9">
-        <f>J46*1.25</f>
-        <v/>
-      </c>
-      <c r="J46" s="10" t="n">
-        <v>449</v>
-      </c>
-      <c r="K46" s="5" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="L46" s="10" t="n">
-        <v>515.4400000000001</v>
-      </c>
-      <c r="M46" s="10" t="n">
-        <v>1300</v>
-      </c>
-      <c r="N46" s="11">
-        <f>IF(OR(L46="",M46=""),"",L46/M46)</f>
-        <v/>
-      </c>
-      <c r="O46" s="5" t="inlineStr">
-        <is>
-          <t>SEED</t>
-        </is>
-      </c>
-      <c r="P46" s="3" t="inlineStr">
-        <is>
-          <t>single source; re-prices lower tiers</t>
-        </is>
-      </c>
-      <c r="Q46" s="3" t="inlineStr"/>
-      <c r="R46" s="5" t="inlineStr">
-        <is>
-          <t>run narrative (the disposition was replaced)</t>
-        </is>
-      </c>
-      <c r="S46" s="3" t="inlineStr">
-        <is>
-          <t>ional players plus resellers. Telefónica Global Solutions offers DIA on its own Tier 1 global infrastructure. A domestic reseller (Direct Telecom) lists 100/100 Mbps DIA at €159.99/month and 1 Gbps dedicated circuit at €449/month (2025 prices). Telefónica and MasOrange are exploring acquisition of Vodafone España (as of mid-2025); if completed this would reduce the market to three</t>
-        </is>
-      </c>
-      <c r="T46" s="5" t="inlineStr"/>
-      <c r="U46" s="5" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="V46" s="5" t="inlineStr">
-        <is>
-          <t>inditex</t>
-        </is>
-      </c>
-      <c r="W46" s="12" t="n">
-        <v>-229632.48</v>
-      </c>
-      <c r="X46" s="5" t="n">
-        <v>28</v>
-      </c>
-      <c r="Y46" s="3" t="inlineStr">
-        <is>
-          <t>iberdrola -164,023; volkswagen -65,609</t>
-        </is>
-      </c>
-      <c r="Z46" s="3" t="inlineStr">
-        <is>
-          <t>500 Mbps at 1196 &gt; 1000 Mbps at 515 USD</t>
-        </is>
-      </c>
-      <c r="AA46" s="3" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="5" t="inlineStr">
-        <is>
-          <t>FR-BROADBAND_PON-100-researched</t>
-        </is>
-      </c>
-      <c r="B47" s="5" t="inlineStr">
-        <is>
-          <t>FR</t>
-        </is>
-      </c>
-      <c r="C47" s="5" t="inlineStr">
-        <is>
-          <t>BROADBAND_PON</t>
-        </is>
-      </c>
-      <c r="D47" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="E47" s="14" t="inlineStr">
-        <is>
-          <t>revoked by Christian Bartosch</t>
-        </is>
-      </c>
-      <c r="F47" s="7" t="inlineStr">
-        <is>
-          <t>Reject</t>
-        </is>
-      </c>
-      <c r="G47" s="8" t="inlineStr">
-        <is>
-          <t>ARCEP's cheapest consumer double-play range, incl. VAT, not a business tariff.</t>
-        </is>
-      </c>
-      <c r="H47" s="9">
-        <f>J47*0.75</f>
-        <v/>
-      </c>
-      <c r="I47" s="9">
-        <f>J47*1.25</f>
-        <v/>
-      </c>
-      <c r="J47" s="10" t="n">
-        <v>26.12</v>
-      </c>
-      <c r="K47" s="5" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="L47" s="10" t="n">
-        <v>29.99</v>
-      </c>
-      <c r="M47" s="10" t="n">
-        <v>68</v>
-      </c>
-      <c r="N47" s="11">
-        <f>IF(OR(L47="",M47=""),"",L47/M47)</f>
-        <v/>
-      </c>
-      <c r="O47" s="5" t="inlineStr">
-        <is>
-          <t>SEED</t>
-        </is>
-      </c>
-      <c r="P47" s="3" t="inlineStr">
-        <is>
-          <t>consumer; single source; read from a snippet; re-prices lower tiers</t>
-        </is>
-      </c>
-      <c r="Q47" s="3" t="inlineStr">
-        <is>
-          <t>BROADBAND_PON France cheapest FttH/coaxial consumer double-play plan</t>
-        </is>
-      </c>
-      <c r="R47" s="5" t="inlineStr">
-        <is>
-          <t>ARCEP; REGULATOR/SNIPPET_ONLY</t>
-        </is>
-      </c>
-      <c r="S47" s="3" t="inlineStr">
-        <is>
-          <t>Les tarifs mensuels des offres FttH ou avec terminaison coaxiale les moins chères sont compris, en juin 2025, entre 20 € et 36 € TTC</t>
-        </is>
-      </c>
-      <c r="T47" s="5" t="inlineStr">
-        <is>
-          <t>https://www.arcep.fr/uploads/tx_gspublication/etude-tarifs-services-fixes-France-evolution-2015-2025_janv2026.pdf</t>
-        </is>
-      </c>
-      <c r="U47" s="5" t="inlineStr">
-        <is>
-          <t>2025-06</t>
-        </is>
-      </c>
-      <c r="V47" s="5" t="inlineStr">
-        <is>
-          <t>air-france-klm</t>
-        </is>
-      </c>
-      <c r="W47" s="12" t="n">
-        <v>-723966.3278903649</v>
-      </c>
-      <c r="X47" s="5" t="n">
-        <v>1784</v>
-      </c>
-      <c r="Y47" s="3" t="inlineStr">
-        <is>
-          <t>bnp-paribas -509,835; heidelberg-materials -93,018; allianz -69,541</t>
-        </is>
-      </c>
-      <c r="Z47" s="3" t="inlineStr">
-        <is>
-          <t>50 Mbps at 56 &gt; 100 Mbps at 30 USD</t>
-        </is>
-      </c>
-      <c r="AA47" s="3" t="inlineStr">
-        <is>
-          <t>air-france-klm 20 EUR; air-france-klm 36 EUR; air-france-klm 26.12 EUR</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="5" t="inlineStr">
-        <is>
-          <t>GB-BROADBAND_HFC-100-researched</t>
-        </is>
-      </c>
-      <c r="B48" s="5" t="inlineStr">
-        <is>
-          <t>GB</t>
-        </is>
-      </c>
-      <c r="C48" s="5" t="inlineStr">
-        <is>
-          <t>BROADBAND_HFC</t>
-        </is>
-      </c>
-      <c r="D48" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="E48" s="14" t="inlineStr">
-        <is>
-          <t>revoked by Christian Bartosch</t>
-        </is>
-      </c>
-      <c r="F48" s="7" t="inlineStr">
-        <is>
-          <t>Reject</t>
-        </is>
-      </c>
-      <c r="G48" s="8" t="inlineStr">
-        <is>
-          <t>The Voom 200 price, filed at 100 Mbps as the closest available. GB HFC 200 already carries it.</t>
-        </is>
-      </c>
-      <c r="H48" s="9">
-        <f>J48*0.75</f>
-        <v/>
-      </c>
-      <c r="I48" s="9">
-        <f>J48*1.25</f>
-        <v/>
-      </c>
-      <c r="J48" s="10" t="n">
-        <v>29.95</v>
-      </c>
-      <c r="K48" s="5" t="inlineStr">
-        <is>
-          <t>GBP</t>
-        </is>
-      </c>
-      <c r="L48" s="10" t="n">
-        <v>40.13</v>
-      </c>
-      <c r="M48" s="10" t="n">
-        <v>80</v>
-      </c>
-      <c r="N48" s="11">
-        <f>IF(OR(L48="",M48=""),"",L48/M48)</f>
-        <v/>
-      </c>
-      <c r="O48" s="5" t="inlineStr">
-        <is>
-          <t>SEED</t>
-        </is>
-      </c>
-      <c r="P48" s="3" t="inlineStr">
-        <is>
-          <t>single source; read from a snippet; re-prices lower tiers</t>
-        </is>
-      </c>
-      <c r="Q48" s="3" t="inlineStr">
-        <is>
-          <t>BROADBAND_HFC 100Mbps MRC</t>
-        </is>
-      </c>
-      <c r="R48" s="5" t="inlineStr">
-        <is>
-          <t>Amvia (citing Virgin Media Business); AGGREGATOR/SNIPPET_ONLY</t>
-        </is>
-      </c>
-      <c r="S48" s="3" t="inlineStr">
-        <is>
-          <t>Virgin Media Business £29.95/mo ex VAT (Voom 200) 24 months</t>
-        </is>
-      </c>
-      <c r="T48" s="5" t="inlineStr">
-        <is>
-          <t>https://amvia.co.uk/compare/business-broadband</t>
-        </is>
-      </c>
-      <c r="U48" s="5" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="V48" s="5" t="inlineStr">
-        <is>
-          <t>siemens</t>
-        </is>
-      </c>
-      <c r="W48" s="12" t="n">
-        <v>-200926.0855755058</v>
-      </c>
-      <c r="X48" s="5" t="n">
-        <v>464</v>
-      </c>
-      <c r="Y48" s="3" t="inlineStr">
-        <is>
-          <t>saint-gobain -174,237; nhs-england -7,802; network-rail -7,368</t>
-        </is>
-      </c>
-      <c r="Z48" s="3" t="inlineStr">
-        <is>
-          <t>50 Mbps at 65 &gt; 100 Mbps at 40 USD; 250 Mbps at 108 &gt; 400 Mbps at 47 USD; 500 Mbps at 140 &gt; 600 Mbps at 52 USD</t>
-        </is>
-      </c>
-      <c r="AA48" s="3" t="inlineStr">
-        <is>
-          <t>siemens ~29.95 GBP</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="5" t="inlineStr">
-        <is>
-          <t>GB-BROADBAND_HFC-500-researched</t>
-        </is>
-      </c>
-      <c r="B49" s="5" t="inlineStr">
-        <is>
-          <t>GB</t>
-        </is>
-      </c>
-      <c r="C49" s="5" t="inlineStr">
-        <is>
-          <t>BROADBAND_HFC</t>
-        </is>
-      </c>
-      <c r="D49" s="5" t="n">
-        <v>500</v>
-      </c>
-      <c r="E49" s="14" t="inlineStr">
-        <is>
-          <t>revoked by Christian Bartosch</t>
-        </is>
-      </c>
-      <c r="F49" s="7" t="inlineStr">
-        <is>
-          <t>Reject</t>
-        </is>
-      </c>
-      <c r="G49" s="8" t="inlineStr">
-        <is>
-          <t>BT Business Full Fibre 500 at GBP 55 is a fibre (PON) tariff filed under cable (HFC). Virgin's cable range has no 500 tier.</t>
-        </is>
-      </c>
-      <c r="H49" s="9">
-        <f>J49*0.75</f>
-        <v/>
-      </c>
-      <c r="I49" s="9">
-        <f>J49*1.25</f>
-        <v/>
-      </c>
-      <c r="J49" s="10" t="n">
-        <v>55</v>
-      </c>
-      <c r="K49" s="5" t="inlineStr">
-        <is>
-          <t>GBP</t>
-        </is>
-      </c>
-      <c r="L49" s="10" t="n">
-        <v>73.7</v>
-      </c>
-      <c r="M49" s="10" t="n">
-        <v>140</v>
-      </c>
-      <c r="N49" s="11">
-        <f>IF(OR(L49="",M49=""),"",L49/M49)</f>
-        <v/>
-      </c>
-      <c r="O49" s="5" t="inlineStr">
-        <is>
-          <t>SEED</t>
-        </is>
-      </c>
-      <c r="P49" s="3" t="inlineStr">
-        <is>
-          <t>floor; single source; re-prices lower tiers</t>
-        </is>
-      </c>
-      <c r="Q49" s="3" t="inlineStr"/>
-      <c r="R49" s="5" t="inlineStr">
-        <is>
-          <t>run narrative (the disposition was replaced)</t>
-        </is>
-      </c>
-      <c r="S49" s="3" t="inlineStr">
+      <c r="S45" s="3" t="inlineStr">
         <is>
           <t>he model's assumed GB MPLS 100 Mbps of USD 750–1,250/month is within this band.
 **GB — BROADBAND_PON / HFC**
 BT Business published tariffs (verified May 2026): Full Fibre 100 Mbps £35/month ex-VAT; Full Fibre 500 Mbps £55/month; Full Fibre 900 Mbps £65/month. Virgin Media Business (cable/HFC): from £29.95/month. Vodafone Business entry-level fro…</t>
         </is>
       </c>
-      <c r="T49" s="5" t="inlineStr"/>
+      <c r="T45" s="5" t="inlineStr"/>
+      <c r="U45" s="5" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="V45" s="5" t="inlineStr">
+        <is>
+          <t>saint-gobain</t>
+        </is>
+      </c>
+      <c r="W45" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y45" s="3" t="inlineStr"/>
+      <c r="Z45" s="3" t="inlineStr">
+        <is>
+          <t>100 Mbps at 80 &gt; 200 Mbps at 40 USD; 250 Mbps at 108 &gt; 400 Mbps at 47 USD; 500 Mbps at 74 &gt; 600 Mbps at 52 USD</t>
+        </is>
+      </c>
+      <c r="AA45" s="3" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>GB-BROADBAND_PON-1000-researched</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>BROADBAND_PON</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E46" s="14" t="inlineStr">
+        <is>
+          <t>revoked by Christian Bartosch</t>
+        </is>
+      </c>
+      <c r="F46" s="7" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+      <c r="G46" s="8" t="inlineStr">
+        <is>
+          <t>Openreach GEA-FTTP wholesale. Retail ISPs add margin, VAT and equipment.</t>
+        </is>
+      </c>
+      <c r="H46" s="9">
+        <f>J46*0.75</f>
+        <v/>
+      </c>
+      <c r="I46" s="9">
+        <f>J46*1.25</f>
+        <v/>
+      </c>
+      <c r="J46" s="10" t="n">
+        <v>39.1</v>
+      </c>
+      <c r="K46" s="5" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="L46" s="10" t="n">
+        <v>52.39</v>
+      </c>
+      <c r="M46" s="10" t="n">
+        <v>155</v>
+      </c>
+      <c r="N46" s="11">
+        <f>IF(OR(L46="",M46=""),"",L46/M46)</f>
+        <v/>
+      </c>
+      <c r="O46" s="5" t="inlineStr">
+        <is>
+          <t>SEED</t>
+        </is>
+      </c>
+      <c r="P46" s="3" t="inlineStr">
+        <is>
+          <t>wholesale; single source; read from a snippet; re-prices lower tiers</t>
+        </is>
+      </c>
+      <c r="Q46" s="3" t="inlineStr">
+        <is>
+          <t>BROADBAND_PON 1000 Mbps wholesale MRC (Openreach GEA-FTTP, asymmetric)</t>
+        </is>
+      </c>
+      <c r="R46" s="5" t="inlineStr">
+        <is>
+          <t>thinkbroadband.com; TRADE_PRESS/SNIPPET_ONLY</t>
+        </is>
+      </c>
+      <c r="S46" s="3" t="inlineStr">
+        <is>
+          <t>The more common 1000 Mbps download and 115 Mbps upload service is a lot cheaper at £39.10 a month</t>
+        </is>
+      </c>
+      <c r="T46" s="5" t="inlineStr">
+        <is>
+          <t>https://www.thinkbroadband.com/news/openreach-reduces-the-price-of-one-of-its-gigabit-fttp-services</t>
+        </is>
+      </c>
+      <c r="U46" s="5" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="V46" s="5" t="inlineStr">
+        <is>
+          <t>tesco</t>
+        </is>
+      </c>
+      <c r="W46" s="12" t="n">
+        <v>-28389.02</v>
+      </c>
+      <c r="X46" s="5" t="n">
+        <v>39</v>
+      </c>
+      <c r="Y46" s="3" t="inlineStr">
+        <is>
+          <t>saint-gobain -13,831; unilever -8,007; siemens -6,551</t>
+        </is>
+      </c>
+      <c r="Z46" s="3" t="inlineStr">
+        <is>
+          <t>50 Mbps at 58 &gt; 100 Mbps at 47 USD; 500 Mbps at 120 &gt; 1000 Mbps at 52 USD</t>
+        </is>
+      </c>
+      <c r="AA46" s="3" t="inlineStr">
+        <is>
+          <t>tesco 39.10 GBP</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>GB-DIA-50-researched</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>DIA</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="E47" s="14" t="inlineStr">
+        <is>
+          <t>revoked by Christian Bartosch</t>
+        </is>
+      </c>
+      <c r="F47" s="7" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+      <c r="G47" s="8" t="inlineStr">
+        <is>
+          <t>Cambridge Fibre, a regional altnet on a 60-month term. The research itself says it is not a national benchmark.</t>
+        </is>
+      </c>
+      <c r="H47" s="9">
+        <f>J47*0.75</f>
+        <v/>
+      </c>
+      <c r="I47" s="9">
+        <f>J47*1.25</f>
+        <v/>
+      </c>
+      <c r="J47" s="10" t="n">
+        <v>119</v>
+      </c>
+      <c r="K47" s="5" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="L47" s="10" t="n">
+        <v>159.45</v>
+      </c>
+      <c r="M47" s="10" t="n"/>
+      <c r="N47" s="11">
+        <f>IF(OR(L47="",M47=""),"",L47/M47)</f>
+        <v/>
+      </c>
+      <c r="O47" s="5" t="inlineStr">
+        <is>
+          <t>none - new tier</t>
+        </is>
+      </c>
+      <c r="P47" s="3" t="inlineStr">
+        <is>
+          <t>single source; read from a snippet</t>
+        </is>
+      </c>
+      <c r="Q47" s="3" t="inlineStr">
+        <is>
+          <t>DIA 50Mbps MRC</t>
+        </is>
+      </c>
+      <c r="R47" s="5" t="inlineStr">
+        <is>
+          <t>Cambridge Fibre; COMPANY_PUBLISHED/SNIPPET_ONLY</t>
+        </is>
+      </c>
+      <c r="S47" s="3" t="inlineStr">
+        <is>
+          <t>Dedicated Internet 50 Mbps — £119 / month — 60 months</t>
+        </is>
+      </c>
+      <c r="T47" s="5" t="inlineStr">
+        <is>
+          <t>https://www.cambridgefibre.uk/business-dedicated-internet-access</t>
+        </is>
+      </c>
+      <c r="U47" s="5" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="V47" s="5" t="inlineStr">
+        <is>
+          <t>network-rail</t>
+        </is>
+      </c>
+      <c r="W47" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X47" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y47" s="3" t="inlineStr"/>
+      <c r="Z47" s="3" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="AA47" s="3" t="inlineStr">
+        <is>
+          <t>network-rail 119 GBP</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>GB-DIA-100-researched</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>DIA</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E48" s="14" t="inlineStr">
+        <is>
+          <t>revoked by Christian Bartosch</t>
+        </is>
+      </c>
+      <c r="F48" s="7" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+      <c r="G48" s="8" t="inlineStr">
+        <is>
+          <t>Rejected against second sources: the GBP 185 is in Virgin Media Business's FAQ, while the same page lists its 100 Mbps plan from GBP 312. Vodafone is from GBP 206-222 on 60 months and Purple gives GBP 180-350 on 36 (2026). The card's survey band, GBP 150-350, already spans them and records the 185 as its floor.</t>
+        </is>
+      </c>
+      <c r="H48" s="9">
+        <f>J48*0.75</f>
+        <v/>
+      </c>
+      <c r="I48" s="9">
+        <f>J48*1.25</f>
+        <v/>
+      </c>
+      <c r="J48" s="10" t="n">
+        <v>185</v>
+      </c>
+      <c r="K48" s="5" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="L48" s="10" t="n">
+        <v>247.89</v>
+      </c>
+      <c r="M48" s="10" t="n">
+        <v>335</v>
+      </c>
+      <c r="N48" s="11">
+        <f>IF(OR(L48="",M48=""),"",L48/M48)</f>
+        <v/>
+      </c>
+      <c r="O48" s="5" t="inlineStr">
+        <is>
+          <t>SEED</t>
+        </is>
+      </c>
+      <c r="P48" s="3" t="inlineStr">
+        <is>
+          <t>floor; read from a snippet</t>
+        </is>
+      </c>
+      <c r="Q48" s="3" t="inlineStr">
+        <is>
+          <t>GB DIA 100 Mbps MRC – Virgin Media Business published tariff</t>
+        </is>
+      </c>
+      <c r="R48" s="5" t="inlineStr">
+        <is>
+          <t>Virgin Media Business; COMPANY_PUBLISHED/SNIPPET_ONLY</t>
+        </is>
+      </c>
+      <c r="S48" s="3" t="inlineStr">
+        <is>
+          <t>Our packages start at £185 per month which provided 100Mbps upload and download speeds.</t>
+        </is>
+      </c>
+      <c r="T48" s="5" t="inlineStr">
+        <is>
+          <t>https://www.virginmediabusiness.co.uk/connectivity/internet-access/leased-lines-for-business/</t>
+        </is>
+      </c>
+      <c r="U48" s="5" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="V48" s="5" t="inlineStr">
+        <is>
+          <t>unilever</t>
+        </is>
+      </c>
+      <c r="W48" s="12" t="n">
+        <v>-2414090.918069141</v>
+      </c>
+      <c r="X48" s="5" t="n">
+        <v>2429</v>
+      </c>
+      <c r="Y48" s="3" t="inlineStr">
+        <is>
+          <t>nhs-england -1,121,155; saint-gobain -796,760; santander -280,459</t>
+        </is>
+      </c>
+      <c r="Z48" s="3" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="AA48" s="3" t="inlineStr">
+        <is>
+          <t>deutsche-post-dhl 206 GBP; eon 139 GBP; iberdrola 130 GBP; nhs-england 222 GBP; unilever 185 GBP</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>GB-DIA-500-researched</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>DIA</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="n">
+        <v>500</v>
+      </c>
+      <c r="E49" s="14" t="inlineStr">
+        <is>
+          <t>revoked by Christian Bartosch</t>
+        </is>
+      </c>
+      <c r="F49" s="7" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+      <c r="G49" s="8" t="inlineStr">
+        <is>
+          <t>Rejected against second sources: Vodafone's published 'from' price on its longest, 60-month term (GBP 243 without a managed router). Virgin Media Business is from GBP 332 and Purple gives GBP 280-550 (2026). The card now prices 500 Mbps at the survey's GBP 250-600 band.</t>
+        </is>
+      </c>
+      <c r="H49" s="9">
+        <f>J49*0.75</f>
+        <v/>
+      </c>
+      <c r="I49" s="9">
+        <f>J49*1.25</f>
+        <v/>
+      </c>
+      <c r="J49" s="10" t="n">
+        <v>257</v>
+      </c>
+      <c r="K49" s="5" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="L49" s="10" t="n">
+        <v>344.37</v>
+      </c>
+      <c r="M49" s="10" t="n">
+        <v>569</v>
+      </c>
+      <c r="N49" s="11">
+        <f>IF(OR(L49="",M49=""),"",L49/M49)</f>
+        <v/>
+      </c>
+      <c r="O49" s="5" t="inlineStr">
+        <is>
+          <t>SEED</t>
+        </is>
+      </c>
+      <c r="P49" s="3" t="inlineStr">
+        <is>
+          <t>floor; single source; re-prices lower tiers</t>
+        </is>
+      </c>
+      <c r="Q49" s="3" t="inlineStr">
+        <is>
+          <t>DIA 500Mbps MRC – Vodafone Business published retail tariff</t>
+        </is>
+      </c>
+      <c r="R49" s="5" t="inlineStr">
+        <is>
+          <t>Vodafone Business; COMPANY_PUBLISHED/FULL_PAGE</t>
+        </is>
+      </c>
+      <c r="S49" s="3" t="inlineStr">
+        <is>
+          <t>Vodafone Dedicated Internet Access (Managed) 500 Mbps Monthly price from £257 (ex. VAT) 60 months</t>
+        </is>
+      </c>
+      <c r="T49" s="5" t="inlineStr">
+        <is>
+          <t>https://www.vodafone.co.uk/business/connectivity/data-connectivity/dedicated-internet-access</t>
+        </is>
+      </c>
       <c r="U49" s="5" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="V49" s="5" t="inlineStr">
         <is>
-          <t>saint-gobain</t>
+          <t>nhs-england</t>
         </is>
       </c>
       <c r="W49" s="12" t="n">
-        <v>0</v>
+        <v>-1514556.076986082</v>
       </c>
       <c r="X49" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y49" s="3" t="inlineStr"/>
+        <v>520</v>
+      </c>
+      <c r="Y49" s="3" t="inlineStr">
+        <is>
+          <t>deutsche-post-dhl -1,229,843; royal-mail -177,285; ups -73,380</t>
+        </is>
+      </c>
       <c r="Z49" s="3" t="inlineStr">
         <is>
-          <t>100 Mbps at 80 &gt; 200 Mbps at 40 USD; 250 Mbps at 108 &gt; 400 Mbps at 47 USD; 500 Mbps at 74 &gt; 600 Mbps at 52 USD</t>
-        </is>
-      </c>
-      <c r="AA49" s="3" t="inlineStr"/>
+          <t>300 Mbps at 481 &gt; 500 Mbps at 344 USD</t>
+        </is>
+      </c>
+      <c r="AA49" s="3" t="inlineStr">
+        <is>
+          <t>deutsche-post-dhl 243 GBP; nhs-england 257 GBP</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>GB-BROADBAND_PON-1000-researched</t>
+          <t>GB-DIA-1000-researched</t>
         </is>
       </c>
       <c r="B50" s="5" t="inlineStr">
@@ -6407,7 +6407,7 @@
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>BROADBAND_PON</t>
+          <t>DIA</t>
         </is>
       </c>
       <c r="D50" s="5" t="n">
@@ -6425,7 +6425,7 @@
       </c>
       <c r="G50" s="8" t="inlineStr">
         <is>
-          <t>Openreach GEA-FTTP wholesale. Retail ISPs add margin, VAT and equipment.</t>
+          <t>Rejected against second sources: CompareNET's indicative 'from' price is the bottom of every 2026 figure for 1 Gbps - Spitfire from GBP 203, Vodafone from GBP 267-300 (60 months), Virgin Media Business from GBP 358, Purple GBP 340-850. As a 1 Gbps rate it would also undercut the 300 and 500 Mbps tiers.</t>
         </is>
       </c>
       <c r="H50" s="9">
@@ -6437,7 +6437,7 @@
         <v/>
       </c>
       <c r="J50" s="10" t="n">
-        <v>39.1</v>
+        <v>195</v>
       </c>
       <c r="K50" s="5" t="inlineStr">
         <is>
@@ -6445,10 +6445,10 @@
         </is>
       </c>
       <c r="L50" s="10" t="n">
-        <v>52.39</v>
+        <v>261.29</v>
       </c>
       <c r="M50" s="10" t="n">
-        <v>155</v>
+        <v>737</v>
       </c>
       <c r="N50" s="11">
         <f>IF(OR(L50="",M50=""),"",L50/M50)</f>
@@ -6461,65 +6461,65 @@
       </c>
       <c r="P50" s="3" t="inlineStr">
         <is>
-          <t>wholesale; single source; read from a snippet; re-prices lower tiers</t>
+          <t>floor; single source; read from a snippet; re-prices lower tiers</t>
         </is>
       </c>
       <c r="Q50" s="3" t="inlineStr">
         <is>
-          <t>BROADBAND_PON 1000 Mbps wholesale MRC (Openreach GEA-FTTP, asymmetric)</t>
+          <t>GB enterprise leased line (DIA) monthly cost — 1 Gbps enterprise</t>
         </is>
       </c>
       <c r="R50" s="5" t="inlineStr">
         <is>
-          <t>thinkbroadband.com; TRADE_PRESS/SNIPPET_ONLY</t>
+          <t>ComparenetUK; AGGREGATOR/SNIPPET_ONLY</t>
         </is>
       </c>
       <c r="S50" s="3" t="inlineStr">
         <is>
-          <t>The more common 1000 Mbps download and 115 Mbps upload service is a lot cheaper at £39.10 a month</t>
+          <t>1Gbps Symmetric — From £195/month, enterprise-grade with dedicated account manager</t>
         </is>
       </c>
       <c r="T50" s="5" t="inlineStr">
         <is>
-          <t>https://www.thinkbroadband.com/news/openreach-reduces-the-price-of-one-of-its-gigabit-fttp-services</t>
+          <t>https://comparenet.co.uk/dedicated-fibre-leased-lines</t>
         </is>
       </c>
       <c r="U50" s="5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="V50" s="5" t="inlineStr">
         <is>
-          <t>tesco</t>
+          <t>iberdrola</t>
         </is>
       </c>
       <c r="W50" s="12" t="n">
-        <v>-28389.02</v>
+        <v>-659380.2940418924</v>
       </c>
       <c r="X50" s="5" t="n">
-        <v>39</v>
+        <v>133</v>
       </c>
       <c r="Y50" s="3" t="inlineStr">
         <is>
-          <t>saint-gobain -13,831; unilever -8,007; siemens -6,551</t>
+          <t>nhs-england -183,990; siemens -119,345; network-rail -119,345</t>
         </is>
       </c>
       <c r="Z50" s="3" t="inlineStr">
         <is>
-          <t>50 Mbps at 58 &gt; 100 Mbps at 47 USD; 500 Mbps at 120 &gt; 1000 Mbps at 52 USD</t>
+          <t>500 Mbps at 569 &gt; 1000 Mbps at 261 USD</t>
         </is>
       </c>
       <c r="AA50" s="3" t="inlineStr">
         <is>
-          <t>tesco 39.10 GBP</t>
+          <t>deutsche-post-dhl 267 GBP; iberdrola 195 GBP; nhs-england 300 GBP</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>GB-DIA-50-researched</t>
+          <t>GB-DIA-10000-researched</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
@@ -6533,7 +6533,7 @@
         </is>
       </c>
       <c r="D51" s="5" t="n">
-        <v>50</v>
+        <v>10000</v>
       </c>
       <c r="E51" s="14" t="inlineStr">
         <is>
@@ -6547,7 +6547,7 @@
       </c>
       <c r="G51" s="8" t="inlineStr">
         <is>
-          <t>Cambridge Fibre, a regional altnet on a 60-month term. The research itself says it is not a national benchmark.</t>
+          <t>Rejected against second sources: Spitfire's 'from' GBP 450 is about a third of typical 10 Gbps prices - CompareNET from GBP 650, Purple GBP 1,200-3,500 (2026). No circuit in the set uses it.</t>
         </is>
       </c>
       <c r="H51" s="9">
@@ -6559,7 +6559,7 @@
         <v/>
       </c>
       <c r="J51" s="10" t="n">
-        <v>119</v>
+        <v>450</v>
       </c>
       <c r="K51" s="5" t="inlineStr">
         <is>
@@ -6567,7 +6567,7 @@
         </is>
       </c>
       <c r="L51" s="10" t="n">
-        <v>159.45</v>
+        <v>602.97</v>
       </c>
       <c r="M51" s="10" t="n"/>
       <c r="N51" s="11">
@@ -6581,27 +6581,27 @@
       </c>
       <c r="P51" s="3" t="inlineStr">
         <is>
-          <t>single source; read from a snippet</t>
+          <t>single source; read from a snippet; re-prices lower tiers</t>
         </is>
       </c>
       <c r="Q51" s="3" t="inlineStr">
         <is>
-          <t>DIA 50Mbps MRC</t>
+          <t>DIA 10000Mbps MRC (Spitfire, retail)</t>
         </is>
       </c>
       <c r="R51" s="5" t="inlineStr">
         <is>
-          <t>Cambridge Fibre; COMPANY_PUBLISHED/SNIPPET_ONLY</t>
+          <t>Spitfire Networks — product page; COMPANY_PUBLISHED/SNIPPET_ONLY</t>
         </is>
       </c>
       <c r="S51" s="3" t="inlineStr">
         <is>
-          <t>Dedicated Internet 50 Mbps — £119 / month — 60 months</t>
+          <t>10 Gbps From: £450/month — 10Gbps Upload — 10Gbps Download</t>
         </is>
       </c>
       <c r="T51" s="5" t="inlineStr">
         <is>
-          <t>https://www.cambridgefibre.uk/business-dedicated-internet-access</t>
+          <t>https://www.spitfire.co.uk/connectivity/fibre-ethernet-leased-line/</t>
         </is>
       </c>
       <c r="U51" s="5" t="inlineStr">
@@ -6611,7 +6611,7 @@
       </c>
       <c r="V51" s="5" t="inlineStr">
         <is>
-          <t>network-rail</t>
+          <t>deutsche-post-dhl</t>
         </is>
       </c>
       <c r="W51" s="12" t="n">
@@ -6623,12 +6623,12 @@
       <c r="Y51" s="3" t="inlineStr"/>
       <c r="Z51" s="3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>1000 Mbps at 737 &gt; 10000 Mbps at 603 USD</t>
         </is>
       </c>
       <c r="AA51" s="3" t="inlineStr">
         <is>
-          <t>network-rail 119 GBP</t>
+          <t>deutsche-post-dhl 450 GBP</t>
         </is>
       </c>
     </row>
@@ -8040,14 +8040,14 @@
       </c>
       <c r="D13" s="15" t="inlineStr">
         <is>
-          <t>100, 500, 1000, 10000</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E13" s="16" t="n">
         <v>0</v>
       </c>
       <c r="F13" s="16" t="n">
-        <v>-5403847.282126876</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -8496,7 +8496,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E44"/>
+  <dimension ref="A1:E43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -8540,7 +8540,7 @@
         </is>
       </c>
       <c r="B2" s="16" t="n">
-        <v>65839101.18</v>
+        <v>65837836.35</v>
       </c>
       <c r="C2" s="16" t="n">
         <v>-16128633.003194</v>
@@ -8550,7 +8550,7 @@
         <v/>
       </c>
       <c r="E2" s="16" t="n">
-        <v>-3612.983071</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -8560,7 +8560,7 @@
         </is>
       </c>
       <c r="B3" s="16" t="n">
-        <v>19084116.27</v>
+        <v>19070203.07</v>
       </c>
       <c r="C3" s="16" t="n">
         <v>-2729944.141842423</v>
@@ -8570,7 +8570,7 @@
         <v/>
       </c>
       <c r="E3" s="16" t="n">
-        <v>-62507.40702800483</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -8580,7 +8580,7 @@
         </is>
       </c>
       <c r="B4" s="16" t="n">
-        <v>9544151.92</v>
+        <v>9540989.82</v>
       </c>
       <c r="C4" s="16" t="n">
         <v>-1535238.860845505</v>
@@ -8590,7 +8590,7 @@
         <v/>
       </c>
       <c r="E4" s="16" t="n">
-        <v>-12447.14708294252</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -8640,7 +8640,7 @@
         </is>
       </c>
       <c r="B7" s="16" t="n">
-        <v>21820648.8</v>
+        <v>21781122.63</v>
       </c>
       <c r="C7" s="16" t="n">
         <v>-884341.338481</v>
@@ -8650,7 +8650,7 @@
         <v/>
       </c>
       <c r="E7" s="16" t="n">
-        <v>-112905.814612</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -8710,7 +8710,7 @@
         <v/>
       </c>
       <c r="E10" s="16" t="n">
-        <v>-126526.3</v>
+        <v>-7181.45</v>
       </c>
     </row>
     <row r="11">
@@ -8720,7 +8720,7 @@
         </is>
       </c>
       <c r="B11" s="16" t="n">
-        <v>19147742.96</v>
+        <v>18485284.48</v>
       </c>
       <c r="C11" s="16" t="n">
         <v>-349440.29</v>
@@ -8730,7 +8730,7 @@
         <v/>
       </c>
       <c r="E11" s="16" t="n">
-        <v>-1892301.51</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -8750,7 +8750,7 @@
         <v/>
       </c>
       <c r="E12" s="16" t="n">
-        <v>-19890.810643</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -8770,7 +8770,7 @@
         <v/>
       </c>
       <c r="E13" s="16" t="n">
-        <v>-38354.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -8790,7 +8790,7 @@
         <v/>
       </c>
       <c r="E14" s="16" t="n">
-        <v>-153491.6951869222</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -8810,7 +8810,7 @@
         <v/>
       </c>
       <c r="E15" s="16" t="n">
-        <v>-1305144.73499799</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -8850,7 +8850,7 @@
         <v/>
       </c>
       <c r="E17" s="16" t="n">
-        <v>-14918.11016</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -8870,7 +8870,7 @@
         <v/>
       </c>
       <c r="E18" s="16" t="n">
-        <v>-44754.32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -8910,7 +8910,7 @@
         <v/>
       </c>
       <c r="E20" s="16" t="n">
-        <v>-67152.52</v>
+        <v>-7181.45</v>
       </c>
     </row>
     <row r="21">
@@ -8920,7 +8920,7 @@
         </is>
       </c>
       <c r="B21" s="16" t="n">
-        <v>7600305.07</v>
+        <v>7504809.87</v>
       </c>
       <c r="C21" s="16" t="n">
         <v>-61732.40466032427</v>
@@ -8930,7 +8930,7 @@
         <v/>
       </c>
       <c r="E21" s="16" t="n">
-        <v>-402447.4062870159</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -8950,7 +8950,7 @@
         <v/>
       </c>
       <c r="E22" s="16" t="n">
-        <v>-2041166.52</v>
+        <v>-1760707.09</v>
       </c>
     </row>
     <row r="23">
@@ -9030,7 +9030,7 @@
         <v/>
       </c>
       <c r="E26" s="16" t="n">
-        <v>-39781.612575</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -9190,7 +9190,7 @@
         <v/>
       </c>
       <c r="E34" s="16" t="n">
-        <v>-796759.73</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -9276,11 +9276,11 @@
     <row r="39">
       <c r="A39" s="15" t="inlineStr">
         <is>
-          <t>carrefour</t>
+          <t>anglo-american</t>
         </is>
       </c>
       <c r="B39" s="16" t="n">
-        <v>39782444.83</v>
+        <v>373694.9</v>
       </c>
       <c r="C39" s="16" t="n">
         <v>0</v>
@@ -9290,17 +9290,17 @@
         <v/>
       </c>
       <c r="E39" s="16" t="n">
-        <v>-16202.83</v>
+        <v>-16474.2432</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="15" t="inlineStr">
         <is>
-          <t>anglo-american</t>
+          <t>carrefour</t>
         </is>
       </c>
       <c r="B40" s="16" t="n">
-        <v>373694.9</v>
+        <v>39782444.83</v>
       </c>
       <c r="C40" s="16" t="n">
         <v>0</v>
@@ -9310,40 +9310,40 @@
         <v/>
       </c>
       <c r="E40" s="16" t="n">
-        <v>-21446.943683</v>
+        <v>-16202.83</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="15" t="inlineStr">
         <is>
-          <t>eon</t>
+          <t>maersk</t>
         </is>
       </c>
       <c r="B41" s="16" t="n">
-        <v>4934058.18</v>
+        <v>2907843.4</v>
       </c>
       <c r="C41" s="16" t="n">
-        <v>0</v>
+        <v>2575.66848</v>
       </c>
       <c r="D41" s="19">
         <f>IF(B41=0,"",C41/B41)</f>
         <v/>
       </c>
       <c r="E41" s="16" t="n">
-        <v>-39781.62</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="15" t="inlineStr">
         <is>
-          <t>maersk</t>
+          <t>heidelberg-materials</t>
         </is>
       </c>
       <c r="B42" s="16" t="n">
-        <v>2907843.4</v>
+        <v>6531734.23</v>
       </c>
       <c r="C42" s="16" t="n">
-        <v>2575.66848</v>
+        <v>3213.97</v>
       </c>
       <c r="D42" s="19">
         <f>IF(B42=0,"",C42/B42)</f>
@@ -9356,40 +9356,20 @@
     <row r="43">
       <c r="A43" s="15" t="inlineStr">
         <is>
-          <t>heidelberg-materials</t>
+          <t>fresenius</t>
         </is>
       </c>
       <c r="B43" s="16" t="n">
-        <v>6531734.23</v>
+        <v>33199591.55</v>
       </c>
       <c r="C43" s="16" t="n">
-        <v>3213.97</v>
+        <v>635912.58</v>
       </c>
       <c r="D43" s="19">
         <f>IF(B43=0,"",C43/B43)</f>
         <v/>
       </c>
       <c r="E43" s="16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="15" t="inlineStr">
-        <is>
-          <t>fresenius</t>
-        </is>
-      </c>
-      <c r="B44" s="16" t="n">
-        <v>33199591.55</v>
-      </c>
-      <c r="C44" s="16" t="n">
-        <v>635912.58</v>
-      </c>
-      <c r="D44" s="19">
-        <f>IF(B44=0,"",C44/B44)</f>
-        <v/>
-      </c>
-      <c r="E44" s="16" t="n">
         <v>-580601.26</v>
       </c>
     </row>

--- a/docs/price-review.xlsx
+++ b/docs/price-review.xlsx
@@ -542,7 +542,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>Every researched price on the rate card - 28 approved, 25 revoked, 6 undecided - beside the rate it would replace, with its evidence and what its approval does to the sample baselines.</t>
+          <t>Every researched price on the rate card - 29 approved, 25 revoked, 5 undecided - beside the rate it would replace, with its evidence and what its approval does to the sample baselines.</t>
         </is>
       </c>
     </row>
@@ -789,21 +789,21 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>AU-DIA-250-researched</t>
+          <t>BE-BROADBAND_PON-2500-researched</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>DIA</t>
+          <t>BROADBAND_PON</t>
         </is>
       </c>
       <c r="D2" s="5" t="n">
-        <v>250</v>
+        <v>2500</v>
       </c>
       <c r="E2" s="6" t="inlineStr">
         <is>
@@ -817,7 +817,7 @@
       </c>
       <c r="G2" s="8" t="inlineStr">
         <is>
-          <t>Vocus publishes Fast Fibre from A$339/month ex GST. Hold because it is a floor and the same research cites materially higher enterprise dedicated-fibre ranges.</t>
+          <t>Proximus Flex+ is a small-business pack 'from' EUR 95 with services bundled in, not a connectivity price. No circuit in the set uses it.</t>
         </is>
       </c>
       <c r="H2" s="9">
@@ -829,15 +829,15 @@
         <v/>
       </c>
       <c r="J2" s="10" t="n">
-        <v>339</v>
+        <v>95</v>
       </c>
       <c r="K2" s="5" t="inlineStr">
         <is>
-          <t>AUD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="L2" s="10" t="n">
-        <v>229.05</v>
+        <v>109.06</v>
       </c>
       <c r="M2" s="10" t="n"/>
       <c r="N2" s="11">
@@ -851,67 +851,75 @@
       </c>
       <c r="P2" s="3" t="inlineStr">
         <is>
-          <t>single source</t>
-        </is>
-      </c>
-      <c r="Q2" s="3" t="inlineStr"/>
+          <t>floor; single source; re-prices lower tiers</t>
+        </is>
+      </c>
+      <c r="Q2" s="3" t="inlineStr">
+        <is>
+          <t>BROADBAND_PON 2500 Mbps MRC (Proximus Flex+ Giga Fiber 2.5 Gbps)</t>
+        </is>
+      </c>
       <c r="R2" s="5" t="inlineStr">
         <is>
-          <t>run narrative (the disposition was replaced)</t>
+          <t>Proximus (proximus.com press release Jul 2025); COMPANY_PUBLISHED/FULL_PAGE</t>
         </is>
       </c>
       <c r="S2" s="3" t="inlineStr">
         <is>
-          <t>advertised price ~A$65-80/mo (not enterprise). AU DIA (Dedicated Internet Access – direct fibre): Nexthop AU lists 1 Gbps datacenter DIA at A$499/mo (24-month, on-net); Vocus Fast Fibre (direct fibre, enterprise) from A$339/mo excl. GST for 250 Mbps+. AyeTech 2026 guide cites enterprise dedicated fibre 100 Mbps–1 Gbps at A$2,500–A$8,000/mo for large-enterprise/data-centre grade. N</t>
-        </is>
-      </c>
-      <c r="T2" s="5" t="inlineStr"/>
+          <t>Business Flex+ Giga Fiber 2.5 Gbps symmetric: from €95/month</t>
+        </is>
+      </c>
+      <c r="T2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.proximus.com/news/2025/202507-business-flex-plus-packs-as-of-july-1-2025.html</t>
+        </is>
+      </c>
       <c r="U2" s="5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="V2" s="5" t="inlineStr">
         <is>
-          <t>woolworths</t>
+          <t>bnp-paribas</t>
         </is>
       </c>
       <c r="W2" s="12" t="n">
-        <v>-459004.9560810811</v>
+        <v>0</v>
       </c>
       <c r="X2" s="5" t="n">
-        <v>30</v>
-      </c>
-      <c r="Y2" s="3" t="inlineStr">
-        <is>
-          <t>woolworths -459,005</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Y2" s="3" t="inlineStr"/>
       <c r="Z2" s="3" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="AA2" s="3" t="inlineStr"/>
+          <t>1000 Mbps at 136 &gt; 2500 Mbps at 109 USD</t>
+        </is>
+      </c>
+      <c r="AA2" s="3" t="inlineStr">
+        <is>
+          <t>bnp-paribas 95 EUR</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>BE-BROADBAND_PON-2500-researched</t>
+          <t>ES-DIA-100-researched</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>BE</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>BROADBAND_PON</t>
+          <t>DIA</t>
         </is>
       </c>
       <c r="D3" s="5" t="n">
-        <v>2500</v>
+        <v>100</v>
       </c>
       <c r="E3" s="6" t="inlineStr">
         <is>
@@ -925,7 +933,7 @@
       </c>
       <c r="G3" s="8" t="inlineStr">
         <is>
-          <t>Proximus Flex+ is a small-business pack 'from' EUR 95 with services bundled in, not a connectivity price. No circuit in the set uses it.</t>
+          <t>Held: Direct Telecom's EUR 159.99 is a guaranteed rather than dedicated circuit, below Kompara's EUR 200-300 for 100 Mbps dedicated fibre. The card now prices Spain DIA 100 at that range's EUR 250 midpoint as a sourced rate; approving this row would displace it.</t>
         </is>
       </c>
       <c r="H3" s="9">
@@ -937,7 +945,7 @@
         <v/>
       </c>
       <c r="J3" s="10" t="n">
-        <v>95</v>
+        <v>159.99</v>
       </c>
       <c r="K3" s="5" t="inlineStr">
         <is>
@@ -945,80 +953,74 @@
         </is>
       </c>
       <c r="L3" s="10" t="n">
-        <v>109.06</v>
-      </c>
-      <c r="M3" s="10" t="n"/>
+        <v>183.66</v>
+      </c>
+      <c r="M3" s="10" t="n">
+        <v>287</v>
+      </c>
       <c r="N3" s="11">
         <f>IF(OR(L3="",M3=""),"",L3/M3)</f>
         <v/>
       </c>
       <c r="O3" s="5" t="inlineStr">
         <is>
-          <t>none - new tier</t>
+          <t>SEED</t>
         </is>
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
-          <t>floor; single source; re-prices lower tiers</t>
-        </is>
-      </c>
-      <c r="Q3" s="3" t="inlineStr">
-        <is>
-          <t>BROADBAND_PON 2500 Mbps MRC (Proximus Flex+ Giga Fiber 2.5 Gbps)</t>
-        </is>
-      </c>
+          <t>single source</t>
+        </is>
+      </c>
+      <c r="Q3" s="3" t="inlineStr"/>
       <c r="R3" s="5" t="inlineStr">
         <is>
-          <t>Proximus (proximus.com press release Jul 2025); COMPANY_PUBLISHED/FULL_PAGE</t>
+          <t>run narrative (the disposition was replaced)</t>
         </is>
       </c>
       <c r="S3" s="3" t="inlineStr">
         <is>
-          <t>Business Flex+ Giga Fiber 2.5 Gbps symmetric: from €95/month</t>
-        </is>
-      </c>
-      <c r="T3" s="5" t="inlineStr">
-        <is>
-          <t>https://www.proximus.com/news/2025/202507-business-flex-plus-packs-as-of-july-1-2025.html</t>
-        </is>
-      </c>
+          <t>band, MPLS/IP-VPN and SD-WAN from all four national players plus resellers. Telefónica Global Solutions offers DIA on its own Tier 1 global infrastructure. A domestic reseller (Direct Telecom) lists 100/100 Mbps DIA at €159.99/month and 1 Gbps dedicated circuit at €449/month (2025 prices). Telefónica and MasOrange are exploring acquisition of Vodafone España (as of mid-2025); if comp</t>
+        </is>
+      </c>
+      <c r="T3" s="5" t="inlineStr"/>
       <c r="U3" s="5" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="V3" s="5" t="inlineStr">
         <is>
-          <t>bnp-paribas</t>
+          <t>inditex</t>
         </is>
       </c>
       <c r="W3" s="12" t="n">
-        <v>0</v>
+        <v>-2357511.18</v>
       </c>
       <c r="X3" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y3" s="3" t="inlineStr"/>
+        <v>2072</v>
+      </c>
+      <c r="Y3" s="3" t="inlineStr">
+        <is>
+          <t>santander -1,760,707; fresenius -580,601; carrefour -16,203</t>
+        </is>
+      </c>
       <c r="Z3" s="3" t="inlineStr">
         <is>
-          <t>1000 Mbps at 136 &gt; 2500 Mbps at 109 USD</t>
-        </is>
-      </c>
-      <c r="AA3" s="3" t="inlineStr">
-        <is>
-          <t>bnp-paribas 95 EUR</t>
-        </is>
-      </c>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="AA3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>ES-DIA-100-researched</t>
+          <t>SG-DIA-100-researched</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
@@ -1041,7 +1043,7 @@
       </c>
       <c r="G4" s="8" t="inlineStr">
         <is>
-          <t>Held: Direct Telecom's EUR 159.99 is a guaranteed rather than dedicated circuit, below Kompara's EUR 200-300 for 100 Mbps dedicated fibre. The card now prices Spain DIA 100 at that range's EUR 250 midpoint as a sourced rate; approving this row would displace it.</t>
+          <t>Published on SPTel's promotion page (valid to 31 Dec 2026). No circuit in the set uses it.</t>
         </is>
       </c>
       <c r="H4" s="9">
@@ -1053,18 +1055,18 @@
         <v/>
       </c>
       <c r="J4" s="10" t="n">
-        <v>159.99</v>
+        <v>312</v>
       </c>
       <c r="K4" s="5" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>SGD</t>
         </is>
       </c>
       <c r="L4" s="10" t="n">
-        <v>183.66</v>
+        <v>243.75</v>
       </c>
       <c r="M4" s="10" t="n">
-        <v>287</v>
+        <v>660</v>
       </c>
       <c r="N4" s="11">
         <f>IF(OR(L4="",M4=""),"",L4/M4)</f>
@@ -1077,67 +1079,75 @@
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t>single source</t>
-        </is>
-      </c>
-      <c r="Q4" s="3" t="inlineStr"/>
+          <t>single source; read from a snippet</t>
+        </is>
+      </c>
+      <c r="Q4" s="3" t="inlineStr">
+        <is>
+          <t>DIA 100 Mbps MRC — Singapore (SPTel enterprise tariff)</t>
+        </is>
+      </c>
       <c r="R4" s="5" t="inlineStr">
         <is>
-          <t>run narrative (the disposition was replaced)</t>
+          <t>SPTel; COMPANY_PUBLISHED/SNIPPET_ONLY</t>
         </is>
       </c>
       <c r="S4" s="3" t="inlineStr">
         <is>
-          <t>band, MPLS/IP-VPN and SD-WAN from all four national players plus resellers. Telefónica Global Solutions offers DIA on its own Tier 1 global infrastructure. A domestic reseller (Direct Telecom) lists 100/100 Mbps DIA at €159.99/month and 1 Gbps dedicated circuit at €449/month (2025 prices). Telefónica and MasOrange are exploring acquisition of Vodafone España (as of mid-2025); if comp</t>
-        </is>
-      </c>
-      <c r="T4" s="5" t="inlineStr"/>
+          <t>Enterprise Internet 100Mbps $312/mth (on 24-month contract)</t>
+        </is>
+      </c>
+      <c r="T4" s="5" t="inlineStr">
+        <is>
+          <t>https://sptel.com/promotion/business-broadband-singapore/</t>
+        </is>
+      </c>
       <c r="U4" s="5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="V4" s="5" t="inlineStr">
         <is>
-          <t>inditex</t>
+          <t>dbs</t>
         </is>
       </c>
       <c r="W4" s="12" t="n">
-        <v>-2357511.18</v>
+        <v>0</v>
       </c>
       <c r="X4" s="5" t="n">
-        <v>2072</v>
-      </c>
-      <c r="Y4" s="3" t="inlineStr">
-        <is>
-          <t>santander -1,760,707; fresenius -580,601; carrefour -16,203</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Y4" s="3" t="inlineStr"/>
       <c r="Z4" s="3" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AA4" s="3" t="inlineStr"/>
+      <c r="AA4" s="3" t="inlineStr">
+        <is>
+          <t>dbs 312 SGD; dbs 312 SGD</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>SG-DIA-100-researched</t>
+          <t>US-BROADBAND_PON-300-researched</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>DIA</t>
+          <t>BROADBAND_PON</t>
         </is>
       </c>
       <c r="D5" s="5" t="n">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
@@ -1151,7 +1161,7 @@
       </c>
       <c r="G5" s="8" t="inlineStr">
         <is>
-          <t>Published on SPTel's promotion page (valid to 31 Dec 2026). No circuit in the set uses it.</t>
+          <t>AT&amp;T Business Fiber 300, inside AT&amp;T's footprint only. At $70 it is below the national median for 100 Mbps, and would price every US PON circuit up to 300 Mbps at it.</t>
         </is>
       </c>
       <c r="H5" s="9">
@@ -1163,51 +1173,49 @@
         <v/>
       </c>
       <c r="J5" s="10" t="n">
-        <v>312</v>
+        <v>70</v>
       </c>
       <c r="K5" s="5" t="inlineStr">
         <is>
-          <t>SGD</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="L5" s="10" t="n">
-        <v>243.75</v>
-      </c>
-      <c r="M5" s="10" t="n">
-        <v>660</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="M5" s="10" t="n"/>
       <c r="N5" s="11">
         <f>IF(OR(L5="",M5=""),"",L5/M5)</f>
         <v/>
       </c>
       <c r="O5" s="5" t="inlineStr">
         <is>
-          <t>SEED</t>
+          <t>none - new tier</t>
         </is>
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t>single source; read from a snippet</t>
+          <t>read from a snippet; re-prices lower tiers</t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr">
         <is>
-          <t>DIA 100 Mbps MRC — Singapore (SPTel enterprise tariff)</t>
+          <t>BROADBAND_PON 300 Mbps MRC – US (AT&amp;T Business Fiber published rate)</t>
         </is>
       </c>
       <c r="R5" s="5" t="inlineStr">
         <is>
-          <t>SPTel; COMPANY_PUBLISHED/SNIPPET_ONLY</t>
+          <t>business.org (AT&amp;T Business Internet Review 2026); AGGREGATOR/SNIPPET_ONLY</t>
         </is>
       </c>
       <c r="S5" s="3" t="inlineStr">
         <is>
-          <t>Enterprise Internet 100Mbps $312/mth (on 24-month contract)</t>
+          <t>Business Fiber 300: $70.00/mo</t>
         </is>
       </c>
       <c r="T5" s="5" t="inlineStr">
         <is>
-          <t>https://sptel.com/promotion/business-broadband-singapore/</t>
+          <t>https://www.business.org/services/internet/att-business-internet-review/</t>
         </is>
       </c>
       <c r="U5" s="5" t="inlineStr">
@@ -1217,45 +1225,49 @@
       </c>
       <c r="V5" s="5" t="inlineStr">
         <is>
-          <t>dbs</t>
+          <t>simmons-bank</t>
         </is>
       </c>
       <c r="W5" s="12" t="n">
-        <v>0</v>
+        <v>-75873.6111235</v>
       </c>
       <c r="X5" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y5" s="3" t="inlineStr"/>
+        <v>243</v>
+      </c>
+      <c r="Y5" s="3" t="inlineStr">
+        <is>
+          <t>simmons-bank -39,654; basf -8,430; siemens -7,181</t>
+        </is>
+      </c>
       <c r="Z5" s="3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>250 Mbps at 114 &gt; 300 Mbps at 70 USD</t>
         </is>
       </c>
       <c r="AA5" s="3" t="inlineStr">
         <is>
-          <t>dbs 312 SGD; dbs 312 SGD</t>
+          <t>simmons-bank 70 USD</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>US-BROADBAND_PON-300-researched</t>
+          <t>ZA-DIA-100-researched</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>ZA</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>BROADBAND_PON</t>
+          <t>DIA</t>
         </is>
       </c>
       <c r="D6" s="5" t="n">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
@@ -1269,7 +1281,7 @@
       </c>
       <c r="G6" s="8" t="inlineStr">
         <is>
-          <t>AT&amp;T Business Fiber 300, inside AT&amp;T's footprint only. At $70 it is below the national median for 100 Mbps, and would price every US PON circuit up to 300 Mbps at it.</t>
+          <t>MWCom 'from around R8,000'; the same research gives R8,000-25,000 depending on distance and capacity.</t>
         </is>
       </c>
       <c r="H6" s="9">
@@ -1281,15 +1293,15 @@
         <v/>
       </c>
       <c r="J6" s="10" t="n">
-        <v>70</v>
+        <v>8000</v>
       </c>
       <c r="K6" s="5" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>ZAR</t>
         </is>
       </c>
       <c r="L6" s="10" t="n">
-        <v>70</v>
+        <v>444.44</v>
       </c>
       <c r="M6" s="10" t="n"/>
       <c r="N6" s="11">
@@ -1303,27 +1315,27 @@
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t>read from a snippet; re-prices lower tiers</t>
+          <t>floor; read from a snippet</t>
         </is>
       </c>
       <c r="Q6" s="3" t="inlineStr">
         <is>
-          <t>BROADBAND_PON 300 Mbps MRC – US (AT&amp;T Business Fiber published rate)</t>
+          <t>DIA 100 Mbps MRC ZA (leased line / dedicated fibre)</t>
         </is>
       </c>
       <c r="R6" s="5" t="inlineStr">
         <is>
-          <t>business.org (AT&amp;T Business Internet Review 2026); AGGREGATOR/SNIPPET_ONLY</t>
+          <t>mwcom.co.za; COMPANY_PUBLISHED/SNIPPET_ONLY</t>
         </is>
       </c>
       <c r="S6" s="3" t="inlineStr">
         <is>
-          <t>Business Fiber 300: $70.00/mo</t>
+          <t>Leased lines start from around R8,000/mo for 100 Mbps symmetric.</t>
         </is>
       </c>
       <c r="T6" s="5" t="inlineStr">
         <is>
-          <t>https://www.business.org/services/internet/att-business-internet-review/</t>
+          <t>https://www.mwcom.co.za/business-internet-south-africa</t>
         </is>
       </c>
       <c r="U6" s="5" t="inlineStr">
@@ -1333,63 +1345,59 @@
       </c>
       <c r="V6" s="5" t="inlineStr">
         <is>
-          <t>simmons-bank</t>
+          <t>not recorded</t>
         </is>
       </c>
       <c r="W6" s="12" t="n">
-        <v>-75873.6111235</v>
+        <v>-16474.2432</v>
       </c>
       <c r="X6" s="5" t="n">
-        <v>243</v>
+        <v>1</v>
       </c>
       <c r="Y6" s="3" t="inlineStr">
         <is>
-          <t>simmons-bank -39,654; basf -8,430; siemens -7,181</t>
+          <t>anglo-american -16,474</t>
         </is>
       </c>
       <c r="Z6" s="3" t="inlineStr">
         <is>
-          <t>250 Mbps at 114 &gt; 300 Mbps at 70 USD</t>
-        </is>
-      </c>
-      <c r="AA6" s="3" t="inlineStr">
-        <is>
-          <t>simmons-bank 70 USD</t>
-        </is>
-      </c>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="AA6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>ZA-DIA-100-researched</t>
+          <t>AU-BROADBAND_HFC-250-researched</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>ZA</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>DIA</t>
+          <t>BROADBAND_HFC</t>
         </is>
       </c>
       <c r="D7" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>undecided</t>
+        <v>250</v>
+      </c>
+      <c r="E7" s="13" t="inlineStr">
+        <is>
+          <t>approved by Christian Bartosch</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Approve</t>
         </is>
       </c>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>MWCom 'from around R8,000'; the same research gives R8,000-25,000 depending on distance and capacity.</t>
+          <t>Swoop's published standard business nbn 250/100 price of A$104/month. The introductory discount is excluded.</t>
         </is>
       </c>
       <c r="H7" s="9">
@@ -1401,75 +1409,69 @@
         <v/>
       </c>
       <c r="J7" s="10" t="n">
-        <v>8000</v>
+        <v>104</v>
       </c>
       <c r="K7" s="5" t="inlineStr">
         <is>
-          <t>ZAR</t>
+          <t>AUD</t>
         </is>
       </c>
       <c r="L7" s="10" t="n">
-        <v>444.44</v>
-      </c>
-      <c r="M7" s="10" t="n"/>
+        <v>70.27</v>
+      </c>
+      <c r="M7" s="10" t="n">
+        <v>155</v>
+      </c>
       <c r="N7" s="11">
         <f>IF(OR(L7="",M7=""),"",L7/M7)</f>
         <v/>
       </c>
       <c r="O7" s="5" t="inlineStr">
         <is>
-          <t>none - new tier</t>
+          <t>SEED</t>
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t>floor; read from a snippet</t>
-        </is>
-      </c>
-      <c r="Q7" s="3" t="inlineStr">
-        <is>
-          <t>DIA 100 Mbps MRC ZA (leased line / dedicated fibre)</t>
-        </is>
-      </c>
+          <t>single source; re-prices lower tiers</t>
+        </is>
+      </c>
+      <c r="Q7" s="3" t="inlineStr"/>
       <c r="R7" s="5" t="inlineStr">
         <is>
-          <t>mwcom.co.za; COMPANY_PUBLISHED/SNIPPET_ONLY</t>
+          <t>run narrative (the disposition was replaced)</t>
         </is>
       </c>
       <c r="S7" s="3" t="inlineStr">
         <is>
-          <t>Leased lines start from around R8,000/mo for 100 Mbps symmetric.</t>
-        </is>
-      </c>
-      <c r="T7" s="5" t="inlineStr">
-        <is>
-          <t>https://www.mwcom.co.za/business-internet-south-africa</t>
-        </is>
-      </c>
+          <t>ise NBN (symmetric, SLA-backed) list prices in AUD excl. GST: 100/100 Mbps A$399/mo, 250/250 Mbps A$399/mo, 500/500 Mbps A$469/mo, 1000/1000 Mbps A$699/mo (36-month term). Swoop published business NBN prices: 250 Mbps A$104/mo (FTTP), 1000 Mbps A$129/mo (FTTP/HFC). Kookaburra Comms (trade press, 2026) cites typical published range A$400 for 100-250 Mbps to A$700-A$1,500 for 1 Gbps</t>
+        </is>
+      </c>
+      <c r="T7" s="5" t="inlineStr"/>
       <c r="U7" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="V7" s="5" t="inlineStr">
         <is>
-          <t>not recorded</t>
+          <t>woolworths</t>
         </is>
       </c>
       <c r="W7" s="12" t="n">
-        <v>-16474.2432</v>
+        <v>-925814.4972972973</v>
       </c>
       <c r="X7" s="5" t="n">
-        <v>1</v>
+        <v>1130</v>
       </c>
       <c r="Y7" s="3" t="inlineStr">
         <is>
-          <t>anglo-american -16,474</t>
+          <t>woolworths -925,814</t>
         </is>
       </c>
       <c r="Z7" s="3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>100 Mbps at 115 &gt; 250 Mbps at 70 USD; 1000 Mbps at 250 &gt; 2000 Mbps at 149 USD</t>
         </is>
       </c>
       <c r="AA7" s="3" t="inlineStr"/>
@@ -1477,7 +1479,7 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>AU-BROADBAND_HFC-250-researched</t>
+          <t>AU-BROADBAND_HFC-2000-researched</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
@@ -1491,7 +1493,7 @@
         </is>
       </c>
       <c r="D8" s="5" t="n">
-        <v>250</v>
+        <v>2000</v>
       </c>
       <c r="E8" s="13" t="inlineStr">
         <is>
@@ -1505,7 +1507,7 @@
       </c>
       <c r="G8" s="8" t="inlineStr">
         <is>
-          <t>Swoop's published standard business nbn 250/100 price of A$104/month. The introductory discount is excluded.</t>
+          <t>Aussie Broadband business Hyperfast 2000, published; a trade guide puts business fibre plans at A$100-220.</t>
         </is>
       </c>
       <c r="H8" s="9">
@@ -1517,7 +1519,7 @@
         <v/>
       </c>
       <c r="J8" s="10" t="n">
-        <v>104</v>
+        <v>220</v>
       </c>
       <c r="K8" s="5" t="inlineStr">
         <is>
@@ -1525,40 +1527,46 @@
         </is>
       </c>
       <c r="L8" s="10" t="n">
-        <v>70.27</v>
-      </c>
-      <c r="M8" s="10" t="n">
-        <v>155</v>
-      </c>
+        <v>148.65</v>
+      </c>
+      <c r="M8" s="10" t="n"/>
       <c r="N8" s="11">
         <f>IF(OR(L8="",M8=""),"",L8/M8)</f>
         <v/>
       </c>
       <c r="O8" s="5" t="inlineStr">
         <is>
-          <t>SEED</t>
+          <t>none - new tier</t>
         </is>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t>single source; re-prices lower tiers</t>
-        </is>
-      </c>
-      <c r="Q8" s="3" t="inlineStr"/>
+          <t>read from a snippet; re-prices lower tiers</t>
+        </is>
+      </c>
+      <c r="Q8" s="3" t="inlineStr">
+        <is>
+          <t>BROADBAND_HFC AU 2000Mbps MRC (Aussie Broadband Business Hyperfast HFC)</t>
+        </is>
+      </c>
       <c r="R8" s="5" t="inlineStr">
         <is>
-          <t>run narrative (the disposition was replaced)</t>
+          <t>Aussie Broadband / WhistleOut; AGGREGATOR/SNIPPET_ONLY</t>
         </is>
       </c>
       <c r="S8" s="3" t="inlineStr">
         <is>
-          <t>ise NBN (symmetric, SLA-backed) list prices in AUD excl. GST: 100/100 Mbps A$399/mo, 250/250 Mbps A$399/mo, 500/500 Mbps A$469/mo, 1000/1000 Mbps A$699/mo (36-month term). Swoop published business NBN prices: 250 Mbps A$104/mo (FTTP), 1000 Mbps A$129/mo (FTTP/HFC). Kookaburra Comms (trade press, 2026) cites typical published range A$400 for 100-250 Mbps to A$700-A$1,500 for 1 Gbps</t>
-        </is>
-      </c>
-      <c r="T8" s="5" t="inlineStr"/>
+          <t>Aussie Broadband FTTP Business Hyperfast Plus 2000/500 Unlimited Data $220/mth</t>
+        </is>
+      </c>
+      <c r="T8" s="5" t="inlineStr">
+        <is>
+          <t>https://www.whistleout.com.au/Broadband/Guides/NBN-business-plans-compared</t>
+        </is>
+      </c>
       <c r="U8" s="5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="V8" s="5" t="inlineStr">
@@ -1567,27 +1575,27 @@
         </is>
       </c>
       <c r="W8" s="12" t="n">
-        <v>-925814.4972972973</v>
+        <v>0</v>
       </c>
       <c r="X8" s="5" t="n">
-        <v>1130</v>
-      </c>
-      <c r="Y8" s="3" t="inlineStr">
-        <is>
-          <t>woolworths -925,814</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Y8" s="3" t="inlineStr"/>
       <c r="Z8" s="3" t="inlineStr">
         <is>
           <t>100 Mbps at 115 &gt; 250 Mbps at 70 USD; 1000 Mbps at 250 &gt; 2000 Mbps at 149 USD</t>
         </is>
       </c>
-      <c r="AA8" s="3" t="inlineStr"/>
+      <c r="AA8" s="3" t="inlineStr">
+        <is>
+          <t>woolworths 220 AUD</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>AU-BROADBAND_HFC-2000-researched</t>
+          <t>AU-BROADBAND_PON-250-researched</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
@@ -1597,11 +1605,11 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>BROADBAND_HFC</t>
+          <t>BROADBAND_PON</t>
         </is>
       </c>
       <c r="D9" s="5" t="n">
-        <v>2000</v>
+        <v>250</v>
       </c>
       <c r="E9" s="13" t="inlineStr">
         <is>
@@ -1615,7 +1623,7 @@
       </c>
       <c r="G9" s="8" t="inlineStr">
         <is>
-          <t>Aussie Broadband business Hyperfast 2000, published; a trade guide puts business fibre plans at A$100-220.</t>
+          <t>Aussie Broadband business FTTP 250/100, published by the provider and confirmed by an aggregator.</t>
         </is>
       </c>
       <c r="H9" s="9">
@@ -1627,7 +1635,7 @@
         <v/>
       </c>
       <c r="J9" s="10" t="n">
-        <v>220</v>
+        <v>114</v>
       </c>
       <c r="K9" s="5" t="inlineStr">
         <is>
@@ -1635,41 +1643,43 @@
         </is>
       </c>
       <c r="L9" s="10" t="n">
-        <v>148.65</v>
-      </c>
-      <c r="M9" s="10" t="n"/>
+        <v>77.03</v>
+      </c>
+      <c r="M9" s="10" t="n">
+        <v>101</v>
+      </c>
       <c r="N9" s="11">
         <f>IF(OR(L9="",M9=""),"",L9/M9)</f>
         <v/>
       </c>
       <c r="O9" s="5" t="inlineStr">
         <is>
-          <t>none - new tier</t>
+          <t>SEED</t>
         </is>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t>read from a snippet; re-prices lower tiers</t>
+          <t>read from a snippet</t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t>BROADBAND_HFC AU 2000Mbps MRC (Aussie Broadband Business Hyperfast HFC)</t>
+          <t>BROADBAND_PON AU 250Mbps MRC (Aussie Broadband Business FTTP 250/100)</t>
         </is>
       </c>
       <c r="R9" s="5" t="inlineStr">
         <is>
-          <t>Aussie Broadband / WhistleOut; AGGREGATOR/SNIPPET_ONLY</t>
+          <t>Aussie Broadband Enterprise; COMPANY_PUBLISHED/SNIPPET_ONLY</t>
         </is>
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t>Aussie Broadband FTTP Business Hyperfast Plus 2000/500 Unlimited Data $220/mth</t>
+          <t>Superfast Plus 250/100 $114/month</t>
         </is>
       </c>
       <c r="T9" s="5" t="inlineStr">
         <is>
-          <t>https://www.whistleout.com.au/Broadband/Guides/NBN-business-plans-compared</t>
+          <t>https://www.aussiebroadband.com.au/enterprise/internet/nbn-plans/</t>
         </is>
       </c>
       <c r="U9" s="5" t="inlineStr">
@@ -1691,19 +1701,19 @@
       <c r="Y9" s="3" t="inlineStr"/>
       <c r="Z9" s="3" t="inlineStr">
         <is>
-          <t>100 Mbps at 115 &gt; 250 Mbps at 70 USD; 1000 Mbps at 250 &gt; 2000 Mbps at 149 USD</t>
+          <t>no</t>
         </is>
       </c>
       <c r="AA9" s="3" t="inlineStr">
         <is>
-          <t>woolworths 220 AUD</t>
+          <t>woolworths 114 AUD</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>AU-BROADBAND_PON-250-researched</t>
+          <t>AU-DIA-250-researched</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
@@ -1713,7 +1723,7 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>BROADBAND_PON</t>
+          <t>DIA</t>
         </is>
       </c>
       <c r="D10" s="5" t="n">
@@ -1731,19 +1741,17 @@
       </c>
       <c r="G10" s="8" t="inlineStr">
         <is>
-          <t>Aussie Broadband business FTTP 250/100, published by the provider and confirmed by an aggregator.</t>
-        </is>
-      </c>
-      <c r="H10" s="9">
-        <f>J10*0.75</f>
-        <v/>
-      </c>
-      <c r="I10" s="9">
-        <f>J10*1.25</f>
-        <v/>
+          <t>Vocus Fast Fibre 250/250: dedicated 1:1 fibre with internet, a static IP and a 4-hour restoration SLA, at its on-net 48-month price ex GST. Second sources sit within 18%: Telair resells it at A$349 on 36 months, and Vocus and Swoop sell 250/250 nbn Enterprise Ethernet at A$399. The band runs from the 48-month price to the 36-month Enterprise Ethernet one. The A$2,500-8,000 in the same research is data-centre-grade carrier fibre, which no seller publishes.</t>
+        </is>
+      </c>
+      <c r="H10" s="9" t="n">
+        <v>339</v>
+      </c>
+      <c r="I10" s="9" t="n">
+        <v>399</v>
       </c>
       <c r="J10" s="10" t="n">
-        <v>114</v>
+        <v>339</v>
       </c>
       <c r="K10" s="5" t="inlineStr">
         <is>
@@ -1751,48 +1759,38 @@
         </is>
       </c>
       <c r="L10" s="10" t="n">
-        <v>77.03</v>
-      </c>
-      <c r="M10" s="10" t="n">
-        <v>101</v>
-      </c>
+        <v>229.05</v>
+      </c>
+      <c r="M10" s="10" t="n"/>
       <c r="N10" s="11">
         <f>IF(OR(L10="",M10=""),"",L10/M10)</f>
         <v/>
       </c>
       <c r="O10" s="5" t="inlineStr">
         <is>
-          <t>SEED</t>
+          <t>none - new tier</t>
         </is>
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t>read from a snippet</t>
-        </is>
-      </c>
-      <c r="Q10" s="3" t="inlineStr">
-        <is>
-          <t>BROADBAND_PON AU 250Mbps MRC (Aussie Broadband Business FTTP 250/100)</t>
-        </is>
-      </c>
+          <t>single source</t>
+        </is>
+      </c>
+      <c r="Q10" s="3" t="inlineStr"/>
       <c r="R10" s="5" t="inlineStr">
         <is>
-          <t>Aussie Broadband Enterprise; COMPANY_PUBLISHED/SNIPPET_ONLY</t>
+          <t>run narrative (the disposition was replaced)</t>
         </is>
       </c>
       <c r="S10" s="3" t="inlineStr">
         <is>
-          <t>Superfast Plus 250/100 $114/month</t>
-        </is>
-      </c>
-      <c r="T10" s="5" t="inlineStr">
-        <is>
-          <t>https://www.aussiebroadband.com.au/enterprise/internet/nbn-plans/</t>
-        </is>
-      </c>
+          <t>advertised price ~A$65-80/mo (not enterprise). AU DIA (Dedicated Internet Access – direct fibre): Nexthop AU lists 1 Gbps datacenter DIA at A$499/mo (24-month, on-net); Vocus Fast Fibre (direct fibre, enterprise) from A$339/mo excl. GST for 250 Mbps+. AyeTech 2026 guide cites enterprise dedicated fibre 100 Mbps–1 Gbps at A$2,500–A$8,000/mo for large-enterprise/data-centre grade. N</t>
+        </is>
+      </c>
+      <c r="T10" s="5" t="inlineStr"/>
       <c r="U10" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="V10" s="5" t="inlineStr">
@@ -1801,22 +1799,22 @@
         </is>
       </c>
       <c r="W10" s="12" t="n">
-        <v>0</v>
+        <v>-21538.53608108108</v>
       </c>
       <c r="X10" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y10" s="3" t="inlineStr"/>
+        <v>30</v>
+      </c>
+      <c r="Y10" s="3" t="inlineStr">
+        <is>
+          <t>woolworths -21,539</t>
+        </is>
+      </c>
       <c r="Z10" s="3" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AA10" s="3" t="inlineStr">
-        <is>
-          <t>woolworths 114 AUD</t>
-        </is>
-      </c>
+      <c r="AA10" s="3" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
@@ -4820,7 +4818,7 @@
         <v>337.16</v>
       </c>
       <c r="M36" s="10" t="n">
-        <v>1750</v>
+        <v>742</v>
       </c>
       <c r="N36" s="11">
         <f>IF(OR(L36="",M36=""),"",L36/M36)</f>
@@ -4833,7 +4831,7 @@
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
-          <t>consumer; single source; re-prices lower tiers</t>
+          <t>consumer; single source</t>
         </is>
       </c>
       <c r="Q36" s="3" t="inlineStr"/>
@@ -4859,19 +4857,15 @@
         </is>
       </c>
       <c r="W36" s="12" t="n">
-        <v>-416627.1182432433</v>
+        <v>0</v>
       </c>
       <c r="X36" s="5" t="n">
-        <v>30</v>
-      </c>
-      <c r="Y36" s="3" t="inlineStr">
-        <is>
-          <t>woolworths -416,627</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Y36" s="3" t="inlineStr"/>
       <c r="Z36" s="3" t="inlineStr">
         <is>
-          <t>500 Mbps at 1610 &gt; 1000 Mbps at 337 USD</t>
+          <t>no</t>
         </is>
       </c>
       <c r="AA36" s="3" t="inlineStr"/>
@@ -7783,19 +7777,19 @@
       </c>
       <c r="C4" s="15" t="inlineStr">
         <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="D4" s="15" t="inlineStr">
+        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D4" s="15" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
       <c r="E4" s="16" t="n">
-        <v>0</v>
+        <v>-21538.53608108108</v>
       </c>
       <c r="F4" s="16" t="n">
-        <v>-459004.9560810811</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -8620,17 +8614,17 @@
         </is>
       </c>
       <c r="B6" s="16" t="n">
-        <v>5269388.71</v>
+        <v>4756737.94</v>
       </c>
       <c r="C6" s="16" t="n">
-        <v>-1054065.373135135</v>
+        <v>-1075603.909216216</v>
       </c>
       <c r="D6" s="19">
         <f>IF(B6=0,"",C6/B6)</f>
         <v/>
       </c>
       <c r="E6" s="16" t="n">
-        <v>-459004.9560810811</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -9276,11 +9270,11 @@
     <row r="39">
       <c r="A39" s="15" t="inlineStr">
         <is>
-          <t>anglo-american</t>
+          <t>carrefour</t>
         </is>
       </c>
       <c r="B39" s="16" t="n">
-        <v>373694.9</v>
+        <v>39782444.83</v>
       </c>
       <c r="C39" s="16" t="n">
         <v>0</v>
@@ -9290,17 +9284,17 @@
         <v/>
       </c>
       <c r="E39" s="16" t="n">
-        <v>-16474.2432</v>
+        <v>-16202.83</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="15" t="inlineStr">
         <is>
-          <t>carrefour</t>
+          <t>anglo-american</t>
         </is>
       </c>
       <c r="B40" s="16" t="n">
-        <v>39782444.83</v>
+        <v>373694.9</v>
       </c>
       <c r="C40" s="16" t="n">
         <v>0</v>
@@ -9310,7 +9304,7 @@
         <v/>
       </c>
       <c r="E40" s="16" t="n">
-        <v>-16202.83</v>
+        <v>-16474.2432</v>
       </c>
     </row>
     <row r="41">

--- a/docs/price-review.xlsx
+++ b/docs/price-review.xlsx
@@ -1229,14 +1229,14 @@
         </is>
       </c>
       <c r="W5" s="12" t="n">
-        <v>-75873.6111235</v>
+        <v>-39654.109668</v>
       </c>
       <c r="X5" s="5" t="n">
-        <v>243</v>
+        <v>127</v>
       </c>
       <c r="Y5" s="3" t="inlineStr">
         <is>
-          <t>simmons-bank -39,654; basf -8,430; siemens -7,181</t>
+          <t>simmons-bank -39,654</t>
         </is>
       </c>
       <c r="Z5" s="3" t="inlineStr">
@@ -2393,14 +2393,14 @@
         </is>
       </c>
       <c r="W15" s="12" t="n">
-        <v>-106959.98274275</v>
+        <v>-90582.48274275</v>
       </c>
       <c r="X15" s="5" t="n">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="Y15" s="3" t="inlineStr">
         <is>
-          <t>bnp-paribas -29,777; siemens -26,800; capgemini -14,889</t>
+          <t>bnp-paribas -29,777; siemens -26,800; basf -8,933</t>
         </is>
       </c>
       <c r="Z15" s="3" t="inlineStr">
@@ -2633,14 +2633,14 @@
         </is>
       </c>
       <c r="W17" s="12" t="n">
-        <v>-111641.2488303241</v>
+        <v>-87809.68494200001</v>
       </c>
       <c r="X17" s="5" t="n">
-        <v>1916</v>
+        <v>1507</v>
       </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
-          <t>mcdonalds -87,810; deutsche-post-dhl -20,102; royal-mail -2,622</t>
+          <t>mcdonalds -87,810</t>
         </is>
       </c>
       <c r="Z17" s="3" t="inlineStr">
@@ -3795,14 +3795,14 @@
         </is>
       </c>
       <c r="W27" s="12" t="n">
-        <v>-13448332.818288</v>
+        <v>-13669586.085744</v>
       </c>
       <c r="X27" s="5" t="n">
         <v>17371</v>
       </c>
       <c r="Y27" s="3" t="inlineStr">
         <is>
-          <t>mcdonalds -11,026,179; ahold-delhaize -1,096,373; ups -653,236</t>
+          <t>mcdonalds -11,026,179; ahold-delhaize -1,096,373; ups -865,097</t>
         </is>
       </c>
       <c r="Z27" s="3" t="inlineStr">
@@ -4393,10 +4393,10 @@
         </is>
       </c>
       <c r="W32" s="12" t="n">
-        <v>-1331147.0734</v>
+        <v>-1260744.7734</v>
       </c>
       <c r="X32" s="5" t="n">
-        <v>399</v>
+        <v>384</v>
       </c>
       <c r="Y32" s="3" t="inlineStr">
         <is>
@@ -4511,12 +4511,16 @@
         </is>
       </c>
       <c r="W33" s="12" t="n">
-        <v>0</v>
+        <v>311557.63</v>
       </c>
       <c r="X33" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y33" s="3" t="inlineStr"/>
+        <v>15</v>
+      </c>
+      <c r="Y33" s="3" t="inlineStr">
+        <is>
+          <t>capgemini +311,558</t>
+        </is>
+      </c>
       <c r="Z33" s="3" t="inlineStr">
         <is>
           <t>500 Mbps at 1242 &gt; 1000 Mbps at 901 USD</t>
@@ -4627,14 +4631,14 @@
         </is>
       </c>
       <c r="W34" s="12" t="n">
-        <v>-32322.017413</v>
+        <v>-316911.435413</v>
       </c>
       <c r="X34" s="5" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t>shell -32,322</t>
+          <t>capgemini -198,716; novartis -85,873; shell -32,322</t>
         </is>
       </c>
       <c r="Z34" s="3" t="inlineStr">
@@ -5201,16 +5205,12 @@
         </is>
       </c>
       <c r="W39" s="12" t="n">
-        <v>-131200.10221975</v>
+        <v>0</v>
       </c>
       <c r="X39" s="5" t="n">
-        <v>126</v>
-      </c>
-      <c r="Y39" s="3" t="inlineStr">
-        <is>
-          <t>basf -38,527; siemens -29,156; volkswagen -29,156</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Y39" s="3" t="inlineStr"/>
       <c r="Z39" s="3" t="inlineStr">
         <is>
           <t>500 Mbps at 132 &gt; 750 Mbps at 35 USD</t>
@@ -5323,16 +5323,12 @@
         </is>
       </c>
       <c r="W40" s="12" t="n">
-        <v>-113710.9553765</v>
+        <v>0</v>
       </c>
       <c r="X40" s="5" t="n">
-        <v>126</v>
-      </c>
-      <c r="Y40" s="3" t="inlineStr">
-        <is>
-          <t>basf -33,391; siemens -25,269; volkswagen -25,269</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Y40" s="3" t="inlineStr"/>
       <c r="Z40" s="3" t="inlineStr">
         <is>
           <t>500 Mbps at 132 &gt; 1000 Mbps at 48 USD</t>
@@ -5893,12 +5889,16 @@
         </is>
       </c>
       <c r="W45" s="12" t="n">
-        <v>0</v>
+        <v>-294808.3011926232</v>
       </c>
       <c r="X45" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y45" s="3" t="inlineStr"/>
+        <v>409</v>
+      </c>
+      <c r="Y45" s="3" t="inlineStr">
+        <is>
+          <t>deutsche-post-dhl -248,677; royal-mail -32,436; ups -13,695</t>
+        </is>
+      </c>
       <c r="Z45" s="3" t="inlineStr">
         <is>
           <t>100 Mbps at 80 &gt; 200 Mbps at 40 USD; 250 Mbps at 108 &gt; 400 Mbps at 47 USD; 500 Mbps at 74 &gt; 600 Mbps at 52 USD</t>
@@ -6007,16 +6007,12 @@
         </is>
       </c>
       <c r="W46" s="12" t="n">
-        <v>-28389.02</v>
+        <v>0</v>
       </c>
       <c r="X46" s="5" t="n">
-        <v>39</v>
-      </c>
-      <c r="Y46" s="3" t="inlineStr">
-        <is>
-          <t>saint-gobain -13,831; unilever -8,007; siemens -6,551</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Y46" s="3" t="inlineStr"/>
       <c r="Z46" s="3" t="inlineStr">
         <is>
           <t>50 Mbps at 58 &gt; 100 Mbps at 47 USD; 500 Mbps at 120 &gt; 1000 Mbps at 52 USD</t>
@@ -6489,10 +6485,10 @@
         </is>
       </c>
       <c r="W50" s="12" t="n">
-        <v>-659380.2940418924</v>
+        <v>-614625.9740418924</v>
       </c>
       <c r="X50" s="5" t="n">
-        <v>133</v>
+        <v>124</v>
       </c>
       <c r="Y50" s="3" t="inlineStr">
         <is>
@@ -6609,12 +6605,16 @@
         </is>
       </c>
       <c r="W51" s="12" t="n">
-        <v>0</v>
+        <v>56727.13</v>
       </c>
       <c r="X51" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y51" s="3" t="inlineStr"/>
+        <v>9</v>
+      </c>
+      <c r="Y51" s="3" t="inlineStr">
+        <is>
+          <t>capgemini +56,727</t>
+        </is>
+      </c>
       <c r="Z51" s="3" t="inlineStr">
         <is>
           <t>1000 Mbps at 737 &gt; 10000 Mbps at 603 USD</t>
@@ -6843,14 +6843,14 @@
         </is>
       </c>
       <c r="W53" s="12" t="n">
-        <v>-2777012.718631203</v>
+        <v>-1623268.492463442</v>
       </c>
       <c r="X53" s="5" t="n">
-        <v>550</v>
+        <v>317</v>
       </c>
       <c r="Y53" s="3" t="inlineStr">
         <is>
-          <t>nhs-england -1,312,365; saint-gobain -281,152; royal-mail -191,733</t>
+          <t>saint-gobain -281,152; nhs-england -222,993; royal-mail -191,733</t>
         </is>
       </c>
       <c r="Z53" s="3" t="inlineStr">
@@ -6965,14 +6965,14 @@
         </is>
       </c>
       <c r="W54" s="12" t="n">
-        <v>-1352116.562784881</v>
+        <v>-6527385.909447081</v>
       </c>
       <c r="X54" s="5" t="n">
         <v>572</v>
       </c>
       <c r="Y54" s="3" t="inlineStr">
         <is>
-          <t>network-rail -497,440; nhs-england -492,773; saint-gobain -79,161</t>
+          <t>nhs-england -5,423,338; network-rail -497,440; capgemini -222,470</t>
         </is>
       </c>
       <c r="Z54" s="3" t="inlineStr">
@@ -7954,7 +7954,7 @@
         </is>
       </c>
       <c r="E10" s="16" t="n">
-        <v>-106959.98274275</v>
+        <v>-90582.48274275</v>
       </c>
       <c r="F10" s="16" t="n">
         <v>0</v>
@@ -7982,7 +7982,7 @@
         </is>
       </c>
       <c r="E11" s="16" t="n">
-        <v>-6205842.690308512</v>
+        <v>-5791578.692217927</v>
       </c>
       <c r="F11" s="16" t="n">
         <v>0</v>
@@ -8349,7 +8349,7 @@
         <v>212933.9944155</v>
       </c>
       <c r="F24" s="16" t="n">
-        <v>-75873.6111235</v>
+        <v>-39654.109668</v>
       </c>
     </row>
     <row r="25">
@@ -8374,7 +8374,7 @@
         </is>
       </c>
       <c r="E25" s="16" t="n">
-        <v>-912496.4174</v>
+        <v>-530536.4874</v>
       </c>
       <c r="F25" s="16" t="n">
         <v>0</v>
@@ -8402,7 +8402,7 @@
         </is>
       </c>
       <c r="E26" s="16" t="n">
-        <v>-32322.017413</v>
+        <v>-316911.435413</v>
       </c>
       <c r="F26" s="16" t="n">
         <v>0</v>
@@ -8490,7 +8490,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E43"/>
+  <dimension ref="A1:E41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -8594,7 +8594,7 @@
         </is>
       </c>
       <c r="B5" s="16" t="n">
-        <v>27033676.25</v>
+        <v>27048613.67</v>
       </c>
       <c r="C5" s="16" t="n">
         <v>-1094627.74</v>
@@ -8634,10 +8634,10 @@
         </is>
       </c>
       <c r="B7" s="16" t="n">
-        <v>21781122.63</v>
+        <v>21800367.18</v>
       </c>
       <c r="C7" s="16" t="n">
-        <v>-884341.338481</v>
+        <v>-865096.7969280001</v>
       </c>
       <c r="D7" s="19">
         <f>IF(B7=0,"",C7/B7)</f>
@@ -8704,20 +8704,20 @@
         <v/>
       </c>
       <c r="E10" s="16" t="n">
-        <v>-7181.45</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>deutsche-post-dhl</t>
+          <t>rio-tinto</t>
         </is>
       </c>
       <c r="B11" s="16" t="n">
-        <v>18485284.48</v>
+        <v>1330261.85</v>
       </c>
       <c r="C11" s="16" t="n">
-        <v>-349440.29</v>
+        <v>-304559.635439</v>
       </c>
       <c r="D11" s="19">
         <f>IF(B11=0,"",C11/B11)</f>
@@ -8730,14 +8730,14 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>rio-tinto</t>
+          <t>iberdrola</t>
         </is>
       </c>
       <c r="B12" s="16" t="n">
-        <v>1330261.85</v>
+        <v>12775585.03</v>
       </c>
       <c r="C12" s="16" t="n">
-        <v>-304559.635439</v>
+        <v>-243421.43</v>
       </c>
       <c r="D12" s="19">
         <f>IF(B12=0,"",C12/B12)</f>
@@ -8750,14 +8750,14 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>iberdrola</t>
+          <t>network-rail</t>
         </is>
       </c>
       <c r="B13" s="16" t="n">
-        <v>12758906.54</v>
+        <v>5417814.21</v>
       </c>
       <c r="C13" s="16" t="n">
-        <v>-243421.43</v>
+        <v>-216374.5984898834</v>
       </c>
       <c r="D13" s="19">
         <f>IF(B13=0,"",C13/B13)</f>
@@ -8770,14 +8770,14 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>network-rail</t>
+          <t>novartis</t>
         </is>
       </c>
       <c r="B14" s="16" t="n">
-        <v>5417814.21</v>
+        <v>4384828.7</v>
       </c>
       <c r="C14" s="16" t="n">
-        <v>-216374.5984898834</v>
+        <v>-165251.99283375</v>
       </c>
       <c r="D14" s="19">
         <f>IF(B14=0,"",C14/B14)</f>
@@ -8794,7 +8794,7 @@
         </is>
       </c>
       <c r="B15" s="16" t="n">
-        <v>12775674.03</v>
+        <v>17706239.4</v>
       </c>
       <c r="C15" s="16" t="n">
         <v>-161314.9972477556</v>
@@ -8824,7 +8824,7 @@
         <v/>
       </c>
       <c r="E16" s="16" t="n">
-        <v>-8430.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -8850,14 +8850,14 @@
     <row r="18">
       <c r="A18" s="15" t="inlineStr">
         <is>
-          <t>capgemini</t>
+          <t>unilever</t>
         </is>
       </c>
       <c r="B18" s="16" t="n">
-        <v>4674678.59</v>
+        <v>4722081.52</v>
       </c>
       <c r="C18" s="16" t="n">
-        <v>-85290.94</v>
+        <v>-67713.11</v>
       </c>
       <c r="D18" s="19">
         <f>IF(B18=0,"",C18/B18)</f>
@@ -8870,54 +8870,54 @@
     <row r="19">
       <c r="A19" s="15" t="inlineStr">
         <is>
-          <t>novartis</t>
+          <t>santander</t>
         </is>
       </c>
       <c r="B19" s="16" t="n">
-        <v>4345263.33</v>
+        <v>17697685.39</v>
       </c>
       <c r="C19" s="16" t="n">
-        <v>-79378.95483375</v>
+        <v>-57957.48</v>
       </c>
       <c r="D19" s="19">
         <f>IF(B19=0,"",C19/B19)</f>
         <v/>
       </c>
       <c r="E19" s="16" t="n">
-        <v>-2497.9010275</v>
+        <v>-1760707.09</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="15" t="inlineStr">
         <is>
-          <t>unilever</t>
+          <t>volkswagen</t>
         </is>
       </c>
       <c r="B20" s="16" t="n">
-        <v>4722081.52</v>
+        <v>6180254.35</v>
       </c>
       <c r="C20" s="16" t="n">
-        <v>-67713.11</v>
+        <v>-48420.69</v>
       </c>
       <c r="D20" s="19">
         <f>IF(B20=0,"",C20/B20)</f>
         <v/>
       </c>
       <c r="E20" s="16" t="n">
-        <v>-7181.45</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="15" t="inlineStr">
         <is>
-          <t>royal-mail</t>
+          <t>unfi</t>
         </is>
       </c>
       <c r="B21" s="16" t="n">
-        <v>7504809.87</v>
+        <v>1885106.05</v>
       </c>
       <c r="C21" s="16" t="n">
-        <v>-61732.40466032427</v>
+        <v>-38354.045184</v>
       </c>
       <c r="D21" s="19">
         <f>IF(B21=0,"",C21/B21)</f>
@@ -8930,54 +8930,54 @@
     <row r="22">
       <c r="A22" s="15" t="inlineStr">
         <is>
-          <t>santander</t>
+          <t>bayer</t>
         </is>
       </c>
       <c r="B22" s="16" t="n">
-        <v>17697685.39</v>
+        <v>3025050.32</v>
       </c>
       <c r="C22" s="16" t="n">
-        <v>-57957.48</v>
+        <v>-34035.61</v>
       </c>
       <c r="D22" s="19">
         <f>IF(B22=0,"",C22/B22)</f>
         <v/>
       </c>
       <c r="E22" s="16" t="n">
-        <v>-1760707.09</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>volkswagen</t>
+          <t>shell</t>
         </is>
       </c>
       <c r="B23" s="16" t="n">
-        <v>6180254.35</v>
+        <v>12239938.18</v>
       </c>
       <c r="C23" s="16" t="n">
-        <v>-48420.69</v>
+        <v>-32322.017413</v>
       </c>
       <c r="D23" s="19">
         <f>IF(B23=0,"",C23/B23)</f>
         <v/>
       </c>
       <c r="E23" s="16" t="n">
-        <v>-936.71</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>unfi</t>
+          <t>bnp-paribas</t>
         </is>
       </c>
       <c r="B24" s="16" t="n">
-        <v>1885106.05</v>
+        <v>31836939.35</v>
       </c>
       <c r="C24" s="16" t="n">
-        <v>-38354.045184</v>
+        <v>-29777.28</v>
       </c>
       <c r="D24" s="19">
         <f>IF(B24=0,"",C24/B24)</f>
@@ -8990,14 +8990,14 @@
     <row r="25">
       <c r="A25" s="15" t="inlineStr">
         <is>
-          <t>bayer</t>
+          <t>toyota</t>
         </is>
       </c>
       <c r="B25" s="16" t="n">
-        <v>3025050.32</v>
+        <v>2762186.59</v>
       </c>
       <c r="C25" s="16" t="n">
-        <v>-34035.61</v>
+        <v>-17558.74610201351</v>
       </c>
       <c r="D25" s="19">
         <f>IF(B25=0,"",C25/B25)</f>
@@ -9010,14 +9010,14 @@
     <row r="26">
       <c r="A26" s="15" t="inlineStr">
         <is>
-          <t>shell</t>
+          <t>royal-mail</t>
         </is>
       </c>
       <c r="B26" s="16" t="n">
-        <v>12239938.18</v>
+        <v>7550389.03</v>
       </c>
       <c r="C26" s="16" t="n">
-        <v>-32322.017413</v>
+        <v>-16153.23812273885</v>
       </c>
       <c r="D26" s="19">
         <f>IF(B26=0,"",C26/B26)</f>
@@ -9030,14 +9030,14 @@
     <row r="27">
       <c r="A27" s="15" t="inlineStr">
         <is>
-          <t>bnp-paribas</t>
+          <t>michelin</t>
         </is>
       </c>
       <c r="B27" s="16" t="n">
-        <v>31836939.35</v>
+        <v>2771269.98</v>
       </c>
       <c r="C27" s="16" t="n">
-        <v>-29777.28</v>
+        <v>-14943.12</v>
       </c>
       <c r="D27" s="19">
         <f>IF(B27=0,"",C27/B27)</f>
@@ -9050,14 +9050,14 @@
     <row r="28">
       <c r="A28" s="15" t="inlineStr">
         <is>
-          <t>toyota</t>
+          <t>abb</t>
         </is>
       </c>
       <c r="B28" s="16" t="n">
-        <v>2762186.59</v>
+        <v>1159918.54</v>
       </c>
       <c r="C28" s="16" t="n">
-        <v>-17558.74610201351</v>
+        <v>-8419.634472</v>
       </c>
       <c r="D28" s="19">
         <f>IF(B28=0,"",C28/B28)</f>
@@ -9070,14 +9070,14 @@
     <row r="29">
       <c r="A29" s="15" t="inlineStr">
         <is>
-          <t>michelin</t>
+          <t>accor</t>
         </is>
       </c>
       <c r="B29" s="16" t="n">
-        <v>2771269.98</v>
+        <v>8652050.039999999</v>
       </c>
       <c r="C29" s="16" t="n">
-        <v>-14943.12</v>
+        <v>-7444.32</v>
       </c>
       <c r="D29" s="19">
         <f>IF(B29=0,"",C29/B29)</f>
@@ -9090,34 +9090,34 @@
     <row r="30">
       <c r="A30" s="15" t="inlineStr">
         <is>
-          <t>abb</t>
+          <t>henkel</t>
         </is>
       </c>
       <c r="B30" s="16" t="n">
-        <v>1159918.54</v>
+        <v>704177.1899999999</v>
       </c>
       <c r="C30" s="16" t="n">
-        <v>-8419.634472</v>
+        <v>-7429.09</v>
       </c>
       <c r="D30" s="19">
         <f>IF(B30=0,"",C30/B30)</f>
         <v/>
       </c>
       <c r="E30" s="16" t="n">
-        <v>-5308.030428</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>accor</t>
+          <t>danone</t>
         </is>
       </c>
       <c r="B31" s="16" t="n">
-        <v>8652050.039999999</v>
+        <v>3140600.5</v>
       </c>
       <c r="C31" s="16" t="n">
-        <v>-7444.32</v>
+        <v>-7279.6</v>
       </c>
       <c r="D31" s="19">
         <f>IF(B31=0,"",C31/B31)</f>
@@ -9130,34 +9130,34 @@
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>henkel</t>
+          <t>saint-gobain</t>
         </is>
       </c>
       <c r="B32" s="16" t="n">
-        <v>675430.89</v>
+        <v>21144690.36</v>
       </c>
       <c r="C32" s="16" t="n">
-        <v>-7429.09</v>
+        <v>-5967.71</v>
       </c>
       <c r="D32" s="19">
         <f>IF(B32=0,"",C32/B32)</f>
         <v/>
       </c>
       <c r="E32" s="16" t="n">
-        <v>-4683.56</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="15" t="inlineStr">
         <is>
-          <t>danone</t>
+          <t>air-france-klm</t>
         </is>
       </c>
       <c r="B33" s="16" t="n">
-        <v>3140600.5</v>
+        <v>1049026.5</v>
       </c>
       <c r="C33" s="16" t="n">
-        <v>-7279.6</v>
+        <v>-2977.73</v>
       </c>
       <c r="D33" s="19">
         <f>IF(B33=0,"",C33/B33)</f>
@@ -9170,14 +9170,14 @@
     <row r="34">
       <c r="A34" s="15" t="inlineStr">
         <is>
-          <t>saint-gobain</t>
+          <t>dbs</t>
         </is>
       </c>
       <c r="B34" s="16" t="n">
-        <v>21144690.36</v>
+        <v>11630858.38</v>
       </c>
       <c r="C34" s="16" t="n">
-        <v>-5967.71</v>
+        <v>-2199.09195</v>
       </c>
       <c r="D34" s="19">
         <f>IF(B34=0,"",C34/B34)</f>
@@ -9190,14 +9190,14 @@
     <row r="35">
       <c r="A35" s="15" t="inlineStr">
         <is>
-          <t>air-france-klm</t>
+          <t>totalenergies</t>
         </is>
       </c>
       <c r="B35" s="16" t="n">
-        <v>989602.99</v>
+        <v>10952685.28</v>
       </c>
       <c r="C35" s="16" t="n">
-        <v>-2977.73</v>
+        <v>-1369.752484</v>
       </c>
       <c r="D35" s="19">
         <f>IF(B35=0,"",C35/B35)</f>
@@ -9210,54 +9210,54 @@
     <row r="36">
       <c r="A36" s="15" t="inlineStr">
         <is>
-          <t>dbs</t>
+          <t>anglo-american</t>
         </is>
       </c>
       <c r="B36" s="16" t="n">
-        <v>11630858.38</v>
+        <v>373694.9</v>
       </c>
       <c r="C36" s="16" t="n">
-        <v>-2199.09195</v>
+        <v>0</v>
       </c>
       <c r="D36" s="19">
         <f>IF(B36=0,"",C36/B36)</f>
         <v/>
       </c>
       <c r="E36" s="16" t="n">
-        <v>0</v>
+        <v>-16474.2432</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="15" t="inlineStr">
         <is>
-          <t>allianz</t>
+          <t>carrefour</t>
         </is>
       </c>
       <c r="B37" s="16" t="n">
-        <v>17527788.15</v>
+        <v>39782444.83</v>
       </c>
       <c r="C37" s="16" t="n">
-        <v>-1488.86</v>
+        <v>0</v>
       </c>
       <c r="D37" s="19">
         <f>IF(B37=0,"",C37/B37)</f>
         <v/>
       </c>
       <c r="E37" s="16" t="n">
-        <v>0</v>
+        <v>-16202.83</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="15" t="inlineStr">
         <is>
-          <t>totalenergies</t>
+          <t>maersk</t>
         </is>
       </c>
       <c r="B38" s="16" t="n">
-        <v>10952685.28</v>
+        <v>2907843.4</v>
       </c>
       <c r="C38" s="16" t="n">
-        <v>-1369.752484</v>
+        <v>2575.66848</v>
       </c>
       <c r="D38" s="19">
         <f>IF(B38=0,"",C38/B38)</f>
@@ -9270,100 +9270,60 @@
     <row r="39">
       <c r="A39" s="15" t="inlineStr">
         <is>
-          <t>carrefour</t>
+          <t>heidelberg-materials</t>
         </is>
       </c>
       <c r="B39" s="16" t="n">
-        <v>39782444.83</v>
+        <v>6531734.23</v>
       </c>
       <c r="C39" s="16" t="n">
-        <v>0</v>
+        <v>3213.97</v>
       </c>
       <c r="D39" s="19">
         <f>IF(B39=0,"",C39/B39)</f>
         <v/>
       </c>
       <c r="E39" s="16" t="n">
-        <v>-16202.83</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="15" t="inlineStr">
         <is>
-          <t>anglo-american</t>
+          <t>capgemini</t>
         </is>
       </c>
       <c r="B40" s="16" t="n">
-        <v>373694.9</v>
+        <v>5548150.74</v>
       </c>
       <c r="C40" s="16" t="n">
-        <v>0</v>
+        <v>112841.25</v>
       </c>
       <c r="D40" s="19">
         <f>IF(B40=0,"",C40/B40)</f>
         <v/>
       </c>
       <c r="E40" s="16" t="n">
-        <v>-16474.2432</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="15" t="inlineStr">
         <is>
-          <t>maersk</t>
+          <t>fresenius</t>
         </is>
       </c>
       <c r="B41" s="16" t="n">
-        <v>2907843.4</v>
+        <v>33199591.55</v>
       </c>
       <c r="C41" s="16" t="n">
-        <v>2575.66848</v>
+        <v>635912.58</v>
       </c>
       <c r="D41" s="19">
         <f>IF(B41=0,"",C41/B41)</f>
         <v/>
       </c>
       <c r="E41" s="16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="15" t="inlineStr">
-        <is>
-          <t>heidelberg-materials</t>
-        </is>
-      </c>
-      <c r="B42" s="16" t="n">
-        <v>6531734.23</v>
-      </c>
-      <c r="C42" s="16" t="n">
-        <v>3213.97</v>
-      </c>
-      <c r="D42" s="19">
-        <f>IF(B42=0,"",C42/B42)</f>
-        <v/>
-      </c>
-      <c r="E42" s="16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="15" t="inlineStr">
-        <is>
-          <t>fresenius</t>
-        </is>
-      </c>
-      <c r="B43" s="16" t="n">
-        <v>33199591.55</v>
-      </c>
-      <c r="C43" s="16" t="n">
-        <v>635912.58</v>
-      </c>
-      <c r="D43" s="19">
-        <f>IF(B43=0,"",C43/B43)</f>
-        <v/>
-      </c>
-      <c r="E43" s="16" t="n">
         <v>-580601.26</v>
       </c>
     </row>

--- a/docs/price-review.xlsx
+++ b/docs/price-review.xlsx
@@ -6559,14 +6559,16 @@
       <c r="L51" s="10" t="n">
         <v>602.97</v>
       </c>
-      <c r="M51" s="10" t="n"/>
+      <c r="M51" s="10" t="n">
+        <v>2881</v>
+      </c>
       <c r="N51" s="11">
         <f>IF(OR(L51="",M51=""),"",L51/M51)</f>
         <v/>
       </c>
       <c r="O51" s="5" t="inlineStr">
         <is>
-          <t>none - new tier</t>
+          <t>SEED</t>
         </is>
       </c>
       <c r="P51" s="3" t="inlineStr">
@@ -6605,19 +6607,19 @@
         </is>
       </c>
       <c r="W51" s="12" t="n">
-        <v>56727.13</v>
+        <v>-214313.89</v>
       </c>
       <c r="X51" s="5" t="n">
         <v>9</v>
       </c>
       <c r="Y51" s="3" t="inlineStr">
         <is>
-          <t>capgemini +56,727</t>
+          <t>capgemini -214,314</t>
         </is>
       </c>
       <c r="Z51" s="3" t="inlineStr">
         <is>
-          <t>1000 Mbps at 737 &gt; 10000 Mbps at 603 USD</t>
+          <t>9000 Mbps at 2707 &gt; 10000 Mbps at 603 USD</t>
         </is>
       </c>
       <c r="AA51" s="3" t="inlineStr">
@@ -9210,11 +9212,11 @@
     <row r="36">
       <c r="A36" s="15" t="inlineStr">
         <is>
-          <t>anglo-american</t>
+          <t>carrefour</t>
         </is>
       </c>
       <c r="B36" s="16" t="n">
-        <v>373694.9</v>
+        <v>39782444.83</v>
       </c>
       <c r="C36" s="16" t="n">
         <v>0</v>
@@ -9224,17 +9226,17 @@
         <v/>
       </c>
       <c r="E36" s="16" t="n">
-        <v>-16474.2432</v>
+        <v>-16202.83</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="15" t="inlineStr">
         <is>
-          <t>carrefour</t>
+          <t>anglo-american</t>
         </is>
       </c>
       <c r="B37" s="16" t="n">
-        <v>39782444.83</v>
+        <v>373694.9</v>
       </c>
       <c r="C37" s="16" t="n">
         <v>0</v>
@@ -9244,7 +9246,7 @@
         <v/>
       </c>
       <c r="E37" s="16" t="n">
-        <v>-16202.83</v>
+        <v>-16474.2432</v>
       </c>
     </row>
     <row r="38">
@@ -9294,7 +9296,7 @@
         </is>
       </c>
       <c r="B40" s="16" t="n">
-        <v>5548150.74</v>
+        <v>7264743.88</v>
       </c>
       <c r="C40" s="16" t="n">
         <v>112841.25</v>

--- a/docs/price-review.xlsx
+++ b/docs/price-review.xlsx
@@ -8616,7 +8616,7 @@
         </is>
       </c>
       <c r="B6" s="16" t="n">
-        <v>4756737.94</v>
+        <v>4588807.28</v>
       </c>
       <c r="C6" s="16" t="n">
         <v>-1075603.909216216</v>
@@ -8716,7 +8716,7 @@
         </is>
       </c>
       <c r="B11" s="16" t="n">
-        <v>1330261.85</v>
+        <v>1307212.55</v>
       </c>
       <c r="C11" s="16" t="n">
         <v>-304559.635439</v>

--- a/docs/price-review.xlsx
+++ b/docs/price-review.xlsx
@@ -9176,7 +9176,7 @@
         </is>
       </c>
       <c r="B34" s="16" t="n">
-        <v>11630858.38</v>
+        <v>11182416.1</v>
       </c>
       <c r="C34" s="16" t="n">
         <v>-2199.09195</v>

--- a/docs/price-review.xlsx
+++ b/docs/price-review.xlsx
@@ -13,7 +13,7 @@
     <sheet name="By company" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Prices'!$A$1:$AA$60</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Prices'!$A$1:$AB$60</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -542,7 +542,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>Every researched price on the rate card - 29 approved, 25 revoked, 5 undecided - beside the rate it would replace, with its evidence and what its approval does to the sample baselines.</t>
+          <t>Every researched price on the rate card - 29 approved, 5 held, 25 revoked - beside the rate it would replace, with its evidence and what its approval does to the sample baselines.</t>
         </is>
       </c>
     </row>
@@ -617,7 +617,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA60"/>
+  <dimension ref="A1:AB60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -647,6 +647,7 @@
     <col width="38" customWidth="1" min="25" max="25"/>
     <col width="36" customWidth="1" min="26" max="26"/>
     <col width="30" customWidth="1" min="27" max="27"/>
+    <col width="40" customWidth="1" min="28" max="28"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -785,6 +786,11 @@
           <t>Other companies found</t>
         </is>
       </c>
+      <c r="AB1" s="4" t="inlineStr">
+        <is>
+          <t>Traced URL</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
@@ -807,7 +813,7 @@
       </c>
       <c r="E2" s="6" t="inlineStr">
         <is>
-          <t>undecided</t>
+          <t>held by Christian Bartosch</t>
         </is>
       </c>
       <c r="F2" s="7" t="inlineStr">
@@ -901,6 +907,7 @@
           <t>bnp-paribas 95 EUR</t>
         </is>
       </c>
+      <c r="AB2" s="7" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
@@ -923,7 +930,7 @@
       </c>
       <c r="E3" s="6" t="inlineStr">
         <is>
-          <t>undecided</t>
+          <t>held by Christian Bartosch</t>
         </is>
       </c>
       <c r="F3" s="7" t="inlineStr">
@@ -975,7 +982,7 @@
       <c r="Q3" s="3" t="inlineStr"/>
       <c r="R3" s="5" t="inlineStr">
         <is>
-          <t>run narrative (the disposition was replaced)</t>
+          <t>traced in review; REVIEWER_TRACED</t>
         </is>
       </c>
       <c r="S3" s="3" t="inlineStr">
@@ -983,7 +990,11 @@
           <t>band, MPLS/IP-VPN and SD-WAN from all four national players plus resellers. Telefónica Global Solutions offers DIA on its own Tier 1 global infrastructure. A domestic reseller (Direct Telecom) lists 100/100 Mbps DIA at €159.99/month and 1 Gbps dedicated circuit at €449/month (2025 prices). Telefónica and MasOrange are exploring acquisition of Vodafone España (as of mid-2025); if comp</t>
         </is>
       </c>
-      <c r="T3" s="5" t="inlineStr"/>
+      <c r="T3" s="5" t="inlineStr">
+        <is>
+          <t>https://direct-telecom.es/internet/business_class_fibre/</t>
+        </is>
+      </c>
       <c r="U3" s="5" t="inlineStr">
         <is>
           <t>2025</t>
@@ -1011,6 +1022,11 @@
         </is>
       </c>
       <c r="AA3" s="3" t="inlineStr"/>
+      <c r="AB3" s="7" t="inlineStr">
+        <is>
+          <t>https://direct-telecom.es/internet/business_class_fibre/</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
@@ -1033,7 +1049,7 @@
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>undecided</t>
+          <t>held by Christian Bartosch</t>
         </is>
       </c>
       <c r="F4" s="7" t="inlineStr">
@@ -1129,6 +1145,7 @@
           <t>dbs 312 SGD; dbs 312 SGD</t>
         </is>
       </c>
+      <c r="AB4" s="7" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
@@ -1151,7 +1168,7 @@
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>undecided</t>
+          <t>held by Christian Bartosch</t>
         </is>
       </c>
       <c r="F5" s="7" t="inlineStr">
@@ -1249,6 +1266,7 @@
           <t>simmons-bank 70 USD</t>
         </is>
       </c>
+      <c r="AB5" s="7" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
@@ -1271,7 +1289,7 @@
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>undecided</t>
+          <t>held by Christian Bartosch</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
@@ -1365,6 +1383,7 @@
         </is>
       </c>
       <c r="AA6" s="3" t="inlineStr"/>
+      <c r="AB6" s="7" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
@@ -1439,7 +1458,7 @@
       <c r="Q7" s="3" t="inlineStr"/>
       <c r="R7" s="5" t="inlineStr">
         <is>
-          <t>run narrative (the disposition was replaced)</t>
+          <t>traced in review; REVIEWER_TRACED</t>
         </is>
       </c>
       <c r="S7" s="3" t="inlineStr">
@@ -1447,7 +1466,11 @@
           <t>ise NBN (symmetric, SLA-backed) list prices in AUD excl. GST: 100/100 Mbps A$399/mo, 250/250 Mbps A$399/mo, 500/500 Mbps A$469/mo, 1000/1000 Mbps A$699/mo (36-month term). Swoop published business NBN prices: 250 Mbps A$104/mo (FTTP), 1000 Mbps A$129/mo (FTTP/HFC). Kookaburra Comms (trade press, 2026) cites typical published range A$400 for 100-250 Mbps to A$700-A$1,500 for 1 Gbps</t>
         </is>
       </c>
-      <c r="T7" s="5" t="inlineStr"/>
+      <c r="T7" s="5" t="inlineStr">
+        <is>
+          <t>https://www.swoop.com.au/business/nbn/</t>
+        </is>
+      </c>
       <c r="U7" s="5" t="inlineStr">
         <is>
           <t>2025</t>
@@ -1475,6 +1498,11 @@
         </is>
       </c>
       <c r="AA7" s="3" t="inlineStr"/>
+      <c r="AB7" s="7" t="inlineStr">
+        <is>
+          <t>https://www.swoop.com.au/business/nbn/</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
@@ -1591,6 +1619,7 @@
           <t>woolworths 220 AUD</t>
         </is>
       </c>
+      <c r="AB8" s="7" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
@@ -1709,6 +1738,7 @@
           <t>woolworths 114 AUD</t>
         </is>
       </c>
+      <c r="AB9" s="7" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
@@ -1779,7 +1809,7 @@
       <c r="Q10" s="3" t="inlineStr"/>
       <c r="R10" s="5" t="inlineStr">
         <is>
-          <t>run narrative (the disposition was replaced)</t>
+          <t>traced in review; REVIEWER_TRACED</t>
         </is>
       </c>
       <c r="S10" s="3" t="inlineStr">
@@ -1787,7 +1817,11 @@
           <t>advertised price ~A$65-80/mo (not enterprise). AU DIA (Dedicated Internet Access – direct fibre): Nexthop AU lists 1 Gbps datacenter DIA at A$499/mo (24-month, on-net); Vocus Fast Fibre (direct fibre, enterprise) from A$339/mo excl. GST for 250 Mbps+. AyeTech 2026 guide cites enterprise dedicated fibre 100 Mbps–1 Gbps at A$2,500–A$8,000/mo for large-enterprise/data-centre grade. N</t>
         </is>
       </c>
-      <c r="T10" s="5" t="inlineStr"/>
+      <c r="T10" s="5" t="inlineStr">
+        <is>
+          <t>https://www.vocus.com.au/enterprise/internet-and-networks</t>
+        </is>
+      </c>
       <c r="U10" s="5" t="inlineStr">
         <is>
           <t>2025</t>
@@ -1815,6 +1849,11 @@
         </is>
       </c>
       <c r="AA10" s="3" t="inlineStr"/>
+      <c r="AB10" s="7" t="inlineStr">
+        <is>
+          <t>https://www.vocus.com.au/enterprise/internet-and-networks</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
@@ -1935,6 +1974,7 @@
           <t>woolworths 399 AUD</t>
         </is>
       </c>
+      <c r="AB11" s="7" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
@@ -2053,6 +2093,7 @@
           <t>woolworths 469 AUD</t>
         </is>
       </c>
+      <c r="AB12" s="7" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
@@ -2155,14 +2196,14 @@
         </is>
       </c>
       <c r="W13" s="12" t="n">
-        <v>-304559.635439</v>
+        <v>-359538.4892202162</v>
       </c>
       <c r="X13" s="5" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t>rio-tinto -304,560</t>
+          <t>rio-tinto -325,779; woolworths -33,759</t>
         </is>
       </c>
       <c r="Z13" s="3" t="inlineStr">
@@ -2175,6 +2216,7 @@
           <t>woolworths 699 AUD</t>
         </is>
       </c>
+      <c r="AB13" s="7" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -2291,6 +2333,7 @@
           <t>bnp-paribas 60 EUR</t>
         </is>
       </c>
+      <c r="AB14" s="7" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
@@ -2413,6 +2456,7 @@
           <t>bnp-paribas ~1200 EUR</t>
         </is>
       </c>
+      <c r="AB15" s="7" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
@@ -2533,6 +2577,7 @@
           <t>boots 29.95 GBP</t>
         </is>
       </c>
+      <c r="AB16" s="7" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
@@ -2649,6 +2694,7 @@
         </is>
       </c>
       <c r="AA17" s="3" t="inlineStr"/>
+      <c r="AB17" s="7" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
@@ -2761,6 +2807,7 @@
         </is>
       </c>
       <c r="AA18" s="3" t="inlineStr"/>
+      <c r="AB18" s="7" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
@@ -2879,6 +2926,7 @@
           <t>boots 53.95 GBP</t>
         </is>
       </c>
+      <c r="AB19" s="7" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
@@ -2951,7 +2999,7 @@
       <c r="Q20" s="3" t="inlineStr"/>
       <c r="R20" s="5" t="inlineStr">
         <is>
-          <t>run narrative (the disposition was replaced)</t>
+          <t>traced in review; REVIEWER_TRACED</t>
         </is>
       </c>
       <c r="S20" s="3" t="inlineStr">
@@ -2959,7 +3007,11 @@
           <t>e DIA. (2) BROADBAND_HFC: Virgin Media Business publishes HFC/cable broadband: Voom 200 (200 Mbps) from £29.95/month, Voom 400 (400 Mbps) from £34.95/month, Voom Gig1 (1 Gbps) from £43.95/month, Voom Gig2 (2 Gbps) from £83.95/month, all ex-VAT 24-month contract, October 2026. New symmetric XGS-PON (BROADBAND_PON) Full Fibre X plans: 200 Mbps from £39.95/month, 1 Gbps from £53.95/mon</t>
         </is>
       </c>
-      <c r="T20" s="5" t="inlineStr"/>
+      <c r="T20" s="5" t="inlineStr">
+        <is>
+          <t>https://www.virginmediabusiness.co.uk/connectivity/internet-access/business-broadband/</t>
+        </is>
+      </c>
       <c r="U20" s="5" t="inlineStr">
         <is>
           <t>2026</t>
@@ -2983,6 +3035,11 @@
         </is>
       </c>
       <c r="AA20" s="3" t="inlineStr"/>
+      <c r="AB20" s="7" t="inlineStr">
+        <is>
+          <t>https://www.virginmediabusiness.co.uk/connectivity/internet-access/business-broadband/</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
@@ -3057,7 +3114,7 @@
       <c r="Q21" s="3" t="inlineStr"/>
       <c r="R21" s="5" t="inlineStr">
         <is>
-          <t>run narrative (the disposition was replaced)</t>
+          <t>traced in review; REVIEWER_TRACED</t>
         </is>
       </c>
       <c r="S21" s="3" t="inlineStr">
@@ -3067,7 +3124,11 @@
 BT Business published tariffs (verified May 2026): Full Fibre 100 Mbps £35/month ex-VAT; Full Fibre 500 Mbps £55/month; Full Fibre 900 Mbps £65/month. Virgin Media Business (cable/HFC): from £29.95/month. Vodafone Business entry-level</t>
         </is>
       </c>
-      <c r="T21" s="5" t="inlineStr"/>
+      <c r="T21" s="5" t="inlineStr">
+        <is>
+          <t>https://business.bt.com/products/broadband-and-internet/deals/</t>
+        </is>
+      </c>
       <c r="U21" s="5" t="inlineStr">
         <is>
           <t>2026-05</t>
@@ -3097,6 +3158,11 @@
       <c r="AA21" s="3" t="inlineStr">
         <is>
           <t>deutsche-post-dhl 29 GBP</t>
+        </is>
+      </c>
+      <c r="AB21" s="7" t="inlineStr">
+        <is>
+          <t>https://business.bt.com/products/broadband-and-internet/deals/</t>
         </is>
       </c>
     </row>
@@ -3215,6 +3281,7 @@
           <t>ahold-delhaize 348 EUR; deutsche-post-dhl 348 EUR; douglas 348 EUR; maersk 348 EUR; shell ~€348 EUR; shell 348 EUR; unilever 348 EUR; unilever 348 EUR</t>
         </is>
       </c>
+      <c r="AB22" s="7" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
@@ -3337,6 +3404,7 @@
           <t>dbs 118 SGD; dbs 109 SGD</t>
         </is>
       </c>
+      <c r="AB23" s="7" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
@@ -3459,6 +3527,7 @@
           <t>dbs 178 SGD; dbs 53.89 SGD</t>
         </is>
       </c>
+      <c r="AB24" s="7" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
@@ -3575,6 +3644,7 @@
           <t>dbs 4500 USD; maersk 4500 USD</t>
         </is>
       </c>
+      <c r="AB25" s="7" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
@@ -3695,6 +3765,7 @@
           <t>ahold-delhaize 100 USD; ups 100 USD</t>
         </is>
       </c>
+      <c r="AB26" s="7" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
@@ -3815,6 +3886,7 @@
           <t>ahold-delhaize 110 USD; simmons-bank 100 USD</t>
         </is>
       </c>
+      <c r="AB27" s="7" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
@@ -3931,6 +4003,7 @@
           <t>ahold-delhaize 184 USD; simmons-bank 115 USD; ups 184 USD</t>
         </is>
       </c>
+      <c r="AB28" s="7" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
@@ -4051,6 +4124,7 @@
           <t>volkswagen 100 USD</t>
         </is>
       </c>
+      <c r="AB29" s="7" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
@@ -4173,6 +4247,7 @@
           <t>bayer 99 USD</t>
         </is>
       </c>
+      <c r="AB30" s="7" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
@@ -4293,6 +4368,7 @@
           <t>abb 492 USD; ahold-delhaize 333 USD; ahold-delhaize 492 USD; ahold-delhaize 641 USD; basf 492 USD; basf 625 USD; bayer 492 USD; fresenius 492 USD</t>
         </is>
       </c>
+      <c r="AB31" s="7" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
@@ -4413,6 +4489,7 @@
           <t>abb 901 USD; ahold-delhaize 600 USD; ahold-delhaize 901 USD; ahold-delhaize 1312 USD; basf 901 USD; basf 1070 USD; bayer 901 USD; fresenius 901 USD</t>
         </is>
       </c>
+      <c r="AB32" s="7" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
@@ -4531,6 +4608,7 @@
           <t>abb 1987 USD; ahold-delhaize 1987 USD; bayer 1987 USD; fresenius 1987 USD; mcdonalds 1987 USD; siemens 1987 USD; simmons-bank 1987 USD; ups 1987 USD</t>
         </is>
       </c>
+      <c r="AB33" s="7" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
@@ -4631,14 +4709,14 @@
         </is>
       </c>
       <c r="W34" s="12" t="n">
-        <v>-316911.435413</v>
+        <v>-340047.438102</v>
       </c>
       <c r="X34" s="5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t>capgemini -198,716; novartis -85,873; shell -32,322</t>
+          <t>capgemini -213,237; novartis -85,873; shell -33,693</t>
         </is>
       </c>
       <c r="Z34" s="3" t="inlineStr">
@@ -4651,6 +4729,7 @@
           <t>simmons-bank 1807 USD</t>
         </is>
       </c>
+      <c r="AB34" s="7" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
@@ -4767,6 +4846,7 @@
           <t>abb 1439 USD; basf 1439 USD; bayer 1439 USD; maersk 1439 USD; mcdonalds 1439 USD; siemens 1439 USD; simmons-bank 1439 USD; toyota 1439 USD</t>
         </is>
       </c>
+      <c r="AB35" s="7" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
@@ -4841,7 +4921,7 @@
       <c r="Q36" s="3" t="inlineStr"/>
       <c r="R36" s="5" t="inlineStr">
         <is>
-          <t>run narrative (the disposition was replaced)</t>
+          <t>traced in review; REVIEWER_TRACED</t>
         </is>
       </c>
       <c r="S36" s="3" t="inlineStr">
@@ -4849,7 +4929,11 @@
           <t xml:space="preserve"> not retail MRCs. Residential NBN (consumer, ACCC June 2025): 100 Mbps median advertised price ~A$65-80/mo (not enterprise). AU DIA (Dedicated Internet Access – direct fibre): Nexthop AU lists 1 Gbps datacenter DIA at A$499/mo (24-month, on-net); Vocus Fast Fibre (direct fibre, enterprise) from A$339/mo excl. GST for 250 Mbps+. AyeTech 2026 guide cites enterprise dedicated fibre 1</t>
         </is>
       </c>
-      <c r="T36" s="5" t="inlineStr"/>
+      <c r="T36" s="5" t="inlineStr">
+        <is>
+          <t>https://www.nexthop.com.au/dedicated-internet-access/</t>
+        </is>
+      </c>
       <c r="U36" s="5" t="inlineStr">
         <is>
           <t>2025</t>
@@ -4873,6 +4957,11 @@
         </is>
       </c>
       <c r="AA36" s="3" t="inlineStr"/>
+      <c r="AB36" s="7" t="inlineStr">
+        <is>
+          <t>https://www.nexthop.com.au/dedicated-internet-access/</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
@@ -4989,6 +5078,7 @@
           <t>fresenius 19.22 EUR</t>
         </is>
       </c>
+      <c r="AB37" s="7" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
@@ -5105,6 +5195,7 @@
           <t>fresenius 21.55 EUR</t>
         </is>
       </c>
+      <c r="AB38" s="7" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
@@ -5221,6 +5312,7 @@
           <t>fresenius 30.74 EUR</t>
         </is>
       </c>
+      <c r="AB39" s="7" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
@@ -5339,6 +5431,7 @@
           <t>fresenius 41.97 EUR</t>
         </is>
       </c>
+      <c r="AB40" s="7" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
@@ -5405,17 +5498,21 @@
       </c>
       <c r="P41" s="3" t="inlineStr">
         <is>
-          <t>single source; untraceable</t>
+          <t>single source</t>
         </is>
       </c>
       <c r="Q41" s="3" t="inlineStr"/>
       <c r="R41" s="5" t="inlineStr">
         <is>
-          <t>run narrative (the disposition was replaced)</t>
+          <t>traced in review; REVIEWER_TRACED</t>
         </is>
       </c>
       <c r="S41" s="3" t="inlineStr"/>
-      <c r="T41" s="5" t="inlineStr"/>
+      <c r="T41" s="5" t="inlineStr">
+        <is>
+          <t>https://direct-telecom.es/internet/business_class_fibre/</t>
+        </is>
+      </c>
       <c r="U41" s="5" t="inlineStr">
         <is>
           <t>2025</t>
@@ -5439,6 +5536,11 @@
         </is>
       </c>
       <c r="AA41" s="3" t="inlineStr"/>
+      <c r="AB41" s="7" t="inlineStr">
+        <is>
+          <t>https://direct-telecom.es/internet/business_class_fibre/</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
@@ -5513,7 +5615,7 @@
       <c r="Q42" s="3" t="inlineStr"/>
       <c r="R42" s="5" t="inlineStr">
         <is>
-          <t>run narrative (the disposition was replaced)</t>
+          <t>traced in review; REVIEWER_TRACED</t>
         </is>
       </c>
       <c r="S42" s="3" t="inlineStr">
@@ -5521,7 +5623,11 @@
           <t>ional players plus resellers. Telefónica Global Solutions offers DIA on its own Tier 1 global infrastructure. A domestic reseller (Direct Telecom) lists 100/100 Mbps DIA at €159.99/month and 1 Gbps dedicated circuit at €449/month (2025 prices). Telefónica and MasOrange are exploring acquisition of Vodafone España (as of mid-2025); if completed this would reduce the market to three</t>
         </is>
       </c>
-      <c r="T42" s="5" t="inlineStr"/>
+      <c r="T42" s="5" t="inlineStr">
+        <is>
+          <t>https://direct-telecom.es/internet/business_class_fibre/</t>
+        </is>
+      </c>
       <c r="U42" s="5" t="inlineStr">
         <is>
           <t>2025</t>
@@ -5545,10 +5651,15 @@
       </c>
       <c r="Z42" s="3" t="inlineStr">
         <is>
-          <t>500 Mbps at 1196 &gt; 1000 Mbps at 515 USD</t>
+          <t>500 Mbps at 574 &gt; 1000 Mbps at 515 USD</t>
         </is>
       </c>
       <c r="AA42" s="3" t="inlineStr"/>
+      <c r="AB42" s="7" t="inlineStr">
+        <is>
+          <t>https://direct-telecom.es/internet/business_class_fibre/</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
@@ -5671,6 +5782,7 @@
           <t>air-france-klm 20 EUR; air-france-klm 36 EUR; air-france-klm 26.12 EUR</t>
         </is>
       </c>
+      <c r="AB43" s="7" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
@@ -5793,6 +5905,7 @@
           <t>siemens ~29.95 GBP</t>
         </is>
       </c>
+      <c r="AB44" s="7" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
@@ -5867,7 +5980,7 @@
       <c r="Q45" s="3" t="inlineStr"/>
       <c r="R45" s="5" t="inlineStr">
         <is>
-          <t>run narrative (the disposition was replaced)</t>
+          <t>traced in review; REVIEWER_TRACED</t>
         </is>
       </c>
       <c r="S45" s="3" t="inlineStr">
@@ -5877,7 +5990,11 @@
 BT Business published tariffs (verified May 2026): Full Fibre 100 Mbps £35/month ex-VAT; Full Fibre 500 Mbps £55/month; Full Fibre 900 Mbps £65/month. Virgin Media Business (cable/HFC): from £29.95/month. Vodafone Business entry-level fro…</t>
         </is>
       </c>
-      <c r="T45" s="5" t="inlineStr"/>
+      <c r="T45" s="5" t="inlineStr">
+        <is>
+          <t>https://business.bt.com/products/broadband-and-internet/deals/</t>
+        </is>
+      </c>
       <c r="U45" s="5" t="inlineStr">
         <is>
           <t>2026-05</t>
@@ -5905,6 +6022,11 @@
         </is>
       </c>
       <c r="AA45" s="3" t="inlineStr"/>
+      <c r="AB45" s="7" t="inlineStr">
+        <is>
+          <t>https://business.bt.com/products/broadband-and-internet/deals/</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
@@ -6023,6 +6145,7 @@
           <t>tesco 39.10 GBP</t>
         </is>
       </c>
+      <c r="AB46" s="7" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
@@ -6139,6 +6262,7 @@
           <t>network-rail 119 GBP</t>
         </is>
       </c>
+      <c r="AB47" s="7" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
@@ -6261,6 +6385,7 @@
           <t>deutsche-post-dhl 206 GBP; eon 139 GBP; iberdrola 130 GBP; nhs-england 222 GBP; unilever 185 GBP</t>
         </is>
       </c>
+      <c r="AB48" s="7" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
@@ -6383,6 +6508,7 @@
           <t>deutsche-post-dhl 243 GBP; nhs-england 257 GBP</t>
         </is>
       </c>
+      <c r="AB49" s="7" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
@@ -6505,6 +6631,7 @@
           <t>deutsche-post-dhl 267 GBP; iberdrola 195 GBP; nhs-england 300 GBP</t>
         </is>
       </c>
+      <c r="AB50" s="7" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
@@ -6627,6 +6754,7 @@
           <t>deutsche-post-dhl 450 GBP</t>
         </is>
       </c>
+      <c r="AB51" s="7" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
@@ -6743,6 +6871,7 @@
           <t>eon 139 GBP; nhs-england 203.50 GBP; ups 203.50 GBP</t>
         </is>
       </c>
+      <c r="AB52" s="7" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
@@ -6845,10 +6974,10 @@
         </is>
       </c>
       <c r="W53" s="12" t="n">
-        <v>-1623268.492463442</v>
+        <v>-1683785.43322319</v>
       </c>
       <c r="X53" s="5" t="n">
-        <v>317</v>
+        <v>351</v>
       </c>
       <c r="Y53" s="3" t="inlineStr">
         <is>
@@ -6865,6 +6994,7 @@
           <t>deutsche-post-dhl 155 GBP; eon 203 GBP; heidelberg-materials 260000 None; nhs-england 188.50 GBP; saint-gobain 176 GBP; santander 203.50 GBP; santander 2,358 GBP; shell 2442 GBP</t>
         </is>
       </c>
+      <c r="AB53" s="7" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
@@ -6987,6 +7117,7 @@
           <t>deutsche-post-dhl 304 GBP; eon 450 GBP; nhs-england 415 GBP; saint-gobain 453 GBP; santander 415 GBP</t>
         </is>
       </c>
+      <c r="AB54" s="7" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
@@ -7089,6 +7220,7 @@
         </is>
       </c>
       <c r="AA55" s="3" t="inlineStr"/>
+      <c r="AB55" s="7" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
@@ -7211,6 +7343,7 @@
           <t>tesco 49.99 EUR</t>
         </is>
       </c>
+      <c r="AB56" s="7" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
@@ -7311,6 +7444,7 @@
         </is>
       </c>
       <c r="AA57" s="3" t="inlineStr"/>
+      <c r="AB57" s="7" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
@@ -7433,6 +7567,7 @@
           <t>air-france-klm 23.39 EUR</t>
         </is>
       </c>
+      <c r="AB58" s="7" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
@@ -7533,6 +7668,7 @@
         </is>
       </c>
       <c r="AA59" s="3" t="inlineStr"/>
+      <c r="AB59" s="7" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
@@ -7649,9 +7785,10 @@
           <t>mcdonalds 2050 USD</t>
         </is>
       </c>
+      <c r="AB60" s="7" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AA60"/>
+  <autoFilter ref="A1:AB60"/>
   <dataValidations count="1">
     <dataValidation sqref="F2 F3 F4 F5 F6 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F19 F20 F21 F22 F23 F24 F25 F26 F27 F28 F29 F30 F31 F32 F33 F34 F35 F36 F37 F38 F39 F40 F41 F42 F43 F44 F45 F46 F47 F48 F49 F50 F51 F52 F53 F54 F55 F56 F57 F58 F59 F60" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Approve,Reject,Hold"</formula1>
@@ -7816,7 +7953,7 @@
         </is>
       </c>
       <c r="E5" s="16" t="n">
-        <v>-357787.6123579189</v>
+        <v>-412766.4661391351</v>
       </c>
       <c r="F5" s="16" t="n">
         <v>0</v>
@@ -8404,7 +8541,7 @@
         </is>
       </c>
       <c r="E26" s="16" t="n">
-        <v>-316911.435413</v>
+        <v>-340047.438102</v>
       </c>
       <c r="F26" s="16" t="n">
         <v>0</v>
@@ -8536,7 +8673,7 @@
         </is>
       </c>
       <c r="B2" s="16" t="n">
-        <v>65837836.35</v>
+        <v>64373238.5</v>
       </c>
       <c r="C2" s="16" t="n">
         <v>-16128633.003194</v>
@@ -8556,7 +8693,7 @@
         </is>
       </c>
       <c r="B3" s="16" t="n">
-        <v>19070203.07</v>
+        <v>18559919.66</v>
       </c>
       <c r="C3" s="16" t="n">
         <v>-2729944.141842423</v>
@@ -8576,7 +8713,7 @@
         </is>
       </c>
       <c r="B4" s="16" t="n">
-        <v>9540989.82</v>
+        <v>9245582.4</v>
       </c>
       <c r="C4" s="16" t="n">
         <v>-1535238.860845505</v>
@@ -8592,14 +8729,14 @@
     <row r="5">
       <c r="A5" s="15" t="inlineStr">
         <is>
-          <t>ahold-delhaize</t>
+          <t>woolworths</t>
         </is>
       </c>
       <c r="B5" s="16" t="n">
-        <v>27048613.67</v>
+        <v>4555047.9</v>
       </c>
       <c r="C5" s="16" t="n">
-        <v>-1094627.74</v>
+        <v>-1109363.289657432</v>
       </c>
       <c r="D5" s="19">
         <f>IF(B5=0,"",C5/B5)</f>
@@ -8612,14 +8749,14 @@
     <row r="6">
       <c r="A6" s="15" t="inlineStr">
         <is>
-          <t>woolworths</t>
+          <t>ahold-delhaize</t>
         </is>
       </c>
       <c r="B6" s="16" t="n">
-        <v>4588807.28</v>
+        <v>26370921.61</v>
       </c>
       <c r="C6" s="16" t="n">
-        <v>-1075603.909216216</v>
+        <v>-1101872.46</v>
       </c>
       <c r="D6" s="19">
         <f>IF(B6=0,"",C6/B6)</f>
@@ -8656,7 +8793,7 @@
         </is>
       </c>
       <c r="B8" s="16" t="n">
-        <v>3847343.12</v>
+        <v>3771034.76</v>
       </c>
       <c r="C8" s="16" t="n">
         <v>-852215.94576</v>
@@ -8716,10 +8853,10 @@
         </is>
       </c>
       <c r="B11" s="16" t="n">
-        <v>1307212.55</v>
+        <v>1280285.63</v>
       </c>
       <c r="C11" s="16" t="n">
-        <v>-304559.635439</v>
+        <v>-325779.108779</v>
       </c>
       <c r="D11" s="19">
         <f>IF(B11=0,"",C11/B11)</f>
@@ -8736,7 +8873,7 @@
         </is>
       </c>
       <c r="B12" s="16" t="n">
-        <v>12775585.03</v>
+        <v>12492868.83</v>
       </c>
       <c r="C12" s="16" t="n">
         <v>-243421.43</v>
@@ -8756,7 +8893,7 @@
         </is>
       </c>
       <c r="B13" s="16" t="n">
-        <v>5417814.21</v>
+        <v>5323039.23</v>
       </c>
       <c r="C13" s="16" t="n">
         <v>-216374.5984898834</v>
@@ -8956,10 +9093,10 @@
         </is>
       </c>
       <c r="B23" s="16" t="n">
-        <v>12239938.18</v>
+        <v>12212852.21</v>
       </c>
       <c r="C23" s="16" t="n">
-        <v>-32322.017413</v>
+        <v>-33693.120102</v>
       </c>
       <c r="D23" s="19">
         <f>IF(B23=0,"",C23/B23)</f>
@@ -9016,7 +9153,7 @@
         </is>
       </c>
       <c r="B26" s="16" t="n">
-        <v>7550389.03</v>
+        <v>7505983.84</v>
       </c>
       <c r="C26" s="16" t="n">
         <v>-16153.23812273885</v>
@@ -9076,7 +9213,7 @@
         </is>
       </c>
       <c r="B29" s="16" t="n">
-        <v>8652050.039999999</v>
+        <v>8636746.560000001</v>
       </c>
       <c r="C29" s="16" t="n">
         <v>-7444.32</v>
@@ -9156,7 +9293,7 @@
         </is>
       </c>
       <c r="B33" s="16" t="n">
-        <v>1049026.5</v>
+        <v>1048273.87</v>
       </c>
       <c r="C33" s="16" t="n">
         <v>-2977.73</v>
@@ -9212,11 +9349,11 @@
     <row r="36">
       <c r="A36" s="15" t="inlineStr">
         <is>
-          <t>carrefour</t>
+          <t>anglo-american</t>
         </is>
       </c>
       <c r="B36" s="16" t="n">
-        <v>39782444.83</v>
+        <v>373299.77</v>
       </c>
       <c r="C36" s="16" t="n">
         <v>0</v>
@@ -9226,17 +9363,17 @@
         <v/>
       </c>
       <c r="E36" s="16" t="n">
-        <v>-16202.83</v>
+        <v>-16474.2432</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="15" t="inlineStr">
         <is>
-          <t>anglo-american</t>
+          <t>carrefour</t>
         </is>
       </c>
       <c r="B37" s="16" t="n">
-        <v>373694.9</v>
+        <v>39261279.64</v>
       </c>
       <c r="C37" s="16" t="n">
         <v>0</v>
@@ -9246,7 +9383,7 @@
         <v/>
       </c>
       <c r="E37" s="16" t="n">
-        <v>-16474.2432</v>
+        <v>-16202.83</v>
       </c>
     </row>
     <row r="38">
@@ -9276,7 +9413,7 @@
         </is>
       </c>
       <c r="B39" s="16" t="n">
-        <v>6531734.23</v>
+        <v>6220349.08</v>
       </c>
       <c r="C39" s="16" t="n">
         <v>3213.97</v>
@@ -9296,10 +9433,10 @@
         </is>
       </c>
       <c r="B40" s="16" t="n">
-        <v>7264743.88</v>
+        <v>7336776.19</v>
       </c>
       <c r="C40" s="16" t="n">
-        <v>112841.25</v>
+        <v>98321.07000000001</v>
       </c>
       <c r="D40" s="19">
         <f>IF(B40=0,"",C40/B40)</f>

--- a/docs/price-review.xlsx
+++ b/docs/price-review.xlsx
@@ -2436,10 +2436,10 @@
         </is>
       </c>
       <c r="W15" s="12" t="n">
-        <v>-90582.48274275</v>
+        <v>-92071.34274275</v>
       </c>
       <c r="X15" s="5" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="Y15" s="3" t="inlineStr">
         <is>
@@ -3745,14 +3745,14 @@
         </is>
       </c>
       <c r="W26" s="12" t="n">
-        <v>-6522.79808</v>
+        <v>-2826.54656</v>
       </c>
       <c r="X26" s="5" t="n">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="Y26" s="3" t="inlineStr">
         <is>
-          <t>maersk -3,696; ahold-delhaize -2,174; fresenius -435</t>
+          <t>ahold-delhaize -2,174; fresenius -435; victorias-secret -217</t>
         </is>
       </c>
       <c r="Z26" s="3" t="inlineStr">
@@ -3866,10 +3866,10 @@
         </is>
       </c>
       <c r="W27" s="12" t="n">
-        <v>-13669586.085744</v>
+        <v>-13706874.740784</v>
       </c>
       <c r="X27" s="5" t="n">
-        <v>17371</v>
+        <v>17406</v>
       </c>
       <c r="Y27" s="3" t="inlineStr">
         <is>
@@ -4104,10 +4104,10 @@
         </is>
       </c>
       <c r="W29" s="12" t="n">
-        <v>290896.36184</v>
+        <v>291598.81184</v>
       </c>
       <c r="X29" s="5" t="n">
-        <v>1770</v>
+        <v>1774</v>
       </c>
       <c r="Y29" s="3" t="inlineStr">
         <is>
@@ -4348,14 +4348,14 @@
         </is>
       </c>
       <c r="W31" s="12" t="n">
-        <v>418650.656</v>
+        <v>412378.736</v>
       </c>
       <c r="X31" s="5" t="n">
-        <v>2670</v>
+        <v>2630</v>
       </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t>victorias-secret +314; ahold-delhaize +3,920; maersk +6,272</t>
+          <t>victorias-secret +314; ahold-delhaize +3,920; fresenius +408,145</t>
         </is>
       </c>
       <c r="Z31" s="3" t="inlineStr">
@@ -4469,10 +4469,10 @@
         </is>
       </c>
       <c r="W32" s="12" t="n">
-        <v>-1260744.7734</v>
+        <v>-1256051.2834</v>
       </c>
       <c r="X32" s="5" t="n">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="Y32" s="3" t="inlineStr">
         <is>
@@ -5762,10 +5762,10 @@
         </is>
       </c>
       <c r="W43" s="12" t="n">
-        <v>-723966.3278903649</v>
+        <v>-725746.5878903648</v>
       </c>
       <c r="X43" s="5" t="n">
-        <v>1784</v>
+        <v>1788</v>
       </c>
       <c r="Y43" s="3" t="inlineStr">
         <is>
@@ -8093,7 +8093,7 @@
         </is>
       </c>
       <c r="E10" s="16" t="n">
-        <v>-90582.48274275</v>
+        <v>-92071.34274275</v>
       </c>
       <c r="F10" s="16" t="n">
         <v>0</v>
@@ -8457,7 +8457,7 @@
         </is>
       </c>
       <c r="E23" s="16" t="n">
-        <v>-17460896.489056</v>
+        <v>-17494488.892576</v>
       </c>
       <c r="F23" s="16" t="n">
         <v>0</v>
@@ -8485,7 +8485,7 @@
         </is>
       </c>
       <c r="E24" s="16" t="n">
-        <v>212933.9944155</v>
+        <v>213636.4444155</v>
       </c>
       <c r="F24" s="16" t="n">
         <v>-39654.109668</v>
@@ -8513,7 +8513,7 @@
         </is>
       </c>
       <c r="E25" s="16" t="n">
-        <v>-530536.4874</v>
+        <v>-532114.9174</v>
       </c>
       <c r="F25" s="16" t="n">
         <v>0</v>
@@ -9069,14 +9069,14 @@
     <row r="22">
       <c r="A22" s="15" t="inlineStr">
         <is>
-          <t>bayer</t>
+          <t>maersk</t>
         </is>
       </c>
       <c r="B22" s="16" t="n">
-        <v>3025050.32</v>
+        <v>3746918.52</v>
       </c>
       <c r="C22" s="16" t="n">
-        <v>-34035.61</v>
+        <v>-37288.65504</v>
       </c>
       <c r="D22" s="19">
         <f>IF(B22=0,"",C22/B22)</f>
@@ -9089,14 +9089,14 @@
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>shell</t>
+          <t>bayer</t>
         </is>
       </c>
       <c r="B23" s="16" t="n">
-        <v>12212852.21</v>
+        <v>3025050.32</v>
       </c>
       <c r="C23" s="16" t="n">
-        <v>-33693.120102</v>
+        <v>-34035.61</v>
       </c>
       <c r="D23" s="19">
         <f>IF(B23=0,"",C23/B23)</f>
@@ -9109,14 +9109,14 @@
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>bnp-paribas</t>
+          <t>shell</t>
         </is>
       </c>
       <c r="B24" s="16" t="n">
-        <v>31836939.35</v>
+        <v>12212852.21</v>
       </c>
       <c r="C24" s="16" t="n">
-        <v>-29777.28</v>
+        <v>-33693.120102</v>
       </c>
       <c r="D24" s="19">
         <f>IF(B24=0,"",C24/B24)</f>
@@ -9129,14 +9129,14 @@
     <row r="25">
       <c r="A25" s="15" t="inlineStr">
         <is>
-          <t>toyota</t>
+          <t>bnp-paribas</t>
         </is>
       </c>
       <c r="B25" s="16" t="n">
-        <v>2762186.59</v>
+        <v>31836939.35</v>
       </c>
       <c r="C25" s="16" t="n">
-        <v>-17558.74610201351</v>
+        <v>-29777.28</v>
       </c>
       <c r="D25" s="19">
         <f>IF(B25=0,"",C25/B25)</f>
@@ -9149,14 +9149,14 @@
     <row r="26">
       <c r="A26" s="15" t="inlineStr">
         <is>
-          <t>royal-mail</t>
+          <t>toyota</t>
         </is>
       </c>
       <c r="B26" s="16" t="n">
-        <v>7505983.84</v>
+        <v>2762186.59</v>
       </c>
       <c r="C26" s="16" t="n">
-        <v>-16153.23812273885</v>
+        <v>-17558.74610201351</v>
       </c>
       <c r="D26" s="19">
         <f>IF(B26=0,"",C26/B26)</f>
@@ -9169,14 +9169,14 @@
     <row r="27">
       <c r="A27" s="15" t="inlineStr">
         <is>
-          <t>michelin</t>
+          <t>royal-mail</t>
         </is>
       </c>
       <c r="B27" s="16" t="n">
-        <v>2771269.98</v>
+        <v>7505983.84</v>
       </c>
       <c r="C27" s="16" t="n">
-        <v>-14943.12</v>
+        <v>-16153.23812273885</v>
       </c>
       <c r="D27" s="19">
         <f>IF(B27=0,"",C27/B27)</f>
@@ -9189,14 +9189,14 @@
     <row r="28">
       <c r="A28" s="15" t="inlineStr">
         <is>
-          <t>abb</t>
+          <t>michelin</t>
         </is>
       </c>
       <c r="B28" s="16" t="n">
-        <v>1159918.54</v>
+        <v>2799456.08</v>
       </c>
       <c r="C28" s="16" t="n">
-        <v>-8419.634472</v>
+        <v>-11036.04</v>
       </c>
       <c r="D28" s="19">
         <f>IF(B28=0,"",C28/B28)</f>
@@ -9209,14 +9209,14 @@
     <row r="29">
       <c r="A29" s="15" t="inlineStr">
         <is>
-          <t>accor</t>
+          <t>abb</t>
         </is>
       </c>
       <c r="B29" s="16" t="n">
-        <v>8636746.560000001</v>
+        <v>1159918.54</v>
       </c>
       <c r="C29" s="16" t="n">
-        <v>-7444.32</v>
+        <v>-8419.634472</v>
       </c>
       <c r="D29" s="19">
         <f>IF(B29=0,"",C29/B29)</f>
@@ -9229,14 +9229,14 @@
     <row r="30">
       <c r="A30" s="15" t="inlineStr">
         <is>
-          <t>henkel</t>
+          <t>accor</t>
         </is>
       </c>
       <c r="B30" s="16" t="n">
-        <v>704177.1899999999</v>
+        <v>8636746.560000001</v>
       </c>
       <c r="C30" s="16" t="n">
-        <v>-7429.09</v>
+        <v>-7444.32</v>
       </c>
       <c r="D30" s="19">
         <f>IF(B30=0,"",C30/B30)</f>
@@ -9249,14 +9249,14 @@
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>danone</t>
+          <t>henkel</t>
         </is>
       </c>
       <c r="B31" s="16" t="n">
-        <v>3140600.5</v>
+        <v>704177.1899999999</v>
       </c>
       <c r="C31" s="16" t="n">
-        <v>-7279.6</v>
+        <v>-7429.09</v>
       </c>
       <c r="D31" s="19">
         <f>IF(B31=0,"",C31/B31)</f>
@@ -9269,14 +9269,14 @@
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>saint-gobain</t>
+          <t>danone</t>
         </is>
       </c>
       <c r="B32" s="16" t="n">
-        <v>21144690.36</v>
+        <v>3140600.5</v>
       </c>
       <c r="C32" s="16" t="n">
-        <v>-5967.71</v>
+        <v>-7279.6</v>
       </c>
       <c r="D32" s="19">
         <f>IF(B32=0,"",C32/B32)</f>
@@ -9289,14 +9289,14 @@
     <row r="33">
       <c r="A33" s="15" t="inlineStr">
         <is>
-          <t>air-france-klm</t>
+          <t>saint-gobain</t>
         </is>
       </c>
       <c r="B33" s="16" t="n">
-        <v>1048273.87</v>
+        <v>21144690.36</v>
       </c>
       <c r="C33" s="16" t="n">
-        <v>-2977.73</v>
+        <v>-5967.71</v>
       </c>
       <c r="D33" s="19">
         <f>IF(B33=0,"",C33/B33)</f>
@@ -9309,14 +9309,14 @@
     <row r="34">
       <c r="A34" s="15" t="inlineStr">
         <is>
-          <t>dbs</t>
+          <t>air-france-klm</t>
         </is>
       </c>
       <c r="B34" s="16" t="n">
-        <v>11182416.1</v>
+        <v>1048273.87</v>
       </c>
       <c r="C34" s="16" t="n">
-        <v>-2199.09195</v>
+        <v>-2977.73</v>
       </c>
       <c r="D34" s="19">
         <f>IF(B34=0,"",C34/B34)</f>
@@ -9329,14 +9329,14 @@
     <row r="35">
       <c r="A35" s="15" t="inlineStr">
         <is>
-          <t>totalenergies</t>
+          <t>dbs</t>
         </is>
       </c>
       <c r="B35" s="16" t="n">
-        <v>10952685.28</v>
+        <v>11182416.1</v>
       </c>
       <c r="C35" s="16" t="n">
-        <v>-1369.752484</v>
+        <v>-2199.09195</v>
       </c>
       <c r="D35" s="19">
         <f>IF(B35=0,"",C35/B35)</f>
@@ -9349,31 +9349,31 @@
     <row r="36">
       <c r="A36" s="15" t="inlineStr">
         <is>
-          <t>anglo-american</t>
+          <t>totalenergies</t>
         </is>
       </c>
       <c r="B36" s="16" t="n">
-        <v>373299.77</v>
+        <v>10952685.28</v>
       </c>
       <c r="C36" s="16" t="n">
-        <v>0</v>
+        <v>-1369.752484</v>
       </c>
       <c r="D36" s="19">
         <f>IF(B36=0,"",C36/B36)</f>
         <v/>
       </c>
       <c r="E36" s="16" t="n">
-        <v>-16474.2432</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="15" t="inlineStr">
         <is>
-          <t>carrefour</t>
+          <t>anglo-american</t>
         </is>
       </c>
       <c r="B37" s="16" t="n">
-        <v>39261279.64</v>
+        <v>373299.77</v>
       </c>
       <c r="C37" s="16" t="n">
         <v>0</v>
@@ -9383,27 +9383,27 @@
         <v/>
       </c>
       <c r="E37" s="16" t="n">
-        <v>-16202.83</v>
+        <v>-16474.2432</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="15" t="inlineStr">
         <is>
-          <t>maersk</t>
+          <t>carrefour</t>
         </is>
       </c>
       <c r="B38" s="16" t="n">
-        <v>2907843.4</v>
+        <v>39261279.64</v>
       </c>
       <c r="C38" s="16" t="n">
-        <v>2575.66848</v>
+        <v>0</v>
       </c>
       <c r="D38" s="19">
         <f>IF(B38=0,"",C38/B38)</f>
         <v/>
       </c>
       <c r="E38" s="16" t="n">
-        <v>0</v>
+        <v>-16202.83</v>
       </c>
     </row>
     <row r="39">

--- a/docs/price-review.xlsx
+++ b/docs/price-review.xlsx
@@ -8973,7 +8973,7 @@
         </is>
       </c>
       <c r="B17" s="16" t="n">
-        <v>11574896.57</v>
+        <v>11572999.93</v>
       </c>
       <c r="C17" s="16" t="n">
         <v>-85349.23468125</v>
@@ -9273,7 +9273,7 @@
         </is>
       </c>
       <c r="B32" s="16" t="n">
-        <v>3135858.92</v>
+        <v>3135332.08</v>
       </c>
       <c r="C32" s="16" t="n">
         <v>-7279.6</v>

--- a/docs/price-review.xlsx
+++ b/docs/price-review.xlsx
@@ -8693,7 +8693,7 @@
         </is>
       </c>
       <c r="B3" s="16" t="n">
-        <v>18559919.66</v>
+        <v>16220935.07</v>
       </c>
       <c r="C3" s="16" t="n">
         <v>-2729944.141842423</v>
@@ -8713,7 +8713,7 @@
         </is>
       </c>
       <c r="B4" s="16" t="n">
-        <v>9245582.4</v>
+        <v>7876212.85</v>
       </c>
       <c r="C4" s="16" t="n">
         <v>-1535238.860845505</v>
@@ -8733,7 +8733,7 @@
         </is>
       </c>
       <c r="B5" s="16" t="n">
-        <v>4555047.9</v>
+        <v>5362494.88</v>
       </c>
       <c r="C5" s="16" t="n">
         <v>-1109363.289657432</v>
@@ -8753,7 +8753,7 @@
         </is>
       </c>
       <c r="B6" s="16" t="n">
-        <v>26370921.61</v>
+        <v>24793273.77</v>
       </c>
       <c r="C6" s="16" t="n">
         <v>-1101872.46</v>
@@ -8833,7 +8833,7 @@
         </is>
       </c>
       <c r="B10" s="16" t="n">
-        <v>13256072.84</v>
+        <v>13080006.78</v>
       </c>
       <c r="C10" s="16" t="n">
         <v>-352654.44</v>
@@ -8873,7 +8873,7 @@
         </is>
       </c>
       <c r="B12" s="16" t="n">
-        <v>11944953.9</v>
+        <v>11199077.66</v>
       </c>
       <c r="C12" s="16" t="n">
         <v>-243421.43</v>
@@ -8893,7 +8893,7 @@
         </is>
       </c>
       <c r="B13" s="16" t="n">
-        <v>5323039.23</v>
+        <v>4737934.18</v>
       </c>
       <c r="C13" s="16" t="n">
         <v>-216374.5984898834</v>
@@ -8913,7 +8913,7 @@
         </is>
       </c>
       <c r="B14" s="16" t="n">
-        <v>4375267.77</v>
+        <v>4238396.19</v>
       </c>
       <c r="C14" s="16" t="n">
         <v>-165251.99283375</v>
@@ -8933,7 +8933,7 @@
         </is>
       </c>
       <c r="B15" s="16" t="n">
-        <v>17706239.4</v>
+        <v>16785765.72</v>
       </c>
       <c r="C15" s="16" t="n">
         <v>-161314.9972477556</v>
@@ -8953,7 +8953,7 @@
         </is>
       </c>
       <c r="B16" s="16" t="n">
-        <v>5682427.54</v>
+        <v>5574436.15</v>
       </c>
       <c r="C16" s="16" t="n">
         <v>-88014.36</v>
@@ -8973,7 +8973,7 @@
         </is>
       </c>
       <c r="B17" s="16" t="n">
-        <v>11572999.93</v>
+        <v>11364991.71</v>
       </c>
       <c r="C17" s="16" t="n">
         <v>-85349.23468125</v>
@@ -8993,7 +8993,7 @@
         </is>
       </c>
       <c r="B18" s="16" t="n">
-        <v>4715427.64</v>
+        <v>4613487.33</v>
       </c>
       <c r="C18" s="16" t="n">
         <v>-67713.11</v>
@@ -9013,7 +9013,7 @@
         </is>
       </c>
       <c r="B19" s="16" t="n">
-        <v>17344095.44</v>
+        <v>16747519.43</v>
       </c>
       <c r="C19" s="16" t="n">
         <v>-57957.48</v>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="B20" s="16" t="n">
-        <v>6178316.33</v>
+        <v>6083183.49</v>
       </c>
       <c r="C20" s="16" t="n">
         <v>-48420.69</v>
@@ -9073,7 +9073,7 @@
         </is>
       </c>
       <c r="B22" s="16" t="n">
-        <v>3746918.52</v>
+        <v>4113349.82</v>
       </c>
       <c r="C22" s="16" t="n">
         <v>-37288.65504</v>
@@ -9093,7 +9093,7 @@
         </is>
       </c>
       <c r="B23" s="16" t="n">
-        <v>3021889.27</v>
+        <v>2972431.89</v>
       </c>
       <c r="C23" s="16" t="n">
         <v>-34035.61</v>
@@ -9133,7 +9133,7 @@
         </is>
       </c>
       <c r="B25" s="16" t="n">
-        <v>31720124.84</v>
+        <v>31024714.49</v>
       </c>
       <c r="C25" s="16" t="n">
         <v>-29777.28</v>
@@ -9153,7 +9153,7 @@
         </is>
       </c>
       <c r="B26" s="16" t="n">
-        <v>2762186.59</v>
+        <v>3204432.17</v>
       </c>
       <c r="C26" s="16" t="n">
         <v>-17558.74610201351</v>
@@ -9173,7 +9173,7 @@
         </is>
       </c>
       <c r="B27" s="16" t="n">
-        <v>7505983.84</v>
+        <v>6627214.03</v>
       </c>
       <c r="C27" s="16" t="n">
         <v>-16153.23812273885</v>
@@ -9193,7 +9193,7 @@
         </is>
       </c>
       <c r="B28" s="16" t="n">
-        <v>2794187.67</v>
+        <v>2744730.28</v>
       </c>
       <c r="C28" s="16" t="n">
         <v>-11036.04</v>
@@ -9233,7 +9233,7 @@
         </is>
       </c>
       <c r="B30" s="16" t="n">
-        <v>8636746.560000001</v>
+        <v>8068197.01</v>
       </c>
       <c r="C30" s="16" t="n">
         <v>-7444.32</v>
@@ -9253,7 +9253,7 @@
         </is>
       </c>
       <c r="B31" s="16" t="n">
-        <v>704177.1899999999</v>
+        <v>693839.9300000001</v>
       </c>
       <c r="C31" s="16" t="n">
         <v>-7429.09</v>
@@ -9273,7 +9273,7 @@
         </is>
       </c>
       <c r="B32" s="16" t="n">
-        <v>3135332.08</v>
+        <v>3116170.32</v>
       </c>
       <c r="C32" s="16" t="n">
         <v>-7279.6</v>
@@ -9293,7 +9293,7 @@
         </is>
       </c>
       <c r="B33" s="16" t="n">
-        <v>21144690.36</v>
+        <v>20609089.21</v>
       </c>
       <c r="C33" s="16" t="n">
         <v>-5967.71</v>
@@ -9313,7 +9313,7 @@
         </is>
       </c>
       <c r="B34" s="16" t="n">
-        <v>1048273.87</v>
+        <v>1013692.06</v>
       </c>
       <c r="C34" s="16" t="n">
         <v>-2977.73</v>
@@ -9333,7 +9333,7 @@
         </is>
       </c>
       <c r="B35" s="16" t="n">
-        <v>11182416.1</v>
+        <v>11878347.36</v>
       </c>
       <c r="C35" s="16" t="n">
         <v>-2199.09195</v>
@@ -9393,7 +9393,7 @@
         </is>
       </c>
       <c r="B38" s="16" t="n">
-        <v>39261279.64</v>
+        <v>36971913.55</v>
       </c>
       <c r="C38" s="16" t="n">
         <v>0</v>
@@ -9413,7 +9413,7 @@
         </is>
       </c>
       <c r="B39" s="16" t="n">
-        <v>6180379.39</v>
+        <v>5859419.94</v>
       </c>
       <c r="C39" s="16" t="n">
         <v>3213.97</v>
@@ -9433,7 +9433,7 @@
         </is>
       </c>
       <c r="B40" s="16" t="n">
-        <v>7336776.19</v>
+        <v>7260552.98</v>
       </c>
       <c r="C40" s="16" t="n">
         <v>98321.07000000001</v>
@@ -9453,7 +9453,7 @@
         </is>
       </c>
       <c r="B41" s="16" t="n">
-        <v>33131566.93</v>
+        <v>32253363.5</v>
       </c>
       <c r="C41" s="16" t="n">
         <v>635912.58</v>

--- a/docs/price-review.xlsx
+++ b/docs/price-review.xlsx
@@ -8693,7 +8693,7 @@
         </is>
       </c>
       <c r="B3" s="16" t="n">
-        <v>16220935.07</v>
+        <v>15170875.9</v>
       </c>
       <c r="C3" s="16" t="n">
         <v>-2729944.141842423</v>
@@ -8713,7 +8713,7 @@
         </is>
       </c>
       <c r="B4" s="16" t="n">
-        <v>7876212.85</v>
+        <v>7272295.57</v>
       </c>
       <c r="C4" s="16" t="n">
         <v>-1535238.860845505</v>
@@ -8733,7 +8733,7 @@
         </is>
       </c>
       <c r="B5" s="16" t="n">
-        <v>5362494.88</v>
+        <v>5709060.84</v>
       </c>
       <c r="C5" s="16" t="n">
         <v>-1109363.289657432</v>
@@ -8753,7 +8753,7 @@
         </is>
       </c>
       <c r="B6" s="16" t="n">
-        <v>24793273.77</v>
+        <v>24090137.16</v>
       </c>
       <c r="C6" s="16" t="n">
         <v>-1101872.46</v>
@@ -8833,7 +8833,7 @@
         </is>
       </c>
       <c r="B10" s="16" t="n">
-        <v>13080006.78</v>
+        <v>13021769.76</v>
       </c>
       <c r="C10" s="16" t="n">
         <v>-352654.44</v>
@@ -8873,7 +8873,7 @@
         </is>
       </c>
       <c r="B12" s="16" t="n">
-        <v>11199077.66</v>
+        <v>10878658.04</v>
       </c>
       <c r="C12" s="16" t="n">
         <v>-243421.43</v>
@@ -8893,7 +8893,7 @@
         </is>
       </c>
       <c r="B13" s="16" t="n">
-        <v>4737934.18</v>
+        <v>4494874.8</v>
       </c>
       <c r="C13" s="16" t="n">
         <v>-216374.5984898834</v>
@@ -8913,7 +8913,7 @@
         </is>
       </c>
       <c r="B14" s="16" t="n">
-        <v>4238396.19</v>
+        <v>4213896.5</v>
       </c>
       <c r="C14" s="16" t="n">
         <v>-165251.99283375</v>
@@ -8933,7 +8933,7 @@
         </is>
       </c>
       <c r="B15" s="16" t="n">
-        <v>16785765.72</v>
+        <v>16388395.61</v>
       </c>
       <c r="C15" s="16" t="n">
         <v>-161314.9972477556</v>
@@ -8953,7 +8953,7 @@
         </is>
       </c>
       <c r="B16" s="16" t="n">
-        <v>5574436.15</v>
+        <v>5547521.83</v>
       </c>
       <c r="C16" s="16" t="n">
         <v>-88014.36</v>
@@ -8973,7 +8973,7 @@
         </is>
       </c>
       <c r="B17" s="16" t="n">
-        <v>11364991.71</v>
+        <v>11307760.44</v>
       </c>
       <c r="C17" s="16" t="n">
         <v>-85349.23468125</v>
@@ -8993,7 +8993,7 @@
         </is>
       </c>
       <c r="B18" s="16" t="n">
-        <v>4613487.33</v>
+        <v>4589357.25</v>
       </c>
       <c r="C18" s="16" t="n">
         <v>-67713.11</v>
@@ -9013,7 +9013,7 @@
         </is>
       </c>
       <c r="B19" s="16" t="n">
-        <v>16747519.43</v>
+        <v>16484408.75</v>
       </c>
       <c r="C19" s="16" t="n">
         <v>-57957.48</v>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="B20" s="16" t="n">
-        <v>6083183.49</v>
+        <v>6062185.68</v>
       </c>
       <c r="C20" s="16" t="n">
         <v>-48420.69</v>
@@ -9073,7 +9073,7 @@
         </is>
       </c>
       <c r="B22" s="16" t="n">
-        <v>4113349.82</v>
+        <v>4216836.5</v>
       </c>
       <c r="C22" s="16" t="n">
         <v>-37288.65504</v>
@@ -9093,7 +9093,7 @@
         </is>
       </c>
       <c r="B23" s="16" t="n">
-        <v>2972431.89</v>
+        <v>2961062.91</v>
       </c>
       <c r="C23" s="16" t="n">
         <v>-34035.61</v>
@@ -9133,7 +9133,7 @@
         </is>
       </c>
       <c r="B25" s="16" t="n">
-        <v>31024714.49</v>
+        <v>30716127.89</v>
       </c>
       <c r="C25" s="16" t="n">
         <v>-29777.28</v>
@@ -9153,7 +9153,7 @@
         </is>
       </c>
       <c r="B26" s="16" t="n">
-        <v>3204432.17</v>
+        <v>3255047.2</v>
       </c>
       <c r="C26" s="16" t="n">
         <v>-17558.74610201351</v>
@@ -9173,7 +9173,7 @@
         </is>
       </c>
       <c r="B27" s="16" t="n">
-        <v>6627214.03</v>
+        <v>6249032.82</v>
       </c>
       <c r="C27" s="16" t="n">
         <v>-16153.23812273885</v>
@@ -9193,7 +9193,7 @@
         </is>
       </c>
       <c r="B28" s="16" t="n">
-        <v>2744730.28</v>
+        <v>2733361.3</v>
       </c>
       <c r="C28" s="16" t="n">
         <v>-11036.04</v>
@@ -9233,7 +9233,7 @@
         </is>
       </c>
       <c r="B30" s="16" t="n">
-        <v>8068197.01</v>
+        <v>7806594.46</v>
       </c>
       <c r="C30" s="16" t="n">
         <v>-7444.32</v>
@@ -9253,7 +9253,7 @@
         </is>
       </c>
       <c r="B31" s="16" t="n">
-        <v>693839.9300000001</v>
+        <v>689083.52</v>
       </c>
       <c r="C31" s="16" t="n">
         <v>-7429.09</v>
@@ -9273,7 +9273,7 @@
         </is>
       </c>
       <c r="B32" s="16" t="n">
-        <v>3116170.32</v>
+        <v>3107353.56</v>
       </c>
       <c r="C32" s="16" t="n">
         <v>-7279.6</v>
@@ -9293,7 +9293,7 @@
         </is>
       </c>
       <c r="B33" s="16" t="n">
-        <v>20609089.21</v>
+        <v>20385421.93</v>
       </c>
       <c r="C33" s="16" t="n">
         <v>-5967.71</v>
@@ -9313,7 +9313,7 @@
         </is>
       </c>
       <c r="B34" s="16" t="n">
-        <v>1013692.06</v>
+        <v>1009167.67</v>
       </c>
       <c r="C34" s="16" t="n">
         <v>-2977.73</v>
@@ -9333,7 +9333,7 @@
         </is>
       </c>
       <c r="B35" s="16" t="n">
-        <v>11878347.36</v>
+        <v>12181726.99</v>
       </c>
       <c r="C35" s="16" t="n">
         <v>-2199.09195</v>
@@ -9393,7 +9393,7 @@
         </is>
       </c>
       <c r="B38" s="16" t="n">
-        <v>36971913.55</v>
+        <v>35929911.73</v>
       </c>
       <c r="C38" s="16" t="n">
         <v>0</v>
@@ -9413,7 +9413,7 @@
         </is>
       </c>
       <c r="B39" s="16" t="n">
-        <v>5859419.94</v>
+        <v>5711739.21</v>
       </c>
       <c r="C39" s="16" t="n">
         <v>3213.97</v>
@@ -9433,7 +9433,7 @@
         </is>
       </c>
       <c r="B40" s="16" t="n">
-        <v>7260552.98</v>
+        <v>7248255.92</v>
       </c>
       <c r="C40" s="16" t="n">
         <v>98321.07000000001</v>
@@ -9453,7 +9453,7 @@
         </is>
       </c>
       <c r="B41" s="16" t="n">
-        <v>32253363.5</v>
+        <v>31860669.65</v>
       </c>
       <c r="C41" s="16" t="n">
         <v>635912.58</v>
